--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="95">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -218,12 +218,96 @@
   </si>
   <si>
     <t>Nº</t>
+  </si>
+  <si>
+    <t>Japan J2 League</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>Iwaki</t>
+  </si>
+  <si>
+    <t>Omiya Ardija</t>
+  </si>
+  <si>
+    <t>Ventforet Kofu</t>
+  </si>
+  <si>
+    <t>Jubilo Iwata</t>
+  </si>
+  <si>
+    <t>Fujieda MYFC</t>
+  </si>
+  <si>
+    <t>Sagan Tosu</t>
+  </si>
+  <si>
+    <t>V-Varen Nagasaki</t>
+  </si>
+  <si>
+    <t>JEF United</t>
+  </si>
+  <si>
+    <t>Montedio Yamagata</t>
+  </si>
+  <si>
+    <t>Renofa Yamaguchi</t>
+  </si>
+  <si>
+    <t>Mito Hollyhock</t>
+  </si>
+  <si>
+    <t>Tokushima Vortis</t>
+  </si>
+  <si>
+    <t>Vegalta Sendai</t>
+  </si>
+  <si>
+    <t>Roasso Kumamoto</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>['52', '90+7']</t>
+  </si>
+  <si>
+    <t>['51']</t>
+  </si>
+  <si>
+    <t>['53', '68', '77']</t>
+  </si>
+  <si>
+    <t>['62', '64', '67']</t>
+  </si>
+  <si>
+    <t>['31', '60']</t>
+  </si>
+  <si>
+    <t>['66']</t>
+  </si>
+  <si>
+    <t>['79', '90+5']</t>
+  </si>
+  <si>
+    <t>['52', '75']</t>
+  </si>
+  <si>
+    <t>['71']</t>
+  </si>
+  <si>
+    <t>['10', '89']</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -276,11 +360,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,7 +660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP1"/>
+  <dimension ref="A1:BP8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -784,6 +869,1448 @@
         <v>66</v>
       </c>
     </row>
+    <row r="2" spans="1:68">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>7778489</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="2">
+        <v>45703.08333333334</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+      <c r="N2">
+        <v>2</v>
+      </c>
+      <c r="O2" t="s">
+        <v>84</v>
+      </c>
+      <c r="P2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q2">
+        <v>3.6</v>
+      </c>
+      <c r="R2">
+        <v>2.2</v>
+      </c>
+      <c r="S2">
+        <v>2.7</v>
+      </c>
+      <c r="T2">
+        <v>1.35</v>
+      </c>
+      <c r="U2">
+        <v>3.04</v>
+      </c>
+      <c r="V2">
+        <v>2.55</v>
+      </c>
+      <c r="W2">
+        <v>1.45</v>
+      </c>
+      <c r="X2">
+        <v>6.2</v>
+      </c>
+      <c r="Y2">
+        <v>1.09</v>
+      </c>
+      <c r="Z2">
+        <v>3.14</v>
+      </c>
+      <c r="AA2">
+        <v>3.4</v>
+      </c>
+      <c r="AB2">
+        <v>2.18</v>
+      </c>
+      <c r="AC2">
+        <v>1.02</v>
+      </c>
+      <c r="AD2">
+        <v>10</v>
+      </c>
+      <c r="AE2">
+        <v>1.25</v>
+      </c>
+      <c r="AF2">
+        <v>3.7</v>
+      </c>
+      <c r="AG2">
+        <v>1.77</v>
+      </c>
+      <c r="AH2">
+        <v>1.98</v>
+      </c>
+      <c r="AI2">
+        <v>1.64</v>
+      </c>
+      <c r="AJ2">
+        <v>2.13</v>
+      </c>
+      <c r="AK2">
+        <v>1.62</v>
+      </c>
+      <c r="AL2">
+        <v>1.28</v>
+      </c>
+      <c r="AM2">
+        <v>1.34</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>3</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>5</v>
+      </c>
+      <c r="AV2">
+        <v>4</v>
+      </c>
+      <c r="AW2">
+        <v>15</v>
+      </c>
+      <c r="AX2">
+        <v>2</v>
+      </c>
+      <c r="AY2">
+        <v>20</v>
+      </c>
+      <c r="AZ2">
+        <v>6</v>
+      </c>
+      <c r="BA2">
+        <v>9</v>
+      </c>
+      <c r="BB2">
+        <v>1</v>
+      </c>
+      <c r="BC2">
+        <v>10</v>
+      </c>
+      <c r="BD2">
+        <v>2.33</v>
+      </c>
+      <c r="BE2">
+        <v>8</v>
+      </c>
+      <c r="BF2">
+        <v>1.82</v>
+      </c>
+      <c r="BG2">
+        <v>1.33</v>
+      </c>
+      <c r="BH2">
+        <v>3</v>
+      </c>
+      <c r="BI2">
+        <v>1.56</v>
+      </c>
+      <c r="BJ2">
+        <v>2.33</v>
+      </c>
+      <c r="BK2">
+        <v>2</v>
+      </c>
+      <c r="BL2">
+        <v>1.8</v>
+      </c>
+      <c r="BM2">
+        <v>2.43</v>
+      </c>
+      <c r="BN2">
+        <v>1.49</v>
+      </c>
+      <c r="BO2">
+        <v>3.2</v>
+      </c>
+      <c r="BP2">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:68">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>7778490</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="2">
+        <v>45703.08333333334</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>3</v>
+      </c>
+      <c r="O3" t="s">
+        <v>85</v>
+      </c>
+      <c r="P3" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q3">
+        <v>3.75</v>
+      </c>
+      <c r="R3">
+        <v>2.2</v>
+      </c>
+      <c r="S3">
+        <v>2.75</v>
+      </c>
+      <c r="T3">
+        <v>1.36</v>
+      </c>
+      <c r="U3">
+        <v>3</v>
+      </c>
+      <c r="V3">
+        <v>2.75</v>
+      </c>
+      <c r="W3">
+        <v>1.4</v>
+      </c>
+      <c r="X3">
+        <v>7</v>
+      </c>
+      <c r="Y3">
+        <v>1.1</v>
+      </c>
+      <c r="Z3">
+        <v>3.4</v>
+      </c>
+      <c r="AA3">
+        <v>3.45</v>
+      </c>
+      <c r="AB3">
+        <v>2.05</v>
+      </c>
+      <c r="AC3">
+        <v>1.05</v>
+      </c>
+      <c r="AD3">
+        <v>8.5</v>
+      </c>
+      <c r="AE3">
+        <v>1.25</v>
+      </c>
+      <c r="AF3">
+        <v>3.75</v>
+      </c>
+      <c r="AG3">
+        <v>1.8</v>
+      </c>
+      <c r="AH3">
+        <v>1.94</v>
+      </c>
+      <c r="AI3">
+        <v>1.67</v>
+      </c>
+      <c r="AJ3">
+        <v>2.1</v>
+      </c>
+      <c r="AK3">
+        <v>1.71</v>
+      </c>
+      <c r="AL3">
+        <v>1.27</v>
+      </c>
+      <c r="AM3">
+        <v>1.29</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>3</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>9</v>
+      </c>
+      <c r="AV3">
+        <v>2</v>
+      </c>
+      <c r="AW3">
+        <v>9</v>
+      </c>
+      <c r="AX3">
+        <v>3</v>
+      </c>
+      <c r="AY3">
+        <v>18</v>
+      </c>
+      <c r="AZ3">
+        <v>5</v>
+      </c>
+      <c r="BA3">
+        <v>6</v>
+      </c>
+      <c r="BB3">
+        <v>2</v>
+      </c>
+      <c r="BC3">
+        <v>8</v>
+      </c>
+      <c r="BD3">
+        <v>2.44</v>
+      </c>
+      <c r="BE3">
+        <v>8</v>
+      </c>
+      <c r="BF3">
+        <v>1.75</v>
+      </c>
+      <c r="BG3">
+        <v>1.18</v>
+      </c>
+      <c r="BH3">
+        <v>3.84</v>
+      </c>
+      <c r="BI3">
+        <v>1.44</v>
+      </c>
+      <c r="BJ3">
+        <v>2.58</v>
+      </c>
+      <c r="BK3">
+        <v>1.74</v>
+      </c>
+      <c r="BL3">
+        <v>2.02</v>
+      </c>
+      <c r="BM3">
+        <v>2.19</v>
+      </c>
+      <c r="BN3">
+        <v>1.63</v>
+      </c>
+      <c r="BO3">
+        <v>2.77</v>
+      </c>
+      <c r="BP3">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:68">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>7778491</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="2">
+        <v>45703.08333333334</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" t="s">
+        <v>79</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4" t="s">
+        <v>86</v>
+      </c>
+      <c r="P4" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q4">
+        <v>2.8</v>
+      </c>
+      <c r="R4">
+        <v>2.07</v>
+      </c>
+      <c r="S4">
+        <v>3.8</v>
+      </c>
+      <c r="T4">
+        <v>1.44</v>
+      </c>
+      <c r="U4">
+        <v>2.6</v>
+      </c>
+      <c r="V4">
+        <v>3.04</v>
+      </c>
+      <c r="W4">
+        <v>1.35</v>
+      </c>
+      <c r="X4">
+        <v>7.4</v>
+      </c>
+      <c r="Y4">
+        <v>1.06</v>
+      </c>
+      <c r="Z4">
+        <v>2.21</v>
+      </c>
+      <c r="AA4">
+        <v>3.25</v>
+      </c>
+      <c r="AB4">
+        <v>3.23</v>
+      </c>
+      <c r="AC4">
+        <v>1.01</v>
+      </c>
+      <c r="AD4">
+        <v>8.5</v>
+      </c>
+      <c r="AE4">
+        <v>1.33</v>
+      </c>
+      <c r="AF4">
+        <v>3.1</v>
+      </c>
+      <c r="AG4">
+        <v>2</v>
+      </c>
+      <c r="AH4">
+        <v>1.67</v>
+      </c>
+      <c r="AI4">
+        <v>1.79</v>
+      </c>
+      <c r="AJ4">
+        <v>1.92</v>
+      </c>
+      <c r="AK4">
+        <v>1.33</v>
+      </c>
+      <c r="AL4">
+        <v>1.3</v>
+      </c>
+      <c r="AM4">
+        <v>1.59</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>3</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>4</v>
+      </c>
+      <c r="AV4">
+        <v>2</v>
+      </c>
+      <c r="AW4">
+        <v>4</v>
+      </c>
+      <c r="AX4">
+        <v>7</v>
+      </c>
+      <c r="AY4">
+        <v>8</v>
+      </c>
+      <c r="AZ4">
+        <v>9</v>
+      </c>
+      <c r="BA4">
+        <v>2</v>
+      </c>
+      <c r="BB4">
+        <v>4</v>
+      </c>
+      <c r="BC4">
+        <v>6</v>
+      </c>
+      <c r="BD4">
+        <v>1.82</v>
+      </c>
+      <c r="BE4">
+        <v>7.5</v>
+      </c>
+      <c r="BF4">
+        <v>2.34</v>
+      </c>
+      <c r="BG4">
+        <v>1.39</v>
+      </c>
+      <c r="BH4">
+        <v>2.77</v>
+      </c>
+      <c r="BI4">
+        <v>1.68</v>
+      </c>
+      <c r="BJ4">
+        <v>2.12</v>
+      </c>
+      <c r="BK4">
+        <v>2.11</v>
+      </c>
+      <c r="BL4">
+        <v>1.68</v>
+      </c>
+      <c r="BM4">
+        <v>2.7</v>
+      </c>
+      <c r="BN4">
+        <v>1.41</v>
+      </c>
+      <c r="BO4">
+        <v>3</v>
+      </c>
+      <c r="BP4">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:68">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>7778492</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="2">
+        <v>45703.08333333334</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+      <c r="N5">
+        <v>5</v>
+      </c>
+      <c r="O5" t="s">
+        <v>87</v>
+      </c>
+      <c r="P5" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q5">
+        <v>2.3</v>
+      </c>
+      <c r="R5">
+        <v>2.25</v>
+      </c>
+      <c r="S5">
+        <v>5</v>
+      </c>
+      <c r="T5">
+        <v>1.36</v>
+      </c>
+      <c r="U5">
+        <v>3</v>
+      </c>
+      <c r="V5">
+        <v>2.75</v>
+      </c>
+      <c r="W5">
+        <v>1.4</v>
+      </c>
+      <c r="X5">
+        <v>7</v>
+      </c>
+      <c r="Y5">
+        <v>1.1</v>
+      </c>
+      <c r="Z5">
+        <v>1.75</v>
+      </c>
+      <c r="AA5">
+        <v>3.9</v>
+      </c>
+      <c r="AB5">
+        <v>4.1</v>
+      </c>
+      <c r="AC5">
+        <v>1.04</v>
+      </c>
+      <c r="AD5">
+        <v>9</v>
+      </c>
+      <c r="AE5">
+        <v>1.26</v>
+      </c>
+      <c r="AF5">
+        <v>3.6</v>
+      </c>
+      <c r="AG5">
+        <v>1.8</v>
+      </c>
+      <c r="AH5">
+        <v>1.94</v>
+      </c>
+      <c r="AI5">
+        <v>1.8</v>
+      </c>
+      <c r="AJ5">
+        <v>1.91</v>
+      </c>
+      <c r="AK5">
+        <v>1.21</v>
+      </c>
+      <c r="AL5">
+        <v>1.24</v>
+      </c>
+      <c r="AM5">
+        <v>1.96</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>3</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>7</v>
+      </c>
+      <c r="AV5">
+        <v>5</v>
+      </c>
+      <c r="AW5">
+        <v>5</v>
+      </c>
+      <c r="AX5">
+        <v>6</v>
+      </c>
+      <c r="AY5">
+        <v>12</v>
+      </c>
+      <c r="AZ5">
+        <v>11</v>
+      </c>
+      <c r="BA5">
+        <v>5</v>
+      </c>
+      <c r="BB5">
+        <v>1</v>
+      </c>
+      <c r="BC5">
+        <v>6</v>
+      </c>
+      <c r="BD5">
+        <v>1.55</v>
+      </c>
+      <c r="BE5">
+        <v>8</v>
+      </c>
+      <c r="BF5">
+        <v>3.02</v>
+      </c>
+      <c r="BG5">
+        <v>1.39</v>
+      </c>
+      <c r="BH5">
+        <v>2.77</v>
+      </c>
+      <c r="BI5">
+        <v>1.68</v>
+      </c>
+      <c r="BJ5">
+        <v>2.11</v>
+      </c>
+      <c r="BK5">
+        <v>2.11</v>
+      </c>
+      <c r="BL5">
+        <v>1.68</v>
+      </c>
+      <c r="BM5">
+        <v>2.7</v>
+      </c>
+      <c r="BN5">
+        <v>1.41</v>
+      </c>
+      <c r="BO5">
+        <v>3.6</v>
+      </c>
+      <c r="BP5">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:68">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>7778493</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="2">
+        <v>45703.08333333334</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" t="s">
+        <v>81</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+      <c r="N6">
+        <v>2</v>
+      </c>
+      <c r="O6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P6" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q6">
+        <v>4.1</v>
+      </c>
+      <c r="R6">
+        <v>2.12</v>
+      </c>
+      <c r="S6">
+        <v>2.55</v>
+      </c>
+      <c r="T6">
+        <v>1.42</v>
+      </c>
+      <c r="U6">
+        <v>2.7</v>
+      </c>
+      <c r="V6">
+        <v>2.7</v>
+      </c>
+      <c r="W6">
+        <v>1.41</v>
+      </c>
+      <c r="X6">
+        <v>7.2</v>
+      </c>
+      <c r="Y6">
+        <v>1.06</v>
+      </c>
+      <c r="Z6">
+        <v>3.64</v>
+      </c>
+      <c r="AA6">
+        <v>3.36</v>
+      </c>
+      <c r="AB6">
+        <v>2.01</v>
+      </c>
+      <c r="AC6">
+        <v>1.01</v>
+      </c>
+      <c r="AD6">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE6">
+        <v>1.31</v>
+      </c>
+      <c r="AF6">
+        <v>3.25</v>
+      </c>
+      <c r="AG6">
+        <v>1.98</v>
+      </c>
+      <c r="AH6">
+        <v>1.77</v>
+      </c>
+      <c r="AI6">
+        <v>1.78</v>
+      </c>
+      <c r="AJ6">
+        <v>1.92</v>
+      </c>
+      <c r="AK6">
+        <v>1.72</v>
+      </c>
+      <c r="AL6">
+        <v>1.28</v>
+      </c>
+      <c r="AM6">
+        <v>1.27</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>3</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>4</v>
+      </c>
+      <c r="AW6">
+        <v>7</v>
+      </c>
+      <c r="AX6">
+        <v>7</v>
+      </c>
+      <c r="AY6">
+        <v>7</v>
+      </c>
+      <c r="AZ6">
+        <v>11</v>
+      </c>
+      <c r="BA6">
+        <v>1</v>
+      </c>
+      <c r="BB6">
+        <v>5</v>
+      </c>
+      <c r="BC6">
+        <v>6</v>
+      </c>
+      <c r="BD6">
+        <v>2.53</v>
+      </c>
+      <c r="BE6">
+        <v>7.5</v>
+      </c>
+      <c r="BF6">
+        <v>1.75</v>
+      </c>
+      <c r="BG6">
+        <v>1.55</v>
+      </c>
+      <c r="BH6">
+        <v>2.37</v>
+      </c>
+      <c r="BI6">
+        <v>1.98</v>
+      </c>
+      <c r="BJ6">
+        <v>1.82</v>
+      </c>
+      <c r="BK6">
+        <v>2.46</v>
+      </c>
+      <c r="BL6">
+        <v>1.48</v>
+      </c>
+      <c r="BM6">
+        <v>2.6</v>
+      </c>
+      <c r="BN6">
+        <v>1.43</v>
+      </c>
+      <c r="BO6">
+        <v>3.3</v>
+      </c>
+      <c r="BP6">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:68">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>7778496</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45703.08333333334</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" t="s">
+        <v>82</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7" t="s">
+        <v>84</v>
+      </c>
+      <c r="P7" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q7">
+        <v>2.88</v>
+      </c>
+      <c r="R7">
+        <v>2.1</v>
+      </c>
+      <c r="S7">
+        <v>4</v>
+      </c>
+      <c r="T7">
+        <v>1.44</v>
+      </c>
+      <c r="U7">
+        <v>2.63</v>
+      </c>
+      <c r="V7">
+        <v>3.25</v>
+      </c>
+      <c r="W7">
+        <v>1.33</v>
+      </c>
+      <c r="X7">
+        <v>9</v>
+      </c>
+      <c r="Y7">
+        <v>1.07</v>
+      </c>
+      <c r="Z7">
+        <v>2.08</v>
+      </c>
+      <c r="AA7">
+        <v>3.34</v>
+      </c>
+      <c r="AB7">
+        <v>3.45</v>
+      </c>
+      <c r="AC7">
+        <v>1.05</v>
+      </c>
+      <c r="AD7">
+        <v>8.5</v>
+      </c>
+      <c r="AE7">
+        <v>1.33</v>
+      </c>
+      <c r="AF7">
+        <v>3.15</v>
+      </c>
+      <c r="AG7">
+        <v>1.95</v>
+      </c>
+      <c r="AH7">
+        <v>1.79</v>
+      </c>
+      <c r="AI7">
+        <v>1.83</v>
+      </c>
+      <c r="AJ7">
+        <v>1.83</v>
+      </c>
+      <c r="AK7">
+        <v>1.33</v>
+      </c>
+      <c r="AL7">
+        <v>1.28</v>
+      </c>
+      <c r="AM7">
+        <v>1.62</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>3</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>3</v>
+      </c>
+      <c r="AV7">
+        <v>5</v>
+      </c>
+      <c r="AW7">
+        <v>7</v>
+      </c>
+      <c r="AX7">
+        <v>6</v>
+      </c>
+      <c r="AY7">
+        <v>10</v>
+      </c>
+      <c r="AZ7">
+        <v>14</v>
+      </c>
+      <c r="BA7">
+        <v>7</v>
+      </c>
+      <c r="BB7">
+        <v>4</v>
+      </c>
+      <c r="BC7">
+        <v>11</v>
+      </c>
+      <c r="BD7">
+        <v>1.85</v>
+      </c>
+      <c r="BE7">
+        <v>8</v>
+      </c>
+      <c r="BF7">
+        <v>2.28</v>
+      </c>
+      <c r="BG7">
+        <v>1.26</v>
+      </c>
+      <c r="BH7">
+        <v>3.22</v>
+      </c>
+      <c r="BI7">
+        <v>1.52</v>
+      </c>
+      <c r="BJ7">
+        <v>2.37</v>
+      </c>
+      <c r="BK7">
+        <v>1.95</v>
+      </c>
+      <c r="BL7">
+        <v>1.85</v>
+      </c>
+      <c r="BM7">
+        <v>2.38</v>
+      </c>
+      <c r="BN7">
+        <v>1.54</v>
+      </c>
+      <c r="BO7">
+        <v>3.28</v>
+      </c>
+      <c r="BP7">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:68">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>7778497</v>
+      </c>
+      <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="2">
+        <v>45703.29166666666</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>3</v>
+      </c>
+      <c r="M8">
+        <v>2</v>
+      </c>
+      <c r="N8">
+        <v>5</v>
+      </c>
+      <c r="O8" t="s">
+        <v>88</v>
+      </c>
+      <c r="P8" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q8">
+        <v>2.28</v>
+      </c>
+      <c r="R8">
+        <v>2.39</v>
+      </c>
+      <c r="S8">
+        <v>4.1</v>
+      </c>
+      <c r="T8">
+        <v>1.28</v>
+      </c>
+      <c r="U8">
+        <v>3.4</v>
+      </c>
+      <c r="V8">
+        <v>2.25</v>
+      </c>
+      <c r="W8">
+        <v>1.58</v>
+      </c>
+      <c r="X8">
+        <v>5.1</v>
+      </c>
+      <c r="Y8">
+        <v>1.13</v>
+      </c>
+      <c r="Z8">
+        <v>1.87</v>
+      </c>
+      <c r="AA8">
+        <v>3.68</v>
+      </c>
+      <c r="AB8">
+        <v>3.8</v>
+      </c>
+      <c r="AC8">
+        <v>1.01</v>
+      </c>
+      <c r="AD8">
+        <v>13</v>
+      </c>
+      <c r="AE8">
+        <v>1.18</v>
+      </c>
+      <c r="AF8">
+        <v>4.5</v>
+      </c>
+      <c r="AG8">
+        <v>1.57</v>
+      </c>
+      <c r="AH8">
+        <v>2.15</v>
+      </c>
+      <c r="AI8">
+        <v>1.53</v>
+      </c>
+      <c r="AJ8">
+        <v>2.34</v>
+      </c>
+      <c r="AK8">
+        <v>1.24</v>
+      </c>
+      <c r="AL8">
+        <v>1.24</v>
+      </c>
+      <c r="AM8">
+        <v>1.86</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>3</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>11</v>
+      </c>
+      <c r="AV8">
+        <v>7</v>
+      </c>
+      <c r="AW8">
+        <v>18</v>
+      </c>
+      <c r="AX8">
+        <v>8</v>
+      </c>
+      <c r="AY8">
+        <v>29</v>
+      </c>
+      <c r="AZ8">
+        <v>15</v>
+      </c>
+      <c r="BA8">
+        <v>11</v>
+      </c>
+      <c r="BB8">
+        <v>3</v>
+      </c>
+      <c r="BC8">
+        <v>14</v>
+      </c>
+      <c r="BD8">
+        <v>1.59</v>
+      </c>
+      <c r="BE8">
+        <v>8</v>
+      </c>
+      <c r="BF8">
+        <v>2.8</v>
+      </c>
+      <c r="BG8">
+        <v>1.29</v>
+      </c>
+      <c r="BH8">
+        <v>3.4</v>
+      </c>
+      <c r="BI8">
+        <v>1.52</v>
+      </c>
+      <c r="BJ8">
+        <v>2.37</v>
+      </c>
+      <c r="BK8">
+        <v>1.9</v>
+      </c>
+      <c r="BL8">
+        <v>1.9</v>
+      </c>
+      <c r="BM8">
+        <v>2.38</v>
+      </c>
+      <c r="BN8">
+        <v>1.54</v>
+      </c>
+      <c r="BO8">
+        <v>2.87</v>
+      </c>
+      <c r="BP8">
+        <v>1.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="104">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -247,6 +247,15 @@
     <t>V-Varen Nagasaki</t>
   </si>
   <si>
+    <t>Ehime</t>
+  </si>
+  <si>
+    <t>Imabari</t>
+  </si>
+  <si>
+    <t>Oita Trinita</t>
+  </si>
+  <si>
     <t>JEF United</t>
   </si>
   <si>
@@ -268,6 +277,15 @@
     <t>Roasso Kumamoto</t>
   </si>
   <si>
+    <t>Kataller Toyama</t>
+  </si>
+  <si>
+    <t>Blaublitz Akita</t>
+  </si>
+  <si>
+    <t>Consadole Sapporo</t>
+  </si>
+  <si>
     <t>[]</t>
   </si>
   <si>
@@ -283,6 +301,9 @@
     <t>['62', '64', '67']</t>
   </si>
   <si>
+    <t>['73', '84']</t>
+  </si>
+  <si>
     <t>['31', '60']</t>
   </si>
   <si>
@@ -299,6 +320,12 @@
   </si>
   <si>
     <t>['10', '89']</t>
+  </si>
+  <si>
+    <t>['67']</t>
+  </si>
+  <si>
+    <t>['40']</t>
   </si>
 </sst>
 </file>
@@ -660,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP8"/>
+  <dimension ref="A1:BP11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -892,7 +919,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -913,10 +940,10 @@
         <v>2</v>
       </c>
       <c r="O2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="Q2">
         <v>3.6</v>
@@ -1098,7 +1125,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1119,10 +1146,10 @@
         <v>3</v>
       </c>
       <c r="O3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="Q3">
         <v>3.75</v>
@@ -1304,7 +1331,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1325,10 +1352,10 @@
         <v>1</v>
       </c>
       <c r="O4" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="Q4">
         <v>2.8</v>
@@ -1510,7 +1537,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1531,10 +1558,10 @@
         <v>5</v>
       </c>
       <c r="O5" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -1716,7 +1743,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1737,10 +1764,10 @@
         <v>2</v>
       </c>
       <c r="O6" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="Q6">
         <v>4.1</v>
@@ -1922,7 +1949,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1943,10 +1970,10 @@
         <v>1</v>
       </c>
       <c r="O7" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="Q7">
         <v>2.88</v>
@@ -2128,7 +2155,7 @@
         <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -2149,10 +2176,10 @@
         <v>5</v>
       </c>
       <c r="O8" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="Q8">
         <v>2.28</v>
@@ -2309,6 +2336,624 @@
       </c>
       <c r="BP8">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:68">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>7778494</v>
+      </c>
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="2">
+        <v>45704.03472222222</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" t="s">
+        <v>87</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9" t="s">
+        <v>90</v>
+      </c>
+      <c r="P9" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q9">
+        <v>3.5</v>
+      </c>
+      <c r="R9">
+        <v>2.05</v>
+      </c>
+      <c r="S9">
+        <v>3.25</v>
+      </c>
+      <c r="T9">
+        <v>1.5</v>
+      </c>
+      <c r="U9">
+        <v>2.5</v>
+      </c>
+      <c r="V9">
+        <v>3.4</v>
+      </c>
+      <c r="W9">
+        <v>1.3</v>
+      </c>
+      <c r="X9">
+        <v>10</v>
+      </c>
+      <c r="Y9">
+        <v>1.06</v>
+      </c>
+      <c r="Z9">
+        <v>2.54</v>
+      </c>
+      <c r="AA9">
+        <v>3.27</v>
+      </c>
+      <c r="AB9">
+        <v>2.7</v>
+      </c>
+      <c r="AC9">
+        <v>1</v>
+      </c>
+      <c r="AD9">
+        <v>9.4</v>
+      </c>
+      <c r="AE9">
+        <v>1.37</v>
+      </c>
+      <c r="AF9">
+        <v>2.95</v>
+      </c>
+      <c r="AG9">
+        <v>2.05</v>
+      </c>
+      <c r="AH9">
+        <v>1.61</v>
+      </c>
+      <c r="AI9">
+        <v>1.83</v>
+      </c>
+      <c r="AJ9">
+        <v>1.83</v>
+      </c>
+      <c r="AK9">
+        <v>1.47</v>
+      </c>
+      <c r="AL9">
+        <v>1.31</v>
+      </c>
+      <c r="AM9">
+        <v>1.41</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>3</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>3</v>
+      </c>
+      <c r="AV9">
+        <v>8</v>
+      </c>
+      <c r="AW9">
+        <v>8</v>
+      </c>
+      <c r="AX9">
+        <v>7</v>
+      </c>
+      <c r="AY9">
+        <v>11</v>
+      </c>
+      <c r="AZ9">
+        <v>15</v>
+      </c>
+      <c r="BA9">
+        <v>7</v>
+      </c>
+      <c r="BB9">
+        <v>3</v>
+      </c>
+      <c r="BC9">
+        <v>10</v>
+      </c>
+      <c r="BD9">
+        <v>2.44</v>
+      </c>
+      <c r="BE9">
+        <v>8</v>
+      </c>
+      <c r="BF9">
+        <v>1.75</v>
+      </c>
+      <c r="BG9">
+        <v>1.2</v>
+      </c>
+      <c r="BH9">
+        <v>3.72</v>
+      </c>
+      <c r="BI9">
+        <v>1.44</v>
+      </c>
+      <c r="BJ9">
+        <v>2.58</v>
+      </c>
+      <c r="BK9">
+        <v>1.74</v>
+      </c>
+      <c r="BL9">
+        <v>2.02</v>
+      </c>
+      <c r="BM9">
+        <v>2.19</v>
+      </c>
+      <c r="BN9">
+        <v>1.63</v>
+      </c>
+      <c r="BO9">
+        <v>2.77</v>
+      </c>
+      <c r="BP9">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:68">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>7778495</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="2">
+        <v>45704.04861111111</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" t="s">
+        <v>88</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10" t="s">
+        <v>90</v>
+      </c>
+      <c r="P10" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q10">
+        <v>3.6</v>
+      </c>
+      <c r="R10">
+        <v>1.91</v>
+      </c>
+      <c r="S10">
+        <v>3.6</v>
+      </c>
+      <c r="T10">
+        <v>1.57</v>
+      </c>
+      <c r="U10">
+        <v>2.25</v>
+      </c>
+      <c r="V10">
+        <v>3.75</v>
+      </c>
+      <c r="W10">
+        <v>1.25</v>
+      </c>
+      <c r="X10">
+        <v>13</v>
+      </c>
+      <c r="Y10">
+        <v>1.04</v>
+      </c>
+      <c r="Z10">
+        <v>2.37</v>
+      </c>
+      <c r="AA10">
+        <v>3.01</v>
+      </c>
+      <c r="AB10">
+        <v>3.17</v>
+      </c>
+      <c r="AC10">
+        <v>1.1</v>
+      </c>
+      <c r="AD10">
+        <v>6.4</v>
+      </c>
+      <c r="AE10">
+        <v>1.5</v>
+      </c>
+      <c r="AF10">
+        <v>2.3</v>
+      </c>
+      <c r="AG10">
+        <v>2.59</v>
+      </c>
+      <c r="AH10">
+        <v>1.44</v>
+      </c>
+      <c r="AI10">
+        <v>2.1</v>
+      </c>
+      <c r="AJ10">
+        <v>1.67</v>
+      </c>
+      <c r="AK10">
+        <v>1.43</v>
+      </c>
+      <c r="AL10">
+        <v>1.33</v>
+      </c>
+      <c r="AM10">
+        <v>1.43</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>3</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>4</v>
+      </c>
+      <c r="AV10">
+        <v>5</v>
+      </c>
+      <c r="AW10">
+        <v>12</v>
+      </c>
+      <c r="AX10">
+        <v>4</v>
+      </c>
+      <c r="AY10">
+        <v>16</v>
+      </c>
+      <c r="AZ10">
+        <v>9</v>
+      </c>
+      <c r="BA10">
+        <v>12</v>
+      </c>
+      <c r="BB10">
+        <v>5</v>
+      </c>
+      <c r="BC10">
+        <v>17</v>
+      </c>
+      <c r="BD10">
+        <v>1.82</v>
+      </c>
+      <c r="BE10">
+        <v>8</v>
+      </c>
+      <c r="BF10">
+        <v>2.39</v>
+      </c>
+      <c r="BG10">
+        <v>1.26</v>
+      </c>
+      <c r="BH10">
+        <v>3.22</v>
+      </c>
+      <c r="BI10">
+        <v>1.52</v>
+      </c>
+      <c r="BJ10">
+        <v>2.37</v>
+      </c>
+      <c r="BK10">
+        <v>1.95</v>
+      </c>
+      <c r="BL10">
+        <v>1.85</v>
+      </c>
+      <c r="BM10">
+        <v>2.38</v>
+      </c>
+      <c r="BN10">
+        <v>1.54</v>
+      </c>
+      <c r="BO10">
+        <v>3.28</v>
+      </c>
+      <c r="BP10">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:68">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>7778498</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="2">
+        <v>45704.08333333334</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>2</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>2</v>
+      </c>
+      <c r="O11" t="s">
+        <v>95</v>
+      </c>
+      <c r="P11" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q11">
+        <v>3.75</v>
+      </c>
+      <c r="R11">
+        <v>2.1</v>
+      </c>
+      <c r="S11">
+        <v>2.88</v>
+      </c>
+      <c r="T11">
+        <v>1.44</v>
+      </c>
+      <c r="U11">
+        <v>2.63</v>
+      </c>
+      <c r="V11">
+        <v>3.25</v>
+      </c>
+      <c r="W11">
+        <v>1.33</v>
+      </c>
+      <c r="X11">
+        <v>9</v>
+      </c>
+      <c r="Y11">
+        <v>1.07</v>
+      </c>
+      <c r="Z11">
+        <v>3.21</v>
+      </c>
+      <c r="AA11">
+        <v>3.21</v>
+      </c>
+      <c r="AB11">
+        <v>2.24</v>
+      </c>
+      <c r="AC11">
+        <v>1</v>
+      </c>
+      <c r="AD11">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE11">
+        <v>1.34</v>
+      </c>
+      <c r="AF11">
+        <v>3.05</v>
+      </c>
+      <c r="AG11">
+        <v>2</v>
+      </c>
+      <c r="AH11">
+        <v>1.72</v>
+      </c>
+      <c r="AI11">
+        <v>1.83</v>
+      </c>
+      <c r="AJ11">
+        <v>1.83</v>
+      </c>
+      <c r="AK11">
+        <v>1.61</v>
+      </c>
+      <c r="AL11">
+        <v>1.29</v>
+      </c>
+      <c r="AM11">
+        <v>1.32</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>3</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>7</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <v>5</v>
+      </c>
+      <c r="AX11">
+        <v>4</v>
+      </c>
+      <c r="AY11">
+        <v>12</v>
+      </c>
+      <c r="AZ11">
+        <v>4</v>
+      </c>
+      <c r="BA11">
+        <v>2</v>
+      </c>
+      <c r="BB11">
+        <v>4</v>
+      </c>
+      <c r="BC11">
+        <v>6</v>
+      </c>
+      <c r="BD11">
+        <v>2.1</v>
+      </c>
+      <c r="BE11">
+        <v>8</v>
+      </c>
+      <c r="BF11">
+        <v>1.95</v>
+      </c>
+      <c r="BG11">
+        <v>1.27</v>
+      </c>
+      <c r="BH11">
+        <v>3.14</v>
+      </c>
+      <c r="BI11">
+        <v>1.56</v>
+      </c>
+      <c r="BJ11">
+        <v>2.33</v>
+      </c>
+      <c r="BK11">
+        <v>1.98</v>
+      </c>
+      <c r="BL11">
+        <v>1.82</v>
+      </c>
+      <c r="BM11">
+        <v>2.43</v>
+      </c>
+      <c r="BN11">
+        <v>1.49</v>
+      </c>
+      <c r="BO11">
+        <v>3.34</v>
+      </c>
+      <c r="BP11">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="107">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -302,6 +302,15 @@
   </si>
   <si>
     <t>['73', '84']</t>
+  </si>
+  <si>
+    <t>['82']</t>
+  </si>
+  <si>
+    <t>['35', '50']</t>
+  </si>
+  <si>
+    <t>['13']</t>
   </si>
   <si>
     <t>['31', '60']</t>
@@ -687,7 +696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP11"/>
+  <dimension ref="A1:BP14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -943,7 +952,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="Q2">
         <v>3.6</v>
@@ -1149,7 +1158,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="Q3">
         <v>3.75</v>
@@ -1561,7 +1570,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -1767,7 +1776,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="Q6">
         <v>4.1</v>
@@ -1973,7 +1982,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="Q7">
         <v>2.88</v>
@@ -2179,7 +2188,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="Q8">
         <v>2.28</v>
@@ -2385,7 +2394,7 @@
         <v>90</v>
       </c>
       <c r="P9" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -2466,7 +2475,7 @@
         <v>0</v>
       </c>
       <c r="AQ9">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2591,7 +2600,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -2954,6 +2963,624 @@
       </c>
       <c r="BP11">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:68">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>7778502</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="2">
+        <v>45710.08333333334</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>73</v>
+      </c>
+      <c r="H12" t="s">
+        <v>75</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12" t="s">
+        <v>96</v>
+      </c>
+      <c r="P12" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q12">
+        <v>2.5</v>
+      </c>
+      <c r="R12">
+        <v>2.2</v>
+      </c>
+      <c r="S12">
+        <v>4.5</v>
+      </c>
+      <c r="T12">
+        <v>1.4</v>
+      </c>
+      <c r="U12">
+        <v>2.75</v>
+      </c>
+      <c r="V12">
+        <v>3</v>
+      </c>
+      <c r="W12">
+        <v>1.36</v>
+      </c>
+      <c r="X12">
+        <v>8</v>
+      </c>
+      <c r="Y12">
+        <v>1.08</v>
+      </c>
+      <c r="Z12">
+        <v>1.88</v>
+      </c>
+      <c r="AA12">
+        <v>3.69</v>
+      </c>
+      <c r="AB12">
+        <v>3.74</v>
+      </c>
+      <c r="AC12">
+        <v>1.05</v>
+      </c>
+      <c r="AD12">
+        <v>8.5</v>
+      </c>
+      <c r="AE12">
+        <v>1.32</v>
+      </c>
+      <c r="AF12">
+        <v>3.2</v>
+      </c>
+      <c r="AG12">
+        <v>1.87</v>
+      </c>
+      <c r="AH12">
+        <v>1.87</v>
+      </c>
+      <c r="AI12">
+        <v>1.83</v>
+      </c>
+      <c r="AJ12">
+        <v>1.83</v>
+      </c>
+      <c r="AK12">
+        <v>1.23</v>
+      </c>
+      <c r="AL12">
+        <v>1.27</v>
+      </c>
+      <c r="AM12">
+        <v>1.82</v>
+      </c>
+      <c r="AN12">
+        <v>3</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>3</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>1.68</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>1.68</v>
+      </c>
+      <c r="AU12">
+        <v>3</v>
+      </c>
+      <c r="AV12">
+        <v>8</v>
+      </c>
+      <c r="AW12">
+        <v>3</v>
+      </c>
+      <c r="AX12">
+        <v>8</v>
+      </c>
+      <c r="AY12">
+        <v>6</v>
+      </c>
+      <c r="AZ12">
+        <v>16</v>
+      </c>
+      <c r="BA12">
+        <v>5</v>
+      </c>
+      <c r="BB12">
+        <v>3</v>
+      </c>
+      <c r="BC12">
+        <v>8</v>
+      </c>
+      <c r="BD12">
+        <v>1.7</v>
+      </c>
+      <c r="BE12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF12">
+        <v>2.45</v>
+      </c>
+      <c r="BG12">
+        <v>1.21</v>
+      </c>
+      <c r="BH12">
+        <v>3.58</v>
+      </c>
+      <c r="BI12">
+        <v>1.4</v>
+      </c>
+      <c r="BJ12">
+        <v>2.56</v>
+      </c>
+      <c r="BK12">
+        <v>1.73</v>
+      </c>
+      <c r="BL12">
+        <v>1.95</v>
+      </c>
+      <c r="BM12">
+        <v>2.17</v>
+      </c>
+      <c r="BN12">
+        <v>1.55</v>
+      </c>
+      <c r="BO12">
+        <v>2.88</v>
+      </c>
+      <c r="BP12">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:68">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>7778501</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="2">
+        <v>45710.08333333334</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" t="s">
+        <v>80</v>
+      </c>
+      <c r="H13" t="s">
+        <v>87</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>2</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>2</v>
+      </c>
+      <c r="O13" t="s">
+        <v>97</v>
+      </c>
+      <c r="P13" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q13">
+        <v>2.2</v>
+      </c>
+      <c r="R13">
+        <v>2.25</v>
+      </c>
+      <c r="S13">
+        <v>6</v>
+      </c>
+      <c r="T13">
+        <v>1.4</v>
+      </c>
+      <c r="U13">
+        <v>2.75</v>
+      </c>
+      <c r="V13">
+        <v>2.75</v>
+      </c>
+      <c r="W13">
+        <v>1.4</v>
+      </c>
+      <c r="X13">
+        <v>8</v>
+      </c>
+      <c r="Y13">
+        <v>1.08</v>
+      </c>
+      <c r="Z13">
+        <v>1.45</v>
+      </c>
+      <c r="AA13">
+        <v>4.4</v>
+      </c>
+      <c r="AB13">
+        <v>6.5</v>
+      </c>
+      <c r="AC13">
+        <v>1.05</v>
+      </c>
+      <c r="AD13">
+        <v>8.5</v>
+      </c>
+      <c r="AE13">
+        <v>1.31</v>
+      </c>
+      <c r="AF13">
+        <v>3.3</v>
+      </c>
+      <c r="AG13">
+        <v>1.82</v>
+      </c>
+      <c r="AH13">
+        <v>1.92</v>
+      </c>
+      <c r="AI13">
+        <v>2</v>
+      </c>
+      <c r="AJ13">
+        <v>1.73</v>
+      </c>
+      <c r="AK13">
+        <v>1.15</v>
+      </c>
+      <c r="AL13">
+        <v>1.23</v>
+      </c>
+      <c r="AM13">
+        <v>2.3</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>3</v>
+      </c>
+      <c r="AP13">
+        <v>3</v>
+      </c>
+      <c r="AQ13">
+        <v>1.5</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>1.8</v>
+      </c>
+      <c r="AT13">
+        <v>1.8</v>
+      </c>
+      <c r="AU13">
+        <v>5</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>4</v>
+      </c>
+      <c r="AX13">
+        <v>3</v>
+      </c>
+      <c r="AY13">
+        <v>9</v>
+      </c>
+      <c r="AZ13">
+        <v>3</v>
+      </c>
+      <c r="BA13">
+        <v>6</v>
+      </c>
+      <c r="BB13">
+        <v>1</v>
+      </c>
+      <c r="BC13">
+        <v>7</v>
+      </c>
+      <c r="BD13">
+        <v>1.5</v>
+      </c>
+      <c r="BE13">
+        <v>8.5</v>
+      </c>
+      <c r="BF13">
+        <v>3</v>
+      </c>
+      <c r="BG13">
+        <v>1.27</v>
+      </c>
+      <c r="BH13">
+        <v>3.14</v>
+      </c>
+      <c r="BI13">
+        <v>1.51</v>
+      </c>
+      <c r="BJ13">
+        <v>2.26</v>
+      </c>
+      <c r="BK13">
+        <v>1.89</v>
+      </c>
+      <c r="BL13">
+        <v>1.77</v>
+      </c>
+      <c r="BM13">
+        <v>2.46</v>
+      </c>
+      <c r="BN13">
+        <v>1.43</v>
+      </c>
+      <c r="BO13">
+        <v>3.34</v>
+      </c>
+      <c r="BP13">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:68">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>7778500</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="2">
+        <v>45710.08333333334</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" t="s">
+        <v>72</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14" t="s">
+        <v>98</v>
+      </c>
+      <c r="P14" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q14">
+        <v>2.63</v>
+      </c>
+      <c r="R14">
+        <v>2.1</v>
+      </c>
+      <c r="S14">
+        <v>4.33</v>
+      </c>
+      <c r="T14">
+        <v>1.4</v>
+      </c>
+      <c r="U14">
+        <v>2.75</v>
+      </c>
+      <c r="V14">
+        <v>3</v>
+      </c>
+      <c r="W14">
+        <v>1.36</v>
+      </c>
+      <c r="X14">
+        <v>8</v>
+      </c>
+      <c r="Y14">
+        <v>1.08</v>
+      </c>
+      <c r="Z14">
+        <v>1.95</v>
+      </c>
+      <c r="AA14">
+        <v>3.64</v>
+      </c>
+      <c r="AB14">
+        <v>3.53</v>
+      </c>
+      <c r="AC14">
+        <v>1.06</v>
+      </c>
+      <c r="AD14">
+        <v>8.75</v>
+      </c>
+      <c r="AE14">
+        <v>1.31</v>
+      </c>
+      <c r="AF14">
+        <v>3.1</v>
+      </c>
+      <c r="AG14">
+        <v>1.87</v>
+      </c>
+      <c r="AH14">
+        <v>1.87</v>
+      </c>
+      <c r="AI14">
+        <v>1.83</v>
+      </c>
+      <c r="AJ14">
+        <v>1.83</v>
+      </c>
+      <c r="AK14">
+        <v>1.29</v>
+      </c>
+      <c r="AL14">
+        <v>1.29</v>
+      </c>
+      <c r="AM14">
+        <v>1.73</v>
+      </c>
+      <c r="AN14">
+        <v>3</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>3</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>2.25</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>2.25</v>
+      </c>
+      <c r="AU14">
+        <v>5</v>
+      </c>
+      <c r="AV14">
+        <v>3</v>
+      </c>
+      <c r="AW14">
+        <v>7</v>
+      </c>
+      <c r="AX14">
+        <v>5</v>
+      </c>
+      <c r="AY14">
+        <v>12</v>
+      </c>
+      <c r="AZ14">
+        <v>8</v>
+      </c>
+      <c r="BA14">
+        <v>8</v>
+      </c>
+      <c r="BB14">
+        <v>8</v>
+      </c>
+      <c r="BC14">
+        <v>16</v>
+      </c>
+      <c r="BD14">
+        <v>2.02</v>
+      </c>
+      <c r="BE14">
+        <v>7.8</v>
+      </c>
+      <c r="BF14">
+        <v>2.02</v>
+      </c>
+      <c r="BG14">
+        <v>1.25</v>
+      </c>
+      <c r="BH14">
+        <v>3.28</v>
+      </c>
+      <c r="BI14">
+        <v>1.48</v>
+      </c>
+      <c r="BJ14">
+        <v>2.33</v>
+      </c>
+      <c r="BK14">
+        <v>1.84</v>
+      </c>
+      <c r="BL14">
+        <v>1.82</v>
+      </c>
+      <c r="BM14">
+        <v>2.35</v>
+      </c>
+      <c r="BN14">
+        <v>1.47</v>
+      </c>
+      <c r="BO14">
+        <v>3.2</v>
+      </c>
+      <c r="BP14">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="114">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -259,24 +259,24 @@
     <t>JEF United</t>
   </si>
   <si>
+    <t>Renofa Yamaguchi</t>
+  </si>
+  <si>
+    <t>Roasso Kumamoto</t>
+  </si>
+  <si>
+    <t>Tokushima Vortis</t>
+  </si>
+  <si>
+    <t>Mito Hollyhock</t>
+  </si>
+  <si>
     <t>Montedio Yamagata</t>
   </si>
   <si>
-    <t>Renofa Yamaguchi</t>
-  </si>
-  <si>
-    <t>Mito Hollyhock</t>
-  </si>
-  <si>
-    <t>Tokushima Vortis</t>
-  </si>
-  <si>
     <t>Vegalta Sendai</t>
   </si>
   <si>
-    <t>Roasso Kumamoto</t>
-  </si>
-  <si>
     <t>Kataller Toyama</t>
   </si>
   <si>
@@ -313,6 +313,21 @@
     <t>['13']</t>
   </si>
   <si>
+    <t>['35', '87']</t>
+  </si>
+  <si>
+    <t>['28', '49', '90+1']</t>
+  </si>
+  <si>
+    <t>['52']</t>
+  </si>
+  <si>
+    <t>['28']</t>
+  </si>
+  <si>
+    <t>['68']</t>
+  </si>
+  <si>
     <t>['31', '60']</t>
   </si>
   <si>
@@ -335,6 +350,12 @@
   </si>
   <si>
     <t>['40']</t>
+  </si>
+  <si>
+    <t>['60', '90+3']</t>
+  </si>
+  <si>
+    <t>['17', '54']</t>
   </si>
 </sst>
 </file>
@@ -696,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP14"/>
+  <dimension ref="A1:BP21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -952,7 +973,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="Q2">
         <v>3.6</v>
@@ -1134,7 +1155,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1158,7 +1179,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="Q3">
         <v>3.75</v>
@@ -1340,7 +1361,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1546,7 +1567,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1570,7 +1591,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -1752,7 +1773,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1776,7 +1797,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="Q6">
         <v>4.1</v>
@@ -1958,7 +1979,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1982,7 +2003,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="Q7">
         <v>2.88</v>
@@ -2063,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="AQ7">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2164,7 +2185,7 @@
         <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -2188,7 +2209,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="Q8">
         <v>2.28</v>
@@ -2394,7 +2415,7 @@
         <v>90</v>
       </c>
       <c r="P9" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -2600,7 +2621,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -2678,7 +2699,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ10">
         <v>3</v>
@@ -2884,7 +2905,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ11">
         <v>0</v>
@@ -3581,6 +3602,1448 @@
       </c>
       <c r="BP14">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:68">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>7778503</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="2">
+        <v>45711.04166666666</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15" t="s">
+        <v>81</v>
+      </c>
+      <c r="H15" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>2</v>
+      </c>
+      <c r="M15">
+        <v>2</v>
+      </c>
+      <c r="N15">
+        <v>4</v>
+      </c>
+      <c r="O15" t="s">
+        <v>99</v>
+      </c>
+      <c r="P15" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q15">
+        <v>4.1</v>
+      </c>
+      <c r="R15">
+        <v>2.18</v>
+      </c>
+      <c r="S15">
+        <v>2.5</v>
+      </c>
+      <c r="T15">
+        <v>1.42</v>
+      </c>
+      <c r="U15">
+        <v>2.7</v>
+      </c>
+      <c r="V15">
+        <v>2.6</v>
+      </c>
+      <c r="W15">
+        <v>1.44</v>
+      </c>
+      <c r="X15">
+        <v>7</v>
+      </c>
+      <c r="Y15">
+        <v>1.1</v>
+      </c>
+      <c r="Z15">
+        <v>3.55</v>
+      </c>
+      <c r="AA15">
+        <v>3.45</v>
+      </c>
+      <c r="AB15">
+        <v>2</v>
+      </c>
+      <c r="AC15">
+        <v>1.01</v>
+      </c>
+      <c r="AD15">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE15">
+        <v>1.27</v>
+      </c>
+      <c r="AF15">
+        <v>3.5</v>
+      </c>
+      <c r="AG15">
+        <v>1.83</v>
+      </c>
+      <c r="AH15">
+        <v>1.91</v>
+      </c>
+      <c r="AI15">
+        <v>1.71</v>
+      </c>
+      <c r="AJ15">
+        <v>2.02</v>
+      </c>
+      <c r="AK15">
+        <v>1.75</v>
+      </c>
+      <c r="AL15">
+        <v>1.27</v>
+      </c>
+      <c r="AM15">
+        <v>1.27</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>1</v>
+      </c>
+      <c r="AQ15">
+        <v>1</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>5</v>
+      </c>
+      <c r="AV15">
+        <v>4</v>
+      </c>
+      <c r="AW15">
+        <v>3</v>
+      </c>
+      <c r="AX15">
+        <v>6</v>
+      </c>
+      <c r="AY15">
+        <v>8</v>
+      </c>
+      <c r="AZ15">
+        <v>10</v>
+      </c>
+      <c r="BA15">
+        <v>2</v>
+      </c>
+      <c r="BB15">
+        <v>7</v>
+      </c>
+      <c r="BC15">
+        <v>9</v>
+      </c>
+      <c r="BD15">
+        <v>2.21</v>
+      </c>
+      <c r="BE15">
+        <v>6.25</v>
+      </c>
+      <c r="BF15">
+        <v>1.98</v>
+      </c>
+      <c r="BG15">
+        <v>1.27</v>
+      </c>
+      <c r="BH15">
+        <v>3.14</v>
+      </c>
+      <c r="BI15">
+        <v>1.58</v>
+      </c>
+      <c r="BJ15">
+        <v>2.29</v>
+      </c>
+      <c r="BK15">
+        <v>1.95</v>
+      </c>
+      <c r="BL15">
+        <v>1.85</v>
+      </c>
+      <c r="BM15">
+        <v>2.48</v>
+      </c>
+      <c r="BN15">
+        <v>1.48</v>
+      </c>
+      <c r="BO15">
+        <v>2.88</v>
+      </c>
+      <c r="BP15">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:68">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>7778507</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="2">
+        <v>45711.04166666666</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16" t="s">
+        <v>82</v>
+      </c>
+      <c r="H16" t="s">
+        <v>89</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>3</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>3</v>
+      </c>
+      <c r="O16" t="s">
+        <v>100</v>
+      </c>
+      <c r="P16" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q16">
+        <v>3.4</v>
+      </c>
+      <c r="R16">
+        <v>2.2</v>
+      </c>
+      <c r="S16">
+        <v>3</v>
+      </c>
+      <c r="T16">
+        <v>1.36</v>
+      </c>
+      <c r="U16">
+        <v>3</v>
+      </c>
+      <c r="V16">
+        <v>2.75</v>
+      </c>
+      <c r="W16">
+        <v>1.4</v>
+      </c>
+      <c r="X16">
+        <v>7</v>
+      </c>
+      <c r="Y16">
+        <v>1.1</v>
+      </c>
+      <c r="Z16">
+        <v>2.61</v>
+      </c>
+      <c r="AA16">
+        <v>3.59</v>
+      </c>
+      <c r="AB16">
+        <v>2.45</v>
+      </c>
+      <c r="AC16">
+        <v>1.04</v>
+      </c>
+      <c r="AD16">
+        <v>9</v>
+      </c>
+      <c r="AE16">
+        <v>1.26</v>
+      </c>
+      <c r="AF16">
+        <v>3.6</v>
+      </c>
+      <c r="AG16">
+        <v>1.82</v>
+      </c>
+      <c r="AH16">
+        <v>1.92</v>
+      </c>
+      <c r="AI16">
+        <v>1.67</v>
+      </c>
+      <c r="AJ16">
+        <v>2.1</v>
+      </c>
+      <c r="AK16">
+        <v>1.55</v>
+      </c>
+      <c r="AL16">
+        <v>1.28</v>
+      </c>
+      <c r="AM16">
+        <v>1.43</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>3</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0.59</v>
+      </c>
+      <c r="AT16">
+        <v>0.59</v>
+      </c>
+      <c r="AU16">
+        <v>4</v>
+      </c>
+      <c r="AV16">
+        <v>5</v>
+      </c>
+      <c r="AW16">
+        <v>9</v>
+      </c>
+      <c r="AX16">
+        <v>5</v>
+      </c>
+      <c r="AY16">
+        <v>13</v>
+      </c>
+      <c r="AZ16">
+        <v>10</v>
+      </c>
+      <c r="BA16">
+        <v>7</v>
+      </c>
+      <c r="BB16">
+        <v>6</v>
+      </c>
+      <c r="BC16">
+        <v>13</v>
+      </c>
+      <c r="BD16">
+        <v>1.95</v>
+      </c>
+      <c r="BE16">
+        <v>8</v>
+      </c>
+      <c r="BF16">
+        <v>2.1</v>
+      </c>
+      <c r="BG16">
+        <v>1.25</v>
+      </c>
+      <c r="BH16">
+        <v>3.28</v>
+      </c>
+      <c r="BI16">
+        <v>1.52</v>
+      </c>
+      <c r="BJ16">
+        <v>2.37</v>
+      </c>
+      <c r="BK16">
+        <v>1.87</v>
+      </c>
+      <c r="BL16">
+        <v>1.87</v>
+      </c>
+      <c r="BM16">
+        <v>2.38</v>
+      </c>
+      <c r="BN16">
+        <v>1.54</v>
+      </c>
+      <c r="BO16">
+        <v>3.2</v>
+      </c>
+      <c r="BP16">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:68">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>7778504</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="2">
+        <v>45711.07986111111</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17" t="s">
+        <v>83</v>
+      </c>
+      <c r="H17" t="s">
+        <v>86</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17" t="s">
+        <v>101</v>
+      </c>
+      <c r="P17" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q17">
+        <v>3.2</v>
+      </c>
+      <c r="R17">
+        <v>1.93</v>
+      </c>
+      <c r="S17">
+        <v>3.7</v>
+      </c>
+      <c r="T17">
+        <v>1.56</v>
+      </c>
+      <c r="U17">
+        <v>2.31</v>
+      </c>
+      <c r="V17">
+        <v>3.3</v>
+      </c>
+      <c r="W17">
+        <v>1.3</v>
+      </c>
+      <c r="X17">
+        <v>9.5</v>
+      </c>
+      <c r="Y17">
+        <v>1.06</v>
+      </c>
+      <c r="Z17">
+        <v>2.4</v>
+      </c>
+      <c r="AA17">
+        <v>3.25</v>
+      </c>
+      <c r="AB17">
+        <v>2.9</v>
+      </c>
+      <c r="AC17">
+        <v>1.03</v>
+      </c>
+      <c r="AD17">
+        <v>7.3</v>
+      </c>
+      <c r="AE17">
+        <v>1.46</v>
+      </c>
+      <c r="AF17">
+        <v>2.6</v>
+      </c>
+      <c r="AG17">
+        <v>2.3</v>
+      </c>
+      <c r="AH17">
+        <v>1.5</v>
+      </c>
+      <c r="AI17">
+        <v>2.02</v>
+      </c>
+      <c r="AJ17">
+        <v>1.72</v>
+      </c>
+      <c r="AK17">
+        <v>1.38</v>
+      </c>
+      <c r="AL17">
+        <v>1.32</v>
+      </c>
+      <c r="AM17">
+        <v>1.49</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>3</v>
+      </c>
+      <c r="AP17">
+        <v>3</v>
+      </c>
+      <c r="AQ17">
+        <v>1.5</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>1.41</v>
+      </c>
+      <c r="AT17">
+        <v>1.41</v>
+      </c>
+      <c r="AU17">
+        <v>4</v>
+      </c>
+      <c r="AV17">
+        <v>4</v>
+      </c>
+      <c r="AW17">
+        <v>9</v>
+      </c>
+      <c r="AX17">
+        <v>6</v>
+      </c>
+      <c r="AY17">
+        <v>13</v>
+      </c>
+      <c r="AZ17">
+        <v>10</v>
+      </c>
+      <c r="BA17">
+        <v>2</v>
+      </c>
+      <c r="BB17">
+        <v>6</v>
+      </c>
+      <c r="BC17">
+        <v>8</v>
+      </c>
+      <c r="BD17">
+        <v>2</v>
+      </c>
+      <c r="BE17">
+        <v>6.1</v>
+      </c>
+      <c r="BF17">
+        <v>2.2</v>
+      </c>
+      <c r="BG17">
+        <v>1.39</v>
+      </c>
+      <c r="BH17">
+        <v>2.75</v>
+      </c>
+      <c r="BI17">
+        <v>1.69</v>
+      </c>
+      <c r="BJ17">
+        <v>2.1</v>
+      </c>
+      <c r="BK17">
+        <v>2</v>
+      </c>
+      <c r="BL17">
+        <v>1.8</v>
+      </c>
+      <c r="BM17">
+        <v>2.72</v>
+      </c>
+      <c r="BN17">
+        <v>1.4</v>
+      </c>
+      <c r="BO17">
+        <v>3.6</v>
+      </c>
+      <c r="BP17">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:68">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>7778499</v>
+      </c>
+      <c r="C18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="2">
+        <v>45711.08333333334</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18" t="s">
+        <v>84</v>
+      </c>
+      <c r="H18" t="s">
+        <v>85</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18" t="s">
+        <v>102</v>
+      </c>
+      <c r="P18" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q18">
+        <v>3.7</v>
+      </c>
+      <c r="R18">
+        <v>2.16</v>
+      </c>
+      <c r="S18">
+        <v>2.7</v>
+      </c>
+      <c r="T18">
+        <v>1.36</v>
+      </c>
+      <c r="U18">
+        <v>3</v>
+      </c>
+      <c r="V18">
+        <v>2.65</v>
+      </c>
+      <c r="W18">
+        <v>1.42</v>
+      </c>
+      <c r="X18">
+        <v>7.5</v>
+      </c>
+      <c r="Y18">
+        <v>1.08</v>
+      </c>
+      <c r="Z18">
+        <v>3.1</v>
+      </c>
+      <c r="AA18">
+        <v>3.55</v>
+      </c>
+      <c r="AB18">
+        <v>2.15</v>
+      </c>
+      <c r="AC18">
+        <v>1.03</v>
+      </c>
+      <c r="AD18">
+        <v>9</v>
+      </c>
+      <c r="AE18">
+        <v>1.27</v>
+      </c>
+      <c r="AF18">
+        <v>3.5</v>
+      </c>
+      <c r="AG18">
+        <v>1.87</v>
+      </c>
+      <c r="AH18">
+        <v>1.87</v>
+      </c>
+      <c r="AI18">
+        <v>1.69</v>
+      </c>
+      <c r="AJ18">
+        <v>2.05</v>
+      </c>
+      <c r="AK18">
+        <v>1.64</v>
+      </c>
+      <c r="AL18">
+        <v>1.28</v>
+      </c>
+      <c r="AM18">
+        <v>1.33</v>
+      </c>
+      <c r="AN18">
+        <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <v>3</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0.9</v>
+      </c>
+      <c r="AT18">
+        <v>0.9</v>
+      </c>
+      <c r="AU18">
+        <v>5</v>
+      </c>
+      <c r="AV18">
+        <v>3</v>
+      </c>
+      <c r="AW18">
+        <v>7</v>
+      </c>
+      <c r="AX18">
+        <v>6</v>
+      </c>
+      <c r="AY18">
+        <v>19</v>
+      </c>
+      <c r="AZ18">
+        <v>12</v>
+      </c>
+      <c r="BA18">
+        <v>10</v>
+      </c>
+      <c r="BB18">
+        <v>4</v>
+      </c>
+      <c r="BC18">
+        <v>14</v>
+      </c>
+      <c r="BD18">
+        <v>2.04</v>
+      </c>
+      <c r="BE18">
+        <v>6.15</v>
+      </c>
+      <c r="BF18">
+        <v>2.15</v>
+      </c>
+      <c r="BG18">
+        <v>1.36</v>
+      </c>
+      <c r="BH18">
+        <v>2.88</v>
+      </c>
+      <c r="BI18">
+        <v>1.63</v>
+      </c>
+      <c r="BJ18">
+        <v>2.19</v>
+      </c>
+      <c r="BK18">
+        <v>1.85</v>
+      </c>
+      <c r="BL18">
+        <v>1.95</v>
+      </c>
+      <c r="BM18">
+        <v>2.6</v>
+      </c>
+      <c r="BN18">
+        <v>1.44</v>
+      </c>
+      <c r="BO18">
+        <v>3.58</v>
+      </c>
+      <c r="BP18">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:68">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>7778506</v>
+      </c>
+      <c r="C19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="2">
+        <v>45711.08333333334</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19" t="s">
+        <v>78</v>
+      </c>
+      <c r="H19" t="s">
+        <v>74</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19" t="s">
+        <v>90</v>
+      </c>
+      <c r="P19" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q19">
+        <v>2.75</v>
+      </c>
+      <c r="R19">
+        <v>2.05</v>
+      </c>
+      <c r="S19">
+        <v>4.5</v>
+      </c>
+      <c r="T19">
+        <v>1.44</v>
+      </c>
+      <c r="U19">
+        <v>2.63</v>
+      </c>
+      <c r="V19">
+        <v>3.25</v>
+      </c>
+      <c r="W19">
+        <v>1.33</v>
+      </c>
+      <c r="X19">
+        <v>10</v>
+      </c>
+      <c r="Y19">
+        <v>1.06</v>
+      </c>
+      <c r="Z19">
+        <v>1.92</v>
+      </c>
+      <c r="AA19">
+        <v>3.5</v>
+      </c>
+      <c r="AB19">
+        <v>3.81</v>
+      </c>
+      <c r="AC19">
+        <v>1.06</v>
+      </c>
+      <c r="AD19">
+        <v>8</v>
+      </c>
+      <c r="AE19">
+        <v>1.39</v>
+      </c>
+      <c r="AF19">
+        <v>2.85</v>
+      </c>
+      <c r="AG19">
+        <v>2</v>
+      </c>
+      <c r="AH19">
+        <v>1.65</v>
+      </c>
+      <c r="AI19">
+        <v>2</v>
+      </c>
+      <c r="AJ19">
+        <v>1.73</v>
+      </c>
+      <c r="AK19">
+        <v>1.27</v>
+      </c>
+      <c r="AL19">
+        <v>1.3</v>
+      </c>
+      <c r="AM19">
+        <v>1.77</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>0.5</v>
+      </c>
+      <c r="AQ19">
+        <v>1</v>
+      </c>
+      <c r="AR19">
+        <v>1.74</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>1.74</v>
+      </c>
+      <c r="AU19">
+        <v>2</v>
+      </c>
+      <c r="AV19">
+        <v>3</v>
+      </c>
+      <c r="AW19">
+        <v>0</v>
+      </c>
+      <c r="AX19">
+        <v>4</v>
+      </c>
+      <c r="AY19">
+        <v>2</v>
+      </c>
+      <c r="AZ19">
+        <v>7</v>
+      </c>
+      <c r="BA19">
+        <v>1</v>
+      </c>
+      <c r="BB19">
+        <v>10</v>
+      </c>
+      <c r="BC19">
+        <v>11</v>
+      </c>
+      <c r="BD19">
+        <v>1.64</v>
+      </c>
+      <c r="BE19">
+        <v>8</v>
+      </c>
+      <c r="BF19">
+        <v>2.77</v>
+      </c>
+      <c r="BG19">
+        <v>1.22</v>
+      </c>
+      <c r="BH19">
+        <v>3.5</v>
+      </c>
+      <c r="BI19">
+        <v>1.52</v>
+      </c>
+      <c r="BJ19">
+        <v>2.37</v>
+      </c>
+      <c r="BK19">
+        <v>1.87</v>
+      </c>
+      <c r="BL19">
+        <v>1.87</v>
+      </c>
+      <c r="BM19">
+        <v>2.38</v>
+      </c>
+      <c r="BN19">
+        <v>1.54</v>
+      </c>
+      <c r="BO19">
+        <v>2.93</v>
+      </c>
+      <c r="BP19">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:68">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>7778508</v>
+      </c>
+      <c r="C20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="2">
+        <v>45711.08333333334</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20" t="s">
+        <v>79</v>
+      </c>
+      <c r="H20" t="s">
+        <v>70</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20" t="s">
+        <v>90</v>
+      </c>
+      <c r="P20" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q20">
+        <v>3.05</v>
+      </c>
+      <c r="R20">
+        <v>1.99</v>
+      </c>
+      <c r="S20">
+        <v>3.65</v>
+      </c>
+      <c r="T20">
+        <v>1.5</v>
+      </c>
+      <c r="U20">
+        <v>2.4</v>
+      </c>
+      <c r="V20">
+        <v>3.1</v>
+      </c>
+      <c r="W20">
+        <v>1.35</v>
+      </c>
+      <c r="X20">
+        <v>9.5</v>
+      </c>
+      <c r="Y20">
+        <v>1.06</v>
+      </c>
+      <c r="Z20">
+        <v>2.33</v>
+      </c>
+      <c r="AA20">
+        <v>3.27</v>
+      </c>
+      <c r="AB20">
+        <v>2.98</v>
+      </c>
+      <c r="AC20">
+        <v>1.03</v>
+      </c>
+      <c r="AD20">
+        <v>7.3</v>
+      </c>
+      <c r="AE20">
+        <v>1.4</v>
+      </c>
+      <c r="AF20">
+        <v>2.85</v>
+      </c>
+      <c r="AG20">
+        <v>2.1</v>
+      </c>
+      <c r="AH20">
+        <v>1.6</v>
+      </c>
+      <c r="AI20">
+        <v>1.9</v>
+      </c>
+      <c r="AJ20">
+        <v>1.81</v>
+      </c>
+      <c r="AK20">
+        <v>1.38</v>
+      </c>
+      <c r="AL20">
+        <v>1.31</v>
+      </c>
+      <c r="AM20">
+        <v>1.52</v>
+      </c>
+      <c r="AN20">
+        <v>3</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>2</v>
+      </c>
+      <c r="AQ20">
+        <v>1</v>
+      </c>
+      <c r="AR20">
+        <v>1.61</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>1.61</v>
+      </c>
+      <c r="AU20">
+        <v>4</v>
+      </c>
+      <c r="AV20">
+        <v>4</v>
+      </c>
+      <c r="AW20">
+        <v>6</v>
+      </c>
+      <c r="AX20">
+        <v>2</v>
+      </c>
+      <c r="AY20">
+        <v>10</v>
+      </c>
+      <c r="AZ20">
+        <v>6</v>
+      </c>
+      <c r="BA20">
+        <v>3</v>
+      </c>
+      <c r="BB20">
+        <v>2</v>
+      </c>
+      <c r="BC20">
+        <v>5</v>
+      </c>
+      <c r="BD20">
+        <v>1.82</v>
+      </c>
+      <c r="BE20">
+        <v>6.3</v>
+      </c>
+      <c r="BF20">
+        <v>2.44</v>
+      </c>
+      <c r="BG20">
+        <v>1.26</v>
+      </c>
+      <c r="BH20">
+        <v>3.22</v>
+      </c>
+      <c r="BI20">
+        <v>1.55</v>
+      </c>
+      <c r="BJ20">
+        <v>2.35</v>
+      </c>
+      <c r="BK20">
+        <v>1.91</v>
+      </c>
+      <c r="BL20">
+        <v>1.83</v>
+      </c>
+      <c r="BM20">
+        <v>2.41</v>
+      </c>
+      <c r="BN20">
+        <v>1.5</v>
+      </c>
+      <c r="BO20">
+        <v>3.28</v>
+      </c>
+      <c r="BP20">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:68">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>7778505</v>
+      </c>
+      <c r="C21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="2">
+        <v>45711.125</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21" t="s">
+        <v>77</v>
+      </c>
+      <c r="H21" t="s">
+        <v>88</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>2</v>
+      </c>
+      <c r="N21">
+        <v>3</v>
+      </c>
+      <c r="O21" t="s">
+        <v>103</v>
+      </c>
+      <c r="P21" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q21">
+        <v>4.4</v>
+      </c>
+      <c r="R21">
+        <v>2.07</v>
+      </c>
+      <c r="S21">
+        <v>2.55</v>
+      </c>
+      <c r="T21">
+        <v>1.46</v>
+      </c>
+      <c r="U21">
+        <v>2.55</v>
+      </c>
+      <c r="V21">
+        <v>3</v>
+      </c>
+      <c r="W21">
+        <v>1.36</v>
+      </c>
+      <c r="X21">
+        <v>8.5</v>
+      </c>
+      <c r="Y21">
+        <v>1.07</v>
+      </c>
+      <c r="Z21">
+        <v>4.1</v>
+      </c>
+      <c r="AA21">
+        <v>3.41</v>
+      </c>
+      <c r="AB21">
+        <v>1.88</v>
+      </c>
+      <c r="AC21">
+        <v>1.02</v>
+      </c>
+      <c r="AD21">
+        <v>7.8</v>
+      </c>
+      <c r="AE21">
+        <v>1.35</v>
+      </c>
+      <c r="AF21">
+        <v>3</v>
+      </c>
+      <c r="AG21">
+        <v>2</v>
+      </c>
+      <c r="AH21">
+        <v>1.65</v>
+      </c>
+      <c r="AI21">
+        <v>1.88</v>
+      </c>
+      <c r="AJ21">
+        <v>1.82</v>
+      </c>
+      <c r="AK21">
+        <v>1.75</v>
+      </c>
+      <c r="AL21">
+        <v>1.28</v>
+      </c>
+      <c r="AM21">
+        <v>1.25</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>3</v>
+      </c>
+      <c r="AP21">
+        <v>0</v>
+      </c>
+      <c r="AQ21">
+        <v>3</v>
+      </c>
+      <c r="AR21">
+        <v>1.32</v>
+      </c>
+      <c r="AS21">
+        <v>1.27</v>
+      </c>
+      <c r="AT21">
+        <v>2.59</v>
+      </c>
+      <c r="AU21">
+        <v>4</v>
+      </c>
+      <c r="AV21">
+        <v>3</v>
+      </c>
+      <c r="AW21">
+        <v>3</v>
+      </c>
+      <c r="AX21">
+        <v>7</v>
+      </c>
+      <c r="AY21">
+        <v>7</v>
+      </c>
+      <c r="AZ21">
+        <v>10</v>
+      </c>
+      <c r="BA21">
+        <v>1</v>
+      </c>
+      <c r="BB21">
+        <v>8</v>
+      </c>
+      <c r="BC21">
+        <v>9</v>
+      </c>
+      <c r="BD21">
+        <v>2.92</v>
+      </c>
+      <c r="BE21">
+        <v>6.8</v>
+      </c>
+      <c r="BF21">
+        <v>1.59</v>
+      </c>
+      <c r="BG21">
+        <v>1.2</v>
+      </c>
+      <c r="BH21">
+        <v>4</v>
+      </c>
+      <c r="BI21">
+        <v>1.4</v>
+      </c>
+      <c r="BJ21">
+        <v>2.72</v>
+      </c>
+      <c r="BK21">
+        <v>1.58</v>
+      </c>
+      <c r="BL21">
+        <v>2.29</v>
+      </c>
+      <c r="BM21">
+        <v>2</v>
+      </c>
+      <c r="BN21">
+        <v>1.8</v>
+      </c>
+      <c r="BO21">
+        <v>2.41</v>
+      </c>
+      <c r="BP21">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="122">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -271,12 +271,12 @@
     <t>Mito Hollyhock</t>
   </si>
   <si>
+    <t>Vegalta Sendai</t>
+  </si>
+  <si>
     <t>Montedio Yamagata</t>
   </si>
   <si>
-    <t>Vegalta Sendai</t>
-  </si>
-  <si>
     <t>Kataller Toyama</t>
   </si>
   <si>
@@ -328,6 +328,21 @@
     <t>['68']</t>
   </si>
   <si>
+    <t>['8', '23']</t>
+  </si>
+  <si>
+    <t>['77']</t>
+  </si>
+  <si>
+    <t>['63']</t>
+  </si>
+  <si>
+    <t>['23', '37', '64']</t>
+  </si>
+  <si>
+    <t>['45+2', '88']</t>
+  </si>
+  <si>
     <t>['31', '60']</t>
   </si>
   <si>
@@ -356,6 +371,15 @@
   </si>
   <si>
     <t>['17', '54']</t>
+  </si>
+  <si>
+    <t>['22', '35', '45+3', '83']</t>
+  </si>
+  <si>
+    <t>['13', '39']</t>
+  </si>
+  <si>
+    <t>['27']</t>
   </si>
 </sst>
 </file>
@@ -717,7 +741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP21"/>
+  <dimension ref="A1:BP26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -973,7 +997,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="Q2">
         <v>3.6</v>
@@ -1155,7 +1179,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1179,7 +1203,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="Q3">
         <v>3.75</v>
@@ -1591,7 +1615,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -1797,7 +1821,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="Q6">
         <v>4.1</v>
@@ -1875,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ6">
         <v>3</v>
@@ -1979,7 +2003,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2003,7 +2027,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="Q7">
         <v>2.88</v>
@@ -2209,7 +2233,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="Q8">
         <v>2.28</v>
@@ -2415,7 +2439,7 @@
         <v>90</v>
       </c>
       <c r="P9" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -2621,7 +2645,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -2702,7 +2726,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3651,7 +3675,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="Q15">
         <v>4.1</v>
@@ -4039,7 +4063,7 @@
         <v>83</v>
       </c>
       <c r="H17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -4245,7 +4269,7 @@
         <v>84</v>
       </c>
       <c r="H18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -4887,7 +4911,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="Q21">
         <v>4.4</v>
@@ -4968,7 +4992,7 @@
         <v>0</v>
       </c>
       <c r="AQ21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR21">
         <v>1.32</v>
@@ -5044,6 +5068,1036 @@
       </c>
       <c r="BP21">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:68">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>7778509</v>
+      </c>
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="2">
+        <v>45717.04166666666</v>
+      </c>
+      <c r="F22">
+        <v>3</v>
+      </c>
+      <c r="G22" t="s">
+        <v>85</v>
+      </c>
+      <c r="H22" t="s">
+        <v>79</v>
+      </c>
+      <c r="I22">
+        <v>2</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>2</v>
+      </c>
+      <c r="L22">
+        <v>2</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>2</v>
+      </c>
+      <c r="O22" t="s">
+        <v>104</v>
+      </c>
+      <c r="P22" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q22">
+        <v>2.75</v>
+      </c>
+      <c r="R22">
+        <v>1.95</v>
+      </c>
+      <c r="S22">
+        <v>4.4</v>
+      </c>
+      <c r="T22">
+        <v>1.54</v>
+      </c>
+      <c r="U22">
+        <v>2.34</v>
+      </c>
+      <c r="V22">
+        <v>3.48</v>
+      </c>
+      <c r="W22">
+        <v>1.27</v>
+      </c>
+      <c r="X22">
+        <v>9.1</v>
+      </c>
+      <c r="Y22">
+        <v>1.03</v>
+      </c>
+      <c r="Z22">
+        <v>2</v>
+      </c>
+      <c r="AA22">
+        <v>3.36</v>
+      </c>
+      <c r="AB22">
+        <v>3.68</v>
+      </c>
+      <c r="AC22">
+        <v>1.02</v>
+      </c>
+      <c r="AD22">
+        <v>7.9</v>
+      </c>
+      <c r="AE22">
+        <v>1.46</v>
+      </c>
+      <c r="AF22">
+        <v>2.6</v>
+      </c>
+      <c r="AG22">
+        <v>2.2</v>
+      </c>
+      <c r="AH22">
+        <v>1.55</v>
+      </c>
+      <c r="AI22">
+        <v>2.07</v>
+      </c>
+      <c r="AJ22">
+        <v>1.68</v>
+      </c>
+      <c r="AK22">
+        <v>1.26</v>
+      </c>
+      <c r="AL22">
+        <v>1.3</v>
+      </c>
+      <c r="AM22">
+        <v>1.7</v>
+      </c>
+      <c r="AN22">
+        <v>0</v>
+      </c>
+      <c r="AO22">
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <v>3</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22">
+        <v>5</v>
+      </c>
+      <c r="AV22">
+        <v>4</v>
+      </c>
+      <c r="AW22">
+        <v>5</v>
+      </c>
+      <c r="AX22">
+        <v>7</v>
+      </c>
+      <c r="AY22">
+        <v>10</v>
+      </c>
+      <c r="AZ22">
+        <v>11</v>
+      </c>
+      <c r="BA22">
+        <v>0</v>
+      </c>
+      <c r="BB22">
+        <v>4</v>
+      </c>
+      <c r="BC22">
+        <v>4</v>
+      </c>
+      <c r="BD22">
+        <v>1.78</v>
+      </c>
+      <c r="BE22">
+        <v>7.9</v>
+      </c>
+      <c r="BF22">
+        <v>2.33</v>
+      </c>
+      <c r="BG22">
+        <v>1.28</v>
+      </c>
+      <c r="BH22">
+        <v>3.05</v>
+      </c>
+      <c r="BI22">
+        <v>1.54</v>
+      </c>
+      <c r="BJ22">
+        <v>2.19</v>
+      </c>
+      <c r="BK22">
+        <v>1.95</v>
+      </c>
+      <c r="BL22">
+        <v>1.72</v>
+      </c>
+      <c r="BM22">
+        <v>2.56</v>
+      </c>
+      <c r="BN22">
+        <v>1.4</v>
+      </c>
+      <c r="BO22">
+        <v>3.5</v>
+      </c>
+      <c r="BP22">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:68">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>7778516</v>
+      </c>
+      <c r="C23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="2">
+        <v>45717.08333333334</v>
+      </c>
+      <c r="F23">
+        <v>3</v>
+      </c>
+      <c r="G23" t="s">
+        <v>75</v>
+      </c>
+      <c r="H23" t="s">
+        <v>78</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>3</v>
+      </c>
+      <c r="K23">
+        <v>3</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>4</v>
+      </c>
+      <c r="N23">
+        <v>5</v>
+      </c>
+      <c r="O23" t="s">
+        <v>105</v>
+      </c>
+      <c r="P23" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q23">
+        <v>3.1</v>
+      </c>
+      <c r="R23">
+        <v>1.95</v>
+      </c>
+      <c r="S23">
+        <v>4.33</v>
+      </c>
+      <c r="T23">
+        <v>1.57</v>
+      </c>
+      <c r="U23">
+        <v>2.25</v>
+      </c>
+      <c r="V23">
+        <v>3.75</v>
+      </c>
+      <c r="W23">
+        <v>1.25</v>
+      </c>
+      <c r="X23">
+        <v>11</v>
+      </c>
+      <c r="Y23">
+        <v>1.05</v>
+      </c>
+      <c r="Z23">
+        <v>2.23</v>
+      </c>
+      <c r="AA23">
+        <v>3.07</v>
+      </c>
+      <c r="AB23">
+        <v>3.37</v>
+      </c>
+      <c r="AC23">
+        <v>1.08</v>
+      </c>
+      <c r="AD23">
+        <v>7</v>
+      </c>
+      <c r="AE23">
+        <v>1.45</v>
+      </c>
+      <c r="AF23">
+        <v>2.6</v>
+      </c>
+      <c r="AG23">
+        <v>2.05</v>
+      </c>
+      <c r="AH23">
+        <v>1.61</v>
+      </c>
+      <c r="AI23">
+        <v>2.2</v>
+      </c>
+      <c r="AJ23">
+        <v>1.62</v>
+      </c>
+      <c r="AK23">
+        <v>1.31</v>
+      </c>
+      <c r="AL23">
+        <v>1.34</v>
+      </c>
+      <c r="AM23">
+        <v>1.62</v>
+      </c>
+      <c r="AN23">
+        <v>0</v>
+      </c>
+      <c r="AO23">
+        <v>0</v>
+      </c>
+      <c r="AP23">
+        <v>0</v>
+      </c>
+      <c r="AQ23">
+        <v>3</v>
+      </c>
+      <c r="AR23">
+        <v>1.4</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>1.4</v>
+      </c>
+      <c r="AU23">
+        <v>4</v>
+      </c>
+      <c r="AV23">
+        <v>7</v>
+      </c>
+      <c r="AW23">
+        <v>6</v>
+      </c>
+      <c r="AX23">
+        <v>7</v>
+      </c>
+      <c r="AY23">
+        <v>10</v>
+      </c>
+      <c r="AZ23">
+        <v>14</v>
+      </c>
+      <c r="BA23">
+        <v>4</v>
+      </c>
+      <c r="BB23">
+        <v>5</v>
+      </c>
+      <c r="BC23">
+        <v>9</v>
+      </c>
+      <c r="BD23">
+        <v>1.66</v>
+      </c>
+      <c r="BE23">
+        <v>6.45</v>
+      </c>
+      <c r="BF23">
+        <v>2.77</v>
+      </c>
+      <c r="BG23">
+        <v>1.24</v>
+      </c>
+      <c r="BH23">
+        <v>3.34</v>
+      </c>
+      <c r="BI23">
+        <v>1.47</v>
+      </c>
+      <c r="BJ23">
+        <v>2.35</v>
+      </c>
+      <c r="BK23">
+        <v>1.83</v>
+      </c>
+      <c r="BL23">
+        <v>1.83</v>
+      </c>
+      <c r="BM23">
+        <v>2.33</v>
+      </c>
+      <c r="BN23">
+        <v>1.48</v>
+      </c>
+      <c r="BO23">
+        <v>3.14</v>
+      </c>
+      <c r="BP23">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:68">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>7778517</v>
+      </c>
+      <c r="C24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="2">
+        <v>45717.08333333334</v>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24" t="s">
+        <v>76</v>
+      </c>
+      <c r="H24" t="s">
+        <v>73</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+      <c r="O24" t="s">
+        <v>106</v>
+      </c>
+      <c r="P24" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q24">
+        <v>3.25</v>
+      </c>
+      <c r="R24">
+        <v>2.1</v>
+      </c>
+      <c r="S24">
+        <v>3.25</v>
+      </c>
+      <c r="T24">
+        <v>1.4</v>
+      </c>
+      <c r="U24">
+        <v>2.75</v>
+      </c>
+      <c r="V24">
+        <v>3</v>
+      </c>
+      <c r="W24">
+        <v>1.36</v>
+      </c>
+      <c r="X24">
+        <v>8</v>
+      </c>
+      <c r="Y24">
+        <v>1.08</v>
+      </c>
+      <c r="Z24">
+        <v>2.37</v>
+      </c>
+      <c r="AA24">
+        <v>3.33</v>
+      </c>
+      <c r="AB24">
+        <v>2.88</v>
+      </c>
+      <c r="AC24">
+        <v>1.06</v>
+      </c>
+      <c r="AD24">
+        <v>8</v>
+      </c>
+      <c r="AE24">
+        <v>1.3</v>
+      </c>
+      <c r="AF24">
+        <v>3.25</v>
+      </c>
+      <c r="AG24">
+        <v>1.77</v>
+      </c>
+      <c r="AH24">
+        <v>1.98</v>
+      </c>
+      <c r="AI24">
+        <v>1.73</v>
+      </c>
+      <c r="AJ24">
+        <v>2</v>
+      </c>
+      <c r="AK24">
+        <v>1.46</v>
+      </c>
+      <c r="AL24">
+        <v>1.32</v>
+      </c>
+      <c r="AM24">
+        <v>1.47</v>
+      </c>
+      <c r="AN24">
+        <v>3</v>
+      </c>
+      <c r="AO24">
+        <v>0</v>
+      </c>
+      <c r="AP24">
+        <v>3</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>3.04</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>3.04</v>
+      </c>
+      <c r="AU24">
+        <v>10</v>
+      </c>
+      <c r="AV24">
+        <v>4</v>
+      </c>
+      <c r="AW24">
+        <v>5</v>
+      </c>
+      <c r="AX24">
+        <v>7</v>
+      </c>
+      <c r="AY24">
+        <v>15</v>
+      </c>
+      <c r="AZ24">
+        <v>11</v>
+      </c>
+      <c r="BA24">
+        <v>5</v>
+      </c>
+      <c r="BB24">
+        <v>7</v>
+      </c>
+      <c r="BC24">
+        <v>12</v>
+      </c>
+      <c r="BD24">
+        <v>2.03</v>
+      </c>
+      <c r="BE24">
+        <v>6.35</v>
+      </c>
+      <c r="BF24">
+        <v>2.14</v>
+      </c>
+      <c r="BG24">
+        <v>1.2</v>
+      </c>
+      <c r="BH24">
+        <v>3.72</v>
+      </c>
+      <c r="BI24">
+        <v>1.39</v>
+      </c>
+      <c r="BJ24">
+        <v>2.59</v>
+      </c>
+      <c r="BK24">
+        <v>1.71</v>
+      </c>
+      <c r="BL24">
+        <v>1.97</v>
+      </c>
+      <c r="BM24">
+        <v>2.15</v>
+      </c>
+      <c r="BN24">
+        <v>1.56</v>
+      </c>
+      <c r="BO24">
+        <v>2.88</v>
+      </c>
+      <c r="BP24">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:68">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>7778512</v>
+      </c>
+      <c r="C25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" s="2">
+        <v>45717.08333333334</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25" t="s">
+        <v>80</v>
+      </c>
+      <c r="H25" t="s">
+        <v>86</v>
+      </c>
+      <c r="I25">
+        <v>2</v>
+      </c>
+      <c r="J25">
+        <v>2</v>
+      </c>
+      <c r="K25">
+        <v>4</v>
+      </c>
+      <c r="L25">
+        <v>3</v>
+      </c>
+      <c r="M25">
+        <v>2</v>
+      </c>
+      <c r="N25">
+        <v>5</v>
+      </c>
+      <c r="O25" t="s">
+        <v>107</v>
+      </c>
+      <c r="P25" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q25">
+        <v>2.5</v>
+      </c>
+      <c r="R25">
+        <v>2.26</v>
+      </c>
+      <c r="S25">
+        <v>3.8</v>
+      </c>
+      <c r="T25">
+        <v>1.33</v>
+      </c>
+      <c r="U25">
+        <v>3.08</v>
+      </c>
+      <c r="V25">
+        <v>2.45</v>
+      </c>
+      <c r="W25">
+        <v>1.49</v>
+      </c>
+      <c r="X25">
+        <v>5.6</v>
+      </c>
+      <c r="Y25">
+        <v>1.11</v>
+      </c>
+      <c r="Z25">
+        <v>2.02</v>
+      </c>
+      <c r="AA25">
+        <v>3.47</v>
+      </c>
+      <c r="AB25">
+        <v>3.5</v>
+      </c>
+      <c r="AC25">
+        <v>1</v>
+      </c>
+      <c r="AD25">
+        <v>9</v>
+      </c>
+      <c r="AE25">
+        <v>1.22</v>
+      </c>
+      <c r="AF25">
+        <v>3.95</v>
+      </c>
+      <c r="AG25">
+        <v>1.8</v>
+      </c>
+      <c r="AH25">
+        <v>1.94</v>
+      </c>
+      <c r="AI25">
+        <v>1.6</v>
+      </c>
+      <c r="AJ25">
+        <v>2.19</v>
+      </c>
+      <c r="AK25">
+        <v>1.3</v>
+      </c>
+      <c r="AL25">
+        <v>1.26</v>
+      </c>
+      <c r="AM25">
+        <v>1.71</v>
+      </c>
+      <c r="AN25">
+        <v>3</v>
+      </c>
+      <c r="AO25">
+        <v>0</v>
+      </c>
+      <c r="AP25">
+        <v>3</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>1.45</v>
+      </c>
+      <c r="AS25">
+        <v>1.01</v>
+      </c>
+      <c r="AT25">
+        <v>2.46</v>
+      </c>
+      <c r="AU25">
+        <v>9</v>
+      </c>
+      <c r="AV25">
+        <v>5</v>
+      </c>
+      <c r="AW25">
+        <v>5</v>
+      </c>
+      <c r="AX25">
+        <v>5</v>
+      </c>
+      <c r="AY25">
+        <v>14</v>
+      </c>
+      <c r="AZ25">
+        <v>10</v>
+      </c>
+      <c r="BA25">
+        <v>7</v>
+      </c>
+      <c r="BB25">
+        <v>1</v>
+      </c>
+      <c r="BC25">
+        <v>8</v>
+      </c>
+      <c r="BD25">
+        <v>1.56</v>
+      </c>
+      <c r="BE25">
+        <v>8.4</v>
+      </c>
+      <c r="BF25">
+        <v>2.79</v>
+      </c>
+      <c r="BG25">
+        <v>1.19</v>
+      </c>
+      <c r="BH25">
+        <v>3.75</v>
+      </c>
+      <c r="BI25">
+        <v>1.39</v>
+      </c>
+      <c r="BJ25">
+        <v>2.59</v>
+      </c>
+      <c r="BK25">
+        <v>1.7</v>
+      </c>
+      <c r="BL25">
+        <v>1.98</v>
+      </c>
+      <c r="BM25">
+        <v>2.14</v>
+      </c>
+      <c r="BN25">
+        <v>1.57</v>
+      </c>
+      <c r="BO25">
+        <v>2.83</v>
+      </c>
+      <c r="BP25">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:68">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>7778514</v>
+      </c>
+      <c r="C26" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="2">
+        <v>45717.08333333334</v>
+      </c>
+      <c r="F26">
+        <v>3</v>
+      </c>
+      <c r="G26" t="s">
+        <v>74</v>
+      </c>
+      <c r="H26" t="s">
+        <v>88</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26">
+        <v>2</v>
+      </c>
+      <c r="L26">
+        <v>2</v>
+      </c>
+      <c r="M26">
+        <v>1</v>
+      </c>
+      <c r="N26">
+        <v>3</v>
+      </c>
+      <c r="O26" t="s">
+        <v>108</v>
+      </c>
+      <c r="P26" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q26">
+        <v>3.95</v>
+      </c>
+      <c r="R26">
+        <v>2.07</v>
+      </c>
+      <c r="S26">
+        <v>2.75</v>
+      </c>
+      <c r="T26">
+        <v>1.46</v>
+      </c>
+      <c r="U26">
+        <v>2.55</v>
+      </c>
+      <c r="V26">
+        <v>2.7</v>
+      </c>
+      <c r="W26">
+        <v>1.41</v>
+      </c>
+      <c r="X26">
+        <v>7.6</v>
+      </c>
+      <c r="Y26">
+        <v>1.05</v>
+      </c>
+      <c r="Z26">
+        <v>3.25</v>
+      </c>
+      <c r="AA26">
+        <v>3.12</v>
+      </c>
+      <c r="AB26">
+        <v>2.26</v>
+      </c>
+      <c r="AC26">
+        <v>1.03</v>
+      </c>
+      <c r="AD26">
+        <v>7.3</v>
+      </c>
+      <c r="AE26">
+        <v>1.34</v>
+      </c>
+      <c r="AF26">
+        <v>3.05</v>
+      </c>
+      <c r="AG26">
+        <v>1.95</v>
+      </c>
+      <c r="AH26">
+        <v>1.79</v>
+      </c>
+      <c r="AI26">
+        <v>1.82</v>
+      </c>
+      <c r="AJ26">
+        <v>1.88</v>
+      </c>
+      <c r="AK26">
+        <v>1.63</v>
+      </c>
+      <c r="AL26">
+        <v>1.3</v>
+      </c>
+      <c r="AM26">
+        <v>1.3</v>
+      </c>
+      <c r="AN26">
+        <v>0</v>
+      </c>
+      <c r="AO26">
+        <v>3</v>
+      </c>
+      <c r="AP26">
+        <v>1.5</v>
+      </c>
+      <c r="AQ26">
+        <v>2</v>
+      </c>
+      <c r="AR26">
+        <v>0.85</v>
+      </c>
+      <c r="AS26">
+        <v>1.3</v>
+      </c>
+      <c r="AT26">
+        <v>2.15</v>
+      </c>
+      <c r="AU26">
+        <v>4</v>
+      </c>
+      <c r="AV26">
+        <v>5</v>
+      </c>
+      <c r="AW26">
+        <v>3</v>
+      </c>
+      <c r="AX26">
+        <v>5</v>
+      </c>
+      <c r="AY26">
+        <v>7</v>
+      </c>
+      <c r="AZ26">
+        <v>10</v>
+      </c>
+      <c r="BA26">
+        <v>4</v>
+      </c>
+      <c r="BB26">
+        <v>6</v>
+      </c>
+      <c r="BC26">
+        <v>10</v>
+      </c>
+      <c r="BD26">
+        <v>2.04</v>
+      </c>
+      <c r="BE26">
+        <v>8</v>
+      </c>
+      <c r="BF26">
+        <v>1.99</v>
+      </c>
+      <c r="BG26">
+        <v>1.26</v>
+      </c>
+      <c r="BH26">
+        <v>3.22</v>
+      </c>
+      <c r="BI26">
+        <v>1.49</v>
+      </c>
+      <c r="BJ26">
+        <v>2.3</v>
+      </c>
+      <c r="BK26">
+        <v>1.86</v>
+      </c>
+      <c r="BL26">
+        <v>1.8</v>
+      </c>
+      <c r="BM26">
+        <v>2.41</v>
+      </c>
+      <c r="BN26">
+        <v>1.45</v>
+      </c>
+      <c r="BO26">
+        <v>3.28</v>
+      </c>
+      <c r="BP26">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="128">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -274,12 +274,12 @@
     <t>Vegalta Sendai</t>
   </si>
   <si>
+    <t>Kataller Toyama</t>
+  </si>
+  <si>
     <t>Montedio Yamagata</t>
   </si>
   <si>
-    <t>Kataller Toyama</t>
-  </si>
-  <si>
     <t>Blaublitz Akita</t>
   </si>
   <si>
@@ -343,6 +343,18 @@
     <t>['45+2', '88']</t>
   </si>
   <si>
+    <t>['12']</t>
+  </si>
+  <si>
+    <t>['21', '74']</t>
+  </si>
+  <si>
+    <t>['64']</t>
+  </si>
+  <si>
+    <t>['39', '79']</t>
+  </si>
+  <si>
     <t>['31', '60']</t>
   </si>
   <si>
@@ -380,6 +392,12 @@
   </si>
   <si>
     <t>['27']</t>
+  </si>
+  <si>
+    <t>['55', '57', '62', '90+4']</t>
+  </si>
+  <si>
+    <t>['3']</t>
   </si>
 </sst>
 </file>
@@ -741,7 +759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP26"/>
+  <dimension ref="A1:BP31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -997,7 +1015,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="Q2">
         <v>3.6</v>
@@ -1075,7 +1093,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ2">
         <v>3</v>
@@ -1179,7 +1197,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1203,7 +1221,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="Q3">
         <v>3.75</v>
@@ -1615,7 +1633,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -1821,7 +1839,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="Q6">
         <v>4.1</v>
@@ -1902,7 +1920,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2027,7 +2045,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="Q7">
         <v>2.88</v>
@@ -2233,7 +2251,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="Q8">
         <v>2.28</v>
@@ -2415,7 +2433,7 @@
         <v>77</v>
       </c>
       <c r="H9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -2439,7 +2457,7 @@
         <v>90</v>
       </c>
       <c r="P9" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -2645,7 +2663,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -3239,7 +3257,7 @@
         <v>80</v>
       </c>
       <c r="H13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I13">
         <v>1</v>
@@ -3675,7 +3693,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="Q15">
         <v>4.1</v>
@@ -3753,7 +3771,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ15">
         <v>1</v>
@@ -3959,7 +3977,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AQ16">
         <v>0</v>
@@ -4269,7 +4287,7 @@
         <v>84</v>
       </c>
       <c r="H18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -4371,7 +4389,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ18">
         <v>0</v>
@@ -4911,7 +4929,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="Q21">
         <v>4.4</v>
@@ -5323,7 +5341,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5711,7 +5729,7 @@
         <v>80</v>
       </c>
       <c r="H25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I25">
         <v>2</v>
@@ -5735,7 +5753,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -5941,7 +5959,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="Q26">
         <v>3.95</v>
@@ -6098,6 +6116,1036 @@
       </c>
       <c r="BP26">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:68">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>7778518</v>
+      </c>
+      <c r="C27" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="2">
+        <v>45718.04166666666</v>
+      </c>
+      <c r="F27">
+        <v>3</v>
+      </c>
+      <c r="G27" t="s">
+        <v>82</v>
+      </c>
+      <c r="H27" t="s">
+        <v>71</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>4</v>
+      </c>
+      <c r="N27">
+        <v>4</v>
+      </c>
+      <c r="O27" t="s">
+        <v>90</v>
+      </c>
+      <c r="P27" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q27">
+        <v>3.2</v>
+      </c>
+      <c r="R27">
+        <v>2.1</v>
+      </c>
+      <c r="S27">
+        <v>3.4</v>
+      </c>
+      <c r="T27">
+        <v>1.44</v>
+      </c>
+      <c r="U27">
+        <v>2.63</v>
+      </c>
+      <c r="V27">
+        <v>3</v>
+      </c>
+      <c r="W27">
+        <v>1.36</v>
+      </c>
+      <c r="X27">
+        <v>9</v>
+      </c>
+      <c r="Y27">
+        <v>1.07</v>
+      </c>
+      <c r="Z27">
+        <v>2.47</v>
+      </c>
+      <c r="AA27">
+        <v>3.18</v>
+      </c>
+      <c r="AB27">
+        <v>2.85</v>
+      </c>
+      <c r="AC27">
+        <v>1.06</v>
+      </c>
+      <c r="AD27">
+        <v>8</v>
+      </c>
+      <c r="AE27">
+        <v>1.33</v>
+      </c>
+      <c r="AF27">
+        <v>3.1</v>
+      </c>
+      <c r="AG27">
+        <v>1.98</v>
+      </c>
+      <c r="AH27">
+        <v>1.77</v>
+      </c>
+      <c r="AI27">
+        <v>1.8</v>
+      </c>
+      <c r="AJ27">
+        <v>1.91</v>
+      </c>
+      <c r="AK27">
+        <v>1.41</v>
+      </c>
+      <c r="AL27">
+        <v>1.33</v>
+      </c>
+      <c r="AM27">
+        <v>1.51</v>
+      </c>
+      <c r="AN27">
+        <v>3</v>
+      </c>
+      <c r="AO27">
+        <v>0</v>
+      </c>
+      <c r="AP27">
+        <v>1.5</v>
+      </c>
+      <c r="AQ27">
+        <v>3</v>
+      </c>
+      <c r="AR27">
+        <v>1.59</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>1.59</v>
+      </c>
+      <c r="AU27">
+        <v>4</v>
+      </c>
+      <c r="AV27">
+        <v>6</v>
+      </c>
+      <c r="AW27">
+        <v>2</v>
+      </c>
+      <c r="AX27">
+        <v>8</v>
+      </c>
+      <c r="AY27">
+        <v>6</v>
+      </c>
+      <c r="AZ27">
+        <v>14</v>
+      </c>
+      <c r="BA27">
+        <v>3</v>
+      </c>
+      <c r="BB27">
+        <v>1</v>
+      </c>
+      <c r="BC27">
+        <v>4</v>
+      </c>
+      <c r="BD27">
+        <v>1.41</v>
+      </c>
+      <c r="BE27">
+        <v>7.1</v>
+      </c>
+      <c r="BF27">
+        <v>3.74</v>
+      </c>
+      <c r="BG27">
+        <v>1.25</v>
+      </c>
+      <c r="BH27">
+        <v>3.28</v>
+      </c>
+      <c r="BI27">
+        <v>1.48</v>
+      </c>
+      <c r="BJ27">
+        <v>2.33</v>
+      </c>
+      <c r="BK27">
+        <v>1.85</v>
+      </c>
+      <c r="BL27">
+        <v>1.81</v>
+      </c>
+      <c r="BM27">
+        <v>2.38</v>
+      </c>
+      <c r="BN27">
+        <v>1.46</v>
+      </c>
+      <c r="BO27">
+        <v>3.2</v>
+      </c>
+      <c r="BP27">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:68">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>7778510</v>
+      </c>
+      <c r="C28" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="2">
+        <v>45718.08333333334</v>
+      </c>
+      <c r="F28">
+        <v>3</v>
+      </c>
+      <c r="G28" t="s">
+        <v>70</v>
+      </c>
+      <c r="H28" t="s">
+        <v>83</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <v>1</v>
+      </c>
+      <c r="N28">
+        <v>2</v>
+      </c>
+      <c r="O28" t="s">
+        <v>109</v>
+      </c>
+      <c r="P28" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q28">
+        <v>3.35</v>
+      </c>
+      <c r="R28">
+        <v>1.95</v>
+      </c>
+      <c r="S28">
+        <v>3.4</v>
+      </c>
+      <c r="T28">
+        <v>1.53</v>
+      </c>
+      <c r="U28">
+        <v>2.36</v>
+      </c>
+      <c r="V28">
+        <v>3.3</v>
+      </c>
+      <c r="W28">
+        <v>1.3</v>
+      </c>
+      <c r="X28">
+        <v>10</v>
+      </c>
+      <c r="Y28">
+        <v>1.05</v>
+      </c>
+      <c r="Z28">
+        <v>2.64</v>
+      </c>
+      <c r="AA28">
+        <v>3.23</v>
+      </c>
+      <c r="AB28">
+        <v>2.61</v>
+      </c>
+      <c r="AC28">
+        <v>1.04</v>
+      </c>
+      <c r="AD28">
+        <v>6.75</v>
+      </c>
+      <c r="AE28">
+        <v>1.43</v>
+      </c>
+      <c r="AF28">
+        <v>2.7</v>
+      </c>
+      <c r="AG28">
+        <v>2.2</v>
+      </c>
+      <c r="AH28">
+        <v>1.53</v>
+      </c>
+      <c r="AI28">
+        <v>1.97</v>
+      </c>
+      <c r="AJ28">
+        <v>1.75</v>
+      </c>
+      <c r="AK28">
+        <v>1.43</v>
+      </c>
+      <c r="AL28">
+        <v>1.32</v>
+      </c>
+      <c r="AM28">
+        <v>1.44</v>
+      </c>
+      <c r="AN28">
+        <v>0</v>
+      </c>
+      <c r="AO28">
+        <v>3</v>
+      </c>
+      <c r="AP28">
+        <v>0.5</v>
+      </c>
+      <c r="AQ28">
+        <v>2</v>
+      </c>
+      <c r="AR28">
+        <v>2.36</v>
+      </c>
+      <c r="AS28">
+        <v>1.41</v>
+      </c>
+      <c r="AT28">
+        <v>3.77</v>
+      </c>
+      <c r="AU28">
+        <v>3</v>
+      </c>
+      <c r="AV28">
+        <v>5</v>
+      </c>
+      <c r="AW28">
+        <v>5</v>
+      </c>
+      <c r="AX28">
+        <v>6</v>
+      </c>
+      <c r="AY28">
+        <v>8</v>
+      </c>
+      <c r="AZ28">
+        <v>11</v>
+      </c>
+      <c r="BA28">
+        <v>2</v>
+      </c>
+      <c r="BB28">
+        <v>3</v>
+      </c>
+      <c r="BC28">
+        <v>5</v>
+      </c>
+      <c r="BD28">
+        <v>2.01</v>
+      </c>
+      <c r="BE28">
+        <v>6.2</v>
+      </c>
+      <c r="BF28">
+        <v>2.18</v>
+      </c>
+      <c r="BG28">
+        <v>1.27</v>
+      </c>
+      <c r="BH28">
+        <v>3.14</v>
+      </c>
+      <c r="BI28">
+        <v>1.52</v>
+      </c>
+      <c r="BJ28">
+        <v>2.24</v>
+      </c>
+      <c r="BK28">
+        <v>1.91</v>
+      </c>
+      <c r="BL28">
+        <v>1.76</v>
+      </c>
+      <c r="BM28">
+        <v>2.46</v>
+      </c>
+      <c r="BN28">
+        <v>1.43</v>
+      </c>
+      <c r="BO28">
+        <v>3.42</v>
+      </c>
+      <c r="BP28">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:68">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>7778513</v>
+      </c>
+      <c r="C29" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="2">
+        <v>45718.08333333334</v>
+      </c>
+      <c r="F29">
+        <v>3</v>
+      </c>
+      <c r="G29" t="s">
+        <v>86</v>
+      </c>
+      <c r="H29" t="s">
+        <v>72</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <v>2</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>2</v>
+      </c>
+      <c r="O29" t="s">
+        <v>110</v>
+      </c>
+      <c r="P29" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q29">
+        <v>3.4</v>
+      </c>
+      <c r="R29">
+        <v>1.95</v>
+      </c>
+      <c r="S29">
+        <v>3.6</v>
+      </c>
+      <c r="T29">
+        <v>1.53</v>
+      </c>
+      <c r="U29">
+        <v>2.38</v>
+      </c>
+      <c r="V29">
+        <v>3.5</v>
+      </c>
+      <c r="W29">
+        <v>1.29</v>
+      </c>
+      <c r="X29">
+        <v>11</v>
+      </c>
+      <c r="Y29">
+        <v>1.05</v>
+      </c>
+      <c r="Z29">
+        <v>2.58</v>
+      </c>
+      <c r="AA29">
+        <v>3.04</v>
+      </c>
+      <c r="AB29">
+        <v>2.83</v>
+      </c>
+      <c r="AC29">
+        <v>1.09</v>
+      </c>
+      <c r="AD29">
+        <v>6.75</v>
+      </c>
+      <c r="AE29">
+        <v>1.44</v>
+      </c>
+      <c r="AF29">
+        <v>2.55</v>
+      </c>
+      <c r="AG29">
+        <v>2.1</v>
+      </c>
+      <c r="AH29">
+        <v>1.61</v>
+      </c>
+      <c r="AI29">
+        <v>2.1</v>
+      </c>
+      <c r="AJ29">
+        <v>1.67</v>
+      </c>
+      <c r="AK29">
+        <v>1.43</v>
+      </c>
+      <c r="AL29">
+        <v>1.34</v>
+      </c>
+      <c r="AM29">
+        <v>1.47</v>
+      </c>
+      <c r="AN29">
+        <v>0</v>
+      </c>
+      <c r="AO29">
+        <v>0</v>
+      </c>
+      <c r="AP29">
+        <v>3</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>1.08</v>
+      </c>
+      <c r="AT29">
+        <v>1.08</v>
+      </c>
+      <c r="AU29">
+        <v>5</v>
+      </c>
+      <c r="AV29">
+        <v>3</v>
+      </c>
+      <c r="AW29">
+        <v>5</v>
+      </c>
+      <c r="AX29">
+        <v>4</v>
+      </c>
+      <c r="AY29">
+        <v>12</v>
+      </c>
+      <c r="AZ29">
+        <v>8</v>
+      </c>
+      <c r="BA29">
+        <v>2</v>
+      </c>
+      <c r="BB29">
+        <v>4</v>
+      </c>
+      <c r="BC29">
+        <v>6</v>
+      </c>
+      <c r="BD29">
+        <v>2.07</v>
+      </c>
+      <c r="BE29">
+        <v>6.15</v>
+      </c>
+      <c r="BF29">
+        <v>2.12</v>
+      </c>
+      <c r="BG29">
+        <v>1.27</v>
+      </c>
+      <c r="BH29">
+        <v>3.14</v>
+      </c>
+      <c r="BI29">
+        <v>1.51</v>
+      </c>
+      <c r="BJ29">
+        <v>2.26</v>
+      </c>
+      <c r="BK29">
+        <v>1.89</v>
+      </c>
+      <c r="BL29">
+        <v>1.77</v>
+      </c>
+      <c r="BM29">
+        <v>2.46</v>
+      </c>
+      <c r="BN29">
+        <v>1.43</v>
+      </c>
+      <c r="BO29">
+        <v>3.34</v>
+      </c>
+      <c r="BP29">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:68">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>7778511</v>
+      </c>
+      <c r="C30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="2">
+        <v>45718.08333333334</v>
+      </c>
+      <c r="F30">
+        <v>3</v>
+      </c>
+      <c r="G30" t="s">
+        <v>84</v>
+      </c>
+      <c r="H30" t="s">
+        <v>77</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30">
+        <v>1</v>
+      </c>
+      <c r="M30">
+        <v>1</v>
+      </c>
+      <c r="N30">
+        <v>2</v>
+      </c>
+      <c r="O30" t="s">
+        <v>111</v>
+      </c>
+      <c r="P30" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q30">
+        <v>2.38</v>
+      </c>
+      <c r="R30">
+        <v>2.2</v>
+      </c>
+      <c r="S30">
+        <v>4.4</v>
+      </c>
+      <c r="T30">
+        <v>1.35</v>
+      </c>
+      <c r="U30">
+        <v>3.1</v>
+      </c>
+      <c r="V30">
+        <v>2.65</v>
+      </c>
+      <c r="W30">
+        <v>1.42</v>
+      </c>
+      <c r="X30">
+        <v>7</v>
+      </c>
+      <c r="Y30">
+        <v>1.08</v>
+      </c>
+      <c r="Z30">
+        <v>1.81</v>
+      </c>
+      <c r="AA30">
+        <v>3.64</v>
+      </c>
+      <c r="AB30">
+        <v>4.1</v>
+      </c>
+      <c r="AC30">
+        <v>1</v>
+      </c>
+      <c r="AD30">
+        <v>9</v>
+      </c>
+      <c r="AE30">
+        <v>1.28</v>
+      </c>
+      <c r="AF30">
+        <v>3.5</v>
+      </c>
+      <c r="AG30">
+        <v>1.87</v>
+      </c>
+      <c r="AH30">
+        <v>1.87</v>
+      </c>
+      <c r="AI30">
+        <v>1.75</v>
+      </c>
+      <c r="AJ30">
+        <v>1.97</v>
+      </c>
+      <c r="AK30">
+        <v>1.23</v>
+      </c>
+      <c r="AL30">
+        <v>1.26</v>
+      </c>
+      <c r="AM30">
+        <v>1.85</v>
+      </c>
+      <c r="AN30">
+        <v>3</v>
+      </c>
+      <c r="AO30">
+        <v>0</v>
+      </c>
+      <c r="AP30">
+        <v>2</v>
+      </c>
+      <c r="AQ30">
+        <v>1</v>
+      </c>
+      <c r="AR30">
+        <v>1.54</v>
+      </c>
+      <c r="AS30">
+        <v>0</v>
+      </c>
+      <c r="AT30">
+        <v>1.54</v>
+      </c>
+      <c r="AU30">
+        <v>3</v>
+      </c>
+      <c r="AV30">
+        <v>2</v>
+      </c>
+      <c r="AW30">
+        <v>9</v>
+      </c>
+      <c r="AX30">
+        <v>3</v>
+      </c>
+      <c r="AY30">
+        <v>12</v>
+      </c>
+      <c r="AZ30">
+        <v>5</v>
+      </c>
+      <c r="BA30">
+        <v>10</v>
+      </c>
+      <c r="BB30">
+        <v>1</v>
+      </c>
+      <c r="BC30">
+        <v>11</v>
+      </c>
+      <c r="BD30">
+        <v>1.45</v>
+      </c>
+      <c r="BE30">
+        <v>6.95</v>
+      </c>
+      <c r="BF30">
+        <v>3.52</v>
+      </c>
+      <c r="BG30">
+        <v>1.24</v>
+      </c>
+      <c r="BH30">
+        <v>3.34</v>
+      </c>
+      <c r="BI30">
+        <v>1.46</v>
+      </c>
+      <c r="BJ30">
+        <v>2.38</v>
+      </c>
+      <c r="BK30">
+        <v>1.82</v>
+      </c>
+      <c r="BL30">
+        <v>1.84</v>
+      </c>
+      <c r="BM30">
+        <v>2.3</v>
+      </c>
+      <c r="BN30">
+        <v>1.49</v>
+      </c>
+      <c r="BO30">
+        <v>3.14</v>
+      </c>
+      <c r="BP30">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:68">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>7778515</v>
+      </c>
+      <c r="C31" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="2">
+        <v>45718.08333333334</v>
+      </c>
+      <c r="F31">
+        <v>3</v>
+      </c>
+      <c r="G31" t="s">
+        <v>81</v>
+      </c>
+      <c r="H31" t="s">
+        <v>89</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31">
+        <v>2</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>2</v>
+      </c>
+      <c r="O31" t="s">
+        <v>112</v>
+      </c>
+      <c r="P31" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q31">
+        <v>3.5</v>
+      </c>
+      <c r="R31">
+        <v>2.1</v>
+      </c>
+      <c r="S31">
+        <v>3.1</v>
+      </c>
+      <c r="T31">
+        <v>1.44</v>
+      </c>
+      <c r="U31">
+        <v>2.63</v>
+      </c>
+      <c r="V31">
+        <v>3.25</v>
+      </c>
+      <c r="W31">
+        <v>1.33</v>
+      </c>
+      <c r="X31">
+        <v>9</v>
+      </c>
+      <c r="Y31">
+        <v>1.07</v>
+      </c>
+      <c r="Z31">
+        <v>3.12</v>
+      </c>
+      <c r="AA31">
+        <v>3.32</v>
+      </c>
+      <c r="AB31">
+        <v>2.23</v>
+      </c>
+      <c r="AC31">
+        <v>1.06</v>
+      </c>
+      <c r="AD31">
+        <v>8</v>
+      </c>
+      <c r="AE31">
+        <v>1.33</v>
+      </c>
+      <c r="AF31">
+        <v>3.1</v>
+      </c>
+      <c r="AG31">
+        <v>2</v>
+      </c>
+      <c r="AH31">
+        <v>1.75</v>
+      </c>
+      <c r="AI31">
+        <v>1.8</v>
+      </c>
+      <c r="AJ31">
+        <v>1.91</v>
+      </c>
+      <c r="AK31">
+        <v>1.51</v>
+      </c>
+      <c r="AL31">
+        <v>1.32</v>
+      </c>
+      <c r="AM31">
+        <v>1.43</v>
+      </c>
+      <c r="AN31">
+        <v>1</v>
+      </c>
+      <c r="AO31">
+        <v>0</v>
+      </c>
+      <c r="AP31">
+        <v>2</v>
+      </c>
+      <c r="AQ31">
+        <v>0</v>
+      </c>
+      <c r="AR31">
+        <v>1.27</v>
+      </c>
+      <c r="AS31">
+        <v>1.06</v>
+      </c>
+      <c r="AT31">
+        <v>2.33</v>
+      </c>
+      <c r="AU31">
+        <v>5</v>
+      </c>
+      <c r="AV31">
+        <v>3</v>
+      </c>
+      <c r="AW31">
+        <v>3</v>
+      </c>
+      <c r="AX31">
+        <v>6</v>
+      </c>
+      <c r="AY31">
+        <v>8</v>
+      </c>
+      <c r="AZ31">
+        <v>9</v>
+      </c>
+      <c r="BA31">
+        <v>2</v>
+      </c>
+      <c r="BB31">
+        <v>6</v>
+      </c>
+      <c r="BC31">
+        <v>8</v>
+      </c>
+      <c r="BD31">
+        <v>2.15</v>
+      </c>
+      <c r="BE31">
+        <v>6.15</v>
+      </c>
+      <c r="BF31">
+        <v>2.04</v>
+      </c>
+      <c r="BG31">
+        <v>1.28</v>
+      </c>
+      <c r="BH31">
+        <v>3.08</v>
+      </c>
+      <c r="BI31">
+        <v>1.52</v>
+      </c>
+      <c r="BJ31">
+        <v>2.24</v>
+      </c>
+      <c r="BK31">
+        <v>1.92</v>
+      </c>
+      <c r="BL31">
+        <v>1.75</v>
+      </c>
+      <c r="BM31">
+        <v>2.49</v>
+      </c>
+      <c r="BN31">
+        <v>1.42</v>
+      </c>
+      <c r="BO31">
+        <v>3.42</v>
+      </c>
+      <c r="BP31">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="134">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -355,6 +355,15 @@
     <t>['39', '79']</t>
   </si>
   <si>
+    <t>['26']</t>
+  </si>
+  <si>
+    <t>['53', '79']</t>
+  </si>
+  <si>
+    <t>['35', '69']</t>
+  </si>
+  <si>
     <t>['31', '60']</t>
   </si>
   <si>
@@ -398,6 +407,15 @@
   </si>
   <si>
     <t>['3']</t>
+  </si>
+  <si>
+    <t>['24']</t>
+  </si>
+  <si>
+    <t>['50']</t>
+  </si>
+  <si>
+    <t>['48', '82', '87']</t>
   </si>
 </sst>
 </file>
@@ -759,7 +777,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP31"/>
+  <dimension ref="A1:BP34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1015,7 +1033,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Q2">
         <v>3.6</v>
@@ -1221,7 +1239,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="Q3">
         <v>3.75</v>
@@ -1633,7 +1651,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -1839,7 +1857,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="Q6">
         <v>4.1</v>
@@ -2045,7 +2063,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="Q7">
         <v>2.88</v>
@@ -2251,7 +2269,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Q8">
         <v>2.28</v>
@@ -2457,7 +2475,7 @@
         <v>90</v>
       </c>
       <c r="P9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -2663,7 +2681,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -3693,7 +3711,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="Q15">
         <v>4.1</v>
@@ -4929,7 +4947,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="Q21">
         <v>4.4</v>
@@ -5213,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ22">
         <v>0</v>
@@ -5341,7 +5359,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5753,7 +5771,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -5959,7 +5977,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="Q26">
         <v>3.95</v>
@@ -6165,7 +6183,7 @@
         <v>90</v>
       </c>
       <c r="P27" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="Q27">
         <v>3.2</v>
@@ -6371,7 +6389,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="Q28">
         <v>3.35</v>
@@ -6783,7 +6801,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="Q30">
         <v>2.38</v>
@@ -7146,6 +7164,624 @@
       </c>
       <c r="BP31">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:68">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>7778520</v>
+      </c>
+      <c r="C32" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" s="2">
+        <v>45724.04166666666</v>
+      </c>
+      <c r="F32">
+        <v>4</v>
+      </c>
+      <c r="G32" t="s">
+        <v>85</v>
+      </c>
+      <c r="H32" t="s">
+        <v>76</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+      <c r="K32">
+        <v>2</v>
+      </c>
+      <c r="L32">
+        <v>1</v>
+      </c>
+      <c r="M32">
+        <v>1</v>
+      </c>
+      <c r="N32">
+        <v>2</v>
+      </c>
+      <c r="O32" t="s">
+        <v>113</v>
+      </c>
+      <c r="P32" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q32">
+        <v>3.45</v>
+      </c>
+      <c r="R32">
+        <v>2.09</v>
+      </c>
+      <c r="S32">
+        <v>2.86</v>
+      </c>
+      <c r="T32">
+        <v>1.36</v>
+      </c>
+      <c r="U32">
+        <v>2.88</v>
+      </c>
+      <c r="V32">
+        <v>2.76</v>
+      </c>
+      <c r="W32">
+        <v>1.39</v>
+      </c>
+      <c r="X32">
+        <v>6.6</v>
+      </c>
+      <c r="Y32">
+        <v>1.07</v>
+      </c>
+      <c r="Z32">
+        <v>2.85</v>
+      </c>
+      <c r="AA32">
+        <v>3.37</v>
+      </c>
+      <c r="AB32">
+        <v>2.37</v>
+      </c>
+      <c r="AC32">
+        <v>1.03</v>
+      </c>
+      <c r="AD32">
+        <v>9</v>
+      </c>
+      <c r="AE32">
+        <v>1.24</v>
+      </c>
+      <c r="AF32">
+        <v>3.34</v>
+      </c>
+      <c r="AG32">
+        <v>1.87</v>
+      </c>
+      <c r="AH32">
+        <v>1.87</v>
+      </c>
+      <c r="AI32">
+        <v>1.68</v>
+      </c>
+      <c r="AJ32">
+        <v>2.01</v>
+      </c>
+      <c r="AK32">
+        <v>1.53</v>
+      </c>
+      <c r="AL32">
+        <v>1.27</v>
+      </c>
+      <c r="AM32">
+        <v>1.36</v>
+      </c>
+      <c r="AN32">
+        <v>3</v>
+      </c>
+      <c r="AO32">
+        <v>1</v>
+      </c>
+      <c r="AP32">
+        <v>2</v>
+      </c>
+      <c r="AQ32">
+        <v>1</v>
+      </c>
+      <c r="AR32">
+        <v>1.26</v>
+      </c>
+      <c r="AS32">
+        <v>1.43</v>
+      </c>
+      <c r="AT32">
+        <v>2.69</v>
+      </c>
+      <c r="AU32">
+        <v>4</v>
+      </c>
+      <c r="AV32">
+        <v>3</v>
+      </c>
+      <c r="AW32">
+        <v>5</v>
+      </c>
+      <c r="AX32">
+        <v>5</v>
+      </c>
+      <c r="AY32">
+        <v>9</v>
+      </c>
+      <c r="AZ32">
+        <v>8</v>
+      </c>
+      <c r="BA32">
+        <v>0</v>
+      </c>
+      <c r="BB32">
+        <v>2</v>
+      </c>
+      <c r="BC32">
+        <v>2</v>
+      </c>
+      <c r="BD32">
+        <v>1.82</v>
+      </c>
+      <c r="BE32">
+        <v>8</v>
+      </c>
+      <c r="BF32">
+        <v>2.33</v>
+      </c>
+      <c r="BG32">
+        <v>1.36</v>
+      </c>
+      <c r="BH32">
+        <v>2.92</v>
+      </c>
+      <c r="BI32">
+        <v>1.62</v>
+      </c>
+      <c r="BJ32">
+        <v>2.22</v>
+      </c>
+      <c r="BK32">
+        <v>2.02</v>
+      </c>
+      <c r="BL32">
+        <v>1.74</v>
+      </c>
+      <c r="BM32">
+        <v>2.57</v>
+      </c>
+      <c r="BN32">
+        <v>1.45</v>
+      </c>
+      <c r="BO32">
+        <v>3.42</v>
+      </c>
+      <c r="BP32">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:68">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>7778523</v>
+      </c>
+      <c r="C33" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E33" s="2">
+        <v>45724.08333333334</v>
+      </c>
+      <c r="F33">
+        <v>4</v>
+      </c>
+      <c r="G33" t="s">
+        <v>71</v>
+      </c>
+      <c r="H33" t="s">
+        <v>81</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>2</v>
+      </c>
+      <c r="M33">
+        <v>1</v>
+      </c>
+      <c r="N33">
+        <v>3</v>
+      </c>
+      <c r="O33" t="s">
+        <v>114</v>
+      </c>
+      <c r="P33" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q33">
+        <v>2.5</v>
+      </c>
+      <c r="R33">
+        <v>2.2</v>
+      </c>
+      <c r="S33">
+        <v>4.5</v>
+      </c>
+      <c r="T33">
+        <v>1.4</v>
+      </c>
+      <c r="U33">
+        <v>2.75</v>
+      </c>
+      <c r="V33">
+        <v>3</v>
+      </c>
+      <c r="W33">
+        <v>1.36</v>
+      </c>
+      <c r="X33">
+        <v>8</v>
+      </c>
+      <c r="Y33">
+        <v>1.08</v>
+      </c>
+      <c r="Z33">
+        <v>2.3</v>
+      </c>
+      <c r="AA33">
+        <v>3.3</v>
+      </c>
+      <c r="AB33">
+        <v>3</v>
+      </c>
+      <c r="AC33">
+        <v>1.06</v>
+      </c>
+      <c r="AD33">
+        <v>8</v>
+      </c>
+      <c r="AE33">
+        <v>1.3</v>
+      </c>
+      <c r="AF33">
+        <v>3.25</v>
+      </c>
+      <c r="AG33">
+        <v>1.92</v>
+      </c>
+      <c r="AH33">
+        <v>1.82</v>
+      </c>
+      <c r="AI33">
+        <v>1.83</v>
+      </c>
+      <c r="AJ33">
+        <v>1.83</v>
+      </c>
+      <c r="AK33">
+        <v>1.25</v>
+      </c>
+      <c r="AL33">
+        <v>1.25</v>
+      </c>
+      <c r="AM33">
+        <v>1.77</v>
+      </c>
+      <c r="AN33">
+        <v>3</v>
+      </c>
+      <c r="AO33">
+        <v>0</v>
+      </c>
+      <c r="AP33">
+        <v>3</v>
+      </c>
+      <c r="AQ33">
+        <v>0</v>
+      </c>
+      <c r="AR33">
+        <v>1.88</v>
+      </c>
+      <c r="AS33">
+        <v>1.02</v>
+      </c>
+      <c r="AT33">
+        <v>2.9</v>
+      </c>
+      <c r="AU33">
+        <v>7</v>
+      </c>
+      <c r="AV33">
+        <v>5</v>
+      </c>
+      <c r="AW33">
+        <v>9</v>
+      </c>
+      <c r="AX33">
+        <v>7</v>
+      </c>
+      <c r="AY33">
+        <v>20</v>
+      </c>
+      <c r="AZ33">
+        <v>14</v>
+      </c>
+      <c r="BA33">
+        <v>8</v>
+      </c>
+      <c r="BB33">
+        <v>5</v>
+      </c>
+      <c r="BC33">
+        <v>13</v>
+      </c>
+      <c r="BD33">
+        <v>1.77</v>
+      </c>
+      <c r="BE33">
+        <v>6.25</v>
+      </c>
+      <c r="BF33">
+        <v>2.63</v>
+      </c>
+      <c r="BG33">
+        <v>1.33</v>
+      </c>
+      <c r="BH33">
+        <v>2.83</v>
+      </c>
+      <c r="BI33">
+        <v>1.68</v>
+      </c>
+      <c r="BJ33">
+        <v>2.15</v>
+      </c>
+      <c r="BK33">
+        <v>2.1</v>
+      </c>
+      <c r="BL33">
+        <v>1.71</v>
+      </c>
+      <c r="BM33">
+        <v>2.7</v>
+      </c>
+      <c r="BN33">
+        <v>1.36</v>
+      </c>
+      <c r="BO33">
+        <v>3.8</v>
+      </c>
+      <c r="BP33">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:68">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>7778527</v>
+      </c>
+      <c r="C34" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="2">
+        <v>45724.25694444445</v>
+      </c>
+      <c r="F34">
+        <v>4</v>
+      </c>
+      <c r="G34" t="s">
+        <v>77</v>
+      </c>
+      <c r="H34" t="s">
+        <v>78</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>1</v>
+      </c>
+      <c r="L34">
+        <v>2</v>
+      </c>
+      <c r="M34">
+        <v>3</v>
+      </c>
+      <c r="N34">
+        <v>5</v>
+      </c>
+      <c r="O34" t="s">
+        <v>115</v>
+      </c>
+      <c r="P34" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q34">
+        <v>3.75</v>
+      </c>
+      <c r="R34">
+        <v>2.05</v>
+      </c>
+      <c r="S34">
+        <v>3</v>
+      </c>
+      <c r="T34">
+        <v>1.44</v>
+      </c>
+      <c r="U34">
+        <v>2.63</v>
+      </c>
+      <c r="V34">
+        <v>3.25</v>
+      </c>
+      <c r="W34">
+        <v>1.33</v>
+      </c>
+      <c r="X34">
+        <v>10</v>
+      </c>
+      <c r="Y34">
+        <v>1.06</v>
+      </c>
+      <c r="Z34">
+        <v>2.62</v>
+      </c>
+      <c r="AA34">
+        <v>3.23</v>
+      </c>
+      <c r="AB34">
+        <v>2.64</v>
+      </c>
+      <c r="AC34">
+        <v>1.07</v>
+      </c>
+      <c r="AD34">
+        <v>7.5</v>
+      </c>
+      <c r="AE34">
+        <v>1.36</v>
+      </c>
+      <c r="AF34">
+        <v>2.95</v>
+      </c>
+      <c r="AG34">
+        <v>2.05</v>
+      </c>
+      <c r="AH34">
+        <v>1.7</v>
+      </c>
+      <c r="AI34">
+        <v>1.83</v>
+      </c>
+      <c r="AJ34">
+        <v>1.83</v>
+      </c>
+      <c r="AK34">
+        <v>1.63</v>
+      </c>
+      <c r="AL34">
+        <v>1.32</v>
+      </c>
+      <c r="AM34">
+        <v>1.32</v>
+      </c>
+      <c r="AN34">
+        <v>0</v>
+      </c>
+      <c r="AO34">
+        <v>3</v>
+      </c>
+      <c r="AP34">
+        <v>0</v>
+      </c>
+      <c r="AQ34">
+        <v>3</v>
+      </c>
+      <c r="AR34">
+        <v>1.24</v>
+      </c>
+      <c r="AS34">
+        <v>1.78</v>
+      </c>
+      <c r="AT34">
+        <v>3.02</v>
+      </c>
+      <c r="AU34">
+        <v>3</v>
+      </c>
+      <c r="AV34">
+        <v>7</v>
+      </c>
+      <c r="AW34">
+        <v>0</v>
+      </c>
+      <c r="AX34">
+        <v>4</v>
+      </c>
+      <c r="AY34">
+        <v>3</v>
+      </c>
+      <c r="AZ34">
+        <v>11</v>
+      </c>
+      <c r="BA34">
+        <v>5</v>
+      </c>
+      <c r="BB34">
+        <v>4</v>
+      </c>
+      <c r="BC34">
+        <v>9</v>
+      </c>
+      <c r="BD34">
+        <v>2.53</v>
+      </c>
+      <c r="BE34">
+        <v>8.5</v>
+      </c>
+      <c r="BF34">
+        <v>1.69</v>
+      </c>
+      <c r="BG34">
+        <v>1.11</v>
+      </c>
+      <c r="BH34">
+        <v>5.15</v>
+      </c>
+      <c r="BI34">
+        <v>1.23</v>
+      </c>
+      <c r="BJ34">
+        <v>3.55</v>
+      </c>
+      <c r="BK34">
+        <v>1.43</v>
+      </c>
+      <c r="BL34">
+        <v>2.62</v>
+      </c>
+      <c r="BM34">
+        <v>1.71</v>
+      </c>
+      <c r="BN34">
+        <v>2.06</v>
+      </c>
+      <c r="BO34">
+        <v>2.11</v>
+      </c>
+      <c r="BP34">
+        <v>1.68</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="141">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -277,15 +277,15 @@
     <t>Kataller Toyama</t>
   </si>
   <si>
+    <t>Consadole Sapporo</t>
+  </si>
+  <si>
     <t>Montedio Yamagata</t>
   </si>
   <si>
     <t>Blaublitz Akita</t>
   </si>
   <si>
-    <t>Consadole Sapporo</t>
-  </si>
-  <si>
     <t>[]</t>
   </si>
   <si>
@@ -364,6 +364,18 @@
     <t>['35', '69']</t>
   </si>
   <si>
+    <t>['38']</t>
+  </si>
+  <si>
+    <t>['12', '14', '57', '85']</t>
+  </si>
+  <si>
+    <t>['26', '41', '54']</t>
+  </si>
+  <si>
+    <t>['33', '75', '81']</t>
+  </si>
+  <si>
     <t>['31', '60']</t>
   </si>
   <si>
@@ -416,6 +428,15 @@
   </si>
   <si>
     <t>['48', '82', '87']</t>
+  </si>
+  <si>
+    <t>['11', '32', '90+2']</t>
+  </si>
+  <si>
+    <t>['30', '65']</t>
+  </si>
+  <si>
+    <t>['22', '39', '90+6']</t>
   </si>
 </sst>
 </file>
@@ -777,7 +798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP34"/>
+  <dimension ref="A1:BP41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1033,7 +1054,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="Q2">
         <v>3.6</v>
@@ -1111,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AQ2">
         <v>3</v>
@@ -1215,7 +1236,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1239,7 +1260,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="Q3">
         <v>3.75</v>
@@ -1523,7 +1544,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ4">
         <v>0</v>
@@ -1651,7 +1672,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -1732,7 +1753,7 @@
         <v>3</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1857,7 +1878,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="Q6">
         <v>4.1</v>
@@ -2063,7 +2084,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="Q7">
         <v>2.88</v>
@@ -2269,7 +2290,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="Q8">
         <v>2.28</v>
@@ -2350,7 +2371,7 @@
         <v>3</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2475,7 +2496,7 @@
         <v>90</v>
       </c>
       <c r="P9" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -2657,7 +2678,7 @@
         <v>78</v>
       </c>
       <c r="H10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -2681,7 +2702,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -2762,7 +2783,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ10">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -2863,7 +2884,7 @@
         <v>79</v>
       </c>
       <c r="H11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -2965,7 +2986,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ11">
         <v>0</v>
@@ -3174,7 +3195,7 @@
         <v>3</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR12">
         <v>1.68</v>
@@ -3711,7 +3732,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="Q15">
         <v>4.1</v>
@@ -3893,7 +3914,7 @@
         <v>82</v>
       </c>
       <c r="H16" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I16">
         <v>1</v>
@@ -4201,7 +4222,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ17">
         <v>1.5</v>
@@ -4305,7 +4326,7 @@
         <v>84</v>
       </c>
       <c r="H18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -4819,7 +4840,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ20">
         <v>1</v>
@@ -4923,7 +4944,7 @@
         <v>77</v>
       </c>
       <c r="H21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -4947,7 +4968,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="Q21">
         <v>4.4</v>
@@ -5028,7 +5049,7 @@
         <v>0</v>
       </c>
       <c r="AQ21">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AR21">
         <v>1.32</v>
@@ -5359,7 +5380,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5747,7 +5768,7 @@
         <v>80</v>
       </c>
       <c r="H25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I25">
         <v>2</v>
@@ -5771,7 +5792,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -5953,7 +5974,7 @@
         <v>74</v>
       </c>
       <c r="H26" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I26">
         <v>1</v>
@@ -5977,7 +5998,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="Q26">
         <v>3.95</v>
@@ -6058,7 +6079,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ26">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AR26">
         <v>0.85</v>
@@ -6183,7 +6204,7 @@
         <v>90</v>
       </c>
       <c r="P27" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="Q27">
         <v>3.2</v>
@@ -6389,7 +6410,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="Q28">
         <v>3.35</v>
@@ -6467,7 +6488,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AQ28">
         <v>2</v>
@@ -6801,7 +6822,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="Q30">
         <v>2.38</v>
@@ -6983,7 +7004,7 @@
         <v>81</v>
       </c>
       <c r="H31" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I31">
         <v>1</v>
@@ -7213,7 +7234,7 @@
         <v>113</v>
       </c>
       <c r="P32" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="Q32">
         <v>3.45</v>
@@ -7419,7 +7440,7 @@
         <v>114</v>
       </c>
       <c r="P33" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -7625,7 +7646,7 @@
         <v>115</v>
       </c>
       <c r="P34" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -7782,6 +7803,1448 @@
       </c>
       <c r="BP34">
         <v>1.68</v>
+      </c>
+    </row>
+    <row r="35" spans="1:68">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>7778519</v>
+      </c>
+      <c r="C35" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="2">
+        <v>45725.04513888889</v>
+      </c>
+      <c r="F35">
+        <v>4</v>
+      </c>
+      <c r="G35" t="s">
+        <v>87</v>
+      </c>
+      <c r="H35" t="s">
+        <v>80</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
+      </c>
+      <c r="J35">
+        <v>2</v>
+      </c>
+      <c r="K35">
+        <v>3</v>
+      </c>
+      <c r="L35">
+        <v>1</v>
+      </c>
+      <c r="M35">
+        <v>3</v>
+      </c>
+      <c r="N35">
+        <v>4</v>
+      </c>
+      <c r="O35" t="s">
+        <v>116</v>
+      </c>
+      <c r="P35" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q35">
+        <v>3.4</v>
+      </c>
+      <c r="R35">
+        <v>2.25</v>
+      </c>
+      <c r="S35">
+        <v>3</v>
+      </c>
+      <c r="T35">
+        <v>1.36</v>
+      </c>
+      <c r="U35">
+        <v>3</v>
+      </c>
+      <c r="V35">
+        <v>2.63</v>
+      </c>
+      <c r="W35">
+        <v>1.44</v>
+      </c>
+      <c r="X35">
+        <v>7</v>
+      </c>
+      <c r="Y35">
+        <v>1.1</v>
+      </c>
+      <c r="Z35">
+        <v>3</v>
+      </c>
+      <c r="AA35">
+        <v>3.3</v>
+      </c>
+      <c r="AB35">
+        <v>2.3</v>
+      </c>
+      <c r="AC35">
+        <v>1.05</v>
+      </c>
+      <c r="AD35">
+        <v>8.5</v>
+      </c>
+      <c r="AE35">
+        <v>1.25</v>
+      </c>
+      <c r="AF35">
+        <v>3.7</v>
+      </c>
+      <c r="AG35">
+        <v>1.82</v>
+      </c>
+      <c r="AH35">
+        <v>1.92</v>
+      </c>
+      <c r="AI35">
+        <v>1.62</v>
+      </c>
+      <c r="AJ35">
+        <v>2.2</v>
+      </c>
+      <c r="AK35">
+        <v>1.55</v>
+      </c>
+      <c r="AL35">
+        <v>1.3</v>
+      </c>
+      <c r="AM35">
+        <v>1.41</v>
+      </c>
+      <c r="AN35">
+        <v>0</v>
+      </c>
+      <c r="AO35">
+        <v>3</v>
+      </c>
+      <c r="AP35">
+        <v>0</v>
+      </c>
+      <c r="AQ35">
+        <v>3</v>
+      </c>
+      <c r="AR35">
+        <v>0</v>
+      </c>
+      <c r="AS35">
+        <v>1.04</v>
+      </c>
+      <c r="AT35">
+        <v>1.04</v>
+      </c>
+      <c r="AU35">
+        <v>5</v>
+      </c>
+      <c r="AV35">
+        <v>5</v>
+      </c>
+      <c r="AW35">
+        <v>8</v>
+      </c>
+      <c r="AX35">
+        <v>0</v>
+      </c>
+      <c r="AY35">
+        <v>17</v>
+      </c>
+      <c r="AZ35">
+        <v>5</v>
+      </c>
+      <c r="BA35">
+        <v>11</v>
+      </c>
+      <c r="BB35">
+        <v>2</v>
+      </c>
+      <c r="BC35">
+        <v>13</v>
+      </c>
+      <c r="BD35">
+        <v>1.91</v>
+      </c>
+      <c r="BE35">
+        <v>7.5</v>
+      </c>
+      <c r="BF35">
+        <v>2.2</v>
+      </c>
+      <c r="BG35">
+        <v>1.39</v>
+      </c>
+      <c r="BH35">
+        <v>2.77</v>
+      </c>
+      <c r="BI35">
+        <v>1.68</v>
+      </c>
+      <c r="BJ35">
+        <v>2.11</v>
+      </c>
+      <c r="BK35">
+        <v>2.11</v>
+      </c>
+      <c r="BL35">
+        <v>1.68</v>
+      </c>
+      <c r="BM35">
+        <v>2.7</v>
+      </c>
+      <c r="BN35">
+        <v>1.41</v>
+      </c>
+      <c r="BO35">
+        <v>3.65</v>
+      </c>
+      <c r="BP35">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:68">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>7778521</v>
+      </c>
+      <c r="C36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" s="2">
+        <v>45725.08333333334</v>
+      </c>
+      <c r="F36">
+        <v>4</v>
+      </c>
+      <c r="G36" t="s">
+        <v>88</v>
+      </c>
+      <c r="H36" t="s">
+        <v>89</v>
+      </c>
+      <c r="I36">
+        <v>2</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
+      </c>
+      <c r="K36">
+        <v>3</v>
+      </c>
+      <c r="L36">
+        <v>4</v>
+      </c>
+      <c r="M36">
+        <v>2</v>
+      </c>
+      <c r="N36">
+        <v>6</v>
+      </c>
+      <c r="O36" t="s">
+        <v>117</v>
+      </c>
+      <c r="P36" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q36">
+        <v>2.8</v>
+      </c>
+      <c r="R36">
+        <v>2.1</v>
+      </c>
+      <c r="S36">
+        <v>3.8</v>
+      </c>
+      <c r="T36">
+        <v>1.4</v>
+      </c>
+      <c r="U36">
+        <v>2.75</v>
+      </c>
+      <c r="V36">
+        <v>3.2</v>
+      </c>
+      <c r="W36">
+        <v>1.33</v>
+      </c>
+      <c r="X36">
+        <v>9.5</v>
+      </c>
+      <c r="Y36">
+        <v>1.06</v>
+      </c>
+      <c r="Z36">
+        <v>2.18</v>
+      </c>
+      <c r="AA36">
+        <v>3.28</v>
+      </c>
+      <c r="AB36">
+        <v>3.28</v>
+      </c>
+      <c r="AC36">
+        <v>1.03</v>
+      </c>
+      <c r="AD36">
+        <v>7.4</v>
+      </c>
+      <c r="AE36">
+        <v>1.34</v>
+      </c>
+      <c r="AF36">
+        <v>2.78</v>
+      </c>
+      <c r="AG36">
+        <v>2.1</v>
+      </c>
+      <c r="AH36">
+        <v>1.6</v>
+      </c>
+      <c r="AI36">
+        <v>1.85</v>
+      </c>
+      <c r="AJ36">
+        <v>1.85</v>
+      </c>
+      <c r="AK36">
+        <v>1.3</v>
+      </c>
+      <c r="AL36">
+        <v>1.35</v>
+      </c>
+      <c r="AM36">
+        <v>1.67</v>
+      </c>
+      <c r="AN36">
+        <v>0</v>
+      </c>
+      <c r="AO36">
+        <v>2</v>
+      </c>
+      <c r="AP36">
+        <v>3</v>
+      </c>
+      <c r="AQ36">
+        <v>1.5</v>
+      </c>
+      <c r="AR36">
+        <v>0</v>
+      </c>
+      <c r="AS36">
+        <v>1.39</v>
+      </c>
+      <c r="AT36">
+        <v>1.39</v>
+      </c>
+      <c r="AU36">
+        <v>6</v>
+      </c>
+      <c r="AV36">
+        <v>5</v>
+      </c>
+      <c r="AW36">
+        <v>6</v>
+      </c>
+      <c r="AX36">
+        <v>12</v>
+      </c>
+      <c r="AY36">
+        <v>12</v>
+      </c>
+      <c r="AZ36">
+        <v>17</v>
+      </c>
+      <c r="BA36">
+        <v>3</v>
+      </c>
+      <c r="BB36">
+        <v>3</v>
+      </c>
+      <c r="BC36">
+        <v>6</v>
+      </c>
+      <c r="BD36">
+        <v>1.75</v>
+      </c>
+      <c r="BE36">
+        <v>8</v>
+      </c>
+      <c r="BF36">
+        <v>2.42</v>
+      </c>
+      <c r="BG36">
+        <v>1.19</v>
+      </c>
+      <c r="BH36">
+        <v>3.98</v>
+      </c>
+      <c r="BI36">
+        <v>1.38</v>
+      </c>
+      <c r="BJ36">
+        <v>2.82</v>
+      </c>
+      <c r="BK36">
+        <v>1.63</v>
+      </c>
+      <c r="BL36">
+        <v>2.18</v>
+      </c>
+      <c r="BM36">
+        <v>2.02</v>
+      </c>
+      <c r="BN36">
+        <v>1.74</v>
+      </c>
+      <c r="BO36">
+        <v>2.53</v>
+      </c>
+      <c r="BP36">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="37" spans="1:68">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>7778522</v>
+      </c>
+      <c r="C37" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="2">
+        <v>45725.08333333334</v>
+      </c>
+      <c r="F37">
+        <v>4</v>
+      </c>
+      <c r="G37" t="s">
+        <v>70</v>
+      </c>
+      <c r="H37" t="s">
+        <v>75</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>1</v>
+      </c>
+      <c r="K37">
+        <v>1</v>
+      </c>
+      <c r="L37">
+        <v>1</v>
+      </c>
+      <c r="M37">
+        <v>1</v>
+      </c>
+      <c r="N37">
+        <v>2</v>
+      </c>
+      <c r="O37" t="s">
+        <v>92</v>
+      </c>
+      <c r="P37" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q37">
+        <v>3.1</v>
+      </c>
+      <c r="R37">
+        <v>2.05</v>
+      </c>
+      <c r="S37">
+        <v>3.75</v>
+      </c>
+      <c r="T37">
+        <v>1.44</v>
+      </c>
+      <c r="U37">
+        <v>2.63</v>
+      </c>
+      <c r="V37">
+        <v>3.4</v>
+      </c>
+      <c r="W37">
+        <v>1.3</v>
+      </c>
+      <c r="X37">
+        <v>10</v>
+      </c>
+      <c r="Y37">
+        <v>1.06</v>
+      </c>
+      <c r="Z37">
+        <v>2.3</v>
+      </c>
+      <c r="AA37">
+        <v>3.3</v>
+      </c>
+      <c r="AB37">
+        <v>3</v>
+      </c>
+      <c r="AC37">
+        <v>1.07</v>
+      </c>
+      <c r="AD37">
+        <v>7.5</v>
+      </c>
+      <c r="AE37">
+        <v>1.38</v>
+      </c>
+      <c r="AF37">
+        <v>2.88</v>
+      </c>
+      <c r="AG37">
+        <v>1.92</v>
+      </c>
+      <c r="AH37">
+        <v>1.82</v>
+      </c>
+      <c r="AI37">
+        <v>1.83</v>
+      </c>
+      <c r="AJ37">
+        <v>1.83</v>
+      </c>
+      <c r="AK37">
+        <v>1.37</v>
+      </c>
+      <c r="AL37">
+        <v>1.33</v>
+      </c>
+      <c r="AM37">
+        <v>1.55</v>
+      </c>
+      <c r="AN37">
+        <v>0.5</v>
+      </c>
+      <c r="AO37">
+        <v>0</v>
+      </c>
+      <c r="AP37">
+        <v>0.67</v>
+      </c>
+      <c r="AQ37">
+        <v>0.5</v>
+      </c>
+      <c r="AR37">
+        <v>1.86</v>
+      </c>
+      <c r="AS37">
+        <v>1.97</v>
+      </c>
+      <c r="AT37">
+        <v>3.83</v>
+      </c>
+      <c r="AU37">
+        <v>7</v>
+      </c>
+      <c r="AV37">
+        <v>4</v>
+      </c>
+      <c r="AW37">
+        <v>5</v>
+      </c>
+      <c r="AX37">
+        <v>6</v>
+      </c>
+      <c r="AY37">
+        <v>12</v>
+      </c>
+      <c r="AZ37">
+        <v>10</v>
+      </c>
+      <c r="BA37">
+        <v>3</v>
+      </c>
+      <c r="BB37">
+        <v>3</v>
+      </c>
+      <c r="BC37">
+        <v>6</v>
+      </c>
+      <c r="BD37">
+        <v>1.91</v>
+      </c>
+      <c r="BE37">
+        <v>8</v>
+      </c>
+      <c r="BF37">
+        <v>2.1</v>
+      </c>
+      <c r="BG37">
+        <v>1.26</v>
+      </c>
+      <c r="BH37">
+        <v>3.38</v>
+      </c>
+      <c r="BI37">
+        <v>1.48</v>
+      </c>
+      <c r="BJ37">
+        <v>2.45</v>
+      </c>
+      <c r="BK37">
+        <v>1.82</v>
+      </c>
+      <c r="BL37">
+        <v>1.93</v>
+      </c>
+      <c r="BM37">
+        <v>2.3</v>
+      </c>
+      <c r="BN37">
+        <v>1.57</v>
+      </c>
+      <c r="BO37">
+        <v>2.93</v>
+      </c>
+      <c r="BP37">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:68">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>7778524</v>
+      </c>
+      <c r="C38" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45725.08333333334</v>
+      </c>
+      <c r="F38">
+        <v>4</v>
+      </c>
+      <c r="G38" t="s">
+        <v>72</v>
+      </c>
+      <c r="H38" t="s">
+        <v>74</v>
+      </c>
+      <c r="I38">
+        <v>2</v>
+      </c>
+      <c r="J38">
+        <v>2</v>
+      </c>
+      <c r="K38">
+        <v>4</v>
+      </c>
+      <c r="L38">
+        <v>3</v>
+      </c>
+      <c r="M38">
+        <v>3</v>
+      </c>
+      <c r="N38">
+        <v>6</v>
+      </c>
+      <c r="O38" t="s">
+        <v>118</v>
+      </c>
+      <c r="P38" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q38">
+        <v>2.6</v>
+      </c>
+      <c r="R38">
+        <v>2.15</v>
+      </c>
+      <c r="S38">
+        <v>4</v>
+      </c>
+      <c r="T38">
+        <v>1.4</v>
+      </c>
+      <c r="U38">
+        <v>2.8</v>
+      </c>
+      <c r="V38">
+        <v>2.9</v>
+      </c>
+      <c r="W38">
+        <v>1.36</v>
+      </c>
+      <c r="X38">
+        <v>7.5</v>
+      </c>
+      <c r="Y38">
+        <v>1.08</v>
+      </c>
+      <c r="Z38">
+        <v>1.9</v>
+      </c>
+      <c r="AA38">
+        <v>3.39</v>
+      </c>
+      <c r="AB38">
+        <v>4</v>
+      </c>
+      <c r="AC38">
+        <v>1.01</v>
+      </c>
+      <c r="AD38">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE38">
+        <v>1.28</v>
+      </c>
+      <c r="AF38">
+        <v>3.05</v>
+      </c>
+      <c r="AG38">
+        <v>1.98</v>
+      </c>
+      <c r="AH38">
+        <v>1.77</v>
+      </c>
+      <c r="AI38">
+        <v>1.8</v>
+      </c>
+      <c r="AJ38">
+        <v>1.95</v>
+      </c>
+      <c r="AK38">
+        <v>1.25</v>
+      </c>
+      <c r="AL38">
+        <v>1.3</v>
+      </c>
+      <c r="AM38">
+        <v>1.8</v>
+      </c>
+      <c r="AN38">
+        <v>3</v>
+      </c>
+      <c r="AO38">
+        <v>1</v>
+      </c>
+      <c r="AP38">
+        <v>2</v>
+      </c>
+      <c r="AQ38">
+        <v>1</v>
+      </c>
+      <c r="AR38">
+        <v>1.1</v>
+      </c>
+      <c r="AS38">
+        <v>1.03</v>
+      </c>
+      <c r="AT38">
+        <v>2.13</v>
+      </c>
+      <c r="AU38">
+        <v>4</v>
+      </c>
+      <c r="AV38">
+        <v>5</v>
+      </c>
+      <c r="AW38">
+        <v>0</v>
+      </c>
+      <c r="AX38">
+        <v>0</v>
+      </c>
+      <c r="AY38">
+        <v>4</v>
+      </c>
+      <c r="AZ38">
+        <v>5</v>
+      </c>
+      <c r="BA38">
+        <v>5</v>
+      </c>
+      <c r="BB38">
+        <v>9</v>
+      </c>
+      <c r="BC38">
+        <v>14</v>
+      </c>
+      <c r="BD38">
+        <v>1.55</v>
+      </c>
+      <c r="BE38">
+        <v>8.5</v>
+      </c>
+      <c r="BF38">
+        <v>3.01</v>
+      </c>
+      <c r="BG38">
+        <v>1.28</v>
+      </c>
+      <c r="BH38">
+        <v>3.25</v>
+      </c>
+      <c r="BI38">
+        <v>1.52</v>
+      </c>
+      <c r="BJ38">
+        <v>2.37</v>
+      </c>
+      <c r="BK38">
+        <v>1.87</v>
+      </c>
+      <c r="BL38">
+        <v>1.87</v>
+      </c>
+      <c r="BM38">
+        <v>2.38</v>
+      </c>
+      <c r="BN38">
+        <v>1.54</v>
+      </c>
+      <c r="BO38">
+        <v>3.12</v>
+      </c>
+      <c r="BP38">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:68">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>7778525</v>
+      </c>
+      <c r="C39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" s="2">
+        <v>45725.08333333334</v>
+      </c>
+      <c r="F39">
+        <v>4</v>
+      </c>
+      <c r="G39" t="s">
+        <v>86</v>
+      </c>
+      <c r="H39" t="s">
+        <v>73</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>1</v>
+      </c>
+      <c r="L39">
+        <v>3</v>
+      </c>
+      <c r="M39">
+        <v>1</v>
+      </c>
+      <c r="N39">
+        <v>4</v>
+      </c>
+      <c r="O39" t="s">
+        <v>119</v>
+      </c>
+      <c r="P39" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q39">
+        <v>4</v>
+      </c>
+      <c r="R39">
+        <v>2.05</v>
+      </c>
+      <c r="S39">
+        <v>3</v>
+      </c>
+      <c r="T39">
+        <v>1.44</v>
+      </c>
+      <c r="U39">
+        <v>2.63</v>
+      </c>
+      <c r="V39">
+        <v>3.4</v>
+      </c>
+      <c r="W39">
+        <v>1.3</v>
+      </c>
+      <c r="X39">
+        <v>10</v>
+      </c>
+      <c r="Y39">
+        <v>1.06</v>
+      </c>
+      <c r="Z39">
+        <v>3</v>
+      </c>
+      <c r="AA39">
+        <v>3.3</v>
+      </c>
+      <c r="AB39">
+        <v>2.3</v>
+      </c>
+      <c r="AC39">
+        <v>1.07</v>
+      </c>
+      <c r="AD39">
+        <v>7.5</v>
+      </c>
+      <c r="AE39">
+        <v>1.38</v>
+      </c>
+      <c r="AF39">
+        <v>2.9</v>
+      </c>
+      <c r="AG39">
+        <v>1.98</v>
+      </c>
+      <c r="AH39">
+        <v>1.77</v>
+      </c>
+      <c r="AI39">
+        <v>1.83</v>
+      </c>
+      <c r="AJ39">
+        <v>1.83</v>
+      </c>
+      <c r="AK39">
+        <v>1.66</v>
+      </c>
+      <c r="AL39">
+        <v>1.33</v>
+      </c>
+      <c r="AM39">
+        <v>1.3</v>
+      </c>
+      <c r="AN39">
+        <v>3</v>
+      </c>
+      <c r="AO39">
+        <v>0</v>
+      </c>
+      <c r="AP39">
+        <v>3</v>
+      </c>
+      <c r="AQ39">
+        <v>0</v>
+      </c>
+      <c r="AR39">
+        <v>1.33</v>
+      </c>
+      <c r="AS39">
+        <v>1.36</v>
+      </c>
+      <c r="AT39">
+        <v>2.69</v>
+      </c>
+      <c r="AU39">
+        <v>4</v>
+      </c>
+      <c r="AV39">
+        <v>4</v>
+      </c>
+      <c r="AW39">
+        <v>5</v>
+      </c>
+      <c r="AX39">
+        <v>0</v>
+      </c>
+      <c r="AY39">
+        <v>9</v>
+      </c>
+      <c r="AZ39">
+        <v>4</v>
+      </c>
+      <c r="BA39">
+        <v>7</v>
+      </c>
+      <c r="BB39">
+        <v>8</v>
+      </c>
+      <c r="BC39">
+        <v>15</v>
+      </c>
+      <c r="BD39">
+        <v>2.1</v>
+      </c>
+      <c r="BE39">
+        <v>8</v>
+      </c>
+      <c r="BF39">
+        <v>1.95</v>
+      </c>
+      <c r="BG39">
+        <v>1.28</v>
+      </c>
+      <c r="BH39">
+        <v>3.25</v>
+      </c>
+      <c r="BI39">
+        <v>1.52</v>
+      </c>
+      <c r="BJ39">
+        <v>2.37</v>
+      </c>
+      <c r="BK39">
+        <v>1.87</v>
+      </c>
+      <c r="BL39">
+        <v>1.87</v>
+      </c>
+      <c r="BM39">
+        <v>2.38</v>
+      </c>
+      <c r="BN39">
+        <v>1.54</v>
+      </c>
+      <c r="BO39">
+        <v>3.12</v>
+      </c>
+      <c r="BP39">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="40" spans="1:68">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>7778526</v>
+      </c>
+      <c r="C40" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E40" s="2">
+        <v>45725.08333333334</v>
+      </c>
+      <c r="F40">
+        <v>4</v>
+      </c>
+      <c r="G40" t="s">
+        <v>83</v>
+      </c>
+      <c r="H40" t="s">
+        <v>82</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40" t="s">
+        <v>90</v>
+      </c>
+      <c r="P40" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q40">
+        <v>3</v>
+      </c>
+      <c r="R40">
+        <v>2.05</v>
+      </c>
+      <c r="S40">
+        <v>3.6</v>
+      </c>
+      <c r="T40">
+        <v>1.44</v>
+      </c>
+      <c r="U40">
+        <v>2.62</v>
+      </c>
+      <c r="V40">
+        <v>3.1</v>
+      </c>
+      <c r="W40">
+        <v>1.33</v>
+      </c>
+      <c r="X40">
+        <v>9</v>
+      </c>
+      <c r="Y40">
+        <v>1.06</v>
+      </c>
+      <c r="Z40">
+        <v>2.44</v>
+      </c>
+      <c r="AA40">
+        <v>3.12</v>
+      </c>
+      <c r="AB40">
+        <v>2.94</v>
+      </c>
+      <c r="AC40">
+        <v>1.03</v>
+      </c>
+      <c r="AD40">
+        <v>7.3</v>
+      </c>
+      <c r="AE40">
+        <v>1.35</v>
+      </c>
+      <c r="AF40">
+        <v>2.74</v>
+      </c>
+      <c r="AG40">
+        <v>2.15</v>
+      </c>
+      <c r="AH40">
+        <v>1.6</v>
+      </c>
+      <c r="AI40">
+        <v>1.85</v>
+      </c>
+      <c r="AJ40">
+        <v>1.85</v>
+      </c>
+      <c r="AK40">
+        <v>1.36</v>
+      </c>
+      <c r="AL40">
+        <v>1.36</v>
+      </c>
+      <c r="AM40">
+        <v>1.55</v>
+      </c>
+      <c r="AN40">
+        <v>3</v>
+      </c>
+      <c r="AO40">
+        <v>0</v>
+      </c>
+      <c r="AP40">
+        <v>2</v>
+      </c>
+      <c r="AQ40">
+        <v>0.5</v>
+      </c>
+      <c r="AR40">
+        <v>1.47</v>
+      </c>
+      <c r="AS40">
+        <v>1.86</v>
+      </c>
+      <c r="AT40">
+        <v>3.33</v>
+      </c>
+      <c r="AU40">
+        <v>4</v>
+      </c>
+      <c r="AV40">
+        <v>3</v>
+      </c>
+      <c r="AW40">
+        <v>7</v>
+      </c>
+      <c r="AX40">
+        <v>4</v>
+      </c>
+      <c r="AY40">
+        <v>11</v>
+      </c>
+      <c r="AZ40">
+        <v>7</v>
+      </c>
+      <c r="BA40">
+        <v>4</v>
+      </c>
+      <c r="BB40">
+        <v>7</v>
+      </c>
+      <c r="BC40">
+        <v>11</v>
+      </c>
+      <c r="BD40">
+        <v>1.95</v>
+      </c>
+      <c r="BE40">
+        <v>8</v>
+      </c>
+      <c r="BF40">
+        <v>2.1</v>
+      </c>
+      <c r="BG40">
+        <v>1.28</v>
+      </c>
+      <c r="BH40">
+        <v>3.25</v>
+      </c>
+      <c r="BI40">
+        <v>1.52</v>
+      </c>
+      <c r="BJ40">
+        <v>2.37</v>
+      </c>
+      <c r="BK40">
+        <v>1.87</v>
+      </c>
+      <c r="BL40">
+        <v>1.87</v>
+      </c>
+      <c r="BM40">
+        <v>2.38</v>
+      </c>
+      <c r="BN40">
+        <v>1.54</v>
+      </c>
+      <c r="BO40">
+        <v>3.12</v>
+      </c>
+      <c r="BP40">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:68">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>7778528</v>
+      </c>
+      <c r="C41" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" t="s">
+        <v>69</v>
+      </c>
+      <c r="E41" s="2">
+        <v>45725.08333333334</v>
+      </c>
+      <c r="F41">
+        <v>4</v>
+      </c>
+      <c r="G41" t="s">
+        <v>79</v>
+      </c>
+      <c r="H41" t="s">
+        <v>84</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41" t="s">
+        <v>90</v>
+      </c>
+      <c r="P41" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q41">
+        <v>2.8</v>
+      </c>
+      <c r="R41">
+        <v>2.05</v>
+      </c>
+      <c r="S41">
+        <v>3.9</v>
+      </c>
+      <c r="T41">
+        <v>1.44</v>
+      </c>
+      <c r="U41">
+        <v>2.62</v>
+      </c>
+      <c r="V41">
+        <v>3.25</v>
+      </c>
+      <c r="W41">
+        <v>1.3</v>
+      </c>
+      <c r="X41">
+        <v>9.5</v>
+      </c>
+      <c r="Y41">
+        <v>1.06</v>
+      </c>
+      <c r="Z41">
+        <v>2.16</v>
+      </c>
+      <c r="AA41">
+        <v>3.13</v>
+      </c>
+      <c r="AB41">
+        <v>3.47</v>
+      </c>
+      <c r="AC41">
+        <v>1.03</v>
+      </c>
+      <c r="AD41">
+        <v>7.3</v>
+      </c>
+      <c r="AE41">
+        <v>1.38</v>
+      </c>
+      <c r="AF41">
+        <v>2.62</v>
+      </c>
+      <c r="AG41">
+        <v>2.2</v>
+      </c>
+      <c r="AH41">
+        <v>1.55</v>
+      </c>
+      <c r="AI41">
+        <v>1.95</v>
+      </c>
+      <c r="AJ41">
+        <v>1.75</v>
+      </c>
+      <c r="AK41">
+        <v>1.3</v>
+      </c>
+      <c r="AL41">
+        <v>1.36</v>
+      </c>
+      <c r="AM41">
+        <v>1.67</v>
+      </c>
+      <c r="AN41">
+        <v>2</v>
+      </c>
+      <c r="AO41">
+        <v>0</v>
+      </c>
+      <c r="AP41">
+        <v>1.67</v>
+      </c>
+      <c r="AQ41">
+        <v>0.5</v>
+      </c>
+      <c r="AR41">
+        <v>1.46</v>
+      </c>
+      <c r="AS41">
+        <v>1.52</v>
+      </c>
+      <c r="AT41">
+        <v>2.98</v>
+      </c>
+      <c r="AU41">
+        <v>0</v>
+      </c>
+      <c r="AV41">
+        <v>5</v>
+      </c>
+      <c r="AW41">
+        <v>3</v>
+      </c>
+      <c r="AX41">
+        <v>3</v>
+      </c>
+      <c r="AY41">
+        <v>3</v>
+      </c>
+      <c r="AZ41">
+        <v>8</v>
+      </c>
+      <c r="BA41">
+        <v>1</v>
+      </c>
+      <c r="BB41">
+        <v>7</v>
+      </c>
+      <c r="BC41">
+        <v>8</v>
+      </c>
+      <c r="BD41">
+        <v>1.51</v>
+      </c>
+      <c r="BE41">
+        <v>8.5</v>
+      </c>
+      <c r="BF41">
+        <v>3.16</v>
+      </c>
+      <c r="BG41">
+        <v>1.28</v>
+      </c>
+      <c r="BH41">
+        <v>3.25</v>
+      </c>
+      <c r="BI41">
+        <v>1.52</v>
+      </c>
+      <c r="BJ41">
+        <v>2.37</v>
+      </c>
+      <c r="BK41">
+        <v>1.87</v>
+      </c>
+      <c r="BL41">
+        <v>1.87</v>
+      </c>
+      <c r="BM41">
+        <v>2.38</v>
+      </c>
+      <c r="BN41">
+        <v>1.54</v>
+      </c>
+      <c r="BO41">
+        <v>3.12</v>
+      </c>
+      <c r="BP41">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="146">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -376,6 +376,18 @@
     <t>['33', '75', '81']</t>
   </si>
   <si>
+    <t>['16', '40']</t>
+  </si>
+  <si>
+    <t>['43', '75']</t>
+  </si>
+  <si>
+    <t>['39']</t>
+  </si>
+  <si>
+    <t>['70']</t>
+  </si>
+  <si>
     <t>['31', '60']</t>
   </si>
   <si>
@@ -437,6 +449,9 @@
   </si>
   <si>
     <t>['22', '39', '90+6']</t>
+  </si>
+  <si>
+    <t>['15', '23', '48']</t>
   </si>
 </sst>
 </file>
@@ -798,7 +813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP41"/>
+  <dimension ref="A1:BP46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1054,7 +1069,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="Q2">
         <v>3.6</v>
@@ -1260,7 +1275,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="Q3">
         <v>3.75</v>
@@ -1672,7 +1687,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -1878,7 +1893,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="Q6">
         <v>4.1</v>
@@ -1956,10 +1971,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ6">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2084,7 +2099,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="Q7">
         <v>2.88</v>
@@ -2162,7 +2177,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ7">
         <v>1.5</v>
@@ -2290,7 +2305,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="Q8">
         <v>2.28</v>
@@ -2496,7 +2511,7 @@
         <v>90</v>
       </c>
       <c r="P9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -2702,7 +2717,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -2989,7 +3004,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3732,7 +3747,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="Q15">
         <v>4.1</v>
@@ -4019,7 +4034,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4843,7 +4858,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ20">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR20">
         <v>1.61</v>
@@ -4968,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="Q21">
         <v>4.4</v>
@@ -5380,7 +5395,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5458,7 +5473,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ23">
         <v>3</v>
@@ -5792,7 +5807,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -5998,7 +6013,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="Q26">
         <v>3.95</v>
@@ -6076,7 +6091,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ26">
         <v>1.5</v>
@@ -6204,7 +6219,7 @@
         <v>90</v>
       </c>
       <c r="P27" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="Q27">
         <v>3.2</v>
@@ -6285,7 +6300,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ27">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AR27">
         <v>1.59</v>
@@ -6410,7 +6425,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="Q28">
         <v>3.35</v>
@@ -6491,7 +6506,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ28">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AR28">
         <v>2.36</v>
@@ -6822,7 +6837,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="Q30">
         <v>2.38</v>
@@ -7109,7 +7124,7 @@
         <v>2</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AR31">
         <v>1.27</v>
@@ -7234,7 +7249,7 @@
         <v>113</v>
       </c>
       <c r="P32" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="Q32">
         <v>3.45</v>
@@ -7440,7 +7455,7 @@
         <v>114</v>
       </c>
       <c r="P33" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -7646,7 +7661,7 @@
         <v>115</v>
       </c>
       <c r="P34" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -7852,7 +7867,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="Q35">
         <v>3.4</v>
@@ -8058,7 +8073,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="Q36">
         <v>2.8</v>
@@ -8470,7 +8485,7 @@
         <v>118</v>
       </c>
       <c r="P38" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="Q38">
         <v>2.6</v>
@@ -8676,7 +8691,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="Q39">
         <v>4</v>
@@ -9245,6 +9260,1036 @@
       </c>
       <c r="BP41">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:68">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>7778529</v>
+      </c>
+      <c r="C42" t="s">
+        <v>68</v>
+      </c>
+      <c r="D42" t="s">
+        <v>69</v>
+      </c>
+      <c r="E42" s="2">
+        <v>45731.04166666666</v>
+      </c>
+      <c r="F42">
+        <v>5</v>
+      </c>
+      <c r="G42" t="s">
+        <v>89</v>
+      </c>
+      <c r="H42" t="s">
+        <v>87</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>2</v>
+      </c>
+      <c r="K42">
+        <v>2</v>
+      </c>
+      <c r="L42">
+        <v>1</v>
+      </c>
+      <c r="M42">
+        <v>3</v>
+      </c>
+      <c r="N42">
+        <v>4</v>
+      </c>
+      <c r="O42" t="s">
+        <v>92</v>
+      </c>
+      <c r="P42" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q42">
+        <v>3</v>
+      </c>
+      <c r="R42">
+        <v>2.1</v>
+      </c>
+      <c r="S42">
+        <v>3.75</v>
+      </c>
+      <c r="T42">
+        <v>1.44</v>
+      </c>
+      <c r="U42">
+        <v>2.63</v>
+      </c>
+      <c r="V42">
+        <v>3.25</v>
+      </c>
+      <c r="W42">
+        <v>1.33</v>
+      </c>
+      <c r="X42">
+        <v>9</v>
+      </c>
+      <c r="Y42">
+        <v>1.07</v>
+      </c>
+      <c r="Z42">
+        <v>2.65</v>
+      </c>
+      <c r="AA42">
+        <v>3.17</v>
+      </c>
+      <c r="AB42">
+        <v>2.65</v>
+      </c>
+      <c r="AC42">
+        <v>1.06</v>
+      </c>
+      <c r="AD42">
+        <v>8</v>
+      </c>
+      <c r="AE42">
+        <v>1.33</v>
+      </c>
+      <c r="AF42">
+        <v>3.1</v>
+      </c>
+      <c r="AG42">
+        <v>2</v>
+      </c>
+      <c r="AH42">
+        <v>1.75</v>
+      </c>
+      <c r="AI42">
+        <v>1.8</v>
+      </c>
+      <c r="AJ42">
+        <v>1.91</v>
+      </c>
+      <c r="AK42">
+        <v>1.37</v>
+      </c>
+      <c r="AL42">
+        <v>1.32</v>
+      </c>
+      <c r="AM42">
+        <v>1.62</v>
+      </c>
+      <c r="AN42">
+        <v>0</v>
+      </c>
+      <c r="AO42">
+        <v>0</v>
+      </c>
+      <c r="AP42">
+        <v>0</v>
+      </c>
+      <c r="AQ42">
+        <v>0.75</v>
+      </c>
+      <c r="AR42">
+        <v>0</v>
+      </c>
+      <c r="AS42">
+        <v>1.08</v>
+      </c>
+      <c r="AT42">
+        <v>1.08</v>
+      </c>
+      <c r="AU42">
+        <v>6</v>
+      </c>
+      <c r="AV42">
+        <v>5</v>
+      </c>
+      <c r="AW42">
+        <v>8</v>
+      </c>
+      <c r="AX42">
+        <v>3</v>
+      </c>
+      <c r="AY42">
+        <v>14</v>
+      </c>
+      <c r="AZ42">
+        <v>8</v>
+      </c>
+      <c r="BA42">
+        <v>3</v>
+      </c>
+      <c r="BB42">
+        <v>4</v>
+      </c>
+      <c r="BC42">
+        <v>7</v>
+      </c>
+      <c r="BD42">
+        <v>1.85</v>
+      </c>
+      <c r="BE42">
+        <v>8.5</v>
+      </c>
+      <c r="BF42">
+        <v>2.15</v>
+      </c>
+      <c r="BG42">
+        <v>1.23</v>
+      </c>
+      <c r="BH42">
+        <v>3.42</v>
+      </c>
+      <c r="BI42">
+        <v>1.44</v>
+      </c>
+      <c r="BJ42">
+        <v>2.42</v>
+      </c>
+      <c r="BK42">
+        <v>1.85</v>
+      </c>
+      <c r="BL42">
+        <v>1.85</v>
+      </c>
+      <c r="BM42">
+        <v>2.3</v>
+      </c>
+      <c r="BN42">
+        <v>1.49</v>
+      </c>
+      <c r="BO42">
+        <v>3.08</v>
+      </c>
+      <c r="BP42">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="43" spans="1:68">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>7778533</v>
+      </c>
+      <c r="C43" t="s">
+        <v>68</v>
+      </c>
+      <c r="D43" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" s="2">
+        <v>45731.08333333334</v>
+      </c>
+      <c r="F43">
+        <v>5</v>
+      </c>
+      <c r="G43" t="s">
+        <v>74</v>
+      </c>
+      <c r="H43" t="s">
+        <v>70</v>
+      </c>
+      <c r="I43">
+        <v>2</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>2</v>
+      </c>
+      <c r="L43">
+        <v>2</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>2</v>
+      </c>
+      <c r="O43" t="s">
+        <v>120</v>
+      </c>
+      <c r="P43" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q43">
+        <v>3.75</v>
+      </c>
+      <c r="R43">
+        <v>2.1</v>
+      </c>
+      <c r="S43">
+        <v>2.88</v>
+      </c>
+      <c r="T43">
+        <v>1.4</v>
+      </c>
+      <c r="U43">
+        <v>2.75</v>
+      </c>
+      <c r="V43">
+        <v>3</v>
+      </c>
+      <c r="W43">
+        <v>1.36</v>
+      </c>
+      <c r="X43">
+        <v>9</v>
+      </c>
+      <c r="Y43">
+        <v>1.07</v>
+      </c>
+      <c r="Z43">
+        <v>2.8</v>
+      </c>
+      <c r="AA43">
+        <v>3.34</v>
+      </c>
+      <c r="AB43">
+        <v>2.42</v>
+      </c>
+      <c r="AC43">
+        <v>1.05</v>
+      </c>
+      <c r="AD43">
+        <v>8.5</v>
+      </c>
+      <c r="AE43">
+        <v>1.33</v>
+      </c>
+      <c r="AF43">
+        <v>3.2</v>
+      </c>
+      <c r="AG43">
+        <v>1.95</v>
+      </c>
+      <c r="AH43">
+        <v>1.79</v>
+      </c>
+      <c r="AI43">
+        <v>1.8</v>
+      </c>
+      <c r="AJ43">
+        <v>1.91</v>
+      </c>
+      <c r="AK43">
+        <v>1.64</v>
+      </c>
+      <c r="AL43">
+        <v>1.31</v>
+      </c>
+      <c r="AM43">
+        <v>1.37</v>
+      </c>
+      <c r="AN43">
+        <v>1.5</v>
+      </c>
+      <c r="AO43">
+        <v>1</v>
+      </c>
+      <c r="AP43">
+        <v>2</v>
+      </c>
+      <c r="AQ43">
+        <v>0.5</v>
+      </c>
+      <c r="AR43">
+        <v>1.09</v>
+      </c>
+      <c r="AS43">
+        <v>1</v>
+      </c>
+      <c r="AT43">
+        <v>2.09</v>
+      </c>
+      <c r="AU43">
+        <v>3</v>
+      </c>
+      <c r="AV43">
+        <v>0</v>
+      </c>
+      <c r="AW43">
+        <v>2</v>
+      </c>
+      <c r="AX43">
+        <v>2</v>
+      </c>
+      <c r="AY43">
+        <v>5</v>
+      </c>
+      <c r="AZ43">
+        <v>2</v>
+      </c>
+      <c r="BA43">
+        <v>6</v>
+      </c>
+      <c r="BB43">
+        <v>3</v>
+      </c>
+      <c r="BC43">
+        <v>9</v>
+      </c>
+      <c r="BD43">
+        <v>2.1</v>
+      </c>
+      <c r="BE43">
+        <v>8</v>
+      </c>
+      <c r="BF43">
+        <v>1.91</v>
+      </c>
+      <c r="BG43">
+        <v>1.23</v>
+      </c>
+      <c r="BH43">
+        <v>3.42</v>
+      </c>
+      <c r="BI43">
+        <v>1.52</v>
+      </c>
+      <c r="BJ43">
+        <v>2.48</v>
+      </c>
+      <c r="BK43">
+        <v>1.86</v>
+      </c>
+      <c r="BL43">
+        <v>1.93</v>
+      </c>
+      <c r="BM43">
+        <v>2.35</v>
+      </c>
+      <c r="BN43">
+        <v>1.57</v>
+      </c>
+      <c r="BO43">
+        <v>3.08</v>
+      </c>
+      <c r="BP43">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="44" spans="1:68">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>7778532</v>
+      </c>
+      <c r="C44" t="s">
+        <v>68</v>
+      </c>
+      <c r="D44" t="s">
+        <v>69</v>
+      </c>
+      <c r="E44" s="2">
+        <v>45731.08333333334</v>
+      </c>
+      <c r="F44">
+        <v>5</v>
+      </c>
+      <c r="G44" t="s">
+        <v>73</v>
+      </c>
+      <c r="H44" t="s">
+        <v>72</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>1</v>
+      </c>
+      <c r="L44">
+        <v>2</v>
+      </c>
+      <c r="M44">
+        <v>1</v>
+      </c>
+      <c r="N44">
+        <v>3</v>
+      </c>
+      <c r="O44" t="s">
+        <v>121</v>
+      </c>
+      <c r="P44" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q44">
+        <v>2.5</v>
+      </c>
+      <c r="R44">
+        <v>2.2</v>
+      </c>
+      <c r="S44">
+        <v>4.5</v>
+      </c>
+      <c r="T44">
+        <v>1.4</v>
+      </c>
+      <c r="U44">
+        <v>2.75</v>
+      </c>
+      <c r="V44">
+        <v>2.75</v>
+      </c>
+      <c r="W44">
+        <v>1.4</v>
+      </c>
+      <c r="X44">
+        <v>8</v>
+      </c>
+      <c r="Y44">
+        <v>1.08</v>
+      </c>
+      <c r="Z44">
+        <v>1.83</v>
+      </c>
+      <c r="AA44">
+        <v>3.59</v>
+      </c>
+      <c r="AB44">
+        <v>4.1</v>
+      </c>
+      <c r="AC44">
+        <v>1.06</v>
+      </c>
+      <c r="AD44">
+        <v>8</v>
+      </c>
+      <c r="AE44">
+        <v>1.33</v>
+      </c>
+      <c r="AF44">
+        <v>3.2</v>
+      </c>
+      <c r="AG44">
+        <v>2</v>
+      </c>
+      <c r="AH44">
+        <v>1.75</v>
+      </c>
+      <c r="AI44">
+        <v>1.8</v>
+      </c>
+      <c r="AJ44">
+        <v>1.91</v>
+      </c>
+      <c r="AK44">
+        <v>1.23</v>
+      </c>
+      <c r="AL44">
+        <v>1.29</v>
+      </c>
+      <c r="AM44">
+        <v>1.95</v>
+      </c>
+      <c r="AN44">
+        <v>3</v>
+      </c>
+      <c r="AO44">
+        <v>0</v>
+      </c>
+      <c r="AP44">
+        <v>3</v>
+      </c>
+      <c r="AQ44">
+        <v>0</v>
+      </c>
+      <c r="AR44">
+        <v>1.37</v>
+      </c>
+      <c r="AS44">
+        <v>1.06</v>
+      </c>
+      <c r="AT44">
+        <v>2.43</v>
+      </c>
+      <c r="AU44">
+        <v>3</v>
+      </c>
+      <c r="AV44">
+        <v>4</v>
+      </c>
+      <c r="AW44">
+        <v>6</v>
+      </c>
+      <c r="AX44">
+        <v>5</v>
+      </c>
+      <c r="AY44">
+        <v>9</v>
+      </c>
+      <c r="AZ44">
+        <v>9</v>
+      </c>
+      <c r="BA44">
+        <v>7</v>
+      </c>
+      <c r="BB44">
+        <v>3</v>
+      </c>
+      <c r="BC44">
+        <v>10</v>
+      </c>
+      <c r="BD44">
+        <v>1.55</v>
+      </c>
+      <c r="BE44">
+        <v>8.5</v>
+      </c>
+      <c r="BF44">
+        <v>2.75</v>
+      </c>
+      <c r="BG44">
+        <v>1.26</v>
+      </c>
+      <c r="BH44">
+        <v>3.22</v>
+      </c>
+      <c r="BI44">
+        <v>1.5</v>
+      </c>
+      <c r="BJ44">
+        <v>2.28</v>
+      </c>
+      <c r="BK44">
+        <v>1.85</v>
+      </c>
+      <c r="BL44">
+        <v>1.85</v>
+      </c>
+      <c r="BM44">
+        <v>2.42</v>
+      </c>
+      <c r="BN44">
+        <v>1.44</v>
+      </c>
+      <c r="BO44">
+        <v>3.28</v>
+      </c>
+      <c r="BP44">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:68">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>7778536</v>
+      </c>
+      <c r="C45" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" t="s">
+        <v>69</v>
+      </c>
+      <c r="E45" s="2">
+        <v>45731.08333333334</v>
+      </c>
+      <c r="F45">
+        <v>5</v>
+      </c>
+      <c r="G45" t="s">
+        <v>75</v>
+      </c>
+      <c r="H45" t="s">
+        <v>71</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>1</v>
+      </c>
+      <c r="L45">
+        <v>1</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>1</v>
+      </c>
+      <c r="O45" t="s">
+        <v>122</v>
+      </c>
+      <c r="P45" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q45">
+        <v>3</v>
+      </c>
+      <c r="R45">
+        <v>2.2</v>
+      </c>
+      <c r="S45">
+        <v>3.6</v>
+      </c>
+      <c r="T45">
+        <v>1.4</v>
+      </c>
+      <c r="U45">
+        <v>2.75</v>
+      </c>
+      <c r="V45">
+        <v>2.75</v>
+      </c>
+      <c r="W45">
+        <v>1.4</v>
+      </c>
+      <c r="X45">
+        <v>8</v>
+      </c>
+      <c r="Y45">
+        <v>1.08</v>
+      </c>
+      <c r="Z45">
+        <v>2.29</v>
+      </c>
+      <c r="AA45">
+        <v>3.38</v>
+      </c>
+      <c r="AB45">
+        <v>2.96</v>
+      </c>
+      <c r="AC45">
+        <v>1.05</v>
+      </c>
+      <c r="AD45">
+        <v>8.5</v>
+      </c>
+      <c r="AE45">
+        <v>1.28</v>
+      </c>
+      <c r="AF45">
+        <v>3.45</v>
+      </c>
+      <c r="AG45">
+        <v>1.87</v>
+      </c>
+      <c r="AH45">
+        <v>1.87</v>
+      </c>
+      <c r="AI45">
+        <v>1.73</v>
+      </c>
+      <c r="AJ45">
+        <v>2</v>
+      </c>
+      <c r="AK45">
+        <v>1.72</v>
+      </c>
+      <c r="AL45">
+        <v>1.28</v>
+      </c>
+      <c r="AM45">
+        <v>1.34</v>
+      </c>
+      <c r="AN45">
+        <v>0</v>
+      </c>
+      <c r="AO45">
+        <v>3</v>
+      </c>
+      <c r="AP45">
+        <v>1</v>
+      </c>
+      <c r="AQ45">
+        <v>1.5</v>
+      </c>
+      <c r="AR45">
+        <v>1.47</v>
+      </c>
+      <c r="AS45">
+        <v>1.75</v>
+      </c>
+      <c r="AT45">
+        <v>3.22</v>
+      </c>
+      <c r="AU45">
+        <v>3</v>
+      </c>
+      <c r="AV45">
+        <v>6</v>
+      </c>
+      <c r="AW45">
+        <v>4</v>
+      </c>
+      <c r="AX45">
+        <v>3</v>
+      </c>
+      <c r="AY45">
+        <v>7</v>
+      </c>
+      <c r="AZ45">
+        <v>9</v>
+      </c>
+      <c r="BA45">
+        <v>5</v>
+      </c>
+      <c r="BB45">
+        <v>4</v>
+      </c>
+      <c r="BC45">
+        <v>9</v>
+      </c>
+      <c r="BD45">
+        <v>1.95</v>
+      </c>
+      <c r="BE45">
+        <v>8</v>
+      </c>
+      <c r="BF45">
+        <v>2.05</v>
+      </c>
+      <c r="BG45">
+        <v>1.24</v>
+      </c>
+      <c r="BH45">
+        <v>3.34</v>
+      </c>
+      <c r="BI45">
+        <v>1.45</v>
+      </c>
+      <c r="BJ45">
+        <v>2.41</v>
+      </c>
+      <c r="BK45">
+        <v>1.85</v>
+      </c>
+      <c r="BL45">
+        <v>1.85</v>
+      </c>
+      <c r="BM45">
+        <v>2.3</v>
+      </c>
+      <c r="BN45">
+        <v>1.49</v>
+      </c>
+      <c r="BO45">
+        <v>3.08</v>
+      </c>
+      <c r="BP45">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="46" spans="1:68">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>7778537</v>
+      </c>
+      <c r="C46" t="s">
+        <v>68</v>
+      </c>
+      <c r="D46" t="s">
+        <v>69</v>
+      </c>
+      <c r="E46" s="2">
+        <v>45731.16666666666</v>
+      </c>
+      <c r="F46">
+        <v>5</v>
+      </c>
+      <c r="G46" t="s">
+        <v>76</v>
+      </c>
+      <c r="H46" t="s">
+        <v>83</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>1</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>1</v>
+      </c>
+      <c r="O46" t="s">
+        <v>123</v>
+      </c>
+      <c r="P46" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q46">
+        <v>2.88</v>
+      </c>
+      <c r="R46">
+        <v>2.05</v>
+      </c>
+      <c r="S46">
+        <v>4</v>
+      </c>
+      <c r="T46">
+        <v>1.44</v>
+      </c>
+      <c r="U46">
+        <v>2.63</v>
+      </c>
+      <c r="V46">
+        <v>3.4</v>
+      </c>
+      <c r="W46">
+        <v>1.3</v>
+      </c>
+      <c r="X46">
+        <v>10</v>
+      </c>
+      <c r="Y46">
+        <v>1.06</v>
+      </c>
+      <c r="Z46">
+        <v>2.14</v>
+      </c>
+      <c r="AA46">
+        <v>3.26</v>
+      </c>
+      <c r="AB46">
+        <v>3.37</v>
+      </c>
+      <c r="AC46">
+        <v>1.07</v>
+      </c>
+      <c r="AD46">
+        <v>7.5</v>
+      </c>
+      <c r="AE46">
+        <v>1.36</v>
+      </c>
+      <c r="AF46">
+        <v>3.09</v>
+      </c>
+      <c r="AG46">
+        <v>2.05</v>
+      </c>
+      <c r="AH46">
+        <v>1.61</v>
+      </c>
+      <c r="AI46">
+        <v>1.91</v>
+      </c>
+      <c r="AJ46">
+        <v>1.8</v>
+      </c>
+      <c r="AK46">
+        <v>1.32</v>
+      </c>
+      <c r="AL46">
+        <v>1.33</v>
+      </c>
+      <c r="AM46">
+        <v>1.69</v>
+      </c>
+      <c r="AN46">
+        <v>3</v>
+      </c>
+      <c r="AO46">
+        <v>2</v>
+      </c>
+      <c r="AP46">
+        <v>3</v>
+      </c>
+      <c r="AQ46">
+        <v>1.33</v>
+      </c>
+      <c r="AR46">
+        <v>2.49</v>
+      </c>
+      <c r="AS46">
+        <v>1.38</v>
+      </c>
+      <c r="AT46">
+        <v>3.87</v>
+      </c>
+      <c r="AU46">
+        <v>7</v>
+      </c>
+      <c r="AV46">
+        <v>5</v>
+      </c>
+      <c r="AW46">
+        <v>12</v>
+      </c>
+      <c r="AX46">
+        <v>6</v>
+      </c>
+      <c r="AY46">
+        <v>19</v>
+      </c>
+      <c r="AZ46">
+        <v>11</v>
+      </c>
+      <c r="BA46">
+        <v>3</v>
+      </c>
+      <c r="BB46">
+        <v>0</v>
+      </c>
+      <c r="BC46">
+        <v>3</v>
+      </c>
+      <c r="BD46">
+        <v>1.91</v>
+      </c>
+      <c r="BE46">
+        <v>8</v>
+      </c>
+      <c r="BF46">
+        <v>2.1</v>
+      </c>
+      <c r="BG46">
+        <v>1.26</v>
+      </c>
+      <c r="BH46">
+        <v>3.22</v>
+      </c>
+      <c r="BI46">
+        <v>1.56</v>
+      </c>
+      <c r="BJ46">
+        <v>2.35</v>
+      </c>
+      <c r="BK46">
+        <v>1.94</v>
+      </c>
+      <c r="BL46">
+        <v>1.85</v>
+      </c>
+      <c r="BM46">
+        <v>2.47</v>
+      </c>
+      <c r="BN46">
+        <v>1.51</v>
+      </c>
+      <c r="BO46">
+        <v>3.28</v>
+      </c>
+      <c r="BP46">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="152">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -388,6 +388,12 @@
     <t>['70']</t>
   </si>
   <si>
+    <t>['56', '60']</t>
+  </si>
+  <si>
+    <t>['21', '50', '56', '72', '89']</t>
+  </si>
+  <si>
     <t>['31', '60']</t>
   </si>
   <si>
@@ -452,6 +458,18 @@
   </si>
   <si>
     <t>['15', '23', '48']</t>
+  </si>
+  <si>
+    <t>['33', '82', '89']</t>
+  </si>
+  <si>
+    <t>['72', '90+3']</t>
+  </si>
+  <si>
+    <t>['56']</t>
+  </si>
+  <si>
+    <t>['8']</t>
   </si>
 </sst>
 </file>
@@ -813,7 +831,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP46"/>
+  <dimension ref="A1:BP51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1069,7 +1087,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q2">
         <v>3.6</v>
@@ -1275,7 +1293,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="Q3">
         <v>3.75</v>
@@ -1356,7 +1374,7 @@
         <v>3</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1687,7 +1705,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -1893,7 +1911,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Q6">
         <v>4.1</v>
@@ -2099,7 +2117,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="Q7">
         <v>2.88</v>
@@ -2180,7 +2198,7 @@
         <v>1</v>
       </c>
       <c r="AQ7">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2305,7 +2323,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="Q8">
         <v>2.28</v>
@@ -2511,7 +2529,7 @@
         <v>90</v>
       </c>
       <c r="P9" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -2592,7 +2610,7 @@
         <v>0</v>
       </c>
       <c r="AQ9">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2717,7 +2735,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -2795,7 +2813,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AQ10">
         <v>1.5</v>
@@ -3416,7 +3434,7 @@
         <v>3</v>
       </c>
       <c r="AQ13">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3747,7 +3765,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Q15">
         <v>4.1</v>
@@ -3825,7 +3843,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ15">
         <v>1</v>
@@ -4031,7 +4049,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ16">
         <v>0.75</v>
@@ -4240,7 +4258,7 @@
         <v>2</v>
       </c>
       <c r="AQ17">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4443,10 +4461,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -4649,7 +4667,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AQ19">
         <v>1</v>
@@ -4983,7 +5001,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q21">
         <v>4.4</v>
@@ -5270,7 +5288,7 @@
         <v>2</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5395,7 +5413,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5807,7 +5825,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -5888,7 +5906,7 @@
         <v>3</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AR25">
         <v>1.45</v>
@@ -6013,7 +6031,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="Q26">
         <v>3.95</v>
@@ -6219,7 +6237,7 @@
         <v>90</v>
       </c>
       <c r="P27" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="Q27">
         <v>3.2</v>
@@ -6297,7 +6315,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ27">
         <v>1.5</v>
@@ -6425,7 +6443,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="Q28">
         <v>3.35</v>
@@ -6837,7 +6855,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Q30">
         <v>2.38</v>
@@ -6915,10 +6933,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ30">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR30">
         <v>1.54</v>
@@ -7121,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ31">
         <v>0.75</v>
@@ -7249,7 +7267,7 @@
         <v>113</v>
       </c>
       <c r="P32" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Q32">
         <v>3.45</v>
@@ -7455,7 +7473,7 @@
         <v>114</v>
       </c>
       <c r="P33" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -7661,7 +7679,7 @@
         <v>115</v>
       </c>
       <c r="P34" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -7867,7 +7885,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q35">
         <v>3.4</v>
@@ -8073,7 +8091,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="Q36">
         <v>2.8</v>
@@ -8485,7 +8503,7 @@
         <v>118</v>
       </c>
       <c r="P38" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q38">
         <v>2.6</v>
@@ -8691,7 +8709,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="Q39">
         <v>4</v>
@@ -9309,7 +9327,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9721,7 +9739,7 @@
         <v>121</v>
       </c>
       <c r="P44" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10290,6 +10308,1036 @@
       </c>
       <c r="BP46">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:68">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>7778538</v>
+      </c>
+      <c r="C47" t="s">
+        <v>68</v>
+      </c>
+      <c r="D47" t="s">
+        <v>69</v>
+      </c>
+      <c r="E47" s="2">
+        <v>45732.04166666666</v>
+      </c>
+      <c r="F47">
+        <v>5</v>
+      </c>
+      <c r="G47" t="s">
+        <v>82</v>
+      </c>
+      <c r="H47" t="s">
+        <v>88</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>1</v>
+      </c>
+      <c r="K47">
+        <v>1</v>
+      </c>
+      <c r="L47">
+        <v>1</v>
+      </c>
+      <c r="M47">
+        <v>3</v>
+      </c>
+      <c r="N47">
+        <v>4</v>
+      </c>
+      <c r="O47" t="s">
+        <v>105</v>
+      </c>
+      <c r="P47" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q47">
+        <v>3</v>
+      </c>
+      <c r="R47">
+        <v>2.2</v>
+      </c>
+      <c r="S47">
+        <v>3.4</v>
+      </c>
+      <c r="T47">
+        <v>1.36</v>
+      </c>
+      <c r="U47">
+        <v>3</v>
+      </c>
+      <c r="V47">
+        <v>2.63</v>
+      </c>
+      <c r="W47">
+        <v>1.44</v>
+      </c>
+      <c r="X47">
+        <v>7</v>
+      </c>
+      <c r="Y47">
+        <v>1.1</v>
+      </c>
+      <c r="Z47">
+        <v>2.39</v>
+      </c>
+      <c r="AA47">
+        <v>3.41</v>
+      </c>
+      <c r="AB47">
+        <v>2.79</v>
+      </c>
+      <c r="AC47">
+        <v>1.05</v>
+      </c>
+      <c r="AD47">
+        <v>8.5</v>
+      </c>
+      <c r="AE47">
+        <v>1.25</v>
+      </c>
+      <c r="AF47">
+        <v>3.7</v>
+      </c>
+      <c r="AG47">
+        <v>1.77</v>
+      </c>
+      <c r="AH47">
+        <v>1.98</v>
+      </c>
+      <c r="AI47">
+        <v>1.62</v>
+      </c>
+      <c r="AJ47">
+        <v>2.2</v>
+      </c>
+      <c r="AK47">
+        <v>1.43</v>
+      </c>
+      <c r="AL47">
+        <v>1.31</v>
+      </c>
+      <c r="AM47">
+        <v>1.55</v>
+      </c>
+      <c r="AN47">
+        <v>1.5</v>
+      </c>
+      <c r="AO47">
+        <v>0</v>
+      </c>
+      <c r="AP47">
+        <v>1</v>
+      </c>
+      <c r="AQ47">
+        <v>0.75</v>
+      </c>
+      <c r="AR47">
+        <v>1.58</v>
+      </c>
+      <c r="AS47">
+        <v>1.2</v>
+      </c>
+      <c r="AT47">
+        <v>2.78</v>
+      </c>
+      <c r="AU47">
+        <v>3</v>
+      </c>
+      <c r="AV47">
+        <v>5</v>
+      </c>
+      <c r="AW47">
+        <v>4</v>
+      </c>
+      <c r="AX47">
+        <v>7</v>
+      </c>
+      <c r="AY47">
+        <v>7</v>
+      </c>
+      <c r="AZ47">
+        <v>12</v>
+      </c>
+      <c r="BA47">
+        <v>3</v>
+      </c>
+      <c r="BB47">
+        <v>2</v>
+      </c>
+      <c r="BC47">
+        <v>5</v>
+      </c>
+      <c r="BD47">
+        <v>1.57</v>
+      </c>
+      <c r="BE47">
+        <v>8.5</v>
+      </c>
+      <c r="BF47">
+        <v>2.7</v>
+      </c>
+      <c r="BG47">
+        <v>1.21</v>
+      </c>
+      <c r="BH47">
+        <v>3.78</v>
+      </c>
+      <c r="BI47">
+        <v>1.36</v>
+      </c>
+      <c r="BJ47">
+        <v>2.7</v>
+      </c>
+      <c r="BK47">
+        <v>1.69</v>
+      </c>
+      <c r="BL47">
+        <v>2.12</v>
+      </c>
+      <c r="BM47">
+        <v>2.12</v>
+      </c>
+      <c r="BN47">
+        <v>1.69</v>
+      </c>
+      <c r="BO47">
+        <v>2.7</v>
+      </c>
+      <c r="BP47">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="48" spans="1:68">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>7778530</v>
+      </c>
+      <c r="C48" t="s">
+        <v>68</v>
+      </c>
+      <c r="D48" t="s">
+        <v>69</v>
+      </c>
+      <c r="E48" s="2">
+        <v>45732.08333333334</v>
+      </c>
+      <c r="F48">
+        <v>5</v>
+      </c>
+      <c r="G48" t="s">
+        <v>84</v>
+      </c>
+      <c r="H48" t="s">
+        <v>85</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>2</v>
+      </c>
+      <c r="M48">
+        <v>2</v>
+      </c>
+      <c r="N48">
+        <v>4</v>
+      </c>
+      <c r="O48" t="s">
+        <v>124</v>
+      </c>
+      <c r="P48" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q48">
+        <v>3.6</v>
+      </c>
+      <c r="R48">
+        <v>2</v>
+      </c>
+      <c r="S48">
+        <v>3.4</v>
+      </c>
+      <c r="T48">
+        <v>1.5</v>
+      </c>
+      <c r="U48">
+        <v>2.5</v>
+      </c>
+      <c r="V48">
+        <v>3.5</v>
+      </c>
+      <c r="W48">
+        <v>1.29</v>
+      </c>
+      <c r="X48">
+        <v>10</v>
+      </c>
+      <c r="Y48">
+        <v>1.06</v>
+      </c>
+      <c r="Z48">
+        <v>2.77</v>
+      </c>
+      <c r="AA48">
+        <v>3.25</v>
+      </c>
+      <c r="AB48">
+        <v>2.49</v>
+      </c>
+      <c r="AC48">
+        <v>1.07</v>
+      </c>
+      <c r="AD48">
+        <v>7.5</v>
+      </c>
+      <c r="AE48">
+        <v>1.4</v>
+      </c>
+      <c r="AF48">
+        <v>2.8</v>
+      </c>
+      <c r="AG48">
+        <v>2.15</v>
+      </c>
+      <c r="AH48">
+        <v>1.57</v>
+      </c>
+      <c r="AI48">
+        <v>1.91</v>
+      </c>
+      <c r="AJ48">
+        <v>1.8</v>
+      </c>
+      <c r="AK48">
+        <v>1.52</v>
+      </c>
+      <c r="AL48">
+        <v>1.34</v>
+      </c>
+      <c r="AM48">
+        <v>1.42</v>
+      </c>
+      <c r="AN48">
+        <v>2</v>
+      </c>
+      <c r="AO48">
+        <v>1.5</v>
+      </c>
+      <c r="AP48">
+        <v>1.67</v>
+      </c>
+      <c r="AQ48">
+        <v>1.33</v>
+      </c>
+      <c r="AR48">
+        <v>1.52</v>
+      </c>
+      <c r="AS48">
+        <v>1.34</v>
+      </c>
+      <c r="AT48">
+        <v>2.86</v>
+      </c>
+      <c r="AU48">
+        <v>5</v>
+      </c>
+      <c r="AV48">
+        <v>9</v>
+      </c>
+      <c r="AW48">
+        <v>5</v>
+      </c>
+      <c r="AX48">
+        <v>10</v>
+      </c>
+      <c r="AY48">
+        <v>10</v>
+      </c>
+      <c r="AZ48">
+        <v>19</v>
+      </c>
+      <c r="BA48">
+        <v>5</v>
+      </c>
+      <c r="BB48">
+        <v>8</v>
+      </c>
+      <c r="BC48">
+        <v>13</v>
+      </c>
+      <c r="BD48">
+        <v>1.85</v>
+      </c>
+      <c r="BE48">
+        <v>8</v>
+      </c>
+      <c r="BF48">
+        <v>2.15</v>
+      </c>
+      <c r="BG48">
+        <v>1.36</v>
+      </c>
+      <c r="BH48">
+        <v>2.7</v>
+      </c>
+      <c r="BI48">
+        <v>1.74</v>
+      </c>
+      <c r="BJ48">
+        <v>2.06</v>
+      </c>
+      <c r="BK48">
+        <v>2.2</v>
+      </c>
+      <c r="BL48">
+        <v>1.64</v>
+      </c>
+      <c r="BM48">
+        <v>2.88</v>
+      </c>
+      <c r="BN48">
+        <v>1.32</v>
+      </c>
+      <c r="BO48">
+        <v>3.82</v>
+      </c>
+      <c r="BP48">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:68">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>7778534</v>
+      </c>
+      <c r="C49" t="s">
+        <v>68</v>
+      </c>
+      <c r="D49" t="s">
+        <v>69</v>
+      </c>
+      <c r="E49" s="2">
+        <v>45732.08333333334</v>
+      </c>
+      <c r="F49">
+        <v>5</v>
+      </c>
+      <c r="G49" t="s">
+        <v>81</v>
+      </c>
+      <c r="H49" t="s">
+        <v>79</v>
+      </c>
+      <c r="I49">
+        <v>1</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>1</v>
+      </c>
+      <c r="L49">
+        <v>1</v>
+      </c>
+      <c r="M49">
+        <v>1</v>
+      </c>
+      <c r="N49">
+        <v>2</v>
+      </c>
+      <c r="O49" t="s">
+        <v>116</v>
+      </c>
+      <c r="P49" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q49">
+        <v>3.6</v>
+      </c>
+      <c r="R49">
+        <v>1.91</v>
+      </c>
+      <c r="S49">
+        <v>3.6</v>
+      </c>
+      <c r="T49">
+        <v>1.57</v>
+      </c>
+      <c r="U49">
+        <v>2.25</v>
+      </c>
+      <c r="V49">
+        <v>4</v>
+      </c>
+      <c r="W49">
+        <v>1.22</v>
+      </c>
+      <c r="X49">
+        <v>13</v>
+      </c>
+      <c r="Y49">
+        <v>1.04</v>
+      </c>
+      <c r="Z49">
+        <v>2.64</v>
+      </c>
+      <c r="AA49">
+        <v>3.15</v>
+      </c>
+      <c r="AB49">
+        <v>2.68</v>
+      </c>
+      <c r="AC49">
+        <v>1.09</v>
+      </c>
+      <c r="AD49">
+        <v>6.5</v>
+      </c>
+      <c r="AE49">
+        <v>1.48</v>
+      </c>
+      <c r="AF49">
+        <v>2.37</v>
+      </c>
+      <c r="AG49">
+        <v>2.52</v>
+      </c>
+      <c r="AH49">
+        <v>1.46</v>
+      </c>
+      <c r="AI49">
+        <v>2.2</v>
+      </c>
+      <c r="AJ49">
+        <v>1.62</v>
+      </c>
+      <c r="AK49">
+        <v>1.44</v>
+      </c>
+      <c r="AL49">
+        <v>1.37</v>
+      </c>
+      <c r="AM49">
+        <v>1.43</v>
+      </c>
+      <c r="AN49">
+        <v>2</v>
+      </c>
+      <c r="AO49">
+        <v>0</v>
+      </c>
+      <c r="AP49">
+        <v>1.67</v>
+      </c>
+      <c r="AQ49">
+        <v>0.5</v>
+      </c>
+      <c r="AR49">
+        <v>1.15</v>
+      </c>
+      <c r="AS49">
+        <v>1.34</v>
+      </c>
+      <c r="AT49">
+        <v>2.49</v>
+      </c>
+      <c r="AU49">
+        <v>3</v>
+      </c>
+      <c r="AV49">
+        <v>3</v>
+      </c>
+      <c r="AW49">
+        <v>1</v>
+      </c>
+      <c r="AX49">
+        <v>1</v>
+      </c>
+      <c r="AY49">
+        <v>4</v>
+      </c>
+      <c r="AZ49">
+        <v>4</v>
+      </c>
+      <c r="BA49">
+        <v>7</v>
+      </c>
+      <c r="BB49">
+        <v>3</v>
+      </c>
+      <c r="BC49">
+        <v>10</v>
+      </c>
+      <c r="BD49">
+        <v>2.1</v>
+      </c>
+      <c r="BE49">
+        <v>8</v>
+      </c>
+      <c r="BF49">
+        <v>1.91</v>
+      </c>
+      <c r="BG49">
+        <v>1.3</v>
+      </c>
+      <c r="BH49">
+        <v>2.97</v>
+      </c>
+      <c r="BI49">
+        <v>1.66</v>
+      </c>
+      <c r="BJ49">
+        <v>2.17</v>
+      </c>
+      <c r="BK49">
+        <v>2.08</v>
+      </c>
+      <c r="BL49">
+        <v>1.72</v>
+      </c>
+      <c r="BM49">
+        <v>2.59</v>
+      </c>
+      <c r="BN49">
+        <v>1.39</v>
+      </c>
+      <c r="BO49">
+        <v>3.58</v>
+      </c>
+      <c r="BP49">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="50" spans="1:68">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>7778535</v>
+      </c>
+      <c r="C50" t="s">
+        <v>68</v>
+      </c>
+      <c r="D50" t="s">
+        <v>69</v>
+      </c>
+      <c r="E50" s="2">
+        <v>45732.08333333334</v>
+      </c>
+      <c r="F50">
+        <v>5</v>
+      </c>
+      <c r="G50" t="s">
+        <v>78</v>
+      </c>
+      <c r="H50" t="s">
+        <v>86</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50" t="s">
+        <v>90</v>
+      </c>
+      <c r="P50" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q50">
+        <v>2.75</v>
+      </c>
+      <c r="R50">
+        <v>2.05</v>
+      </c>
+      <c r="S50">
+        <v>4.33</v>
+      </c>
+      <c r="T50">
+        <v>1.5</v>
+      </c>
+      <c r="U50">
+        <v>2.5</v>
+      </c>
+      <c r="V50">
+        <v>3.4</v>
+      </c>
+      <c r="W50">
+        <v>1.3</v>
+      </c>
+      <c r="X50">
+        <v>10</v>
+      </c>
+      <c r="Y50">
+        <v>1.06</v>
+      </c>
+      <c r="Z50">
+        <v>2.29</v>
+      </c>
+      <c r="AA50">
+        <v>3.38</v>
+      </c>
+      <c r="AB50">
+        <v>2.96</v>
+      </c>
+      <c r="AC50">
+        <v>1.07</v>
+      </c>
+      <c r="AD50">
+        <v>7.5</v>
+      </c>
+      <c r="AE50">
+        <v>1.42</v>
+      </c>
+      <c r="AF50">
+        <v>2.75</v>
+      </c>
+      <c r="AG50">
+        <v>1.92</v>
+      </c>
+      <c r="AH50">
+        <v>1.82</v>
+      </c>
+      <c r="AI50">
+        <v>1.91</v>
+      </c>
+      <c r="AJ50">
+        <v>1.8</v>
+      </c>
+      <c r="AK50">
+        <v>1.27</v>
+      </c>
+      <c r="AL50">
+        <v>1.35</v>
+      </c>
+      <c r="AM50">
+        <v>1.74</v>
+      </c>
+      <c r="AN50">
+        <v>0.5</v>
+      </c>
+      <c r="AO50">
+        <v>1.5</v>
+      </c>
+      <c r="AP50">
+        <v>0.67</v>
+      </c>
+      <c r="AQ50">
+        <v>1.33</v>
+      </c>
+      <c r="AR50">
+        <v>1.08</v>
+      </c>
+      <c r="AS50">
+        <v>1.15</v>
+      </c>
+      <c r="AT50">
+        <v>2.23</v>
+      </c>
+      <c r="AU50">
+        <v>4</v>
+      </c>
+      <c r="AV50">
+        <v>2</v>
+      </c>
+      <c r="AW50">
+        <v>7</v>
+      </c>
+      <c r="AX50">
+        <v>12</v>
+      </c>
+      <c r="AY50">
+        <v>11</v>
+      </c>
+      <c r="AZ50">
+        <v>14</v>
+      </c>
+      <c r="BA50">
+        <v>8</v>
+      </c>
+      <c r="BB50">
+        <v>2</v>
+      </c>
+      <c r="BC50">
+        <v>10</v>
+      </c>
+      <c r="BD50">
+        <v>1.62</v>
+      </c>
+      <c r="BE50">
+        <v>8.5</v>
+      </c>
+      <c r="BF50">
+        <v>2.6</v>
+      </c>
+      <c r="BG50">
+        <v>1.27</v>
+      </c>
+      <c r="BH50">
+        <v>3.14</v>
+      </c>
+      <c r="BI50">
+        <v>1.52</v>
+      </c>
+      <c r="BJ50">
+        <v>2.24</v>
+      </c>
+      <c r="BK50">
+        <v>1.91</v>
+      </c>
+      <c r="BL50">
+        <v>1.8</v>
+      </c>
+      <c r="BM50">
+        <v>2.46</v>
+      </c>
+      <c r="BN50">
+        <v>1.43</v>
+      </c>
+      <c r="BO50">
+        <v>3.34</v>
+      </c>
+      <c r="BP50">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="51" spans="1:68">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>7778531</v>
+      </c>
+      <c r="C51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E51" s="2">
+        <v>45732.08333333334</v>
+      </c>
+      <c r="F51">
+        <v>5</v>
+      </c>
+      <c r="G51" t="s">
+        <v>80</v>
+      </c>
+      <c r="H51" t="s">
+        <v>77</v>
+      </c>
+      <c r="I51">
+        <v>1</v>
+      </c>
+      <c r="J51">
+        <v>1</v>
+      </c>
+      <c r="K51">
+        <v>2</v>
+      </c>
+      <c r="L51">
+        <v>5</v>
+      </c>
+      <c r="M51">
+        <v>1</v>
+      </c>
+      <c r="N51">
+        <v>6</v>
+      </c>
+      <c r="O51" t="s">
+        <v>125</v>
+      </c>
+      <c r="P51" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q51">
+        <v>1.91</v>
+      </c>
+      <c r="R51">
+        <v>2.5</v>
+      </c>
+      <c r="S51">
+        <v>6.5</v>
+      </c>
+      <c r="T51">
+        <v>1.3</v>
+      </c>
+      <c r="U51">
+        <v>3.4</v>
+      </c>
+      <c r="V51">
+        <v>2.5</v>
+      </c>
+      <c r="W51">
+        <v>1.5</v>
+      </c>
+      <c r="X51">
+        <v>6</v>
+      </c>
+      <c r="Y51">
+        <v>1.13</v>
+      </c>
+      <c r="Z51">
+        <v>1.46</v>
+      </c>
+      <c r="AA51">
+        <v>4.5</v>
+      </c>
+      <c r="AB51">
+        <v>6.2</v>
+      </c>
+      <c r="AC51">
+        <v>1.03</v>
+      </c>
+      <c r="AD51">
+        <v>10</v>
+      </c>
+      <c r="AE51">
+        <v>1.2</v>
+      </c>
+      <c r="AF51">
+        <v>4.33</v>
+      </c>
+      <c r="AG51">
+        <v>1.6</v>
+      </c>
+      <c r="AH51">
+        <v>2.15</v>
+      </c>
+      <c r="AI51">
+        <v>1.83</v>
+      </c>
+      <c r="AJ51">
+        <v>1.83</v>
+      </c>
+      <c r="AK51">
+        <v>1.11</v>
+      </c>
+      <c r="AL51">
+        <v>1.18</v>
+      </c>
+      <c r="AM51">
+        <v>2.75</v>
+      </c>
+      <c r="AN51">
+        <v>3</v>
+      </c>
+      <c r="AO51">
+        <v>1</v>
+      </c>
+      <c r="AP51">
+        <v>3</v>
+      </c>
+      <c r="AQ51">
+        <v>0.5</v>
+      </c>
+      <c r="AR51">
+        <v>1.69</v>
+      </c>
+      <c r="AS51">
+        <v>0.74</v>
+      </c>
+      <c r="AT51">
+        <v>2.43</v>
+      </c>
+      <c r="AU51">
+        <v>7</v>
+      </c>
+      <c r="AV51">
+        <v>7</v>
+      </c>
+      <c r="AW51">
+        <v>9</v>
+      </c>
+      <c r="AX51">
+        <v>4</v>
+      </c>
+      <c r="AY51">
+        <v>16</v>
+      </c>
+      <c r="AZ51">
+        <v>11</v>
+      </c>
+      <c r="BA51">
+        <v>9</v>
+      </c>
+      <c r="BB51">
+        <v>3</v>
+      </c>
+      <c r="BC51">
+        <v>12</v>
+      </c>
+      <c r="BD51">
+        <v>1.18</v>
+      </c>
+      <c r="BE51">
+        <v>11</v>
+      </c>
+      <c r="BF51">
+        <v>5.5</v>
+      </c>
+      <c r="BG51">
+        <v>1.19</v>
+      </c>
+      <c r="BH51">
+        <v>3.82</v>
+      </c>
+      <c r="BI51">
+        <v>1.38</v>
+      </c>
+      <c r="BJ51">
+        <v>2.62</v>
+      </c>
+      <c r="BK51">
+        <v>1.71</v>
+      </c>
+      <c r="BL51">
+        <v>2.09</v>
+      </c>
+      <c r="BM51">
+        <v>2.12</v>
+      </c>
+      <c r="BN51">
+        <v>1.69</v>
+      </c>
+      <c r="BO51">
+        <v>2.55</v>
+      </c>
+      <c r="BP51">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -10677,10 +10677,10 @@
         <v>5</v>
       </c>
       <c r="BB48">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC48">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD48">
         <v>1.85</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="164">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -394,6 +394,27 @@
     <t>['21', '50', '56', '72', '89']</t>
   </si>
   <si>
+    <t>['67', '87']</t>
+  </si>
+  <si>
+    <t>['19', '52', '62', '89', '90+4']</t>
+  </si>
+  <si>
+    <t>['16']</t>
+  </si>
+  <si>
+    <t>['9']</t>
+  </si>
+  <si>
+    <t>['80', '83']</t>
+  </si>
+  <si>
+    <t>['88']</t>
+  </si>
+  <si>
+    <t>['1']</t>
+  </si>
+  <si>
     <t>['31', '60']</t>
   </si>
   <si>
@@ -470,6 +491,21 @@
   </si>
   <si>
     <t>['8']</t>
+  </si>
+  <si>
+    <t>['23', '38', '88']</t>
+  </si>
+  <si>
+    <t>['43']</t>
+  </si>
+  <si>
+    <t>['36', '82']</t>
+  </si>
+  <si>
+    <t>['90+4']</t>
+  </si>
+  <si>
+    <t>['58', '90+4']</t>
   </si>
 </sst>
 </file>
@@ -831,7 +867,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP51"/>
+  <dimension ref="A1:BP61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1087,7 +1123,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="Q2">
         <v>3.6</v>
@@ -1165,7 +1201,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AQ2">
         <v>3</v>
@@ -1293,7 +1329,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="Q3">
         <v>3.75</v>
@@ -1577,7 +1613,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ4">
         <v>0</v>
@@ -1705,7 +1741,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -1786,7 +1822,7 @@
         <v>3</v>
       </c>
       <c r="AQ5">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1911,7 +1947,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="Q6">
         <v>4.1</v>
@@ -1992,7 +2028,7 @@
         <v>2</v>
       </c>
       <c r="AQ6">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2117,7 +2153,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="Q7">
         <v>2.88</v>
@@ -2195,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ7">
         <v>1.33</v>
@@ -2323,7 +2359,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="Q8">
         <v>2.28</v>
@@ -2404,7 +2440,7 @@
         <v>3</v>
       </c>
       <c r="AQ8">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2529,7 +2565,7 @@
         <v>90</v>
       </c>
       <c r="P9" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -2610,7 +2646,7 @@
         <v>0</v>
       </c>
       <c r="AQ9">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2735,7 +2771,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -2816,7 +2852,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ10">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3019,10 +3055,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ11">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3434,7 +3470,7 @@
         <v>3</v>
       </c>
       <c r="AQ13">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3765,7 +3801,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="Q15">
         <v>4.1</v>
@@ -3843,7 +3879,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ15">
         <v>1</v>
@@ -4052,7 +4088,7 @@
         <v>1</v>
       </c>
       <c r="AQ16">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4873,7 +4909,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ20">
         <v>0.5</v>
@@ -5001,7 +5037,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="Q21">
         <v>4.4</v>
@@ -5082,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="AQ21">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AR21">
         <v>1.32</v>
@@ -5285,7 +5321,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ22">
         <v>0.5</v>
@@ -5413,7 +5449,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5491,7 +5527,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ23">
         <v>3</v>
@@ -5700,7 +5736,7 @@
         <v>3</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR24">
         <v>3.04</v>
@@ -5825,7 +5861,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -6031,7 +6067,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="Q26">
         <v>3.95</v>
@@ -6112,7 +6148,7 @@
         <v>2</v>
       </c>
       <c r="AQ26">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AR26">
         <v>0.85</v>
@@ -6237,7 +6273,7 @@
         <v>90</v>
       </c>
       <c r="P27" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="Q27">
         <v>3.2</v>
@@ -6443,7 +6479,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="Q28">
         <v>3.35</v>
@@ -6521,10 +6557,10 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AQ28">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR28">
         <v>2.36</v>
@@ -6855,7 +6891,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="Q30">
         <v>2.38</v>
@@ -7139,10 +7175,10 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ31">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AR31">
         <v>1.27</v>
@@ -7267,7 +7303,7 @@
         <v>113</v>
       </c>
       <c r="P32" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="Q32">
         <v>3.45</v>
@@ -7345,7 +7381,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ32">
         <v>1</v>
@@ -7473,7 +7509,7 @@
         <v>114</v>
       </c>
       <c r="P33" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -7679,7 +7715,7 @@
         <v>115</v>
       </c>
       <c r="P34" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -7885,7 +7921,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="Q35">
         <v>3.4</v>
@@ -8091,7 +8127,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="Q36">
         <v>2.8</v>
@@ -8169,10 +8205,10 @@
         <v>2</v>
       </c>
       <c r="AP36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ36">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AR36">
         <v>0</v>
@@ -8375,7 +8411,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AQ37">
         <v>0.5</v>
@@ -8503,7 +8539,7 @@
         <v>118</v>
       </c>
       <c r="P38" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="Q38">
         <v>2.6</v>
@@ -8581,7 +8617,7 @@
         <v>1</v>
       </c>
       <c r="AP38">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ38">
         <v>1</v>
@@ -8709,7 +8745,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="Q39">
         <v>4</v>
@@ -8790,7 +8826,7 @@
         <v>3</v>
       </c>
       <c r="AQ39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR39">
         <v>1.33</v>
@@ -8996,7 +9032,7 @@
         <v>2</v>
       </c>
       <c r="AQ40">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR40">
         <v>1.47</v>
@@ -9199,10 +9235,10 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ41">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR41">
         <v>1.46</v>
@@ -9327,7 +9363,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9408,7 +9444,7 @@
         <v>0</v>
       </c>
       <c r="AQ42">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AR42">
         <v>0</v>
@@ -9739,7 +9775,7 @@
         <v>121</v>
       </c>
       <c r="P44" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10023,7 +10059,7 @@
         <v>3</v>
       </c>
       <c r="AP45">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ45">
         <v>1.5</v>
@@ -10232,7 +10268,7 @@
         <v>3</v>
       </c>
       <c r="AQ46">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR46">
         <v>2.49</v>
@@ -10357,7 +10393,7 @@
         <v>105</v>
       </c>
       <c r="P47" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10563,7 +10599,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="Q48">
         <v>3.6</v>
@@ -10769,7 +10805,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="Q49">
         <v>3.6</v>
@@ -10847,7 +10883,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ49">
         <v>0.5</v>
@@ -11056,7 +11092,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ50">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR50">
         <v>1.08</v>
@@ -11181,7 +11217,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="Q51">
         <v>1.91</v>
@@ -11338,6 +11374,2066 @@
       </c>
       <c r="BP51">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="52" spans="1:68">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>7778539</v>
+      </c>
+      <c r="C52" t="s">
+        <v>68</v>
+      </c>
+      <c r="D52" t="s">
+        <v>69</v>
+      </c>
+      <c r="E52" s="2">
+        <v>45739.04166666666</v>
+      </c>
+      <c r="F52">
+        <v>6</v>
+      </c>
+      <c r="G52" t="s">
+        <v>85</v>
+      </c>
+      <c r="H52" t="s">
+        <v>73</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>2</v>
+      </c>
+      <c r="K52">
+        <v>2</v>
+      </c>
+      <c r="L52">
+        <v>2</v>
+      </c>
+      <c r="M52">
+        <v>3</v>
+      </c>
+      <c r="N52">
+        <v>5</v>
+      </c>
+      <c r="O52" t="s">
+        <v>126</v>
+      </c>
+      <c r="P52" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q52">
+        <v>3.25</v>
+      </c>
+      <c r="R52">
+        <v>2</v>
+      </c>
+      <c r="S52">
+        <v>3.75</v>
+      </c>
+      <c r="T52">
+        <v>1.53</v>
+      </c>
+      <c r="U52">
+        <v>2.38</v>
+      </c>
+      <c r="V52">
+        <v>3.5</v>
+      </c>
+      <c r="W52">
+        <v>1.29</v>
+      </c>
+      <c r="X52">
+        <v>11</v>
+      </c>
+      <c r="Y52">
+        <v>1.05</v>
+      </c>
+      <c r="Z52">
+        <v>2.49</v>
+      </c>
+      <c r="AA52">
+        <v>3.12</v>
+      </c>
+      <c r="AB52">
+        <v>2.88</v>
+      </c>
+      <c r="AC52">
+        <v>1.04</v>
+      </c>
+      <c r="AD52">
+        <v>7.1</v>
+      </c>
+      <c r="AE52">
+        <v>1.39</v>
+      </c>
+      <c r="AF52">
+        <v>2.59</v>
+      </c>
+      <c r="AG52">
+        <v>2.2</v>
+      </c>
+      <c r="AH52">
+        <v>1.55</v>
+      </c>
+      <c r="AI52">
+        <v>2</v>
+      </c>
+      <c r="AJ52">
+        <v>1.73</v>
+      </c>
+      <c r="AK52">
+        <v>1.36</v>
+      </c>
+      <c r="AL52">
+        <v>1.36</v>
+      </c>
+      <c r="AM52">
+        <v>1.53</v>
+      </c>
+      <c r="AN52">
+        <v>2</v>
+      </c>
+      <c r="AO52">
+        <v>0</v>
+      </c>
+      <c r="AP52">
+        <v>1.33</v>
+      </c>
+      <c r="AQ52">
+        <v>1</v>
+      </c>
+      <c r="AR52">
+        <v>1.25</v>
+      </c>
+      <c r="AS52">
+        <v>0.99</v>
+      </c>
+      <c r="AT52">
+        <v>2.24</v>
+      </c>
+      <c r="AU52">
+        <v>7</v>
+      </c>
+      <c r="AV52">
+        <v>4</v>
+      </c>
+      <c r="AW52">
+        <v>11</v>
+      </c>
+      <c r="AX52">
+        <v>4</v>
+      </c>
+      <c r="AY52">
+        <v>18</v>
+      </c>
+      <c r="AZ52">
+        <v>8</v>
+      </c>
+      <c r="BA52">
+        <v>10</v>
+      </c>
+      <c r="BB52">
+        <v>5</v>
+      </c>
+      <c r="BC52">
+        <v>15</v>
+      </c>
+      <c r="BD52">
+        <v>1.79</v>
+      </c>
+      <c r="BE52">
+        <v>6.2</v>
+      </c>
+      <c r="BF52">
+        <v>2.51</v>
+      </c>
+      <c r="BG52">
+        <v>1.32</v>
+      </c>
+      <c r="BH52">
+        <v>3.1</v>
+      </c>
+      <c r="BI52">
+        <v>1.58</v>
+      </c>
+      <c r="BJ52">
+        <v>2.29</v>
+      </c>
+      <c r="BK52">
+        <v>1.98</v>
+      </c>
+      <c r="BL52">
+        <v>1.82</v>
+      </c>
+      <c r="BM52">
+        <v>2.47</v>
+      </c>
+      <c r="BN52">
+        <v>1.48</v>
+      </c>
+      <c r="BO52">
+        <v>3.27</v>
+      </c>
+      <c r="BP52">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="53" spans="1:68">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>7778544</v>
+      </c>
+      <c r="C53" t="s">
+        <v>68</v>
+      </c>
+      <c r="D53" t="s">
+        <v>69</v>
+      </c>
+      <c r="E53" s="2">
+        <v>45739.05208333334</v>
+      </c>
+      <c r="F53">
+        <v>6</v>
+      </c>
+      <c r="G53" t="s">
+        <v>81</v>
+      </c>
+      <c r="H53" t="s">
+        <v>82</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>1</v>
+      </c>
+      <c r="K53">
+        <v>1</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>1</v>
+      </c>
+      <c r="N53">
+        <v>1</v>
+      </c>
+      <c r="O53" t="s">
+        <v>90</v>
+      </c>
+      <c r="P53" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q53">
+        <v>3.25</v>
+      </c>
+      <c r="R53">
+        <v>2.05</v>
+      </c>
+      <c r="S53">
+        <v>3.5</v>
+      </c>
+      <c r="T53">
+        <v>1.44</v>
+      </c>
+      <c r="U53">
+        <v>2.63</v>
+      </c>
+      <c r="V53">
+        <v>3.25</v>
+      </c>
+      <c r="W53">
+        <v>1.33</v>
+      </c>
+      <c r="X53">
+        <v>10</v>
+      </c>
+      <c r="Y53">
+        <v>1.06</v>
+      </c>
+      <c r="Z53">
+        <v>2.51</v>
+      </c>
+      <c r="AA53">
+        <v>3.19</v>
+      </c>
+      <c r="AB53">
+        <v>2.8</v>
+      </c>
+      <c r="AC53">
+        <v>1.02</v>
+      </c>
+      <c r="AD53">
+        <v>7.8</v>
+      </c>
+      <c r="AE53">
+        <v>1.32</v>
+      </c>
+      <c r="AF53">
+        <v>2.88</v>
+      </c>
+      <c r="AG53">
+        <v>2</v>
+      </c>
+      <c r="AH53">
+        <v>1.67</v>
+      </c>
+      <c r="AI53">
+        <v>1.83</v>
+      </c>
+      <c r="AJ53">
+        <v>1.83</v>
+      </c>
+      <c r="AK53">
+        <v>1.4</v>
+      </c>
+      <c r="AL53">
+        <v>1.36</v>
+      </c>
+      <c r="AM53">
+        <v>1.5</v>
+      </c>
+      <c r="AN53">
+        <v>1.67</v>
+      </c>
+      <c r="AO53">
+        <v>0.5</v>
+      </c>
+      <c r="AP53">
+        <v>1.25</v>
+      </c>
+      <c r="AQ53">
+        <v>1.33</v>
+      </c>
+      <c r="AR53">
+        <v>1.15</v>
+      </c>
+      <c r="AS53">
+        <v>1.39</v>
+      </c>
+      <c r="AT53">
+        <v>2.54</v>
+      </c>
+      <c r="AU53">
+        <v>6</v>
+      </c>
+      <c r="AV53">
+        <v>5</v>
+      </c>
+      <c r="AW53">
+        <v>8</v>
+      </c>
+      <c r="AX53">
+        <v>6</v>
+      </c>
+      <c r="AY53">
+        <v>15</v>
+      </c>
+      <c r="AZ53">
+        <v>14</v>
+      </c>
+      <c r="BA53">
+        <v>5</v>
+      </c>
+      <c r="BB53">
+        <v>3</v>
+      </c>
+      <c r="BC53">
+        <v>8</v>
+      </c>
+      <c r="BD53">
+        <v>1.98</v>
+      </c>
+      <c r="BE53">
+        <v>6.25</v>
+      </c>
+      <c r="BF53">
+        <v>2.21</v>
+      </c>
+      <c r="BG53">
+        <v>1.25</v>
+      </c>
+      <c r="BH53">
+        <v>3.28</v>
+      </c>
+      <c r="BI53">
+        <v>1.56</v>
+      </c>
+      <c r="BJ53">
+        <v>2.39</v>
+      </c>
+      <c r="BK53">
+        <v>1.95</v>
+      </c>
+      <c r="BL53">
+        <v>1.85</v>
+      </c>
+      <c r="BM53">
+        <v>2.44</v>
+      </c>
+      <c r="BN53">
+        <v>1.53</v>
+      </c>
+      <c r="BO53">
+        <v>3.28</v>
+      </c>
+      <c r="BP53">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:68">
+      <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>7778547</v>
+      </c>
+      <c r="C54" t="s">
+        <v>68</v>
+      </c>
+      <c r="D54" t="s">
+        <v>69</v>
+      </c>
+      <c r="E54" s="2">
+        <v>45739.08333333334</v>
+      </c>
+      <c r="F54">
+        <v>6</v>
+      </c>
+      <c r="G54" t="s">
+        <v>76</v>
+      </c>
+      <c r="H54" t="s">
+        <v>89</v>
+      </c>
+      <c r="I54">
+        <v>1</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>1</v>
+      </c>
+      <c r="L54">
+        <v>5</v>
+      </c>
+      <c r="M54">
+        <v>1</v>
+      </c>
+      <c r="N54">
+        <v>6</v>
+      </c>
+      <c r="O54" t="s">
+        <v>127</v>
+      </c>
+      <c r="P54" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q54">
+        <v>2.6</v>
+      </c>
+      <c r="R54">
+        <v>2.2</v>
+      </c>
+      <c r="S54">
+        <v>4.33</v>
+      </c>
+      <c r="T54">
+        <v>1.4</v>
+      </c>
+      <c r="U54">
+        <v>2.75</v>
+      </c>
+      <c r="V54">
+        <v>3</v>
+      </c>
+      <c r="W54">
+        <v>1.36</v>
+      </c>
+      <c r="X54">
+        <v>8</v>
+      </c>
+      <c r="Y54">
+        <v>1.08</v>
+      </c>
+      <c r="Z54">
+        <v>1.98</v>
+      </c>
+      <c r="AA54">
+        <v>3.45</v>
+      </c>
+      <c r="AB54">
+        <v>3.65</v>
+      </c>
+      <c r="AC54">
+        <v>1.01</v>
+      </c>
+      <c r="AD54">
+        <v>8.6</v>
+      </c>
+      <c r="AE54">
+        <v>1.25</v>
+      </c>
+      <c r="AF54">
+        <v>3.28</v>
+      </c>
+      <c r="AG54">
+        <v>1.92</v>
+      </c>
+      <c r="AH54">
+        <v>1.82</v>
+      </c>
+      <c r="AI54">
+        <v>1.8</v>
+      </c>
+      <c r="AJ54">
+        <v>1.91</v>
+      </c>
+      <c r="AK54">
+        <v>1.25</v>
+      </c>
+      <c r="AL54">
+        <v>1.3</v>
+      </c>
+      <c r="AM54">
+        <v>1.83</v>
+      </c>
+      <c r="AN54">
+        <v>3</v>
+      </c>
+      <c r="AO54">
+        <v>1.5</v>
+      </c>
+      <c r="AP54">
+        <v>3</v>
+      </c>
+      <c r="AQ54">
+        <v>1.2</v>
+      </c>
+      <c r="AR54">
+        <v>2.36</v>
+      </c>
+      <c r="AS54">
+        <v>1.48</v>
+      </c>
+      <c r="AT54">
+        <v>3.84</v>
+      </c>
+      <c r="AU54">
+        <v>10</v>
+      </c>
+      <c r="AV54">
+        <v>5</v>
+      </c>
+      <c r="AW54">
+        <v>6</v>
+      </c>
+      <c r="AX54">
+        <v>6</v>
+      </c>
+      <c r="AY54">
+        <v>16</v>
+      </c>
+      <c r="AZ54">
+        <v>11</v>
+      </c>
+      <c r="BA54">
+        <v>5</v>
+      </c>
+      <c r="BB54">
+        <v>5</v>
+      </c>
+      <c r="BC54">
+        <v>10</v>
+      </c>
+      <c r="BD54">
+        <v>1.62</v>
+      </c>
+      <c r="BE54">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF54">
+        <v>2.64</v>
+      </c>
+      <c r="BG54">
+        <v>1.24</v>
+      </c>
+      <c r="BH54">
+        <v>3.34</v>
+      </c>
+      <c r="BI54">
+        <v>1.51</v>
+      </c>
+      <c r="BJ54">
+        <v>2.48</v>
+      </c>
+      <c r="BK54">
+        <v>1.9</v>
+      </c>
+      <c r="BL54">
+        <v>1.9</v>
+      </c>
+      <c r="BM54">
+        <v>2.35</v>
+      </c>
+      <c r="BN54">
+        <v>1.56</v>
+      </c>
+      <c r="BO54">
+        <v>3.14</v>
+      </c>
+      <c r="BP54">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="55" spans="1:68">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>7778546</v>
+      </c>
+      <c r="C55" t="s">
+        <v>68</v>
+      </c>
+      <c r="D55" t="s">
+        <v>69</v>
+      </c>
+      <c r="E55" s="2">
+        <v>45739.08333333334</v>
+      </c>
+      <c r="F55">
+        <v>6</v>
+      </c>
+      <c r="G55" t="s">
+        <v>75</v>
+      </c>
+      <c r="H55" t="s">
+        <v>86</v>
+      </c>
+      <c r="I55">
+        <v>1</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>1</v>
+      </c>
+      <c r="L55">
+        <v>1</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>1</v>
+      </c>
+      <c r="O55" t="s">
+        <v>128</v>
+      </c>
+      <c r="P55" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q55">
+        <v>3</v>
+      </c>
+      <c r="R55">
+        <v>2.05</v>
+      </c>
+      <c r="S55">
+        <v>3.75</v>
+      </c>
+      <c r="T55">
+        <v>1.44</v>
+      </c>
+      <c r="U55">
+        <v>2.63</v>
+      </c>
+      <c r="V55">
+        <v>3.4</v>
+      </c>
+      <c r="W55">
+        <v>1.3</v>
+      </c>
+      <c r="X55">
+        <v>10</v>
+      </c>
+      <c r="Y55">
+        <v>1.06</v>
+      </c>
+      <c r="Z55">
+        <v>2.31</v>
+      </c>
+      <c r="AA55">
+        <v>3.28</v>
+      </c>
+      <c r="AB55">
+        <v>3</v>
+      </c>
+      <c r="AC55">
+        <v>1.03</v>
+      </c>
+      <c r="AD55">
+        <v>7.5</v>
+      </c>
+      <c r="AE55">
+        <v>1.35</v>
+      </c>
+      <c r="AF55">
+        <v>2.95</v>
+      </c>
+      <c r="AG55">
+        <v>2.1</v>
+      </c>
+      <c r="AH55">
+        <v>1.61</v>
+      </c>
+      <c r="AI55">
+        <v>1.83</v>
+      </c>
+      <c r="AJ55">
+        <v>1.83</v>
+      </c>
+      <c r="AK55">
+        <v>1.36</v>
+      </c>
+      <c r="AL55">
+        <v>1.35</v>
+      </c>
+      <c r="AM55">
+        <v>1.57</v>
+      </c>
+      <c r="AN55">
+        <v>1</v>
+      </c>
+      <c r="AO55">
+        <v>1.33</v>
+      </c>
+      <c r="AP55">
+        <v>1.5</v>
+      </c>
+      <c r="AQ55">
+        <v>1</v>
+      </c>
+      <c r="AR55">
+        <v>1.39</v>
+      </c>
+      <c r="AS55">
+        <v>1.22</v>
+      </c>
+      <c r="AT55">
+        <v>2.61</v>
+      </c>
+      <c r="AU55">
+        <v>4</v>
+      </c>
+      <c r="AV55">
+        <v>0</v>
+      </c>
+      <c r="AW55">
+        <v>8</v>
+      </c>
+      <c r="AX55">
+        <v>9</v>
+      </c>
+      <c r="AY55">
+        <v>12</v>
+      </c>
+      <c r="AZ55">
+        <v>9</v>
+      </c>
+      <c r="BA55">
+        <v>3</v>
+      </c>
+      <c r="BB55">
+        <v>6</v>
+      </c>
+      <c r="BC55">
+        <v>9</v>
+      </c>
+      <c r="BD55">
+        <v>1.7</v>
+      </c>
+      <c r="BE55">
+        <v>6.4</v>
+      </c>
+      <c r="BF55">
+        <v>2.68</v>
+      </c>
+      <c r="BG55">
+        <v>1.28</v>
+      </c>
+      <c r="BH55">
+        <v>3.2</v>
+      </c>
+      <c r="BI55">
+        <v>1.54</v>
+      </c>
+      <c r="BJ55">
+        <v>2.38</v>
+      </c>
+      <c r="BK55">
+        <v>1.9</v>
+      </c>
+      <c r="BL55">
+        <v>1.9</v>
+      </c>
+      <c r="BM55">
+        <v>2.37</v>
+      </c>
+      <c r="BN55">
+        <v>1.52</v>
+      </c>
+      <c r="BO55">
+        <v>3.2</v>
+      </c>
+      <c r="BP55">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="56" spans="1:68">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>7778545</v>
+      </c>
+      <c r="C56" t="s">
+        <v>68</v>
+      </c>
+      <c r="D56" t="s">
+        <v>69</v>
+      </c>
+      <c r="E56" s="2">
+        <v>45739.08333333334</v>
+      </c>
+      <c r="F56">
+        <v>6</v>
+      </c>
+      <c r="G56" t="s">
+        <v>77</v>
+      </c>
+      <c r="H56" t="s">
+        <v>87</v>
+      </c>
+      <c r="I56">
+        <v>1</v>
+      </c>
+      <c r="J56">
+        <v>1</v>
+      </c>
+      <c r="K56">
+        <v>2</v>
+      </c>
+      <c r="L56">
+        <v>1</v>
+      </c>
+      <c r="M56">
+        <v>2</v>
+      </c>
+      <c r="N56">
+        <v>3</v>
+      </c>
+      <c r="O56" t="s">
+        <v>129</v>
+      </c>
+      <c r="P56" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q56">
+        <v>4.33</v>
+      </c>
+      <c r="R56">
+        <v>2.2</v>
+      </c>
+      <c r="S56">
+        <v>2.5</v>
+      </c>
+      <c r="T56">
+        <v>1.36</v>
+      </c>
+      <c r="U56">
+        <v>3</v>
+      </c>
+      <c r="V56">
+        <v>2.75</v>
+      </c>
+      <c r="W56">
+        <v>1.4</v>
+      </c>
+      <c r="X56">
+        <v>7</v>
+      </c>
+      <c r="Y56">
+        <v>1.1</v>
+      </c>
+      <c r="Z56">
+        <v>3.7</v>
+      </c>
+      <c r="AA56">
+        <v>3.64</v>
+      </c>
+      <c r="AB56">
+        <v>1.91</v>
+      </c>
+      <c r="AC56">
+        <v>1.02</v>
+      </c>
+      <c r="AD56">
+        <v>10</v>
+      </c>
+      <c r="AE56">
+        <v>1.21</v>
+      </c>
+      <c r="AF56">
+        <v>3.58</v>
+      </c>
+      <c r="AG56">
+        <v>1.79</v>
+      </c>
+      <c r="AH56">
+        <v>1.95</v>
+      </c>
+      <c r="AI56">
+        <v>1.73</v>
+      </c>
+      <c r="AJ56">
+        <v>2</v>
+      </c>
+      <c r="AK56">
+        <v>1.85</v>
+      </c>
+      <c r="AL56">
+        <v>1.3</v>
+      </c>
+      <c r="AM56">
+        <v>1.25</v>
+      </c>
+      <c r="AN56">
+        <v>0</v>
+      </c>
+      <c r="AO56">
+        <v>0.75</v>
+      </c>
+      <c r="AP56">
+        <v>0</v>
+      </c>
+      <c r="AQ56">
+        <v>1.2</v>
+      </c>
+      <c r="AR56">
+        <v>1.03</v>
+      </c>
+      <c r="AS56">
+        <v>1.14</v>
+      </c>
+      <c r="AT56">
+        <v>2.17</v>
+      </c>
+      <c r="AU56">
+        <v>3</v>
+      </c>
+      <c r="AV56">
+        <v>5</v>
+      </c>
+      <c r="AW56">
+        <v>6</v>
+      </c>
+      <c r="AX56">
+        <v>11</v>
+      </c>
+      <c r="AY56">
+        <v>9</v>
+      </c>
+      <c r="AZ56">
+        <v>16</v>
+      </c>
+      <c r="BA56">
+        <v>5</v>
+      </c>
+      <c r="BB56">
+        <v>5</v>
+      </c>
+      <c r="BC56">
+        <v>10</v>
+      </c>
+      <c r="BD56">
+        <v>3.02</v>
+      </c>
+      <c r="BE56">
+        <v>8.6</v>
+      </c>
+      <c r="BF56">
+        <v>1.49</v>
+      </c>
+      <c r="BG56">
+        <v>1.25</v>
+      </c>
+      <c r="BH56">
+        <v>3.45</v>
+      </c>
+      <c r="BI56">
+        <v>1.47</v>
+      </c>
+      <c r="BJ56">
+        <v>2.5</v>
+      </c>
+      <c r="BK56">
+        <v>1.8</v>
+      </c>
+      <c r="BL56">
+        <v>2</v>
+      </c>
+      <c r="BM56">
+        <v>2.26</v>
+      </c>
+      <c r="BN56">
+        <v>1.6</v>
+      </c>
+      <c r="BO56">
+        <v>2.88</v>
+      </c>
+      <c r="BP56">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="57" spans="1:68">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>7778541</v>
+      </c>
+      <c r="C57" t="s">
+        <v>68</v>
+      </c>
+      <c r="D57" t="s">
+        <v>69</v>
+      </c>
+      <c r="E57" s="2">
+        <v>45739.08333333334</v>
+      </c>
+      <c r="F57">
+        <v>6</v>
+      </c>
+      <c r="G57" t="s">
+        <v>70</v>
+      </c>
+      <c r="H57" t="s">
+        <v>78</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>1</v>
+      </c>
+      <c r="N57">
+        <v>1</v>
+      </c>
+      <c r="O57" t="s">
+        <v>90</v>
+      </c>
+      <c r="P57" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q57">
+        <v>3.6</v>
+      </c>
+      <c r="R57">
+        <v>2.05</v>
+      </c>
+      <c r="S57">
+        <v>3.2</v>
+      </c>
+      <c r="T57">
+        <v>1.44</v>
+      </c>
+      <c r="U57">
+        <v>2.63</v>
+      </c>
+      <c r="V57">
+        <v>3.4</v>
+      </c>
+      <c r="W57">
+        <v>1.3</v>
+      </c>
+      <c r="X57">
+        <v>10</v>
+      </c>
+      <c r="Y57">
+        <v>1.06</v>
+      </c>
+      <c r="Z57">
+        <v>2.85</v>
+      </c>
+      <c r="AA57">
+        <v>3.29</v>
+      </c>
+      <c r="AB57">
+        <v>2.41</v>
+      </c>
+      <c r="AC57">
+        <v>1.01</v>
+      </c>
+      <c r="AD57">
+        <v>8.6</v>
+      </c>
+      <c r="AE57">
+        <v>1.31</v>
+      </c>
+      <c r="AF57">
+        <v>2.92</v>
+      </c>
+      <c r="AG57">
+        <v>2.05</v>
+      </c>
+      <c r="AH57">
+        <v>1.65</v>
+      </c>
+      <c r="AI57">
+        <v>1.83</v>
+      </c>
+      <c r="AJ57">
+        <v>1.83</v>
+      </c>
+      <c r="AK57">
+        <v>1.53</v>
+      </c>
+      <c r="AL57">
+        <v>1.36</v>
+      </c>
+      <c r="AM57">
+        <v>1.4</v>
+      </c>
+      <c r="AN57">
+        <v>0.67</v>
+      </c>
+      <c r="AO57">
+        <v>3</v>
+      </c>
+      <c r="AP57">
+        <v>0.5</v>
+      </c>
+      <c r="AQ57">
+        <v>3</v>
+      </c>
+      <c r="AR57">
+        <v>1.77</v>
+      </c>
+      <c r="AS57">
+        <v>1.59</v>
+      </c>
+      <c r="AT57">
+        <v>3.36</v>
+      </c>
+      <c r="AU57">
+        <v>3</v>
+      </c>
+      <c r="AV57">
+        <v>5</v>
+      </c>
+      <c r="AW57">
+        <v>1</v>
+      </c>
+      <c r="AX57">
+        <v>12</v>
+      </c>
+      <c r="AY57">
+        <v>4</v>
+      </c>
+      <c r="AZ57">
+        <v>17</v>
+      </c>
+      <c r="BA57">
+        <v>0</v>
+      </c>
+      <c r="BB57">
+        <v>15</v>
+      </c>
+      <c r="BC57">
+        <v>15</v>
+      </c>
+      <c r="BD57">
+        <v>2.21</v>
+      </c>
+      <c r="BE57">
+        <v>6.15</v>
+      </c>
+      <c r="BF57">
+        <v>1.99</v>
+      </c>
+      <c r="BG57">
+        <v>1.36</v>
+      </c>
+      <c r="BH57">
+        <v>2.92</v>
+      </c>
+      <c r="BI57">
+        <v>1.62</v>
+      </c>
+      <c r="BJ57">
+        <v>2.22</v>
+      </c>
+      <c r="BK57">
+        <v>2</v>
+      </c>
+      <c r="BL57">
+        <v>1.8</v>
+      </c>
+      <c r="BM57">
+        <v>2.57</v>
+      </c>
+      <c r="BN57">
+        <v>1.45</v>
+      </c>
+      <c r="BO57">
+        <v>3.42</v>
+      </c>
+      <c r="BP57">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:68">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>7778542</v>
+      </c>
+      <c r="C58" t="s">
+        <v>68</v>
+      </c>
+      <c r="D58" t="s">
+        <v>69</v>
+      </c>
+      <c r="E58" s="2">
+        <v>45739.08333333334</v>
+      </c>
+      <c r="F58">
+        <v>6</v>
+      </c>
+      <c r="G58" t="s">
+        <v>71</v>
+      </c>
+      <c r="H58" t="s">
+        <v>84</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <v>2</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>2</v>
+      </c>
+      <c r="O58" t="s">
+        <v>130</v>
+      </c>
+      <c r="P58" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q58">
+        <v>2.3</v>
+      </c>
+      <c r="R58">
+        <v>2.2</v>
+      </c>
+      <c r="S58">
+        <v>5</v>
+      </c>
+      <c r="T58">
+        <v>1.4</v>
+      </c>
+      <c r="U58">
+        <v>2.75</v>
+      </c>
+      <c r="V58">
+        <v>2.75</v>
+      </c>
+      <c r="W58">
+        <v>1.4</v>
+      </c>
+      <c r="X58">
+        <v>8</v>
+      </c>
+      <c r="Y58">
+        <v>1.08</v>
+      </c>
+      <c r="Z58">
+        <v>1.75</v>
+      </c>
+      <c r="AA58">
+        <v>3.69</v>
+      </c>
+      <c r="AB58">
+        <v>4.4</v>
+      </c>
+      <c r="AC58">
+        <v>1.01</v>
+      </c>
+      <c r="AD58">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE58">
+        <v>1.22</v>
+      </c>
+      <c r="AF58">
+        <v>3.5</v>
+      </c>
+      <c r="AG58">
+        <v>1.95</v>
+      </c>
+      <c r="AH58">
+        <v>1.79</v>
+      </c>
+      <c r="AI58">
+        <v>1.83</v>
+      </c>
+      <c r="AJ58">
+        <v>1.83</v>
+      </c>
+      <c r="AK58">
+        <v>1.2</v>
+      </c>
+      <c r="AL58">
+        <v>1.29</v>
+      </c>
+      <c r="AM58">
+        <v>2.05</v>
+      </c>
+      <c r="AN58">
+        <v>3</v>
+      </c>
+      <c r="AO58">
+        <v>0.5</v>
+      </c>
+      <c r="AP58">
+        <v>3</v>
+      </c>
+      <c r="AQ58">
+        <v>0.33</v>
+      </c>
+      <c r="AR58">
+        <v>1.9</v>
+      </c>
+      <c r="AS58">
+        <v>1.37</v>
+      </c>
+      <c r="AT58">
+        <v>3.27</v>
+      </c>
+      <c r="AU58">
+        <v>9</v>
+      </c>
+      <c r="AV58">
+        <v>4</v>
+      </c>
+      <c r="AW58">
+        <v>9</v>
+      </c>
+      <c r="AX58">
+        <v>11</v>
+      </c>
+      <c r="AY58">
+        <v>18</v>
+      </c>
+      <c r="AZ58">
+        <v>15</v>
+      </c>
+      <c r="BA58">
+        <v>7</v>
+      </c>
+      <c r="BB58">
+        <v>4</v>
+      </c>
+      <c r="BC58">
+        <v>11</v>
+      </c>
+      <c r="BD58">
+        <v>1.78</v>
+      </c>
+      <c r="BE58">
+        <v>8.1</v>
+      </c>
+      <c r="BF58">
+        <v>2.31</v>
+      </c>
+      <c r="BG58">
+        <v>1.28</v>
+      </c>
+      <c r="BH58">
+        <v>3.2</v>
+      </c>
+      <c r="BI58">
+        <v>1.54</v>
+      </c>
+      <c r="BJ58">
+        <v>2.38</v>
+      </c>
+      <c r="BK58">
+        <v>1.95</v>
+      </c>
+      <c r="BL58">
+        <v>1.85</v>
+      </c>
+      <c r="BM58">
+        <v>2.37</v>
+      </c>
+      <c r="BN58">
+        <v>1.52</v>
+      </c>
+      <c r="BO58">
+        <v>3.2</v>
+      </c>
+      <c r="BP58">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="59" spans="1:68">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>7778548</v>
+      </c>
+      <c r="C59" t="s">
+        <v>68</v>
+      </c>
+      <c r="D59" t="s">
+        <v>69</v>
+      </c>
+      <c r="E59" s="2">
+        <v>45739.08333333334</v>
+      </c>
+      <c r="F59">
+        <v>6</v>
+      </c>
+      <c r="G59" t="s">
+        <v>79</v>
+      </c>
+      <c r="H59" t="s">
+        <v>74</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>1</v>
+      </c>
+      <c r="M59">
+        <v>1</v>
+      </c>
+      <c r="N59">
+        <v>2</v>
+      </c>
+      <c r="O59" t="s">
+        <v>131</v>
+      </c>
+      <c r="P59" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q59">
+        <v>2.88</v>
+      </c>
+      <c r="R59">
+        <v>1.95</v>
+      </c>
+      <c r="S59">
+        <v>4.5</v>
+      </c>
+      <c r="T59">
+        <v>1.57</v>
+      </c>
+      <c r="U59">
+        <v>2.25</v>
+      </c>
+      <c r="V59">
+        <v>3.75</v>
+      </c>
+      <c r="W59">
+        <v>1.25</v>
+      </c>
+      <c r="X59">
+        <v>11</v>
+      </c>
+      <c r="Y59">
+        <v>1.05</v>
+      </c>
+      <c r="Z59">
+        <v>2.15</v>
+      </c>
+      <c r="AA59">
+        <v>3.19</v>
+      </c>
+      <c r="AB59">
+        <v>3.45</v>
+      </c>
+      <c r="AC59">
+        <v>1.03</v>
+      </c>
+      <c r="AD59">
+        <v>7.4</v>
+      </c>
+      <c r="AE59">
+        <v>1.43</v>
+      </c>
+      <c r="AF59">
+        <v>2.46</v>
+      </c>
+      <c r="AG59">
+        <v>2.3</v>
+      </c>
+      <c r="AH59">
+        <v>1.5</v>
+      </c>
+      <c r="AI59">
+        <v>2.2</v>
+      </c>
+      <c r="AJ59">
+        <v>1.62</v>
+      </c>
+      <c r="AK59">
+        <v>1.3</v>
+      </c>
+      <c r="AL59">
+        <v>1.35</v>
+      </c>
+      <c r="AM59">
+        <v>1.67</v>
+      </c>
+      <c r="AN59">
+        <v>1.67</v>
+      </c>
+      <c r="AO59">
+        <v>1</v>
+      </c>
+      <c r="AP59">
+        <v>1.5</v>
+      </c>
+      <c r="AQ59">
+        <v>1</v>
+      </c>
+      <c r="AR59">
+        <v>1.09</v>
+      </c>
+      <c r="AS59">
+        <v>1.03</v>
+      </c>
+      <c r="AT59">
+        <v>2.12</v>
+      </c>
+      <c r="AU59">
+        <v>3</v>
+      </c>
+      <c r="AV59">
+        <v>4</v>
+      </c>
+      <c r="AW59">
+        <v>6</v>
+      </c>
+      <c r="AX59">
+        <v>11</v>
+      </c>
+      <c r="AY59">
+        <v>9</v>
+      </c>
+      <c r="AZ59">
+        <v>21</v>
+      </c>
+      <c r="BA59">
+        <v>1</v>
+      </c>
+      <c r="BB59">
+        <v>6</v>
+      </c>
+      <c r="BC59">
+        <v>7</v>
+      </c>
+      <c r="BD59">
+        <v>1.67</v>
+      </c>
+      <c r="BE59">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF59">
+        <v>2.53</v>
+      </c>
+      <c r="BG59">
+        <v>1.26</v>
+      </c>
+      <c r="BH59">
+        <v>3.22</v>
+      </c>
+      <c r="BI59">
+        <v>1.57</v>
+      </c>
+      <c r="BJ59">
+        <v>2.32</v>
+      </c>
+      <c r="BK59">
+        <v>1.88</v>
+      </c>
+      <c r="BL59">
+        <v>1.92</v>
+      </c>
+      <c r="BM59">
+        <v>2.51</v>
+      </c>
+      <c r="BN59">
+        <v>1.5</v>
+      </c>
+      <c r="BO59">
+        <v>3.28</v>
+      </c>
+      <c r="BP59">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:68">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>7778540</v>
+      </c>
+      <c r="C60" t="s">
+        <v>68</v>
+      </c>
+      <c r="D60" t="s">
+        <v>69</v>
+      </c>
+      <c r="E60" s="2">
+        <v>45739.08333333334</v>
+      </c>
+      <c r="F60">
+        <v>6</v>
+      </c>
+      <c r="G60" t="s">
+        <v>88</v>
+      </c>
+      <c r="H60" t="s">
+        <v>83</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60" t="s">
+        <v>90</v>
+      </c>
+      <c r="P60" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q60">
+        <v>3.25</v>
+      </c>
+      <c r="R60">
+        <v>2.05</v>
+      </c>
+      <c r="S60">
+        <v>3.4</v>
+      </c>
+      <c r="T60">
+        <v>1.44</v>
+      </c>
+      <c r="U60">
+        <v>2.63</v>
+      </c>
+      <c r="V60">
+        <v>3.25</v>
+      </c>
+      <c r="W60">
+        <v>1.33</v>
+      </c>
+      <c r="X60">
+        <v>9</v>
+      </c>
+      <c r="Y60">
+        <v>1.07</v>
+      </c>
+      <c r="Z60">
+        <v>2.51</v>
+      </c>
+      <c r="AA60">
+        <v>3.25</v>
+      </c>
+      <c r="AB60">
+        <v>2.75</v>
+      </c>
+      <c r="AC60">
+        <v>1.01</v>
+      </c>
+      <c r="AD60">
+        <v>8.9</v>
+      </c>
+      <c r="AE60">
+        <v>1.31</v>
+      </c>
+      <c r="AF60">
+        <v>2.92</v>
+      </c>
+      <c r="AG60">
+        <v>1.98</v>
+      </c>
+      <c r="AH60">
+        <v>1.77</v>
+      </c>
+      <c r="AI60">
+        <v>1.83</v>
+      </c>
+      <c r="AJ60">
+        <v>1.83</v>
+      </c>
+      <c r="AK60">
+        <v>1.44</v>
+      </c>
+      <c r="AL60">
+        <v>1.33</v>
+      </c>
+      <c r="AM60">
+        <v>1.5</v>
+      </c>
+      <c r="AN60">
+        <v>3</v>
+      </c>
+      <c r="AO60">
+        <v>1.33</v>
+      </c>
+      <c r="AP60">
+        <v>2</v>
+      </c>
+      <c r="AQ60">
+        <v>1.25</v>
+      </c>
+      <c r="AR60">
+        <v>1.48</v>
+      </c>
+      <c r="AS60">
+        <v>1.39</v>
+      </c>
+      <c r="AT60">
+        <v>2.87</v>
+      </c>
+      <c r="AU60">
+        <v>4</v>
+      </c>
+      <c r="AV60">
+        <v>5</v>
+      </c>
+      <c r="AW60">
+        <v>4</v>
+      </c>
+      <c r="AX60">
+        <v>7</v>
+      </c>
+      <c r="AY60">
+        <v>8</v>
+      </c>
+      <c r="AZ60">
+        <v>12</v>
+      </c>
+      <c r="BA60">
+        <v>5</v>
+      </c>
+      <c r="BB60">
+        <v>9</v>
+      </c>
+      <c r="BC60">
+        <v>14</v>
+      </c>
+      <c r="BD60">
+        <v>1.91</v>
+      </c>
+      <c r="BE60">
+        <v>6.15</v>
+      </c>
+      <c r="BF60">
+        <v>2.32</v>
+      </c>
+      <c r="BG60">
+        <v>1.34</v>
+      </c>
+      <c r="BH60">
+        <v>2.78</v>
+      </c>
+      <c r="BI60">
+        <v>1.68</v>
+      </c>
+      <c r="BJ60">
+        <v>2.14</v>
+      </c>
+      <c r="BK60">
+        <v>1.92</v>
+      </c>
+      <c r="BL60">
+        <v>1.88</v>
+      </c>
+      <c r="BM60">
+        <v>2.52</v>
+      </c>
+      <c r="BN60">
+        <v>1.5</v>
+      </c>
+      <c r="BO60">
+        <v>3.4</v>
+      </c>
+      <c r="BP60">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="61" spans="1:68">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>7778543</v>
+      </c>
+      <c r="C61" t="s">
+        <v>68</v>
+      </c>
+      <c r="D61" t="s">
+        <v>69</v>
+      </c>
+      <c r="E61" s="2">
+        <v>45739.08333333334</v>
+      </c>
+      <c r="F61">
+        <v>6</v>
+      </c>
+      <c r="G61" t="s">
+        <v>72</v>
+      </c>
+      <c r="H61" t="s">
+        <v>80</v>
+      </c>
+      <c r="I61">
+        <v>1</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>1</v>
+      </c>
+      <c r="L61">
+        <v>1</v>
+      </c>
+      <c r="M61">
+        <v>2</v>
+      </c>
+      <c r="N61">
+        <v>3</v>
+      </c>
+      <c r="O61" t="s">
+        <v>132</v>
+      </c>
+      <c r="P61" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q61">
+        <v>4</v>
+      </c>
+      <c r="R61">
+        <v>2.2</v>
+      </c>
+      <c r="S61">
+        <v>2.75</v>
+      </c>
+      <c r="T61">
+        <v>1.36</v>
+      </c>
+      <c r="U61">
+        <v>3</v>
+      </c>
+      <c r="V61">
+        <v>2.75</v>
+      </c>
+      <c r="W61">
+        <v>1.4</v>
+      </c>
+      <c r="X61">
+        <v>8</v>
+      </c>
+      <c r="Y61">
+        <v>1.08</v>
+      </c>
+      <c r="Z61">
+        <v>3.13</v>
+      </c>
+      <c r="AA61">
+        <v>3.58</v>
+      </c>
+      <c r="AB61">
+        <v>2.12</v>
+      </c>
+      <c r="AC61">
+        <v>1.02</v>
+      </c>
+      <c r="AD61">
+        <v>10</v>
+      </c>
+      <c r="AE61">
+        <v>1.21</v>
+      </c>
+      <c r="AF61">
+        <v>3.58</v>
+      </c>
+      <c r="AG61">
+        <v>1.82</v>
+      </c>
+      <c r="AH61">
+        <v>1.92</v>
+      </c>
+      <c r="AI61">
+        <v>1.73</v>
+      </c>
+      <c r="AJ61">
+        <v>2</v>
+      </c>
+      <c r="AK61">
+        <v>1.7</v>
+      </c>
+      <c r="AL61">
+        <v>1.3</v>
+      </c>
+      <c r="AM61">
+        <v>1.33</v>
+      </c>
+      <c r="AN61">
+        <v>2</v>
+      </c>
+      <c r="AO61">
+        <v>3</v>
+      </c>
+      <c r="AP61">
+        <v>1.33</v>
+      </c>
+      <c r="AQ61">
+        <v>3</v>
+      </c>
+      <c r="AR61">
+        <v>1.1</v>
+      </c>
+      <c r="AS61">
+        <v>1</v>
+      </c>
+      <c r="AT61">
+        <v>2.1</v>
+      </c>
+      <c r="AU61">
+        <v>2</v>
+      </c>
+      <c r="AV61">
+        <v>6</v>
+      </c>
+      <c r="AW61">
+        <v>12</v>
+      </c>
+      <c r="AX61">
+        <v>3</v>
+      </c>
+      <c r="AY61">
+        <v>14</v>
+      </c>
+      <c r="AZ61">
+        <v>9</v>
+      </c>
+      <c r="BA61">
+        <v>6</v>
+      </c>
+      <c r="BB61">
+        <v>3</v>
+      </c>
+      <c r="BC61">
+        <v>9</v>
+      </c>
+      <c r="BD61">
+        <v>2.29</v>
+      </c>
+      <c r="BE61">
+        <v>6.25</v>
+      </c>
+      <c r="BF61">
+        <v>1.92</v>
+      </c>
+      <c r="BG61">
+        <v>1.25</v>
+      </c>
+      <c r="BH61">
+        <v>3.28</v>
+      </c>
+      <c r="BI61">
+        <v>1.54</v>
+      </c>
+      <c r="BJ61">
+        <v>2.42</v>
+      </c>
+      <c r="BK61">
+        <v>1.98</v>
+      </c>
+      <c r="BL61">
+        <v>1.82</v>
+      </c>
+      <c r="BM61">
+        <v>2.39</v>
+      </c>
+      <c r="BN61">
+        <v>1.56</v>
+      </c>
+      <c r="BO61">
+        <v>3.2</v>
+      </c>
+      <c r="BP61">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="165">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -506,6 +506,9 @@
   </si>
   <si>
     <t>['58', '90+4']</t>
+  </si>
+  <si>
+    <t>['7']</t>
   </si>
 </sst>
 </file>
@@ -867,7 +870,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP61"/>
+  <dimension ref="A1:BP62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3676,7 +3679,7 @@
         <v>3</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AR14">
         <v>2.25</v>
@@ -6766,7 +6769,7 @@
         <v>3</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AR29">
         <v>0</v>
@@ -9856,7 +9859,7 @@
         <v>3</v>
       </c>
       <c r="AQ44">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AR44">
         <v>1.37</v>
@@ -13434,6 +13437,212 @@
       </c>
       <c r="BP61">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="62" spans="1:68">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>7778549</v>
+      </c>
+      <c r="C62" t="s">
+        <v>68</v>
+      </c>
+      <c r="D62" t="s">
+        <v>69</v>
+      </c>
+      <c r="E62" s="2">
+        <v>45745.08333333334</v>
+      </c>
+      <c r="F62">
+        <v>7</v>
+      </c>
+      <c r="G62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H62" t="s">
+        <v>72</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>1</v>
+      </c>
+      <c r="K62">
+        <v>1</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>1</v>
+      </c>
+      <c r="N62">
+        <v>1</v>
+      </c>
+      <c r="O62" t="s">
+        <v>90</v>
+      </c>
+      <c r="P62" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q62">
+        <v>2.75</v>
+      </c>
+      <c r="R62">
+        <v>2.2</v>
+      </c>
+      <c r="S62">
+        <v>3.75</v>
+      </c>
+      <c r="T62">
+        <v>1.36</v>
+      </c>
+      <c r="U62">
+        <v>3</v>
+      </c>
+      <c r="V62">
+        <v>2.75</v>
+      </c>
+      <c r="W62">
+        <v>1.4</v>
+      </c>
+      <c r="X62">
+        <v>8</v>
+      </c>
+      <c r="Y62">
+        <v>1.08</v>
+      </c>
+      <c r="Z62">
+        <v>2.11</v>
+      </c>
+      <c r="AA62">
+        <v>3.41</v>
+      </c>
+      <c r="AB62">
+        <v>3.28</v>
+      </c>
+      <c r="AC62">
+        <v>1.05</v>
+      </c>
+      <c r="AD62">
+        <v>8.5</v>
+      </c>
+      <c r="AE62">
+        <v>1.28</v>
+      </c>
+      <c r="AF62">
+        <v>3.45</v>
+      </c>
+      <c r="AG62">
+        <v>1.87</v>
+      </c>
+      <c r="AH62">
+        <v>1.87</v>
+      </c>
+      <c r="AI62">
+        <v>1.73</v>
+      </c>
+      <c r="AJ62">
+        <v>2</v>
+      </c>
+      <c r="AK62">
+        <v>1.3</v>
+      </c>
+      <c r="AL62">
+        <v>1.25</v>
+      </c>
+      <c r="AM62">
+        <v>1.67</v>
+      </c>
+      <c r="AN62">
+        <v>0</v>
+      </c>
+      <c r="AO62">
+        <v>0</v>
+      </c>
+      <c r="AP62">
+        <v>0</v>
+      </c>
+      <c r="AQ62">
+        <v>0.75</v>
+      </c>
+      <c r="AR62">
+        <v>1.82</v>
+      </c>
+      <c r="AS62">
+        <v>1.07</v>
+      </c>
+      <c r="AT62">
+        <v>2.89</v>
+      </c>
+      <c r="AU62">
+        <v>2</v>
+      </c>
+      <c r="AV62">
+        <v>4</v>
+      </c>
+      <c r="AW62">
+        <v>9</v>
+      </c>
+      <c r="AX62">
+        <v>13</v>
+      </c>
+      <c r="AY62">
+        <v>11</v>
+      </c>
+      <c r="AZ62">
+        <v>17</v>
+      </c>
+      <c r="BA62">
+        <v>4</v>
+      </c>
+      <c r="BB62">
+        <v>5</v>
+      </c>
+      <c r="BC62">
+        <v>9</v>
+      </c>
+      <c r="BD62">
+        <v>0</v>
+      </c>
+      <c r="BE62">
+        <v>0</v>
+      </c>
+      <c r="BF62">
+        <v>0</v>
+      </c>
+      <c r="BG62">
+        <v>1.33</v>
+      </c>
+      <c r="BH62">
+        <v>3</v>
+      </c>
+      <c r="BI62">
+        <v>1.58</v>
+      </c>
+      <c r="BJ62">
+        <v>2.3</v>
+      </c>
+      <c r="BK62">
+        <v>1.98</v>
+      </c>
+      <c r="BL62">
+        <v>1.82</v>
+      </c>
+      <c r="BM62">
+        <v>2.53</v>
+      </c>
+      <c r="BN62">
+        <v>1.49</v>
+      </c>
+      <c r="BO62">
+        <v>3.2</v>
+      </c>
+      <c r="BP62">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="177">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -415,6 +415,27 @@
     <t>['1']</t>
   </si>
   <si>
+    <t>['23', '36', '52']</t>
+  </si>
+  <si>
+    <t>['2', '31', '58', '88']</t>
+  </si>
+  <si>
+    <t>['19', '42', '61']</t>
+  </si>
+  <si>
+    <t>['58', '90+7']</t>
+  </si>
+  <si>
+    <t>['65']</t>
+  </si>
+  <si>
+    <t>['6']</t>
+  </si>
+  <si>
+    <t>['57']</t>
+  </si>
+  <si>
     <t>['31', '60']</t>
   </si>
   <si>
@@ -509,6 +530,21 @@
   </si>
   <si>
     <t>['7']</t>
+  </si>
+  <si>
+    <t>['90+2']</t>
+  </si>
+  <si>
+    <t>['17']</t>
+  </si>
+  <si>
+    <t>['29']</t>
+  </si>
+  <si>
+    <t>['53', '54']</t>
+  </si>
+  <si>
+    <t>['11', '17']</t>
   </si>
 </sst>
 </file>
@@ -870,7 +906,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP62"/>
+  <dimension ref="A1:BP71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1126,7 +1162,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="Q2">
         <v>3.6</v>
@@ -1207,7 +1243,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ2">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1332,7 +1368,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="Q3">
         <v>3.75</v>
@@ -1413,7 +1449,7 @@
         <v>3</v>
       </c>
       <c r="AQ3">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1744,7 +1780,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -1950,7 +1986,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="Q6">
         <v>4.1</v>
@@ -2028,7 +2064,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ6">
         <v>1.25</v>
@@ -2156,7 +2192,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="Q7">
         <v>2.88</v>
@@ -2237,7 +2273,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ7">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2362,7 +2398,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="Q8">
         <v>2.28</v>
@@ -2568,7 +2604,7 @@
         <v>90</v>
       </c>
       <c r="P9" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -2774,7 +2810,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -2852,7 +2888,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AQ10">
         <v>1.2</v>
@@ -3267,7 +3303,7 @@
         <v>3</v>
       </c>
       <c r="AQ12">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR12">
         <v>1.68</v>
@@ -3804,7 +3840,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="Q15">
         <v>4.1</v>
@@ -3885,7 +3921,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ15">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4088,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ16">
         <v>1.2</v>
@@ -4294,10 +4330,10 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ17">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4500,10 +4536,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AQ18">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -4706,7 +4742,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AQ19">
         <v>1</v>
@@ -4915,7 +4951,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ20">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR20">
         <v>1.61</v>
@@ -5040,7 +5076,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="Q21">
         <v>4.4</v>
@@ -5327,7 +5363,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ22">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5452,7 +5488,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5864,7 +5900,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -5945,7 +5981,7 @@
         <v>3</v>
       </c>
       <c r="AQ25">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR25">
         <v>1.45</v>
@@ -6070,7 +6106,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="Q26">
         <v>3.95</v>
@@ -6148,7 +6184,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ26">
         <v>1.2</v>
@@ -6276,7 +6312,7 @@
         <v>90</v>
       </c>
       <c r="P27" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="Q27">
         <v>3.2</v>
@@ -6354,10 +6390,10 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ27">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR27">
         <v>1.59</v>
@@ -6482,7 +6518,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="Q28">
         <v>3.35</v>
@@ -6766,7 +6802,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ29">
         <v>0.75</v>
@@ -6894,7 +6930,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="Q30">
         <v>2.38</v>
@@ -6972,7 +7008,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AQ30">
         <v>0.5</v>
@@ -7306,7 +7342,7 @@
         <v>113</v>
       </c>
       <c r="P32" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="Q32">
         <v>3.45</v>
@@ -7387,7 +7423,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ32">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AR32">
         <v>1.26</v>
@@ -7512,7 +7548,7 @@
         <v>114</v>
       </c>
       <c r="P33" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -7718,7 +7754,7 @@
         <v>115</v>
       </c>
       <c r="P34" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -7924,7 +7960,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="Q35">
         <v>3.4</v>
@@ -8005,7 +8041,7 @@
         <v>0</v>
       </c>
       <c r="AQ35">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AR35">
         <v>0</v>
@@ -8130,7 +8166,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="Q36">
         <v>2.8</v>
@@ -8417,7 +8453,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ37">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR37">
         <v>1.86</v>
@@ -8542,7 +8578,7 @@
         <v>118</v>
       </c>
       <c r="P38" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="Q38">
         <v>2.6</v>
@@ -8748,7 +8784,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="Q39">
         <v>4</v>
@@ -8826,7 +8862,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ39">
         <v>1</v>
@@ -9032,7 +9068,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ40">
         <v>1.33</v>
@@ -9366,7 +9402,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9444,7 +9480,7 @@
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ42">
         <v>1.2</v>
@@ -9650,10 +9686,10 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ43">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR43">
         <v>1.09</v>
@@ -9778,7 +9814,7 @@
         <v>121</v>
       </c>
       <c r="P44" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10065,7 +10101,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ45">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR45">
         <v>1.47</v>
@@ -10396,7 +10432,7 @@
         <v>105</v>
       </c>
       <c r="P47" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10474,10 +10510,10 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ47">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR47">
         <v>1.58</v>
@@ -10602,7 +10638,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="Q48">
         <v>3.6</v>
@@ -10680,10 +10716,10 @@
         <v>1.5</v>
       </c>
       <c r="AP48">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AQ48">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR48">
         <v>1.52</v>
@@ -10808,7 +10844,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="Q49">
         <v>3.6</v>
@@ -10889,7 +10925,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ49">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR49">
         <v>1.15</v>
@@ -11092,7 +11128,7 @@
         <v>1.5</v>
       </c>
       <c r="AP50">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AQ50">
         <v>1</v>
@@ -11220,7 +11256,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="Q51">
         <v>1.91</v>
@@ -11426,7 +11462,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -11632,7 +11668,7 @@
         <v>90</v>
       </c>
       <c r="P53" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12250,7 +12286,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="Q56">
         <v>4.33</v>
@@ -12868,7 +12904,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13280,7 +13316,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13361,7 +13397,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ61">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AR61">
         <v>1.1</v>
@@ -13486,7 +13522,7 @@
         <v>90</v>
       </c>
       <c r="P62" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="Q62">
         <v>2.75</v>
@@ -13643,6 +13679,1860 @@
       </c>
       <c r="BP62">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:68">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>7778558</v>
+      </c>
+      <c r="C63" t="s">
+        <v>68</v>
+      </c>
+      <c r="D63" t="s">
+        <v>69</v>
+      </c>
+      <c r="E63" s="2">
+        <v>45746.04166666666</v>
+      </c>
+      <c r="F63">
+        <v>7</v>
+      </c>
+      <c r="G63" t="s">
+        <v>82</v>
+      </c>
+      <c r="H63" t="s">
+        <v>75</v>
+      </c>
+      <c r="I63">
+        <v>2</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>2</v>
+      </c>
+      <c r="L63">
+        <v>3</v>
+      </c>
+      <c r="M63">
+        <v>1</v>
+      </c>
+      <c r="N63">
+        <v>4</v>
+      </c>
+      <c r="O63" t="s">
+        <v>133</v>
+      </c>
+      <c r="P63" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q63">
+        <v>3</v>
+      </c>
+      <c r="R63">
+        <v>2.1</v>
+      </c>
+      <c r="S63">
+        <v>3.6</v>
+      </c>
+      <c r="T63">
+        <v>1.4</v>
+      </c>
+      <c r="U63">
+        <v>2.75</v>
+      </c>
+      <c r="V63">
+        <v>3</v>
+      </c>
+      <c r="W63">
+        <v>1.36</v>
+      </c>
+      <c r="X63">
+        <v>8</v>
+      </c>
+      <c r="Y63">
+        <v>1.08</v>
+      </c>
+      <c r="Z63">
+        <v>2.2</v>
+      </c>
+      <c r="AA63">
+        <v>3.51</v>
+      </c>
+      <c r="AB63">
+        <v>3.03</v>
+      </c>
+      <c r="AC63">
+        <v>1.01</v>
+      </c>
+      <c r="AD63">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE63">
+        <v>1.26</v>
+      </c>
+      <c r="AF63">
+        <v>3.22</v>
+      </c>
+      <c r="AG63">
+        <v>1.91</v>
+      </c>
+      <c r="AH63">
+        <v>1.83</v>
+      </c>
+      <c r="AI63">
+        <v>1.8</v>
+      </c>
+      <c r="AJ63">
+        <v>1.91</v>
+      </c>
+      <c r="AK63">
+        <v>1.36</v>
+      </c>
+      <c r="AL63">
+        <v>1.33</v>
+      </c>
+      <c r="AM63">
+        <v>1.6</v>
+      </c>
+      <c r="AN63">
+        <v>1</v>
+      </c>
+      <c r="AO63">
+        <v>0.5</v>
+      </c>
+      <c r="AP63">
+        <v>1.5</v>
+      </c>
+      <c r="AQ63">
+        <v>0.33</v>
+      </c>
+      <c r="AR63">
+        <v>1.46</v>
+      </c>
+      <c r="AS63">
+        <v>1.59</v>
+      </c>
+      <c r="AT63">
+        <v>3.05</v>
+      </c>
+      <c r="AU63">
+        <v>7</v>
+      </c>
+      <c r="AV63">
+        <v>5</v>
+      </c>
+      <c r="AW63">
+        <v>9</v>
+      </c>
+      <c r="AX63">
+        <v>3</v>
+      </c>
+      <c r="AY63">
+        <v>16</v>
+      </c>
+      <c r="AZ63">
+        <v>8</v>
+      </c>
+      <c r="BA63">
+        <v>5</v>
+      </c>
+      <c r="BB63">
+        <v>5</v>
+      </c>
+      <c r="BC63">
+        <v>10</v>
+      </c>
+      <c r="BD63">
+        <v>0</v>
+      </c>
+      <c r="BE63">
+        <v>0</v>
+      </c>
+      <c r="BF63">
+        <v>0</v>
+      </c>
+      <c r="BG63">
+        <v>0</v>
+      </c>
+      <c r="BH63">
+        <v>0</v>
+      </c>
+      <c r="BI63">
+        <v>0</v>
+      </c>
+      <c r="BJ63">
+        <v>0</v>
+      </c>
+      <c r="BK63">
+        <v>0</v>
+      </c>
+      <c r="BL63">
+        <v>0</v>
+      </c>
+      <c r="BM63">
+        <v>0</v>
+      </c>
+      <c r="BN63">
+        <v>0</v>
+      </c>
+      <c r="BO63">
+        <v>0</v>
+      </c>
+      <c r="BP63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:68">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>7778551</v>
+      </c>
+      <c r="C64" t="s">
+        <v>68</v>
+      </c>
+      <c r="D64" t="s">
+        <v>69</v>
+      </c>
+      <c r="E64" s="2">
+        <v>45746.08333333334</v>
+      </c>
+      <c r="F64">
+        <v>7</v>
+      </c>
+      <c r="G64" t="s">
+        <v>84</v>
+      </c>
+      <c r="H64" t="s">
+        <v>70</v>
+      </c>
+      <c r="I64">
+        <v>2</v>
+      </c>
+      <c r="J64">
+        <v>1</v>
+      </c>
+      <c r="K64">
+        <v>3</v>
+      </c>
+      <c r="L64">
+        <v>4</v>
+      </c>
+      <c r="M64">
+        <v>1</v>
+      </c>
+      <c r="N64">
+        <v>5</v>
+      </c>
+      <c r="O64" t="s">
+        <v>134</v>
+      </c>
+      <c r="P64" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q64">
+        <v>3.1</v>
+      </c>
+      <c r="R64">
+        <v>2</v>
+      </c>
+      <c r="S64">
+        <v>3.75</v>
+      </c>
+      <c r="T64">
+        <v>1.5</v>
+      </c>
+      <c r="U64">
+        <v>2.5</v>
+      </c>
+      <c r="V64">
+        <v>3.5</v>
+      </c>
+      <c r="W64">
+        <v>1.29</v>
+      </c>
+      <c r="X64">
+        <v>10</v>
+      </c>
+      <c r="Y64">
+        <v>1.06</v>
+      </c>
+      <c r="Z64">
+        <v>2.33</v>
+      </c>
+      <c r="AA64">
+        <v>3.27</v>
+      </c>
+      <c r="AB64">
+        <v>2.98</v>
+      </c>
+      <c r="AC64">
+        <v>1.02</v>
+      </c>
+      <c r="AD64">
+        <v>7.7</v>
+      </c>
+      <c r="AE64">
+        <v>1.36</v>
+      </c>
+      <c r="AF64">
+        <v>2.7</v>
+      </c>
+      <c r="AG64">
+        <v>2.15</v>
+      </c>
+      <c r="AH64">
+        <v>1.57</v>
+      </c>
+      <c r="AI64">
+        <v>1.91</v>
+      </c>
+      <c r="AJ64">
+        <v>1.8</v>
+      </c>
+      <c r="AK64">
+        <v>1.35</v>
+      </c>
+      <c r="AL64">
+        <v>1.36</v>
+      </c>
+      <c r="AM64">
+        <v>1.57</v>
+      </c>
+      <c r="AN64">
+        <v>1.67</v>
+      </c>
+      <c r="AO64">
+        <v>0.5</v>
+      </c>
+      <c r="AP64">
+        <v>2</v>
+      </c>
+      <c r="AQ64">
+        <v>0.33</v>
+      </c>
+      <c r="AR64">
+        <v>1.49</v>
+      </c>
+      <c r="AS64">
+        <v>0.75</v>
+      </c>
+      <c r="AT64">
+        <v>2.24</v>
+      </c>
+      <c r="AU64">
+        <v>7</v>
+      </c>
+      <c r="AV64">
+        <v>5</v>
+      </c>
+      <c r="AW64">
+        <v>7</v>
+      </c>
+      <c r="AX64">
+        <v>4</v>
+      </c>
+      <c r="AY64">
+        <v>14</v>
+      </c>
+      <c r="AZ64">
+        <v>9</v>
+      </c>
+      <c r="BA64">
+        <v>2</v>
+      </c>
+      <c r="BB64">
+        <v>5</v>
+      </c>
+      <c r="BC64">
+        <v>7</v>
+      </c>
+      <c r="BD64">
+        <v>0</v>
+      </c>
+      <c r="BE64">
+        <v>0</v>
+      </c>
+      <c r="BF64">
+        <v>0</v>
+      </c>
+      <c r="BG64">
+        <v>1.33</v>
+      </c>
+      <c r="BH64">
+        <v>3</v>
+      </c>
+      <c r="BI64">
+        <v>1.59</v>
+      </c>
+      <c r="BJ64">
+        <v>2.32</v>
+      </c>
+      <c r="BK64">
+        <v>1.98</v>
+      </c>
+      <c r="BL64">
+        <v>1.82</v>
+      </c>
+      <c r="BM64">
+        <v>2.53</v>
+      </c>
+      <c r="BN64">
+        <v>1.5</v>
+      </c>
+      <c r="BO64">
+        <v>3.2</v>
+      </c>
+      <c r="BP64">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:68">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>7778552</v>
+      </c>
+      <c r="C65" t="s">
+        <v>68</v>
+      </c>
+      <c r="D65" t="s">
+        <v>69</v>
+      </c>
+      <c r="E65" s="2">
+        <v>45746.08333333334</v>
+      </c>
+      <c r="F65">
+        <v>7</v>
+      </c>
+      <c r="G65" t="s">
+        <v>86</v>
+      </c>
+      <c r="H65" t="s">
+        <v>85</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>1</v>
+      </c>
+      <c r="K65">
+        <v>1</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>1</v>
+      </c>
+      <c r="N65">
+        <v>1</v>
+      </c>
+      <c r="O65" t="s">
+        <v>90</v>
+      </c>
+      <c r="P65" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q65">
+        <v>3.6</v>
+      </c>
+      <c r="R65">
+        <v>2</v>
+      </c>
+      <c r="S65">
+        <v>3.1</v>
+      </c>
+      <c r="T65">
+        <v>1.5</v>
+      </c>
+      <c r="U65">
+        <v>2.5</v>
+      </c>
+      <c r="V65">
+        <v>3.4</v>
+      </c>
+      <c r="W65">
+        <v>1.3</v>
+      </c>
+      <c r="X65">
+        <v>10</v>
+      </c>
+      <c r="Y65">
+        <v>1.05</v>
+      </c>
+      <c r="Z65">
+        <v>3.06</v>
+      </c>
+      <c r="AA65">
+        <v>3.01</v>
+      </c>
+      <c r="AB65">
+        <v>2.44</v>
+      </c>
+      <c r="AC65">
+        <v>1.04</v>
+      </c>
+      <c r="AD65">
+        <v>7.1</v>
+      </c>
+      <c r="AE65">
+        <v>1.43</v>
+      </c>
+      <c r="AF65">
+        <v>2.46</v>
+      </c>
+      <c r="AG65">
+        <v>2.3</v>
+      </c>
+      <c r="AH65">
+        <v>1.5</v>
+      </c>
+      <c r="AI65">
+        <v>2</v>
+      </c>
+      <c r="AJ65">
+        <v>1.75</v>
+      </c>
+      <c r="AK65">
+        <v>1.53</v>
+      </c>
+      <c r="AL65">
+        <v>1.36</v>
+      </c>
+      <c r="AM65">
+        <v>1.36</v>
+      </c>
+      <c r="AN65">
+        <v>3</v>
+      </c>
+      <c r="AO65">
+        <v>1.33</v>
+      </c>
+      <c r="AP65">
+        <v>2</v>
+      </c>
+      <c r="AQ65">
+        <v>1.75</v>
+      </c>
+      <c r="AR65">
+        <v>1.13</v>
+      </c>
+      <c r="AS65">
+        <v>1.73</v>
+      </c>
+      <c r="AT65">
+        <v>2.86</v>
+      </c>
+      <c r="AU65">
+        <v>6</v>
+      </c>
+      <c r="AV65">
+        <v>0</v>
+      </c>
+      <c r="AW65">
+        <v>6</v>
+      </c>
+      <c r="AX65">
+        <v>3</v>
+      </c>
+      <c r="AY65">
+        <v>12</v>
+      </c>
+      <c r="AZ65">
+        <v>3</v>
+      </c>
+      <c r="BA65">
+        <v>3</v>
+      </c>
+      <c r="BB65">
+        <v>6</v>
+      </c>
+      <c r="BC65">
+        <v>9</v>
+      </c>
+      <c r="BD65">
+        <v>0</v>
+      </c>
+      <c r="BE65">
+        <v>0</v>
+      </c>
+      <c r="BF65">
+        <v>0</v>
+      </c>
+      <c r="BG65">
+        <v>0</v>
+      </c>
+      <c r="BH65">
+        <v>0</v>
+      </c>
+      <c r="BI65">
+        <v>0</v>
+      </c>
+      <c r="BJ65">
+        <v>0</v>
+      </c>
+      <c r="BK65">
+        <v>0</v>
+      </c>
+      <c r="BL65">
+        <v>0</v>
+      </c>
+      <c r="BM65">
+        <v>0</v>
+      </c>
+      <c r="BN65">
+        <v>0</v>
+      </c>
+      <c r="BO65">
+        <v>0</v>
+      </c>
+      <c r="BP65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:68">
+      <c r="A66" s="1">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>7778554</v>
+      </c>
+      <c r="C66" t="s">
+        <v>68</v>
+      </c>
+      <c r="D66" t="s">
+        <v>69</v>
+      </c>
+      <c r="E66" s="2">
+        <v>45746.08333333334</v>
+      </c>
+      <c r="F66">
+        <v>7</v>
+      </c>
+      <c r="G66" t="s">
+        <v>74</v>
+      </c>
+      <c r="H66" t="s">
+        <v>76</v>
+      </c>
+      <c r="I66">
+        <v>2</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>2</v>
+      </c>
+      <c r="L66">
+        <v>3</v>
+      </c>
+      <c r="M66">
+        <v>2</v>
+      </c>
+      <c r="N66">
+        <v>5</v>
+      </c>
+      <c r="O66" t="s">
+        <v>135</v>
+      </c>
+      <c r="P66" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q66">
+        <v>4.75</v>
+      </c>
+      <c r="R66">
+        <v>2.25</v>
+      </c>
+      <c r="S66">
+        <v>2.38</v>
+      </c>
+      <c r="T66">
+        <v>1.36</v>
+      </c>
+      <c r="U66">
+        <v>3</v>
+      </c>
+      <c r="V66">
+        <v>2.63</v>
+      </c>
+      <c r="W66">
+        <v>1.44</v>
+      </c>
+      <c r="X66">
+        <v>7</v>
+      </c>
+      <c r="Y66">
+        <v>1.1</v>
+      </c>
+      <c r="Z66">
+        <v>3.95</v>
+      </c>
+      <c r="AA66">
+        <v>3.62</v>
+      </c>
+      <c r="AB66">
+        <v>1.85</v>
+      </c>
+      <c r="AC66">
+        <v>1.02</v>
+      </c>
+      <c r="AD66">
+        <v>10</v>
+      </c>
+      <c r="AE66">
+        <v>1.21</v>
+      </c>
+      <c r="AF66">
+        <v>3.58</v>
+      </c>
+      <c r="AG66">
+        <v>1.79</v>
+      </c>
+      <c r="AH66">
+        <v>1.95</v>
+      </c>
+      <c r="AI66">
+        <v>1.73</v>
+      </c>
+      <c r="AJ66">
+        <v>2</v>
+      </c>
+      <c r="AK66">
+        <v>1.95</v>
+      </c>
+      <c r="AL66">
+        <v>1.29</v>
+      </c>
+      <c r="AM66">
+        <v>1.22</v>
+      </c>
+      <c r="AN66">
+        <v>2</v>
+      </c>
+      <c r="AO66">
+        <v>1</v>
+      </c>
+      <c r="AP66">
+        <v>2.25</v>
+      </c>
+      <c r="AQ66">
+        <v>0.67</v>
+      </c>
+      <c r="AR66">
+        <v>1.04</v>
+      </c>
+      <c r="AS66">
+        <v>1.27</v>
+      </c>
+      <c r="AT66">
+        <v>2.31</v>
+      </c>
+      <c r="AU66">
+        <v>6</v>
+      </c>
+      <c r="AV66">
+        <v>8</v>
+      </c>
+      <c r="AW66">
+        <v>7</v>
+      </c>
+      <c r="AX66">
+        <v>10</v>
+      </c>
+      <c r="AY66">
+        <v>13</v>
+      </c>
+      <c r="AZ66">
+        <v>18</v>
+      </c>
+      <c r="BA66">
+        <v>5</v>
+      </c>
+      <c r="BB66">
+        <v>11</v>
+      </c>
+      <c r="BC66">
+        <v>16</v>
+      </c>
+      <c r="BD66">
+        <v>0</v>
+      </c>
+      <c r="BE66">
+        <v>0</v>
+      </c>
+      <c r="BF66">
+        <v>0</v>
+      </c>
+      <c r="BG66">
+        <v>1.3</v>
+      </c>
+      <c r="BH66">
+        <v>3.2</v>
+      </c>
+      <c r="BI66">
+        <v>1.53</v>
+      </c>
+      <c r="BJ66">
+        <v>2.41</v>
+      </c>
+      <c r="BK66">
+        <v>1.91</v>
+      </c>
+      <c r="BL66">
+        <v>1.89</v>
+      </c>
+      <c r="BM66">
+        <v>2.38</v>
+      </c>
+      <c r="BN66">
+        <v>1.55</v>
+      </c>
+      <c r="BO66">
+        <v>3</v>
+      </c>
+      <c r="BP66">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="67" spans="1:68">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>7778557</v>
+      </c>
+      <c r="C67" t="s">
+        <v>68</v>
+      </c>
+      <c r="D67" t="s">
+        <v>69</v>
+      </c>
+      <c r="E67" s="2">
+        <v>45746.08333333334</v>
+      </c>
+      <c r="F67">
+        <v>7</v>
+      </c>
+      <c r="G67" t="s">
+        <v>78</v>
+      </c>
+      <c r="H67" t="s">
+        <v>88</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>2</v>
+      </c>
+      <c r="K67">
+        <v>2</v>
+      </c>
+      <c r="L67">
+        <v>2</v>
+      </c>
+      <c r="M67">
+        <v>2</v>
+      </c>
+      <c r="N67">
+        <v>4</v>
+      </c>
+      <c r="O67" t="s">
+        <v>136</v>
+      </c>
+      <c r="P67" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q67">
+        <v>2.88</v>
+      </c>
+      <c r="R67">
+        <v>2.1</v>
+      </c>
+      <c r="S67">
+        <v>3.75</v>
+      </c>
+      <c r="T67">
+        <v>1.4</v>
+      </c>
+      <c r="U67">
+        <v>2.75</v>
+      </c>
+      <c r="V67">
+        <v>3</v>
+      </c>
+      <c r="W67">
+        <v>1.36</v>
+      </c>
+      <c r="X67">
+        <v>8</v>
+      </c>
+      <c r="Y67">
+        <v>1.08</v>
+      </c>
+      <c r="Z67">
+        <v>2.37</v>
+      </c>
+      <c r="AA67">
+        <v>3.33</v>
+      </c>
+      <c r="AB67">
+        <v>2.87</v>
+      </c>
+      <c r="AC67">
+        <v>1</v>
+      </c>
+      <c r="AD67">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE67">
+        <v>1.25</v>
+      </c>
+      <c r="AF67">
+        <v>3.28</v>
+      </c>
+      <c r="AG67">
+        <v>1.91</v>
+      </c>
+      <c r="AH67">
+        <v>1.83</v>
+      </c>
+      <c r="AI67">
+        <v>1.73</v>
+      </c>
+      <c r="AJ67">
+        <v>2</v>
+      </c>
+      <c r="AK67">
+        <v>1.4</v>
+      </c>
+      <c r="AL67">
+        <v>1.33</v>
+      </c>
+      <c r="AM67">
+        <v>1.55</v>
+      </c>
+      <c r="AN67">
+        <v>0.67</v>
+      </c>
+      <c r="AO67">
+        <v>0.75</v>
+      </c>
+      <c r="AP67">
+        <v>0.75</v>
+      </c>
+      <c r="AQ67">
+        <v>0.8</v>
+      </c>
+      <c r="AR67">
+        <v>1.24</v>
+      </c>
+      <c r="AS67">
+        <v>1.29</v>
+      </c>
+      <c r="AT67">
+        <v>2.53</v>
+      </c>
+      <c r="AU67">
+        <v>9</v>
+      </c>
+      <c r="AV67">
+        <v>3</v>
+      </c>
+      <c r="AW67">
+        <v>10</v>
+      </c>
+      <c r="AX67">
+        <v>5</v>
+      </c>
+      <c r="AY67">
+        <v>19</v>
+      </c>
+      <c r="AZ67">
+        <v>8</v>
+      </c>
+      <c r="BA67">
+        <v>10</v>
+      </c>
+      <c r="BB67">
+        <v>2</v>
+      </c>
+      <c r="BC67">
+        <v>12</v>
+      </c>
+      <c r="BD67">
+        <v>0</v>
+      </c>
+      <c r="BE67">
+        <v>0</v>
+      </c>
+      <c r="BF67">
+        <v>0</v>
+      </c>
+      <c r="BG67">
+        <v>0</v>
+      </c>
+      <c r="BH67">
+        <v>0</v>
+      </c>
+      <c r="BI67">
+        <v>0</v>
+      </c>
+      <c r="BJ67">
+        <v>0</v>
+      </c>
+      <c r="BK67">
+        <v>0</v>
+      </c>
+      <c r="BL67">
+        <v>0</v>
+      </c>
+      <c r="BM67">
+        <v>0</v>
+      </c>
+      <c r="BN67">
+        <v>0</v>
+      </c>
+      <c r="BO67">
+        <v>0</v>
+      </c>
+      <c r="BP67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:68">
+      <c r="A68" s="1">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>7778550</v>
+      </c>
+      <c r="C68" t="s">
+        <v>68</v>
+      </c>
+      <c r="D68" t="s">
+        <v>69</v>
+      </c>
+      <c r="E68" s="2">
+        <v>45746.08333333334</v>
+      </c>
+      <c r="F68">
+        <v>7</v>
+      </c>
+      <c r="G68" t="s">
+        <v>89</v>
+      </c>
+      <c r="H68" t="s">
+        <v>81</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>1</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>1</v>
+      </c>
+      <c r="O68" t="s">
+        <v>137</v>
+      </c>
+      <c r="P68" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q68">
+        <v>3.25</v>
+      </c>
+      <c r="R68">
+        <v>1.91</v>
+      </c>
+      <c r="S68">
+        <v>4</v>
+      </c>
+      <c r="T68">
+        <v>1.57</v>
+      </c>
+      <c r="U68">
+        <v>2.25</v>
+      </c>
+      <c r="V68">
+        <v>3.75</v>
+      </c>
+      <c r="W68">
+        <v>1.25</v>
+      </c>
+      <c r="X68">
+        <v>13</v>
+      </c>
+      <c r="Y68">
+        <v>1.04</v>
+      </c>
+      <c r="Z68">
+        <v>2.33</v>
+      </c>
+      <c r="AA68">
+        <v>2.97</v>
+      </c>
+      <c r="AB68">
+        <v>3.29</v>
+      </c>
+      <c r="AC68">
+        <v>1.05</v>
+      </c>
+      <c r="AD68">
+        <v>6.55</v>
+      </c>
+      <c r="AE68">
+        <v>1.48</v>
+      </c>
+      <c r="AF68">
+        <v>2.37</v>
+      </c>
+      <c r="AG68">
+        <v>2.47</v>
+      </c>
+      <c r="AH68">
+        <v>1.48</v>
+      </c>
+      <c r="AI68">
+        <v>2.1</v>
+      </c>
+      <c r="AJ68">
+        <v>1.67</v>
+      </c>
+      <c r="AK68">
+        <v>1.33</v>
+      </c>
+      <c r="AL68">
+        <v>1.36</v>
+      </c>
+      <c r="AM68">
+        <v>1.6</v>
+      </c>
+      <c r="AN68">
+        <v>0</v>
+      </c>
+      <c r="AO68">
+        <v>0</v>
+      </c>
+      <c r="AP68">
+        <v>1.5</v>
+      </c>
+      <c r="AQ68">
+        <v>0</v>
+      </c>
+      <c r="AR68">
+        <v>1.93</v>
+      </c>
+      <c r="AS68">
+        <v>1.24</v>
+      </c>
+      <c r="AT68">
+        <v>3.17</v>
+      </c>
+      <c r="AU68">
+        <v>5</v>
+      </c>
+      <c r="AV68">
+        <v>0</v>
+      </c>
+      <c r="AW68">
+        <v>10</v>
+      </c>
+      <c r="AX68">
+        <v>12</v>
+      </c>
+      <c r="AY68">
+        <v>15</v>
+      </c>
+      <c r="AZ68">
+        <v>12</v>
+      </c>
+      <c r="BA68">
+        <v>3</v>
+      </c>
+      <c r="BB68">
+        <v>5</v>
+      </c>
+      <c r="BC68">
+        <v>8</v>
+      </c>
+      <c r="BD68">
+        <v>0</v>
+      </c>
+      <c r="BE68">
+        <v>0</v>
+      </c>
+      <c r="BF68">
+        <v>0</v>
+      </c>
+      <c r="BG68">
+        <v>1.33</v>
+      </c>
+      <c r="BH68">
+        <v>3</v>
+      </c>
+      <c r="BI68">
+        <v>1.57</v>
+      </c>
+      <c r="BJ68">
+        <v>2.34</v>
+      </c>
+      <c r="BK68">
+        <v>1.95</v>
+      </c>
+      <c r="BL68">
+        <v>1.84</v>
+      </c>
+      <c r="BM68">
+        <v>2.48</v>
+      </c>
+      <c r="BN68">
+        <v>1.51</v>
+      </c>
+      <c r="BO68">
+        <v>3.2</v>
+      </c>
+      <c r="BP68">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:68">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <v>7778553</v>
+      </c>
+      <c r="C69" t="s">
+        <v>68</v>
+      </c>
+      <c r="D69" t="s">
+        <v>69</v>
+      </c>
+      <c r="E69" s="2">
+        <v>45746.125</v>
+      </c>
+      <c r="F69">
+        <v>7</v>
+      </c>
+      <c r="G69" t="s">
+        <v>73</v>
+      </c>
+      <c r="H69" t="s">
+        <v>80</v>
+      </c>
+      <c r="I69">
+        <v>1</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>1</v>
+      </c>
+      <c r="L69">
+        <v>1</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>1</v>
+      </c>
+      <c r="O69" t="s">
+        <v>138</v>
+      </c>
+      <c r="P69" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q69">
+        <v>3.6</v>
+      </c>
+      <c r="R69">
+        <v>2.2</v>
+      </c>
+      <c r="S69">
+        <v>2.88</v>
+      </c>
+      <c r="T69">
+        <v>1.36</v>
+      </c>
+      <c r="U69">
+        <v>3</v>
+      </c>
+      <c r="V69">
+        <v>2.75</v>
+      </c>
+      <c r="W69">
+        <v>1.4</v>
+      </c>
+      <c r="X69">
+        <v>8</v>
+      </c>
+      <c r="Y69">
+        <v>1.08</v>
+      </c>
+      <c r="Z69">
+        <v>2.86</v>
+      </c>
+      <c r="AA69">
+        <v>3.66</v>
+      </c>
+      <c r="AB69">
+        <v>2.23</v>
+      </c>
+      <c r="AC69">
+        <v>1</v>
+      </c>
+      <c r="AD69">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE69">
+        <v>1.2</v>
+      </c>
+      <c r="AF69">
+        <v>3.72</v>
+      </c>
+      <c r="AG69">
+        <v>1.83</v>
+      </c>
+      <c r="AH69">
+        <v>1.91</v>
+      </c>
+      <c r="AI69">
+        <v>1.73</v>
+      </c>
+      <c r="AJ69">
+        <v>2</v>
+      </c>
+      <c r="AK69">
+        <v>1.6</v>
+      </c>
+      <c r="AL69">
+        <v>1.33</v>
+      </c>
+      <c r="AM69">
+        <v>1.36</v>
+      </c>
+      <c r="AN69">
+        <v>3</v>
+      </c>
+      <c r="AO69">
+        <v>3</v>
+      </c>
+      <c r="AP69">
+        <v>3</v>
+      </c>
+      <c r="AQ69">
+        <v>2.25</v>
+      </c>
+      <c r="AR69">
+        <v>1.3</v>
+      </c>
+      <c r="AS69">
+        <v>1.14</v>
+      </c>
+      <c r="AT69">
+        <v>2.44</v>
+      </c>
+      <c r="AU69">
+        <v>5</v>
+      </c>
+      <c r="AV69">
+        <v>3</v>
+      </c>
+      <c r="AW69">
+        <v>3</v>
+      </c>
+      <c r="AX69">
+        <v>2</v>
+      </c>
+      <c r="AY69">
+        <v>8</v>
+      </c>
+      <c r="AZ69">
+        <v>5</v>
+      </c>
+      <c r="BA69">
+        <v>5</v>
+      </c>
+      <c r="BB69">
+        <v>1</v>
+      </c>
+      <c r="BC69">
+        <v>6</v>
+      </c>
+      <c r="BD69">
+        <v>0</v>
+      </c>
+      <c r="BE69">
+        <v>0</v>
+      </c>
+      <c r="BF69">
+        <v>0</v>
+      </c>
+      <c r="BG69">
+        <v>0</v>
+      </c>
+      <c r="BH69">
+        <v>0</v>
+      </c>
+      <c r="BI69">
+        <v>0</v>
+      </c>
+      <c r="BJ69">
+        <v>0</v>
+      </c>
+      <c r="BK69">
+        <v>0</v>
+      </c>
+      <c r="BL69">
+        <v>0</v>
+      </c>
+      <c r="BM69">
+        <v>0</v>
+      </c>
+      <c r="BN69">
+        <v>0</v>
+      </c>
+      <c r="BO69">
+        <v>0</v>
+      </c>
+      <c r="BP69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:68">
+      <c r="A70" s="1">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>7778556</v>
+      </c>
+      <c r="C70" t="s">
+        <v>68</v>
+      </c>
+      <c r="D70" t="s">
+        <v>69</v>
+      </c>
+      <c r="E70" s="2">
+        <v>45746.125</v>
+      </c>
+      <c r="F70">
+        <v>7</v>
+      </c>
+      <c r="G70" t="s">
+        <v>77</v>
+      </c>
+      <c r="H70" t="s">
+        <v>79</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>1</v>
+      </c>
+      <c r="K70">
+        <v>1</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>1</v>
+      </c>
+      <c r="N70">
+        <v>1</v>
+      </c>
+      <c r="O70" t="s">
+        <v>90</v>
+      </c>
+      <c r="P70" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q70">
+        <v>4.33</v>
+      </c>
+      <c r="R70">
+        <v>1.95</v>
+      </c>
+      <c r="S70">
+        <v>3</v>
+      </c>
+      <c r="T70">
+        <v>1.57</v>
+      </c>
+      <c r="U70">
+        <v>2.25</v>
+      </c>
+      <c r="V70">
+        <v>3.75</v>
+      </c>
+      <c r="W70">
+        <v>1.25</v>
+      </c>
+      <c r="X70">
+        <v>11</v>
+      </c>
+      <c r="Y70">
+        <v>1.05</v>
+      </c>
+      <c r="Z70">
+        <v>3.52</v>
+      </c>
+      <c r="AA70">
+        <v>3.17</v>
+      </c>
+      <c r="AB70">
+        <v>2.13</v>
+      </c>
+      <c r="AC70">
+        <v>1.03</v>
+      </c>
+      <c r="AD70">
+        <v>7.7</v>
+      </c>
+      <c r="AE70">
+        <v>1.44</v>
+      </c>
+      <c r="AF70">
+        <v>2.59</v>
+      </c>
+      <c r="AG70">
+        <v>2.37</v>
+      </c>
+      <c r="AH70">
+        <v>1.48</v>
+      </c>
+      <c r="AI70">
+        <v>2.1</v>
+      </c>
+      <c r="AJ70">
+        <v>1.67</v>
+      </c>
+      <c r="AK70">
+        <v>1.67</v>
+      </c>
+      <c r="AL70">
+        <v>1.36</v>
+      </c>
+      <c r="AM70">
+        <v>1.25</v>
+      </c>
+      <c r="AN70">
+        <v>0</v>
+      </c>
+      <c r="AO70">
+        <v>0.5</v>
+      </c>
+      <c r="AP70">
+        <v>0</v>
+      </c>
+      <c r="AQ70">
+        <v>1.33</v>
+      </c>
+      <c r="AR70">
+        <v>1.09</v>
+      </c>
+      <c r="AS70">
+        <v>1.15</v>
+      </c>
+      <c r="AT70">
+        <v>2.24</v>
+      </c>
+      <c r="AU70">
+        <v>0</v>
+      </c>
+      <c r="AV70">
+        <v>3</v>
+      </c>
+      <c r="AW70">
+        <v>6</v>
+      </c>
+      <c r="AX70">
+        <v>4</v>
+      </c>
+      <c r="AY70">
+        <v>6</v>
+      </c>
+      <c r="AZ70">
+        <v>7</v>
+      </c>
+      <c r="BA70">
+        <v>10</v>
+      </c>
+      <c r="BB70">
+        <v>3</v>
+      </c>
+      <c r="BC70">
+        <v>13</v>
+      </c>
+      <c r="BD70">
+        <v>0</v>
+      </c>
+      <c r="BE70">
+        <v>0</v>
+      </c>
+      <c r="BF70">
+        <v>0</v>
+      </c>
+      <c r="BG70">
+        <v>1.29</v>
+      </c>
+      <c r="BH70">
+        <v>3.4</v>
+      </c>
+      <c r="BI70">
+        <v>1.48</v>
+      </c>
+      <c r="BJ70">
+        <v>2.57</v>
+      </c>
+      <c r="BK70">
+        <v>1.79</v>
+      </c>
+      <c r="BL70">
+        <v>2</v>
+      </c>
+      <c r="BM70">
+        <v>2.23</v>
+      </c>
+      <c r="BN70">
+        <v>1.62</v>
+      </c>
+      <c r="BO70">
+        <v>2.8</v>
+      </c>
+      <c r="BP70">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="71" spans="1:68">
+      <c r="A71" s="1">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>7778555</v>
+      </c>
+      <c r="C71" t="s">
+        <v>68</v>
+      </c>
+      <c r="D71" t="s">
+        <v>69</v>
+      </c>
+      <c r="E71" s="2">
+        <v>45746.16666666666</v>
+      </c>
+      <c r="F71">
+        <v>7</v>
+      </c>
+      <c r="G71" t="s">
+        <v>83</v>
+      </c>
+      <c r="H71" t="s">
+        <v>71</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>1</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>1</v>
+      </c>
+      <c r="O71" t="s">
+        <v>139</v>
+      </c>
+      <c r="P71" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q71">
+        <v>3.75</v>
+      </c>
+      <c r="R71">
+        <v>2</v>
+      </c>
+      <c r="S71">
+        <v>3.25</v>
+      </c>
+      <c r="T71">
+        <v>1.53</v>
+      </c>
+      <c r="U71">
+        <v>2.38</v>
+      </c>
+      <c r="V71">
+        <v>3.5</v>
+      </c>
+      <c r="W71">
+        <v>1.29</v>
+      </c>
+      <c r="X71">
+        <v>11</v>
+      </c>
+      <c r="Y71">
+        <v>1.05</v>
+      </c>
+      <c r="Z71">
+        <v>3.01</v>
+      </c>
+      <c r="AA71">
+        <v>3.32</v>
+      </c>
+      <c r="AB71">
+        <v>2.29</v>
+      </c>
+      <c r="AC71">
+        <v>1.01</v>
+      </c>
+      <c r="AD71">
+        <v>8.6</v>
+      </c>
+      <c r="AE71">
+        <v>1.37</v>
+      </c>
+      <c r="AF71">
+        <v>2.66</v>
+      </c>
+      <c r="AG71">
+        <v>2.2</v>
+      </c>
+      <c r="AH71">
+        <v>1.55</v>
+      </c>
+      <c r="AI71">
+        <v>2</v>
+      </c>
+      <c r="AJ71">
+        <v>1.73</v>
+      </c>
+      <c r="AK71">
+        <v>1.57</v>
+      </c>
+      <c r="AL71">
+        <v>1.35</v>
+      </c>
+      <c r="AM71">
+        <v>1.36</v>
+      </c>
+      <c r="AN71">
+        <v>2</v>
+      </c>
+      <c r="AO71">
+        <v>1.5</v>
+      </c>
+      <c r="AP71">
+        <v>2.33</v>
+      </c>
+      <c r="AQ71">
+        <v>1</v>
+      </c>
+      <c r="AR71">
+        <v>1.39</v>
+      </c>
+      <c r="AS71">
+        <v>1.7</v>
+      </c>
+      <c r="AT71">
+        <v>3.09</v>
+      </c>
+      <c r="AU71">
+        <v>4</v>
+      </c>
+      <c r="AV71">
+        <v>3</v>
+      </c>
+      <c r="AW71">
+        <v>6</v>
+      </c>
+      <c r="AX71">
+        <v>6</v>
+      </c>
+      <c r="AY71">
+        <v>10</v>
+      </c>
+      <c r="AZ71">
+        <v>9</v>
+      </c>
+      <c r="BA71">
+        <v>5</v>
+      </c>
+      <c r="BB71">
+        <v>5</v>
+      </c>
+      <c r="BC71">
+        <v>10</v>
+      </c>
+      <c r="BD71">
+        <v>0</v>
+      </c>
+      <c r="BE71">
+        <v>0</v>
+      </c>
+      <c r="BF71">
+        <v>0</v>
+      </c>
+      <c r="BG71">
+        <v>0</v>
+      </c>
+      <c r="BH71">
+        <v>0</v>
+      </c>
+      <c r="BI71">
+        <v>0</v>
+      </c>
+      <c r="BJ71">
+        <v>0</v>
+      </c>
+      <c r="BK71">
+        <v>0</v>
+      </c>
+      <c r="BL71">
+        <v>0</v>
+      </c>
+      <c r="BM71">
+        <v>0</v>
+      </c>
+      <c r="BN71">
+        <v>0</v>
+      </c>
+      <c r="BO71">
+        <v>0</v>
+      </c>
+      <c r="BP71">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -14251,13 +14251,13 @@
         <v>3</v>
       </c>
       <c r="BA65">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BB65">
         <v>6</v>
       </c>
       <c r="BC65">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BD65">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="184">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -436,6 +436,24 @@
     <t>['57']</t>
   </si>
   <si>
+    <t>['10']</t>
+  </si>
+  <si>
+    <t>['58']</t>
+  </si>
+  <si>
+    <t>['3']</t>
+  </si>
+  <si>
+    <t>['24', '76']</t>
+  </si>
+  <si>
+    <t>['90+5']</t>
+  </si>
+  <si>
+    <t>['21', '90+4']</t>
+  </si>
+  <si>
     <t>['31', '60']</t>
   </si>
   <si>
@@ -478,9 +496,6 @@
     <t>['55', '57', '62', '90+4']</t>
   </si>
   <si>
-    <t>['3']</t>
-  </si>
-  <si>
     <t>['24']</t>
   </si>
   <si>
@@ -545,6 +560,12 @@
   </si>
   <si>
     <t>['11', '17']</t>
+  </si>
+  <si>
+    <t>['90+3']</t>
+  </si>
+  <si>
+    <t>['20', '53']</t>
   </si>
 </sst>
 </file>
@@ -906,7 +927,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP71"/>
+  <dimension ref="A1:BP79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1162,7 +1183,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="Q2">
         <v>3.6</v>
@@ -1368,7 +1389,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="Q3">
         <v>3.75</v>
@@ -1446,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AQ3">
         <v>0.8</v>
@@ -1652,7 +1673,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ4">
         <v>0</v>
@@ -1780,7 +1801,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -1861,7 +1882,7 @@
         <v>3</v>
       </c>
       <c r="AQ5">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1986,7 +2007,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="Q6">
         <v>4.1</v>
@@ -2067,7 +2088,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ6">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2192,7 +2213,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="Q7">
         <v>2.88</v>
@@ -2270,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ7">
         <v>1.75</v>
@@ -2398,7 +2419,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="Q8">
         <v>2.28</v>
@@ -2604,7 +2625,7 @@
         <v>90</v>
       </c>
       <c r="P9" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -2810,7 +2831,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -2891,7 +2912,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ10">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3712,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AQ14">
         <v>0.75</v>
@@ -3840,7 +3861,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="Q15">
         <v>4.1</v>
@@ -3918,7 +3939,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ15">
         <v>0.67</v>
@@ -4745,7 +4766,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ19">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR19">
         <v>1.74</v>
@@ -4951,7 +4972,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ20">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR20">
         <v>1.61</v>
@@ -5076,7 +5097,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q21">
         <v>4.4</v>
@@ -5157,7 +5178,7 @@
         <v>0</v>
       </c>
       <c r="AQ21">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR21">
         <v>1.32</v>
@@ -5360,10 +5381,10 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ22">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5488,7 +5509,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5566,7 +5587,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ23">
         <v>3</v>
@@ -5900,7 +5921,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -6106,7 +6127,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="Q26">
         <v>3.95</v>
@@ -6187,7 +6208,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ26">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR26">
         <v>0.85</v>
@@ -6312,7 +6333,7 @@
         <v>90</v>
       </c>
       <c r="P27" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="Q27">
         <v>3.2</v>
@@ -6518,7 +6539,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="Q28">
         <v>3.35</v>
@@ -6599,7 +6620,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ28">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AR28">
         <v>2.36</v>
@@ -6930,7 +6951,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="Q30">
         <v>2.38</v>
@@ -7011,7 +7032,7 @@
         <v>2</v>
       </c>
       <c r="AQ30">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR30">
         <v>1.54</v>
@@ -7214,7 +7235,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ31">
         <v>1.2</v>
@@ -7342,7 +7363,7 @@
         <v>113</v>
       </c>
       <c r="P32" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="Q32">
         <v>3.45</v>
@@ -7420,7 +7441,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ32">
         <v>0.67</v>
@@ -7548,7 +7569,7 @@
         <v>114</v>
       </c>
       <c r="P33" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -7626,7 +7647,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AQ33">
         <v>0</v>
@@ -7754,7 +7775,7 @@
         <v>115</v>
       </c>
       <c r="P34" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -7960,7 +7981,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="Q35">
         <v>3.4</v>
@@ -8038,7 +8059,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ35">
         <v>2.25</v>
@@ -8166,7 +8187,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="Q36">
         <v>2.8</v>
@@ -8244,10 +8265,10 @@
         <v>2</v>
       </c>
       <c r="AP36">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ36">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR36">
         <v>0</v>
@@ -8578,7 +8599,7 @@
         <v>118</v>
       </c>
       <c r="P38" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="Q38">
         <v>2.6</v>
@@ -8656,10 +8677,10 @@
         <v>1</v>
       </c>
       <c r="AP38">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ38">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR38">
         <v>1.1</v>
@@ -8784,7 +8805,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="Q39">
         <v>4</v>
@@ -9277,7 +9298,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ41">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR41">
         <v>1.46</v>
@@ -9402,7 +9423,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9689,7 +9710,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ43">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR43">
         <v>1.09</v>
@@ -9814,7 +9835,7 @@
         <v>121</v>
       </c>
       <c r="P44" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10098,7 +10119,7 @@
         <v>3</v>
       </c>
       <c r="AP45">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ45">
         <v>1</v>
@@ -10307,7 +10328,7 @@
         <v>3</v>
       </c>
       <c r="AQ46">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AR46">
         <v>2.49</v>
@@ -10432,7 +10453,7 @@
         <v>105</v>
       </c>
       <c r="P47" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10638,7 +10659,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="Q48">
         <v>3.6</v>
@@ -10844,7 +10865,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="Q49">
         <v>3.6</v>
@@ -10922,10 +10943,10 @@
         <v>0</v>
       </c>
       <c r="AP49">
+        <v>1.2</v>
+      </c>
+      <c r="AQ49">
         <v>1.25</v>
-      </c>
-      <c r="AQ49">
-        <v>1.33</v>
       </c>
       <c r="AR49">
         <v>1.15</v>
@@ -11256,7 +11277,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="Q51">
         <v>1.91</v>
@@ -11337,7 +11358,7 @@
         <v>3</v>
       </c>
       <c r="AQ51">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR51">
         <v>1.69</v>
@@ -11462,7 +11483,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -11540,7 +11561,7 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ52">
         <v>1</v>
@@ -11668,7 +11689,7 @@
         <v>90</v>
       </c>
       <c r="P53" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -11746,7 +11767,7 @@
         <v>0.5</v>
       </c>
       <c r="AP53">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ53">
         <v>1.33</v>
@@ -11955,7 +11976,7 @@
         <v>3</v>
       </c>
       <c r="AQ54">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR54">
         <v>2.36</v>
@@ -12158,7 +12179,7 @@
         <v>1.33</v>
       </c>
       <c r="AP55">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ55">
         <v>1</v>
@@ -12286,7 +12307,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="Q56">
         <v>4.33</v>
@@ -12776,10 +12797,10 @@
         <v>0.5</v>
       </c>
       <c r="AP58">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AQ58">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR58">
         <v>1.9</v>
@@ -12904,7 +12925,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -12985,7 +13006,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ59">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR59">
         <v>1.09</v>
@@ -13188,10 +13209,10 @@
         <v>1.33</v>
       </c>
       <c r="AP60">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ60">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AR60">
         <v>1.48</v>
@@ -13316,7 +13337,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13394,7 +13415,7 @@
         <v>3</v>
       </c>
       <c r="AP61">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ61">
         <v>2.25</v>
@@ -13522,7 +13543,7 @@
         <v>90</v>
       </c>
       <c r="P62" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="Q62">
         <v>2.75</v>
@@ -13600,7 +13621,7 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ62">
         <v>0.75</v>
@@ -13728,7 +13749,7 @@
         <v>133</v>
       </c>
       <c r="P63" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="Q63">
         <v>3</v>
@@ -13934,7 +13955,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="Q64">
         <v>3.1</v>
@@ -14015,7 +14036,7 @@
         <v>2</v>
       </c>
       <c r="AQ64">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR64">
         <v>1.49</v>
@@ -14140,7 +14161,7 @@
         <v>90</v>
       </c>
       <c r="P65" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="Q65">
         <v>3.6</v>
@@ -14346,7 +14367,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="Q66">
         <v>4.75</v>
@@ -14552,7 +14573,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="Q67">
         <v>2.88</v>
@@ -15251,7 +15272,7 @@
         <v>0</v>
       </c>
       <c r="AQ70">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR70">
         <v>1.09</v>
@@ -15532,6 +15553,1654 @@
         <v>0</v>
       </c>
       <c r="BP71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:68">
+      <c r="A72" s="1">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>7778560</v>
+      </c>
+      <c r="C72" t="s">
+        <v>68</v>
+      </c>
+      <c r="D72" t="s">
+        <v>69</v>
+      </c>
+      <c r="E72" s="2">
+        <v>45752.04166666666</v>
+      </c>
+      <c r="F72">
+        <v>8</v>
+      </c>
+      <c r="G72" t="s">
+        <v>85</v>
+      </c>
+      <c r="H72" t="s">
+        <v>89</v>
+      </c>
+      <c r="I72">
+        <v>1</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>1</v>
+      </c>
+      <c r="L72">
+        <v>1</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>1</v>
+      </c>
+      <c r="O72" t="s">
+        <v>140</v>
+      </c>
+      <c r="P72" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q72">
+        <v>2.88</v>
+      </c>
+      <c r="R72">
+        <v>2</v>
+      </c>
+      <c r="S72">
+        <v>4</v>
+      </c>
+      <c r="T72">
+        <v>1.5</v>
+      </c>
+      <c r="U72">
+        <v>2.5</v>
+      </c>
+      <c r="V72">
+        <v>3.4</v>
+      </c>
+      <c r="W72">
+        <v>1.3</v>
+      </c>
+      <c r="X72">
+        <v>10</v>
+      </c>
+      <c r="Y72">
+        <v>1.06</v>
+      </c>
+      <c r="Z72">
+        <v>2.21</v>
+      </c>
+      <c r="AA72">
+        <v>3.02</v>
+      </c>
+      <c r="AB72">
+        <v>3.5</v>
+      </c>
+      <c r="AC72">
+        <v>0</v>
+      </c>
+      <c r="AD72">
+        <v>0</v>
+      </c>
+      <c r="AE72">
+        <v>2.1</v>
+      </c>
+      <c r="AF72">
+        <v>1.75</v>
+      </c>
+      <c r="AG72">
+        <v>2.15</v>
+      </c>
+      <c r="AH72">
+        <v>1.57</v>
+      </c>
+      <c r="AI72">
+        <v>1.91</v>
+      </c>
+      <c r="AJ72">
+        <v>1.8</v>
+      </c>
+      <c r="AK72">
+        <v>0</v>
+      </c>
+      <c r="AL72">
+        <v>0</v>
+      </c>
+      <c r="AM72">
+        <v>0</v>
+      </c>
+      <c r="AN72">
+        <v>1.33</v>
+      </c>
+      <c r="AO72">
+        <v>1.2</v>
+      </c>
+      <c r="AP72">
+        <v>1.75</v>
+      </c>
+      <c r="AQ72">
+        <v>1</v>
+      </c>
+      <c r="AR72">
+        <v>1.51</v>
+      </c>
+      <c r="AS72">
+        <v>1.51</v>
+      </c>
+      <c r="AT72">
+        <v>3.02</v>
+      </c>
+      <c r="AU72">
+        <v>3</v>
+      </c>
+      <c r="AV72">
+        <v>5</v>
+      </c>
+      <c r="AW72">
+        <v>2</v>
+      </c>
+      <c r="AX72">
+        <v>5</v>
+      </c>
+      <c r="AY72">
+        <v>6</v>
+      </c>
+      <c r="AZ72">
+        <v>10</v>
+      </c>
+      <c r="BA72">
+        <v>1</v>
+      </c>
+      <c r="BB72">
+        <v>3</v>
+      </c>
+      <c r="BC72">
+        <v>4</v>
+      </c>
+      <c r="BD72">
+        <v>0</v>
+      </c>
+      <c r="BE72">
+        <v>0</v>
+      </c>
+      <c r="BF72">
+        <v>0</v>
+      </c>
+      <c r="BG72">
+        <v>0</v>
+      </c>
+      <c r="BH72">
+        <v>0</v>
+      </c>
+      <c r="BI72">
+        <v>0</v>
+      </c>
+      <c r="BJ72">
+        <v>0</v>
+      </c>
+      <c r="BK72">
+        <v>0</v>
+      </c>
+      <c r="BL72">
+        <v>0</v>
+      </c>
+      <c r="BM72">
+        <v>0</v>
+      </c>
+      <c r="BN72">
+        <v>0</v>
+      </c>
+      <c r="BO72">
+        <v>0</v>
+      </c>
+      <c r="BP72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:68">
+      <c r="A73" s="1">
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <v>7778564</v>
+      </c>
+      <c r="C73" t="s">
+        <v>68</v>
+      </c>
+      <c r="D73" t="s">
+        <v>69</v>
+      </c>
+      <c r="E73" s="2">
+        <v>45752.0625</v>
+      </c>
+      <c r="F73">
+        <v>8</v>
+      </c>
+      <c r="G73" t="s">
+        <v>72</v>
+      </c>
+      <c r="H73" t="s">
+        <v>70</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>1</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>1</v>
+      </c>
+      <c r="O73" t="s">
+        <v>141</v>
+      </c>
+      <c r="P73" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q73">
+        <v>3</v>
+      </c>
+      <c r="R73">
+        <v>2.05</v>
+      </c>
+      <c r="S73">
+        <v>4</v>
+      </c>
+      <c r="T73">
+        <v>1.44</v>
+      </c>
+      <c r="U73">
+        <v>2.63</v>
+      </c>
+      <c r="V73">
+        <v>3.4</v>
+      </c>
+      <c r="W73">
+        <v>1.3</v>
+      </c>
+      <c r="X73">
+        <v>10</v>
+      </c>
+      <c r="Y73">
+        <v>1.06</v>
+      </c>
+      <c r="Z73">
+        <v>2.43</v>
+      </c>
+      <c r="AA73">
+        <v>3.06</v>
+      </c>
+      <c r="AB73">
+        <v>3.01</v>
+      </c>
+      <c r="AC73">
+        <v>0</v>
+      </c>
+      <c r="AD73">
+        <v>0</v>
+      </c>
+      <c r="AE73">
+        <v>2.24</v>
+      </c>
+      <c r="AF73">
+        <v>1.67</v>
+      </c>
+      <c r="AG73">
+        <v>2.05</v>
+      </c>
+      <c r="AH73">
+        <v>1.65</v>
+      </c>
+      <c r="AI73">
+        <v>1.83</v>
+      </c>
+      <c r="AJ73">
+        <v>1.83</v>
+      </c>
+      <c r="AK73">
+        <v>0</v>
+      </c>
+      <c r="AL73">
+        <v>0</v>
+      </c>
+      <c r="AM73">
+        <v>0</v>
+      </c>
+      <c r="AN73">
+        <v>1.33</v>
+      </c>
+      <c r="AO73">
+        <v>0.33</v>
+      </c>
+      <c r="AP73">
+        <v>1.75</v>
+      </c>
+      <c r="AQ73">
+        <v>0.25</v>
+      </c>
+      <c r="AR73">
+        <v>1.25</v>
+      </c>
+      <c r="AS73">
+        <v>1.01</v>
+      </c>
+      <c r="AT73">
+        <v>2.26</v>
+      </c>
+      <c r="AU73">
+        <v>2</v>
+      </c>
+      <c r="AV73">
+        <v>2</v>
+      </c>
+      <c r="AW73">
+        <v>5</v>
+      </c>
+      <c r="AX73">
+        <v>4</v>
+      </c>
+      <c r="AY73">
+        <v>7</v>
+      </c>
+      <c r="AZ73">
+        <v>6</v>
+      </c>
+      <c r="BA73">
+        <v>1</v>
+      </c>
+      <c r="BB73">
+        <v>6</v>
+      </c>
+      <c r="BC73">
+        <v>7</v>
+      </c>
+      <c r="BD73">
+        <v>0</v>
+      </c>
+      <c r="BE73">
+        <v>0</v>
+      </c>
+      <c r="BF73">
+        <v>0</v>
+      </c>
+      <c r="BG73">
+        <v>0</v>
+      </c>
+      <c r="BH73">
+        <v>0</v>
+      </c>
+      <c r="BI73">
+        <v>0</v>
+      </c>
+      <c r="BJ73">
+        <v>0</v>
+      </c>
+      <c r="BK73">
+        <v>0</v>
+      </c>
+      <c r="BL73">
+        <v>0</v>
+      </c>
+      <c r="BM73">
+        <v>0</v>
+      </c>
+      <c r="BN73">
+        <v>0</v>
+      </c>
+      <c r="BO73">
+        <v>0</v>
+      </c>
+      <c r="BP73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:68">
+      <c r="A74" s="1">
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <v>7778565</v>
+      </c>
+      <c r="C74" t="s">
+        <v>68</v>
+      </c>
+      <c r="D74" t="s">
+        <v>69</v>
+      </c>
+      <c r="E74" s="2">
+        <v>45752.08333333334</v>
+      </c>
+      <c r="F74">
+        <v>8</v>
+      </c>
+      <c r="G74" t="s">
+        <v>81</v>
+      </c>
+      <c r="H74" t="s">
+        <v>77</v>
+      </c>
+      <c r="I74">
+        <v>1</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>1</v>
+      </c>
+      <c r="L74">
+        <v>1</v>
+      </c>
+      <c r="M74">
+        <v>1</v>
+      </c>
+      <c r="N74">
+        <v>2</v>
+      </c>
+      <c r="O74" t="s">
+        <v>142</v>
+      </c>
+      <c r="P74" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q74">
+        <v>2.63</v>
+      </c>
+      <c r="R74">
+        <v>2.05</v>
+      </c>
+      <c r="S74">
+        <v>4.75</v>
+      </c>
+      <c r="T74">
+        <v>1.5</v>
+      </c>
+      <c r="U74">
+        <v>2.5</v>
+      </c>
+      <c r="V74">
+        <v>3.4</v>
+      </c>
+      <c r="W74">
+        <v>1.3</v>
+      </c>
+      <c r="X74">
+        <v>10</v>
+      </c>
+      <c r="Y74">
+        <v>1.06</v>
+      </c>
+      <c r="Z74">
+        <v>1.89</v>
+      </c>
+      <c r="AA74">
+        <v>3.47</v>
+      </c>
+      <c r="AB74">
+        <v>3.95</v>
+      </c>
+      <c r="AC74">
+        <v>0</v>
+      </c>
+      <c r="AD74">
+        <v>0</v>
+      </c>
+      <c r="AE74">
+        <v>3.19</v>
+      </c>
+      <c r="AF74">
+        <v>1.37</v>
+      </c>
+      <c r="AG74">
+        <v>2.15</v>
+      </c>
+      <c r="AH74">
+        <v>1.57</v>
+      </c>
+      <c r="AI74">
+        <v>2</v>
+      </c>
+      <c r="AJ74">
+        <v>1.73</v>
+      </c>
+      <c r="AK74">
+        <v>0</v>
+      </c>
+      <c r="AL74">
+        <v>0</v>
+      </c>
+      <c r="AM74">
+        <v>0</v>
+      </c>
+      <c r="AN74">
+        <v>1.25</v>
+      </c>
+      <c r="AO74">
+        <v>0.5</v>
+      </c>
+      <c r="AP74">
+        <v>1.2</v>
+      </c>
+      <c r="AQ74">
+        <v>0.67</v>
+      </c>
+      <c r="AR74">
+        <v>1.3</v>
+      </c>
+      <c r="AS74">
+        <v>1.17</v>
+      </c>
+      <c r="AT74">
+        <v>2.47</v>
+      </c>
+      <c r="AU74">
+        <v>3</v>
+      </c>
+      <c r="AV74">
+        <v>5</v>
+      </c>
+      <c r="AW74">
+        <v>5</v>
+      </c>
+      <c r="AX74">
+        <v>10</v>
+      </c>
+      <c r="AY74">
+        <v>8</v>
+      </c>
+      <c r="AZ74">
+        <v>15</v>
+      </c>
+      <c r="BA74">
+        <v>3</v>
+      </c>
+      <c r="BB74">
+        <v>3</v>
+      </c>
+      <c r="BC74">
+        <v>6</v>
+      </c>
+      <c r="BD74">
+        <v>0</v>
+      </c>
+      <c r="BE74">
+        <v>0</v>
+      </c>
+      <c r="BF74">
+        <v>0</v>
+      </c>
+      <c r="BG74">
+        <v>0</v>
+      </c>
+      <c r="BH74">
+        <v>0</v>
+      </c>
+      <c r="BI74">
+        <v>0</v>
+      </c>
+      <c r="BJ74">
+        <v>0</v>
+      </c>
+      <c r="BK74">
+        <v>0</v>
+      </c>
+      <c r="BL74">
+        <v>0</v>
+      </c>
+      <c r="BM74">
+        <v>0</v>
+      </c>
+      <c r="BN74">
+        <v>0</v>
+      </c>
+      <c r="BO74">
+        <v>0</v>
+      </c>
+      <c r="BP74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:68">
+      <c r="A75" s="1">
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <v>7778563</v>
+      </c>
+      <c r="C75" t="s">
+        <v>68</v>
+      </c>
+      <c r="D75" t="s">
+        <v>69</v>
+      </c>
+      <c r="E75" s="2">
+        <v>45752.08333333334</v>
+      </c>
+      <c r="F75">
+        <v>8</v>
+      </c>
+      <c r="G75" t="s">
+        <v>80</v>
+      </c>
+      <c r="H75" t="s">
+        <v>84</v>
+      </c>
+      <c r="I75">
+        <v>1</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>1</v>
+      </c>
+      <c r="L75">
+        <v>2</v>
+      </c>
+      <c r="M75">
+        <v>1</v>
+      </c>
+      <c r="N75">
+        <v>3</v>
+      </c>
+      <c r="O75" t="s">
+        <v>143</v>
+      </c>
+      <c r="P75" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q75">
+        <v>2.4</v>
+      </c>
+      <c r="R75">
+        <v>2.2</v>
+      </c>
+      <c r="S75">
+        <v>4.75</v>
+      </c>
+      <c r="T75">
+        <v>1.4</v>
+      </c>
+      <c r="U75">
+        <v>2.75</v>
+      </c>
+      <c r="V75">
+        <v>2.75</v>
+      </c>
+      <c r="W75">
+        <v>1.4</v>
+      </c>
+      <c r="X75">
+        <v>8</v>
+      </c>
+      <c r="Y75">
+        <v>1.08</v>
+      </c>
+      <c r="Z75">
+        <v>1.71</v>
+      </c>
+      <c r="AA75">
+        <v>3.81</v>
+      </c>
+      <c r="AB75">
+        <v>4.5</v>
+      </c>
+      <c r="AC75">
+        <v>0</v>
+      </c>
+      <c r="AD75">
+        <v>0</v>
+      </c>
+      <c r="AE75">
+        <v>0</v>
+      </c>
+      <c r="AF75">
+        <v>0</v>
+      </c>
+      <c r="AG75">
+        <v>1.85</v>
+      </c>
+      <c r="AH75">
+        <v>1.89</v>
+      </c>
+      <c r="AI75">
+        <v>1.8</v>
+      </c>
+      <c r="AJ75">
+        <v>1.91</v>
+      </c>
+      <c r="AK75">
+        <v>0</v>
+      </c>
+      <c r="AL75">
+        <v>0</v>
+      </c>
+      <c r="AM75">
+        <v>0</v>
+      </c>
+      <c r="AN75">
+        <v>3</v>
+      </c>
+      <c r="AO75">
+        <v>0.33</v>
+      </c>
+      <c r="AP75">
+        <v>3</v>
+      </c>
+      <c r="AQ75">
+        <v>0.25</v>
+      </c>
+      <c r="AR75">
+        <v>1.77</v>
+      </c>
+      <c r="AS75">
+        <v>1.48</v>
+      </c>
+      <c r="AT75">
+        <v>3.25</v>
+      </c>
+      <c r="AU75">
+        <v>6</v>
+      </c>
+      <c r="AV75">
+        <v>5</v>
+      </c>
+      <c r="AW75">
+        <v>9</v>
+      </c>
+      <c r="AX75">
+        <v>6</v>
+      </c>
+      <c r="AY75">
+        <v>17</v>
+      </c>
+      <c r="AZ75">
+        <v>12</v>
+      </c>
+      <c r="BA75">
+        <v>4</v>
+      </c>
+      <c r="BB75">
+        <v>6</v>
+      </c>
+      <c r="BC75">
+        <v>10</v>
+      </c>
+      <c r="BD75">
+        <v>0</v>
+      </c>
+      <c r="BE75">
+        <v>0</v>
+      </c>
+      <c r="BF75">
+        <v>0</v>
+      </c>
+      <c r="BG75">
+        <v>0</v>
+      </c>
+      <c r="BH75">
+        <v>0</v>
+      </c>
+      <c r="BI75">
+        <v>0</v>
+      </c>
+      <c r="BJ75">
+        <v>0</v>
+      </c>
+      <c r="BK75">
+        <v>0</v>
+      </c>
+      <c r="BL75">
+        <v>0</v>
+      </c>
+      <c r="BM75">
+        <v>0</v>
+      </c>
+      <c r="BN75">
+        <v>0</v>
+      </c>
+      <c r="BO75">
+        <v>0</v>
+      </c>
+      <c r="BP75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:68">
+      <c r="A76" s="1">
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <v>7778567</v>
+      </c>
+      <c r="C76" t="s">
+        <v>68</v>
+      </c>
+      <c r="D76" t="s">
+        <v>69</v>
+      </c>
+      <c r="E76" s="2">
+        <v>45752.08333333334</v>
+      </c>
+      <c r="F76">
+        <v>8</v>
+      </c>
+      <c r="G76" t="s">
+        <v>75</v>
+      </c>
+      <c r="H76" t="s">
+        <v>74</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>1</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>1</v>
+      </c>
+      <c r="O76" t="s">
+        <v>139</v>
+      </c>
+      <c r="P76" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q76">
+        <v>2.88</v>
+      </c>
+      <c r="R76">
+        <v>2.1</v>
+      </c>
+      <c r="S76">
+        <v>4</v>
+      </c>
+      <c r="T76">
+        <v>1.44</v>
+      </c>
+      <c r="U76">
+        <v>2.63</v>
+      </c>
+      <c r="V76">
+        <v>3.25</v>
+      </c>
+      <c r="W76">
+        <v>1.33</v>
+      </c>
+      <c r="X76">
+        <v>9</v>
+      </c>
+      <c r="Y76">
+        <v>1.07</v>
+      </c>
+      <c r="Z76">
+        <v>2.19</v>
+      </c>
+      <c r="AA76">
+        <v>3.11</v>
+      </c>
+      <c r="AB76">
+        <v>3.41</v>
+      </c>
+      <c r="AC76">
+        <v>0</v>
+      </c>
+      <c r="AD76">
+        <v>0</v>
+      </c>
+      <c r="AE76">
+        <v>3.49</v>
+      </c>
+      <c r="AF76">
+        <v>1.32</v>
+      </c>
+      <c r="AG76">
+        <v>1.95</v>
+      </c>
+      <c r="AH76">
+        <v>1.7</v>
+      </c>
+      <c r="AI76">
+        <v>1.83</v>
+      </c>
+      <c r="AJ76">
+        <v>1.83</v>
+      </c>
+      <c r="AK76">
+        <v>0</v>
+      </c>
+      <c r="AL76">
+        <v>0</v>
+      </c>
+      <c r="AM76">
+        <v>0</v>
+      </c>
+      <c r="AN76">
+        <v>1.5</v>
+      </c>
+      <c r="AO76">
+        <v>1</v>
+      </c>
+      <c r="AP76">
+        <v>1.8</v>
+      </c>
+      <c r="AQ76">
+        <v>0.75</v>
+      </c>
+      <c r="AR76">
+        <v>1.39</v>
+      </c>
+      <c r="AS76">
+        <v>1.39</v>
+      </c>
+      <c r="AT76">
+        <v>2.78</v>
+      </c>
+      <c r="AU76">
+        <v>4</v>
+      </c>
+      <c r="AV76">
+        <v>3</v>
+      </c>
+      <c r="AW76">
+        <v>2</v>
+      </c>
+      <c r="AX76">
+        <v>5</v>
+      </c>
+      <c r="AY76">
+        <v>8</v>
+      </c>
+      <c r="AZ76">
+        <v>9</v>
+      </c>
+      <c r="BA76">
+        <v>5</v>
+      </c>
+      <c r="BB76">
+        <v>5</v>
+      </c>
+      <c r="BC76">
+        <v>10</v>
+      </c>
+      <c r="BD76">
+        <v>0</v>
+      </c>
+      <c r="BE76">
+        <v>0</v>
+      </c>
+      <c r="BF76">
+        <v>0</v>
+      </c>
+      <c r="BG76">
+        <v>0</v>
+      </c>
+      <c r="BH76">
+        <v>0</v>
+      </c>
+      <c r="BI76">
+        <v>0</v>
+      </c>
+      <c r="BJ76">
+        <v>0</v>
+      </c>
+      <c r="BK76">
+        <v>0</v>
+      </c>
+      <c r="BL76">
+        <v>0</v>
+      </c>
+      <c r="BM76">
+        <v>0</v>
+      </c>
+      <c r="BN76">
+        <v>0</v>
+      </c>
+      <c r="BO76">
+        <v>0</v>
+      </c>
+      <c r="BP76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:68">
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>7778561</v>
+      </c>
+      <c r="C77" t="s">
+        <v>68</v>
+      </c>
+      <c r="D77" t="s">
+        <v>69</v>
+      </c>
+      <c r="E77" s="2">
+        <v>45752.08333333334</v>
+      </c>
+      <c r="F77">
+        <v>8</v>
+      </c>
+      <c r="G77" t="s">
+        <v>88</v>
+      </c>
+      <c r="H77" t="s">
+        <v>73</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77" t="s">
+        <v>90</v>
+      </c>
+      <c r="P77" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q77">
+        <v>3.1</v>
+      </c>
+      <c r="R77">
+        <v>2.2</v>
+      </c>
+      <c r="S77">
+        <v>3.25</v>
+      </c>
+      <c r="T77">
+        <v>1.36</v>
+      </c>
+      <c r="U77">
+        <v>3</v>
+      </c>
+      <c r="V77">
+        <v>2.63</v>
+      </c>
+      <c r="W77">
+        <v>1.44</v>
+      </c>
+      <c r="X77">
+        <v>7</v>
+      </c>
+      <c r="Y77">
+        <v>1.1</v>
+      </c>
+      <c r="Z77">
+        <v>2.54</v>
+      </c>
+      <c r="AA77">
+        <v>3.38</v>
+      </c>
+      <c r="AB77">
+        <v>2.63</v>
+      </c>
+      <c r="AC77">
+        <v>3.8</v>
+      </c>
+      <c r="AD77">
+        <v>1.28</v>
+      </c>
+      <c r="AE77">
+        <v>0</v>
+      </c>
+      <c r="AF77">
+        <v>0</v>
+      </c>
+      <c r="AG77">
+        <v>1.85</v>
+      </c>
+      <c r="AH77">
+        <v>1.89</v>
+      </c>
+      <c r="AI77">
+        <v>1.67</v>
+      </c>
+      <c r="AJ77">
+        <v>2.1</v>
+      </c>
+      <c r="AK77">
+        <v>0</v>
+      </c>
+      <c r="AL77">
+        <v>0</v>
+      </c>
+      <c r="AM77">
+        <v>0</v>
+      </c>
+      <c r="AN77">
+        <v>2</v>
+      </c>
+      <c r="AO77">
+        <v>1</v>
+      </c>
+      <c r="AP77">
+        <v>1.67</v>
+      </c>
+      <c r="AQ77">
+        <v>1</v>
+      </c>
+      <c r="AR77">
+        <v>1.29</v>
+      </c>
+      <c r="AS77">
+        <v>1.03</v>
+      </c>
+      <c r="AT77">
+        <v>2.32</v>
+      </c>
+      <c r="AU77">
+        <v>5</v>
+      </c>
+      <c r="AV77">
+        <v>2</v>
+      </c>
+      <c r="AW77">
+        <v>8</v>
+      </c>
+      <c r="AX77">
+        <v>6</v>
+      </c>
+      <c r="AY77">
+        <v>16</v>
+      </c>
+      <c r="AZ77">
+        <v>9</v>
+      </c>
+      <c r="BA77">
+        <v>3</v>
+      </c>
+      <c r="BB77">
+        <v>6</v>
+      </c>
+      <c r="BC77">
+        <v>9</v>
+      </c>
+      <c r="BD77">
+        <v>0</v>
+      </c>
+      <c r="BE77">
+        <v>0</v>
+      </c>
+      <c r="BF77">
+        <v>0</v>
+      </c>
+      <c r="BG77">
+        <v>0</v>
+      </c>
+      <c r="BH77">
+        <v>0</v>
+      </c>
+      <c r="BI77">
+        <v>0</v>
+      </c>
+      <c r="BJ77">
+        <v>0</v>
+      </c>
+      <c r="BK77">
+        <v>0</v>
+      </c>
+      <c r="BL77">
+        <v>0</v>
+      </c>
+      <c r="BM77">
+        <v>0</v>
+      </c>
+      <c r="BN77">
+        <v>0</v>
+      </c>
+      <c r="BO77">
+        <v>0</v>
+      </c>
+      <c r="BP77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:68">
+      <c r="A78" s="1">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>7778559</v>
+      </c>
+      <c r="C78" t="s">
+        <v>68</v>
+      </c>
+      <c r="D78" t="s">
+        <v>69</v>
+      </c>
+      <c r="E78" s="2">
+        <v>45752.08333333334</v>
+      </c>
+      <c r="F78">
+        <v>8</v>
+      </c>
+      <c r="G78" t="s">
+        <v>87</v>
+      </c>
+      <c r="H78" t="s">
+        <v>83</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>1</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>1</v>
+      </c>
+      <c r="O78" t="s">
+        <v>144</v>
+      </c>
+      <c r="P78" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q78">
+        <v>3.25</v>
+      </c>
+      <c r="R78">
+        <v>2</v>
+      </c>
+      <c r="S78">
+        <v>3.6</v>
+      </c>
+      <c r="T78">
+        <v>1.5</v>
+      </c>
+      <c r="U78">
+        <v>2.5</v>
+      </c>
+      <c r="V78">
+        <v>3.4</v>
+      </c>
+      <c r="W78">
+        <v>1.3</v>
+      </c>
+      <c r="X78">
+        <v>10</v>
+      </c>
+      <c r="Y78">
+        <v>1.06</v>
+      </c>
+      <c r="Z78">
+        <v>2.55</v>
+      </c>
+      <c r="AA78">
+        <v>3.12</v>
+      </c>
+      <c r="AB78">
+        <v>2.8</v>
+      </c>
+      <c r="AC78">
+        <v>3.06</v>
+      </c>
+      <c r="AD78">
+        <v>1.39</v>
+      </c>
+      <c r="AE78">
+        <v>0</v>
+      </c>
+      <c r="AF78">
+        <v>0</v>
+      </c>
+      <c r="AG78">
+        <v>2.1</v>
+      </c>
+      <c r="AH78">
+        <v>1.6</v>
+      </c>
+      <c r="AI78">
+        <v>1.91</v>
+      </c>
+      <c r="AJ78">
+        <v>1.8</v>
+      </c>
+      <c r="AK78">
+        <v>0</v>
+      </c>
+      <c r="AL78">
+        <v>0</v>
+      </c>
+      <c r="AM78">
+        <v>0</v>
+      </c>
+      <c r="AN78">
+        <v>0</v>
+      </c>
+      <c r="AO78">
+        <v>1.25</v>
+      </c>
+      <c r="AP78">
+        <v>1</v>
+      </c>
+      <c r="AQ78">
+        <v>1</v>
+      </c>
+      <c r="AR78">
+        <v>1.6</v>
+      </c>
+      <c r="AS78">
+        <v>1.44</v>
+      </c>
+      <c r="AT78">
+        <v>3.04</v>
+      </c>
+      <c r="AU78">
+        <v>3</v>
+      </c>
+      <c r="AV78">
+        <v>4</v>
+      </c>
+      <c r="AW78">
+        <v>10</v>
+      </c>
+      <c r="AX78">
+        <v>2</v>
+      </c>
+      <c r="AY78">
+        <v>13</v>
+      </c>
+      <c r="AZ78">
+        <v>6</v>
+      </c>
+      <c r="BA78">
+        <v>6</v>
+      </c>
+      <c r="BB78">
+        <v>4</v>
+      </c>
+      <c r="BC78">
+        <v>10</v>
+      </c>
+      <c r="BD78">
+        <v>0</v>
+      </c>
+      <c r="BE78">
+        <v>0</v>
+      </c>
+      <c r="BF78">
+        <v>0</v>
+      </c>
+      <c r="BG78">
+        <v>0</v>
+      </c>
+      <c r="BH78">
+        <v>0</v>
+      </c>
+      <c r="BI78">
+        <v>0</v>
+      </c>
+      <c r="BJ78">
+        <v>0</v>
+      </c>
+      <c r="BK78">
+        <v>0</v>
+      </c>
+      <c r="BL78">
+        <v>0</v>
+      </c>
+      <c r="BM78">
+        <v>0</v>
+      </c>
+      <c r="BN78">
+        <v>0</v>
+      </c>
+      <c r="BO78">
+        <v>0</v>
+      </c>
+      <c r="BP78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:68">
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>7778562</v>
+      </c>
+      <c r="C79" t="s">
+        <v>68</v>
+      </c>
+      <c r="D79" t="s">
+        <v>69</v>
+      </c>
+      <c r="E79" s="2">
+        <v>45752.08333333334</v>
+      </c>
+      <c r="F79">
+        <v>8</v>
+      </c>
+      <c r="G79" t="s">
+        <v>71</v>
+      </c>
+      <c r="H79" t="s">
+        <v>79</v>
+      </c>
+      <c r="I79">
+        <v>1</v>
+      </c>
+      <c r="J79">
+        <v>1</v>
+      </c>
+      <c r="K79">
+        <v>2</v>
+      </c>
+      <c r="L79">
+        <v>2</v>
+      </c>
+      <c r="M79">
+        <v>2</v>
+      </c>
+      <c r="N79">
+        <v>4</v>
+      </c>
+      <c r="O79" t="s">
+        <v>145</v>
+      </c>
+      <c r="P79" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q79">
+        <v>2.63</v>
+      </c>
+      <c r="R79">
+        <v>2</v>
+      </c>
+      <c r="S79">
+        <v>5</v>
+      </c>
+      <c r="T79">
+        <v>1.53</v>
+      </c>
+      <c r="U79">
+        <v>2.38</v>
+      </c>
+      <c r="V79">
+        <v>3.5</v>
+      </c>
+      <c r="W79">
+        <v>1.29</v>
+      </c>
+      <c r="X79">
+        <v>11</v>
+      </c>
+      <c r="Y79">
+        <v>1.05</v>
+      </c>
+      <c r="Z79">
+        <v>1.86</v>
+      </c>
+      <c r="AA79">
+        <v>3.38</v>
+      </c>
+      <c r="AB79">
+        <v>4.2</v>
+      </c>
+      <c r="AC79">
+        <v>0</v>
+      </c>
+      <c r="AD79">
+        <v>0</v>
+      </c>
+      <c r="AE79">
+        <v>0</v>
+      </c>
+      <c r="AF79">
+        <v>0</v>
+      </c>
+      <c r="AG79">
+        <v>2.4</v>
+      </c>
+      <c r="AH79">
+        <v>1.5</v>
+      </c>
+      <c r="AI79">
+        <v>2.2</v>
+      </c>
+      <c r="AJ79">
+        <v>1.62</v>
+      </c>
+      <c r="AK79">
+        <v>0</v>
+      </c>
+      <c r="AL79">
+        <v>0</v>
+      </c>
+      <c r="AM79">
+        <v>0</v>
+      </c>
+      <c r="AN79">
+        <v>3</v>
+      </c>
+      <c r="AO79">
+        <v>1.33</v>
+      </c>
+      <c r="AP79">
+        <v>2.6</v>
+      </c>
+      <c r="AQ79">
+        <v>1.25</v>
+      </c>
+      <c r="AR79">
+        <v>2.01</v>
+      </c>
+      <c r="AS79">
+        <v>1.16</v>
+      </c>
+      <c r="AT79">
+        <v>3.17</v>
+      </c>
+      <c r="AU79">
+        <v>4</v>
+      </c>
+      <c r="AV79">
+        <v>8</v>
+      </c>
+      <c r="AW79">
+        <v>7</v>
+      </c>
+      <c r="AX79">
+        <v>3</v>
+      </c>
+      <c r="AY79">
+        <v>13</v>
+      </c>
+      <c r="AZ79">
+        <v>11</v>
+      </c>
+      <c r="BA79">
+        <v>3</v>
+      </c>
+      <c r="BB79">
+        <v>3</v>
+      </c>
+      <c r="BC79">
+        <v>6</v>
+      </c>
+      <c r="BD79">
+        <v>0</v>
+      </c>
+      <c r="BE79">
+        <v>0</v>
+      </c>
+      <c r="BF79">
+        <v>0</v>
+      </c>
+      <c r="BG79">
+        <v>0</v>
+      </c>
+      <c r="BH79">
+        <v>0</v>
+      </c>
+      <c r="BI79">
+        <v>0</v>
+      </c>
+      <c r="BJ79">
+        <v>0</v>
+      </c>
+      <c r="BK79">
+        <v>0</v>
+      </c>
+      <c r="BL79">
+        <v>0</v>
+      </c>
+      <c r="BM79">
+        <v>0</v>
+      </c>
+      <c r="BN79">
+        <v>0</v>
+      </c>
+      <c r="BO79">
+        <v>0</v>
+      </c>
+      <c r="BP79">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="186">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -454,6 +454,9 @@
     <t>['21', '90+4']</t>
   </si>
   <si>
+    <t>['6', '51', '53', '65']</t>
+  </si>
+  <si>
     <t>['31', '60']</t>
   </si>
   <si>
@@ -566,6 +569,9 @@
   </si>
   <si>
     <t>['20', '53']</t>
+  </si>
+  <si>
+    <t>['36']</t>
   </si>
 </sst>
 </file>
@@ -927,7 +933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP79"/>
+  <dimension ref="A1:BP81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1183,7 +1189,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q2">
         <v>3.6</v>
@@ -1389,7 +1395,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q3">
         <v>3.75</v>
@@ -1801,7 +1807,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2007,7 +2013,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q6">
         <v>4.1</v>
@@ -2213,7 +2219,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q7">
         <v>2.88</v>
@@ -2419,7 +2425,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q8">
         <v>2.28</v>
@@ -2625,7 +2631,7 @@
         <v>90</v>
       </c>
       <c r="P9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -2831,7 +2837,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -2909,7 +2915,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ10">
         <v>1</v>
@@ -3861,7 +3867,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q15">
         <v>4.1</v>
@@ -3942,7 +3948,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ15">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4145,7 +4151,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ16">
         <v>1.2</v>
@@ -4763,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ19">
         <v>0.75</v>
@@ -5097,7 +5103,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q21">
         <v>4.4</v>
@@ -5509,7 +5515,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5921,7 +5927,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -6127,7 +6133,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q26">
         <v>3.95</v>
@@ -6333,7 +6339,7 @@
         <v>90</v>
       </c>
       <c r="P27" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q27">
         <v>3.2</v>
@@ -6411,7 +6417,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ27">
         <v>1</v>
@@ -6539,7 +6545,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q28">
         <v>3.35</v>
@@ -7363,7 +7369,7 @@
         <v>113</v>
       </c>
       <c r="P32" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q32">
         <v>3.45</v>
@@ -7444,7 +7450,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ32">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AR32">
         <v>1.26</v>
@@ -7569,7 +7575,7 @@
         <v>114</v>
       </c>
       <c r="P33" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -7775,7 +7781,7 @@
         <v>115</v>
       </c>
       <c r="P34" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -7981,7 +7987,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q35">
         <v>3.4</v>
@@ -8187,7 +8193,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q36">
         <v>2.8</v>
@@ -8599,7 +8605,7 @@
         <v>118</v>
       </c>
       <c r="P38" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q38">
         <v>2.6</v>
@@ -8805,7 +8811,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q39">
         <v>4</v>
@@ -9423,7 +9429,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9835,7 +9841,7 @@
         <v>121</v>
       </c>
       <c r="P44" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10453,7 +10459,7 @@
         <v>105</v>
       </c>
       <c r="P47" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10531,7 +10537,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ47">
         <v>0.8</v>
@@ -10659,7 +10665,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q48">
         <v>3.6</v>
@@ -10865,7 +10871,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q49">
         <v>3.6</v>
@@ -11149,7 +11155,7 @@
         <v>1.5</v>
       </c>
       <c r="AP50">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ50">
         <v>1</v>
@@ -11277,7 +11283,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q51">
         <v>1.91</v>
@@ -11483,7 +11489,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -11689,7 +11695,7 @@
         <v>90</v>
       </c>
       <c r="P53" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12307,7 +12313,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q56">
         <v>4.33</v>
@@ -12925,7 +12931,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13337,7 +13343,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13543,7 +13549,7 @@
         <v>90</v>
       </c>
       <c r="P62" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q62">
         <v>2.75</v>
@@ -13749,7 +13755,7 @@
         <v>133</v>
       </c>
       <c r="P63" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q63">
         <v>3</v>
@@ -13827,7 +13833,7 @@
         <v>0.5</v>
       </c>
       <c r="AP63">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ63">
         <v>0.33</v>
@@ -13955,7 +13961,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q64">
         <v>3.1</v>
@@ -14161,7 +14167,7 @@
         <v>90</v>
       </c>
       <c r="P65" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q65">
         <v>3.6</v>
@@ -14367,7 +14373,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q66">
         <v>4.75</v>
@@ -14448,7 +14454,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ66">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AR66">
         <v>1.04</v>
@@ -14573,7 +14579,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q67">
         <v>2.88</v>
@@ -14651,7 +14657,7 @@
         <v>0.75</v>
       </c>
       <c r="AP67">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ67">
         <v>0.8</v>
@@ -16015,7 +16021,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q74">
         <v>2.63</v>
@@ -17045,7 +17051,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q79">
         <v>2.63</v>
@@ -17202,6 +17208,418 @@
       </c>
       <c r="BP79">
         <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:68">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>7778568</v>
+      </c>
+      <c r="C80" t="s">
+        <v>68</v>
+      </c>
+      <c r="D80" t="s">
+        <v>69</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45753.04166666666</v>
+      </c>
+      <c r="F80">
+        <v>8</v>
+      </c>
+      <c r="G80" t="s">
+        <v>82</v>
+      </c>
+      <c r="H80" t="s">
+        <v>86</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80" t="s">
+        <v>90</v>
+      </c>
+      <c r="P80" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q80">
+        <v>3.2</v>
+      </c>
+      <c r="R80">
+        <v>2.1</v>
+      </c>
+      <c r="S80">
+        <v>3.4</v>
+      </c>
+      <c r="T80">
+        <v>1.4</v>
+      </c>
+      <c r="U80">
+        <v>2.75</v>
+      </c>
+      <c r="V80">
+        <v>3</v>
+      </c>
+      <c r="W80">
+        <v>1.36</v>
+      </c>
+      <c r="X80">
+        <v>9</v>
+      </c>
+      <c r="Y80">
+        <v>1.07</v>
+      </c>
+      <c r="Z80">
+        <v>2.42</v>
+      </c>
+      <c r="AA80">
+        <v>3.57</v>
+      </c>
+      <c r="AB80">
+        <v>2.66</v>
+      </c>
+      <c r="AC80">
+        <v>1</v>
+      </c>
+      <c r="AD80">
+        <v>9</v>
+      </c>
+      <c r="AE80">
+        <v>1.27</v>
+      </c>
+      <c r="AF80">
+        <v>3.14</v>
+      </c>
+      <c r="AG80">
+        <v>1.95</v>
+      </c>
+      <c r="AH80">
+        <v>1.79</v>
+      </c>
+      <c r="AI80">
+        <v>1.8</v>
+      </c>
+      <c r="AJ80">
+        <v>1.91</v>
+      </c>
+      <c r="AK80">
+        <v>1.44</v>
+      </c>
+      <c r="AL80">
+        <v>1.3</v>
+      </c>
+      <c r="AM80">
+        <v>1.55</v>
+      </c>
+      <c r="AN80">
+        <v>1.5</v>
+      </c>
+      <c r="AO80">
+        <v>1</v>
+      </c>
+      <c r="AP80">
+        <v>1.4</v>
+      </c>
+      <c r="AQ80">
+        <v>1</v>
+      </c>
+      <c r="AR80">
+        <v>1.56</v>
+      </c>
+      <c r="AS80">
+        <v>1.13</v>
+      </c>
+      <c r="AT80">
+        <v>2.69</v>
+      </c>
+      <c r="AU80">
+        <v>2</v>
+      </c>
+      <c r="AV80">
+        <v>3</v>
+      </c>
+      <c r="AW80">
+        <v>7</v>
+      </c>
+      <c r="AX80">
+        <v>3</v>
+      </c>
+      <c r="AY80">
+        <v>9</v>
+      </c>
+      <c r="AZ80">
+        <v>6</v>
+      </c>
+      <c r="BA80">
+        <v>6</v>
+      </c>
+      <c r="BB80">
+        <v>3</v>
+      </c>
+      <c r="BC80">
+        <v>9</v>
+      </c>
+      <c r="BD80">
+        <v>1.56</v>
+      </c>
+      <c r="BE80">
+        <v>6.55</v>
+      </c>
+      <c r="BF80">
+        <v>3.08</v>
+      </c>
+      <c r="BG80">
+        <v>1.28</v>
+      </c>
+      <c r="BH80">
+        <v>3.08</v>
+      </c>
+      <c r="BI80">
+        <v>1.52</v>
+      </c>
+      <c r="BJ80">
+        <v>2.24</v>
+      </c>
+      <c r="BK80">
+        <v>1.92</v>
+      </c>
+      <c r="BL80">
+        <v>1.75</v>
+      </c>
+      <c r="BM80">
+        <v>2.49</v>
+      </c>
+      <c r="BN80">
+        <v>1.42</v>
+      </c>
+      <c r="BO80">
+        <v>3.42</v>
+      </c>
+      <c r="BP80">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="81" spans="1:68">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>7778566</v>
+      </c>
+      <c r="C81" t="s">
+        <v>68</v>
+      </c>
+      <c r="D81" t="s">
+        <v>69</v>
+      </c>
+      <c r="E81" s="2">
+        <v>45753.0625</v>
+      </c>
+      <c r="F81">
+        <v>8</v>
+      </c>
+      <c r="G81" t="s">
+        <v>78</v>
+      </c>
+      <c r="H81" t="s">
+        <v>76</v>
+      </c>
+      <c r="I81">
+        <v>1</v>
+      </c>
+      <c r="J81">
+        <v>1</v>
+      </c>
+      <c r="K81">
+        <v>2</v>
+      </c>
+      <c r="L81">
+        <v>4</v>
+      </c>
+      <c r="M81">
+        <v>1</v>
+      </c>
+      <c r="N81">
+        <v>5</v>
+      </c>
+      <c r="O81" t="s">
+        <v>146</v>
+      </c>
+      <c r="P81" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q81">
+        <v>3.2</v>
+      </c>
+      <c r="R81">
+        <v>2.2</v>
+      </c>
+      <c r="S81">
+        <v>3.4</v>
+      </c>
+      <c r="T81">
+        <v>1.4</v>
+      </c>
+      <c r="U81">
+        <v>2.75</v>
+      </c>
+      <c r="V81">
+        <v>2.75</v>
+      </c>
+      <c r="W81">
+        <v>1.4</v>
+      </c>
+      <c r="X81">
+        <v>8</v>
+      </c>
+      <c r="Y81">
+        <v>1.08</v>
+      </c>
+      <c r="Z81">
+        <v>2.49</v>
+      </c>
+      <c r="AA81">
+        <v>3.32</v>
+      </c>
+      <c r="AB81">
+        <v>2.73</v>
+      </c>
+      <c r="AC81">
+        <v>1</v>
+      </c>
+      <c r="AD81">
+        <v>9</v>
+      </c>
+      <c r="AE81">
+        <v>1.24</v>
+      </c>
+      <c r="AF81">
+        <v>3.34</v>
+      </c>
+      <c r="AG81">
+        <v>1.87</v>
+      </c>
+      <c r="AH81">
+        <v>1.87</v>
+      </c>
+      <c r="AI81">
+        <v>1.73</v>
+      </c>
+      <c r="AJ81">
+        <v>2</v>
+      </c>
+      <c r="AK81">
+        <v>1.44</v>
+      </c>
+      <c r="AL81">
+        <v>1.33</v>
+      </c>
+      <c r="AM81">
+        <v>1.5</v>
+      </c>
+      <c r="AN81">
+        <v>0.75</v>
+      </c>
+      <c r="AO81">
+        <v>0.67</v>
+      </c>
+      <c r="AP81">
+        <v>1.2</v>
+      </c>
+      <c r="AQ81">
+        <v>0.5</v>
+      </c>
+      <c r="AR81">
+        <v>1.55</v>
+      </c>
+      <c r="AS81">
+        <v>1.63</v>
+      </c>
+      <c r="AT81">
+        <v>3.18</v>
+      </c>
+      <c r="AU81">
+        <v>7</v>
+      </c>
+      <c r="AV81">
+        <v>6</v>
+      </c>
+      <c r="AW81">
+        <v>2</v>
+      </c>
+      <c r="AX81">
+        <v>7</v>
+      </c>
+      <c r="AY81">
+        <v>9</v>
+      </c>
+      <c r="AZ81">
+        <v>13</v>
+      </c>
+      <c r="BA81">
+        <v>1</v>
+      </c>
+      <c r="BB81">
+        <v>4</v>
+      </c>
+      <c r="BC81">
+        <v>5</v>
+      </c>
+      <c r="BD81">
+        <v>1.71</v>
+      </c>
+      <c r="BE81">
+        <v>6.35</v>
+      </c>
+      <c r="BF81">
+        <v>2.66</v>
+      </c>
+      <c r="BG81">
+        <v>1.25</v>
+      </c>
+      <c r="BH81">
+        <v>3.28</v>
+      </c>
+      <c r="BI81">
+        <v>1.48</v>
+      </c>
+      <c r="BJ81">
+        <v>2.33</v>
+      </c>
+      <c r="BK81">
+        <v>1.85</v>
+      </c>
+      <c r="BL81">
+        <v>1.81</v>
+      </c>
+      <c r="BM81">
+        <v>2.38</v>
+      </c>
+      <c r="BN81">
+        <v>1.46</v>
+      </c>
+      <c r="BO81">
+        <v>3.2</v>
+      </c>
+      <c r="BP81">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="185">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -439,13 +439,10 @@
     <t>['10']</t>
   </si>
   <si>
-    <t>['58']</t>
-  </si>
-  <si>
     <t>['3']</t>
   </si>
   <si>
-    <t>['24', '76']</t>
+    <t>['23', '77']</t>
   </si>
   <si>
     <t>['90+5']</t>
@@ -1189,7 +1186,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q2">
         <v>3.6</v>
@@ -1395,7 +1392,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Q3">
         <v>3.75</v>
@@ -1807,7 +1804,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2013,7 +2010,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Q6">
         <v>4.1</v>
@@ -2219,7 +2216,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q7">
         <v>2.88</v>
@@ -2425,7 +2422,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q8">
         <v>2.28</v>
@@ -2631,7 +2628,7 @@
         <v>90</v>
       </c>
       <c r="P9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -2837,7 +2834,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -3867,7 +3864,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q15">
         <v>4.1</v>
@@ -5103,7 +5100,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q21">
         <v>4.4</v>
@@ -5515,7 +5512,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5927,7 +5924,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -6133,7 +6130,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q26">
         <v>3.95</v>
@@ -6339,7 +6336,7 @@
         <v>90</v>
       </c>
       <c r="P27" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q27">
         <v>3.2</v>
@@ -6545,7 +6542,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q28">
         <v>3.35</v>
@@ -6957,7 +6954,7 @@
         <v>111</v>
       </c>
       <c r="P30" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q30">
         <v>2.38</v>
@@ -7369,7 +7366,7 @@
         <v>113</v>
       </c>
       <c r="P32" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q32">
         <v>3.45</v>
@@ -7575,7 +7572,7 @@
         <v>114</v>
       </c>
       <c r="P33" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -7781,7 +7778,7 @@
         <v>115</v>
       </c>
       <c r="P34" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -7987,7 +7984,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q35">
         <v>3.4</v>
@@ -8193,7 +8190,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q36">
         <v>2.8</v>
@@ -8605,7 +8602,7 @@
         <v>118</v>
       </c>
       <c r="P38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q38">
         <v>2.6</v>
@@ -8811,7 +8808,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q39">
         <v>4</v>
@@ -9429,7 +9426,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9841,7 +9838,7 @@
         <v>121</v>
       </c>
       <c r="P44" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10459,7 +10456,7 @@
         <v>105</v>
       </c>
       <c r="P47" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10665,7 +10662,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q48">
         <v>3.6</v>
@@ -10871,7 +10868,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q49">
         <v>3.6</v>
@@ -11283,7 +11280,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q51">
         <v>1.91</v>
@@ -11489,7 +11486,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -11695,7 +11692,7 @@
         <v>90</v>
       </c>
       <c r="P53" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12313,7 +12310,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q56">
         <v>4.33</v>
@@ -12931,7 +12928,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13343,7 +13340,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13549,7 +13546,7 @@
         <v>90</v>
       </c>
       <c r="P62" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q62">
         <v>2.75</v>
@@ -13755,7 +13752,7 @@
         <v>133</v>
       </c>
       <c r="P63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q63">
         <v>3</v>
@@ -13961,7 +13958,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q64">
         <v>3.1</v>
@@ -14167,7 +14164,7 @@
         <v>90</v>
       </c>
       <c r="P65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q65">
         <v>3.6</v>
@@ -14373,7 +14370,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q66">
         <v>4.75</v>
@@ -14579,7 +14576,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q67">
         <v>2.88</v>
@@ -15812,7 +15809,7 @@
         <v>1</v>
       </c>
       <c r="O73" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="P73" t="s">
         <v>90</v>
@@ -16018,10 +16015,10 @@
         <v>2</v>
       </c>
       <c r="O74" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q74">
         <v>2.63</v>
@@ -16224,7 +16221,7 @@
         <v>3</v>
       </c>
       <c r="O75" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P75" t="s">
         <v>101</v>
@@ -16842,7 +16839,7 @@
         <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P78" t="s">
         <v>90</v>
@@ -17048,10 +17045,10 @@
         <v>4</v>
       </c>
       <c r="O79" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q79">
         <v>2.63</v>
@@ -17460,10 +17457,10 @@
         <v>5</v>
       </c>
       <c r="O81" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P81" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q81">
         <v>3.2</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -38041,22 +38041,22 @@
         <v>2.78</v>
       </c>
       <c r="AU179">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV179">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW179">
         <v>7</v>
       </c>
       <c r="AX179">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY179">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ179">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BA179">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="286">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -625,6 +625,9 @@
     <t>['9001']</t>
   </si>
   <si>
+    <t>['84']</t>
+  </si>
+  <si>
     <t>['31', '60']</t>
   </si>
   <si>
@@ -1230,7 +1233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP181"/>
+  <dimension ref="A1:BP182"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1486,7 +1489,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q2">
         <v>3.6</v>
@@ -2104,7 +2107,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2310,7 +2313,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q6">
         <v>4.1</v>
@@ -2722,7 +2725,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q8">
         <v>2.28</v>
@@ -3627,7 +3630,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ12">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR12">
         <v>1.68</v>
@@ -4164,7 +4167,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q15">
         <v>4.1</v>
@@ -4860,7 +4863,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ18">
         <v>0.82</v>
@@ -5400,7 +5403,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q21">
         <v>4.4</v>
@@ -5812,7 +5815,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -6224,7 +6227,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -6636,7 +6639,7 @@
         <v>90</v>
       </c>
       <c r="P27" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q27">
         <v>3.2</v>
@@ -7332,7 +7335,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ30">
         <v>1.33</v>
@@ -7666,7 +7669,7 @@
         <v>113</v>
       </c>
       <c r="P32" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q32">
         <v>3.45</v>
@@ -7872,7 +7875,7 @@
         <v>114</v>
       </c>
       <c r="P33" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8078,7 +8081,7 @@
         <v>115</v>
       </c>
       <c r="P34" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8284,7 +8287,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q35">
         <v>3.4</v>
@@ -8490,7 +8493,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q36">
         <v>2.8</v>
@@ -8777,7 +8780,7 @@
         <v>1</v>
       </c>
       <c r="AQ37">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR37">
         <v>1.86</v>
@@ -8902,7 +8905,7 @@
         <v>118</v>
       </c>
       <c r="P38" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q38">
         <v>2.6</v>
@@ -9726,7 +9729,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10756,7 +10759,7 @@
         <v>105</v>
       </c>
       <c r="P47" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10962,7 +10965,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q48">
         <v>3.6</v>
@@ -11040,7 +11043,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ48">
         <v>1.89</v>
@@ -11168,7 +11171,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q49">
         <v>3.6</v>
@@ -11580,7 +11583,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q51">
         <v>1.91</v>
@@ -11786,7 +11789,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -11992,7 +11995,7 @@
         <v>90</v>
       </c>
       <c r="P53" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12610,7 +12613,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q56">
         <v>4.33</v>
@@ -13228,7 +13231,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13640,7 +13643,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13846,7 +13849,7 @@
         <v>90</v>
       </c>
       <c r="P62" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q62">
         <v>2.75</v>
@@ -14133,7 +14136,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ63">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR63">
         <v>1.46</v>
@@ -14336,7 +14339,7 @@
         <v>0.5</v>
       </c>
       <c r="AP64">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ64">
         <v>1</v>
@@ -14464,7 +14467,7 @@
         <v>90</v>
       </c>
       <c r="P65" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q65">
         <v>3.6</v>
@@ -14670,7 +14673,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q66">
         <v>4.75</v>
@@ -14876,7 +14879,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q67">
         <v>2.88</v>
@@ -17348,7 +17351,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q79">
         <v>2.63</v>
@@ -17760,7 +17763,7 @@
         <v>145</v>
       </c>
       <c r="P81" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q81">
         <v>3.2</v>
@@ -18456,7 +18459,7 @@
         <v>1.2</v>
       </c>
       <c r="AP84">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ84">
         <v>1</v>
@@ -18790,7 +18793,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -18996,7 +18999,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19202,7 +19205,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19408,7 +19411,7 @@
         <v>90</v>
       </c>
       <c r="P89" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19489,7 +19492,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ89">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR89">
         <v>2.31</v>
@@ -20026,7 +20029,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q92">
         <v>4</v>
@@ -20232,7 +20235,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q93">
         <v>3</v>
@@ -20438,7 +20441,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q94">
         <v>2.3</v>
@@ -20644,7 +20647,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q95">
         <v>3.5</v>
@@ -21056,7 +21059,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q97">
         <v>3.25</v>
@@ -21674,7 +21677,7 @@
         <v>157</v>
       </c>
       <c r="P100" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q100">
         <v>2.6</v>
@@ -21880,7 +21883,7 @@
         <v>122</v>
       </c>
       <c r="P101" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q101">
         <v>3.25</v>
@@ -22086,7 +22089,7 @@
         <v>158</v>
       </c>
       <c r="P102" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q102">
         <v>2.25</v>
@@ -22370,7 +22373,7 @@
         <v>0.8</v>
       </c>
       <c r="AP103">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ103">
         <v>1.3</v>
@@ -22704,7 +22707,7 @@
         <v>160</v>
       </c>
       <c r="P105" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q105">
         <v>2.38</v>
@@ -22910,7 +22913,7 @@
         <v>90</v>
       </c>
       <c r="P106" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23116,7 +23119,7 @@
         <v>90</v>
       </c>
       <c r="P107" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q107">
         <v>3.25</v>
@@ -23322,7 +23325,7 @@
         <v>161</v>
       </c>
       <c r="P108" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23528,7 +23531,7 @@
         <v>162</v>
       </c>
       <c r="P109" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q109">
         <v>2.3</v>
@@ -23940,7 +23943,7 @@
         <v>122</v>
       </c>
       <c r="P111" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q111">
         <v>4</v>
@@ -24352,7 +24355,7 @@
         <v>164</v>
       </c>
       <c r="P113" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q113">
         <v>3.6</v>
@@ -24636,7 +24639,7 @@
         <v>2.6</v>
       </c>
       <c r="AP114">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ114">
         <v>2.13</v>
@@ -24764,7 +24767,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q115">
         <v>3.75</v>
@@ -24970,7 +24973,7 @@
         <v>165</v>
       </c>
       <c r="P116" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q116">
         <v>3.25</v>
@@ -25257,7 +25260,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ117">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR117">
         <v>1.11</v>
@@ -26000,7 +26003,7 @@
         <v>167</v>
       </c>
       <c r="P121" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q121">
         <v>3.4</v>
@@ -26206,7 +26209,7 @@
         <v>168</v>
       </c>
       <c r="P122" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26412,7 +26415,7 @@
         <v>169</v>
       </c>
       <c r="P123" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q123">
         <v>3.4</v>
@@ -26618,7 +26621,7 @@
         <v>90</v>
       </c>
       <c r="P124" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q124">
         <v>4</v>
@@ -27236,7 +27239,7 @@
         <v>171</v>
       </c>
       <c r="P127" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27442,7 +27445,7 @@
         <v>90</v>
       </c>
       <c r="P128" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q128">
         <v>2.88</v>
@@ -27648,7 +27651,7 @@
         <v>172</v>
       </c>
       <c r="P129" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -27854,7 +27857,7 @@
         <v>90</v>
       </c>
       <c r="P130" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q130">
         <v>3.4</v>
@@ -28060,7 +28063,7 @@
         <v>173</v>
       </c>
       <c r="P131" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q131">
         <v>2.1</v>
@@ -28266,7 +28269,7 @@
         <v>174</v>
       </c>
       <c r="P132" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q132">
         <v>2.5</v>
@@ -28472,7 +28475,7 @@
         <v>175</v>
       </c>
       <c r="P133" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q133">
         <v>4</v>
@@ -28678,7 +28681,7 @@
         <v>176</v>
       </c>
       <c r="P134" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q134">
         <v>3.4</v>
@@ -28884,7 +28887,7 @@
         <v>177</v>
       </c>
       <c r="P135" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -29296,7 +29299,7 @@
         <v>179</v>
       </c>
       <c r="P137" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q137">
         <v>4</v>
@@ -29502,7 +29505,7 @@
         <v>90</v>
       </c>
       <c r="P138" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q138">
         <v>3.75</v>
@@ -29708,7 +29711,7 @@
         <v>90</v>
       </c>
       <c r="P139" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q139">
         <v>3</v>
@@ -29914,7 +29917,7 @@
         <v>90</v>
       </c>
       <c r="P140" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q140">
         <v>3</v>
@@ -29995,7 +29998,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ140">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR140">
         <v>1.32</v>
@@ -30120,7 +30123,7 @@
         <v>180</v>
       </c>
       <c r="P141" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30532,7 +30535,7 @@
         <v>182</v>
       </c>
       <c r="P143" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q143">
         <v>3.1</v>
@@ -31356,7 +31359,7 @@
         <v>90</v>
       </c>
       <c r="P147" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q147">
         <v>3.1</v>
@@ -31640,7 +31643,7 @@
         <v>0.88</v>
       </c>
       <c r="AP148">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ148">
         <v>1</v>
@@ -32180,7 +32183,7 @@
         <v>186</v>
       </c>
       <c r="P151" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q151">
         <v>2.38</v>
@@ -32798,7 +32801,7 @@
         <v>187</v>
       </c>
       <c r="P154" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q154">
         <v>3.4</v>
@@ -32879,7 +32882,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ154">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR154">
         <v>1.59</v>
@@ -33082,7 +33085,7 @@
         <v>1.33</v>
       </c>
       <c r="AP155">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ155">
         <v>1</v>
@@ -33622,7 +33625,7 @@
         <v>90</v>
       </c>
       <c r="P158" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -34034,7 +34037,7 @@
         <v>141</v>
       </c>
       <c r="P160" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q160">
         <v>3.75</v>
@@ -34240,7 +34243,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q161">
         <v>4.75</v>
@@ -34446,7 +34449,7 @@
         <v>180</v>
       </c>
       <c r="P162" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q162">
         <v>3.75</v>
@@ -34858,7 +34861,7 @@
         <v>191</v>
       </c>
       <c r="P164" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q164">
         <v>3.1</v>
@@ -35270,7 +35273,7 @@
         <v>90</v>
       </c>
       <c r="P166" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q166">
         <v>2.75</v>
@@ -35682,7 +35685,7 @@
         <v>193</v>
       </c>
       <c r="P168" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q168">
         <v>2.75</v>
@@ -35888,7 +35891,7 @@
         <v>194</v>
       </c>
       <c r="P169" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36300,7 +36303,7 @@
         <v>196</v>
       </c>
       <c r="P171" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q171">
         <v>2.75</v>
@@ -36712,7 +36715,7 @@
         <v>197</v>
       </c>
       <c r="P173" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q173">
         <v>3</v>
@@ -37202,7 +37205,7 @@
         <v>1.25</v>
       </c>
       <c r="AP175">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ175">
         <v>1.11</v>
@@ -37330,7 +37333,7 @@
         <v>90</v>
       </c>
       <c r="P176" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q176">
         <v>3.4</v>
@@ -37742,7 +37745,7 @@
         <v>200</v>
       </c>
       <c r="P178" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q178">
         <v>3.4</v>
@@ -38154,7 +38157,7 @@
         <v>202</v>
       </c>
       <c r="P180" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q180">
         <v>2</v>
@@ -38360,7 +38363,7 @@
         <v>90</v>
       </c>
       <c r="P181" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q181">
         <v>4</v>
@@ -38517,6 +38520,212 @@
       </c>
       <c r="BP181">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="182" spans="1:68">
+      <c r="A182" s="1">
+        <v>181</v>
+      </c>
+      <c r="B182">
+        <v>7778671</v>
+      </c>
+      <c r="C182" t="s">
+        <v>68</v>
+      </c>
+      <c r="D182" t="s">
+        <v>69</v>
+      </c>
+      <c r="E182" s="2">
+        <v>45822.25</v>
+      </c>
+      <c r="F182">
+        <v>19</v>
+      </c>
+      <c r="G182" t="s">
+        <v>84</v>
+      </c>
+      <c r="H182" t="s">
+        <v>75</v>
+      </c>
+      <c r="I182">
+        <v>0</v>
+      </c>
+      <c r="J182">
+        <v>0</v>
+      </c>
+      <c r="K182">
+        <v>0</v>
+      </c>
+      <c r="L182">
+        <v>1</v>
+      </c>
+      <c r="M182">
+        <v>0</v>
+      </c>
+      <c r="N182">
+        <v>1</v>
+      </c>
+      <c r="O182" t="s">
+        <v>203</v>
+      </c>
+      <c r="P182" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q182">
+        <v>2.75</v>
+      </c>
+      <c r="R182">
+        <v>1.95</v>
+      </c>
+      <c r="S182">
+        <v>4.15</v>
+      </c>
+      <c r="T182">
+        <v>1.45</v>
+      </c>
+      <c r="U182">
+        <v>2.55</v>
+      </c>
+      <c r="V182">
+        <v>3.1</v>
+      </c>
+      <c r="W182">
+        <v>1.32</v>
+      </c>
+      <c r="X182">
+        <v>7</v>
+      </c>
+      <c r="Y182">
+        <v>1.06</v>
+      </c>
+      <c r="Z182">
+        <v>2.19</v>
+      </c>
+      <c r="AA182">
+        <v>2.97</v>
+      </c>
+      <c r="AB182">
+        <v>3.06</v>
+      </c>
+      <c r="AC182">
+        <v>1.02</v>
+      </c>
+      <c r="AD182">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AE182">
+        <v>1.32</v>
+      </c>
+      <c r="AF182">
+        <v>2.88</v>
+      </c>
+      <c r="AG182">
+        <v>1.95</v>
+      </c>
+      <c r="AH182">
+        <v>1.75</v>
+      </c>
+      <c r="AI182">
+        <v>1.84</v>
+      </c>
+      <c r="AJ182">
+        <v>1.82</v>
+      </c>
+      <c r="AK182">
+        <v>1.26</v>
+      </c>
+      <c r="AL182">
+        <v>1.3</v>
+      </c>
+      <c r="AM182">
+        <v>1.64</v>
+      </c>
+      <c r="AN182">
+        <v>2.2</v>
+      </c>
+      <c r="AO182">
+        <v>1.43</v>
+      </c>
+      <c r="AP182">
+        <v>2.27</v>
+      </c>
+      <c r="AQ182">
+        <v>1.25</v>
+      </c>
+      <c r="AR182">
+        <v>1.66</v>
+      </c>
+      <c r="AS182">
+        <v>1.35</v>
+      </c>
+      <c r="AT182">
+        <v>3.01</v>
+      </c>
+      <c r="AU182">
+        <v>2</v>
+      </c>
+      <c r="AV182">
+        <v>-1</v>
+      </c>
+      <c r="AW182">
+        <v>-1</v>
+      </c>
+      <c r="AX182">
+        <v>-1</v>
+      </c>
+      <c r="AY182">
+        <v>1</v>
+      </c>
+      <c r="AZ182">
+        <v>-2</v>
+      </c>
+      <c r="BA182">
+        <v>-1</v>
+      </c>
+      <c r="BB182">
+        <v>-1</v>
+      </c>
+      <c r="BC182">
+        <v>-1</v>
+      </c>
+      <c r="BD182">
+        <v>1.69</v>
+      </c>
+      <c r="BE182">
+        <v>8</v>
+      </c>
+      <c r="BF182">
+        <v>2.54</v>
+      </c>
+      <c r="BG182">
+        <v>1.24</v>
+      </c>
+      <c r="BH182">
+        <v>3.48</v>
+      </c>
+      <c r="BI182">
+        <v>1.46</v>
+      </c>
+      <c r="BJ182">
+        <v>2.53</v>
+      </c>
+      <c r="BK182">
+        <v>1.76</v>
+      </c>
+      <c r="BL182">
+        <v>2</v>
+      </c>
+      <c r="BM182">
+        <v>2.2</v>
+      </c>
+      <c r="BN182">
+        <v>1.63</v>
+      </c>
+      <c r="BO182">
+        <v>2.77</v>
+      </c>
+      <c r="BP182">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="298">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -628,6 +628,24 @@
     <t>['84']</t>
   </si>
   <si>
+    <t>['23', '9002']</t>
+  </si>
+  <si>
+    <t>['59', '69']</t>
+  </si>
+  <si>
+    <t>['12', '76']</t>
+  </si>
+  <si>
+    <t>['38', '81']</t>
+  </si>
+  <si>
+    <t>['67', '73', '87', '9001']</t>
+  </si>
+  <si>
+    <t>['34', '36', '76']</t>
+  </si>
+  <si>
     <t>['31', '60']</t>
   </si>
   <si>
@@ -872,6 +890,24 @@
   </si>
   <si>
     <t>['42']</t>
+  </si>
+  <si>
+    <t>['15', '68']</t>
+  </si>
+  <si>
+    <t>['36', '9001']</t>
+  </si>
+  <si>
+    <t>['9', '18', '81', '9002']</t>
+  </si>
+  <si>
+    <t>['14', '4502', '55']</t>
+  </si>
+  <si>
+    <t>['73', '83']</t>
+  </si>
+  <si>
+    <t>['23', '40', '65']</t>
   </si>
 </sst>
 </file>
@@ -1233,7 +1269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP182"/>
+  <dimension ref="A1:BP191"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1489,7 +1525,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="Q2">
         <v>3.6</v>
@@ -1570,7 +1606,7 @@
         <v>1</v>
       </c>
       <c r="AQ2">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1979,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ4">
         <v>0.67</v>
@@ -2107,7 +2143,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2185,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ5">
         <v>1.63</v>
@@ -2313,7 +2349,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="Q6">
         <v>4.1</v>
@@ -2600,7 +2636,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ7">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2725,7 +2761,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="Q8">
         <v>2.28</v>
@@ -2803,7 +2839,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ8">
         <v>1</v>
@@ -3218,7 +3254,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ10">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3421,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ11">
         <v>1</v>
@@ -3627,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ12">
         <v>1.25</v>
@@ -4167,7 +4203,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="Q15">
         <v>4.1</v>
@@ -4245,7 +4281,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ15">
         <v>1.11</v>
@@ -4657,10 +4693,10 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ17">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5072,7 +5108,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ19">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR19">
         <v>1.74</v>
@@ -5275,7 +5311,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ20">
         <v>1</v>
@@ -5403,7 +5439,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="Q21">
         <v>4.4</v>
@@ -5484,7 +5520,7 @@
         <v>0.22</v>
       </c>
       <c r="AQ21">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR21">
         <v>1.32</v>
@@ -5815,7 +5851,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5896,7 +5932,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ23">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR23">
         <v>1.4</v>
@@ -6099,7 +6135,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ24">
         <v>1.11</v>
@@ -6227,7 +6263,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -6514,7 +6550,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ26">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR26">
         <v>0.85</v>
@@ -6639,7 +6675,7 @@
         <v>90</v>
       </c>
       <c r="P27" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="Q27">
         <v>3.2</v>
@@ -6720,7 +6756,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ27">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR27">
         <v>1.59</v>
@@ -7129,7 +7165,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ29">
         <v>1.3</v>
@@ -7338,7 +7374,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ30">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR30">
         <v>1.54</v>
@@ -7541,7 +7577,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ31">
         <v>1</v>
@@ -7669,7 +7705,7 @@
         <v>113</v>
       </c>
       <c r="P32" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="Q32">
         <v>3.45</v>
@@ -7875,7 +7911,7 @@
         <v>114</v>
       </c>
       <c r="P33" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8081,7 +8117,7 @@
         <v>115</v>
       </c>
       <c r="P34" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8162,7 +8198,7 @@
         <v>0.22</v>
       </c>
       <c r="AQ34">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR34">
         <v>1.24</v>
@@ -8287,7 +8323,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="Q35">
         <v>3.4</v>
@@ -8365,10 +8401,10 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ35">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AR35">
         <v>0</v>
@@ -8493,7 +8529,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="Q36">
         <v>2.8</v>
@@ -8571,10 +8607,10 @@
         <v>2</v>
       </c>
       <c r="AP36">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ36">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR36">
         <v>0</v>
@@ -8905,7 +8941,7 @@
         <v>118</v>
       </c>
       <c r="P38" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="Q38">
         <v>2.6</v>
@@ -8983,10 +9019,10 @@
         <v>1</v>
       </c>
       <c r="AP38">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ38">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR38">
         <v>1.1</v>
@@ -9189,7 +9225,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ39">
         <v>1.11</v>
@@ -9395,7 +9431,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ40">
         <v>1</v>
@@ -9601,7 +9637,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ41">
         <v>1.63</v>
@@ -9729,7 +9765,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10219,7 +10255,7 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ44">
         <v>1.3</v>
@@ -10428,7 +10464,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ45">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR45">
         <v>1.47</v>
@@ -10631,7 +10667,7 @@
         <v>2</v>
       </c>
       <c r="AP46">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ46">
         <v>1.8</v>
@@ -10759,7 +10795,7 @@
         <v>105</v>
       </c>
       <c r="P47" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10965,7 +11001,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="Q48">
         <v>3.6</v>
@@ -11046,7 +11082,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ48">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR48">
         <v>1.52</v>
@@ -11171,7 +11207,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="Q49">
         <v>3.6</v>
@@ -11249,7 +11285,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ49">
         <v>1</v>
@@ -11583,7 +11619,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="Q51">
         <v>1.91</v>
@@ -11664,7 +11700,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ51">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR51">
         <v>1.69</v>
@@ -11789,7 +11825,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -11995,7 +12031,7 @@
         <v>90</v>
       </c>
       <c r="P53" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12073,7 +12109,7 @@
         <v>0.5</v>
       </c>
       <c r="AP53">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ53">
         <v>1</v>
@@ -12279,10 +12315,10 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ54">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR54">
         <v>2.36</v>
@@ -12613,7 +12649,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="Q56">
         <v>4.33</v>
@@ -12900,7 +12936,7 @@
         <v>1</v>
       </c>
       <c r="AQ57">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR57">
         <v>1.77</v>
@@ -13231,7 +13267,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13309,10 +13345,10 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ59">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR59">
         <v>1.09</v>
@@ -13515,7 +13551,7 @@
         <v>1.33</v>
       </c>
       <c r="AP60">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ60">
         <v>1.8</v>
@@ -13643,7 +13679,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13721,10 +13757,10 @@
         <v>3</v>
       </c>
       <c r="AP61">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ61">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AR61">
         <v>1.1</v>
@@ -13849,7 +13885,7 @@
         <v>90</v>
       </c>
       <c r="P62" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="Q62">
         <v>2.75</v>
@@ -13927,7 +13963,7 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ62">
         <v>1.3</v>
@@ -14467,7 +14503,7 @@
         <v>90</v>
       </c>
       <c r="P65" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="Q65">
         <v>3.6</v>
@@ -14545,10 +14581,10 @@
         <v>1.33</v>
       </c>
       <c r="AP65">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ65">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR65">
         <v>1.13</v>
@@ -14673,7 +14709,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="Q66">
         <v>4.75</v>
@@ -14879,7 +14915,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="Q67">
         <v>2.88</v>
@@ -15369,10 +15405,10 @@
         <v>3</v>
       </c>
       <c r="AP69">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ69">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AR69">
         <v>1.3</v>
@@ -15781,10 +15817,10 @@
         <v>1.5</v>
       </c>
       <c r="AP71">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ71">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR71">
         <v>1.39</v>
@@ -15990,7 +16026,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ72">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR72">
         <v>1.51</v>
@@ -16193,7 +16229,7 @@
         <v>0.33</v>
       </c>
       <c r="AP73">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ73">
         <v>1</v>
@@ -16399,10 +16435,10 @@
         <v>0.5</v>
       </c>
       <c r="AP74">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ74">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR74">
         <v>1.3</v>
@@ -16814,7 +16850,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ76">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR76">
         <v>1.39</v>
@@ -17017,7 +17053,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ77">
         <v>1.11</v>
@@ -17223,7 +17259,7 @@
         <v>1.25</v>
       </c>
       <c r="AP78">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ78">
         <v>1.8</v>
@@ -17351,7 +17387,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="Q79">
         <v>2.63</v>
@@ -17763,7 +17799,7 @@
         <v>145</v>
       </c>
       <c r="P81" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="Q81">
         <v>3.2</v>
@@ -18050,7 +18086,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ82">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR82">
         <v>1.31</v>
@@ -18665,7 +18701,7 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ85">
         <v>1.8</v>
@@ -18793,7 +18829,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -18874,7 +18910,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ86">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR86">
         <v>1.94</v>
@@ -18999,7 +19035,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19077,7 +19113,7 @@
         <v>0</v>
       </c>
       <c r="AP87">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ87">
         <v>0.67</v>
@@ -19205,7 +19241,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19286,7 +19322,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ88">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AR88">
         <v>1.22</v>
@@ -19411,7 +19447,7 @@
         <v>90</v>
       </c>
       <c r="P89" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19489,7 +19525,7 @@
         <v>0.33</v>
       </c>
       <c r="AP89">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ89">
         <v>1.25</v>
@@ -19695,7 +19731,7 @@
         <v>1.33</v>
       </c>
       <c r="AP90">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ90">
         <v>1</v>
@@ -20029,7 +20065,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="Q92">
         <v>4</v>
@@ -20107,7 +20143,7 @@
         <v>0.5</v>
       </c>
       <c r="AP92">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ92">
         <v>1.11</v>
@@ -20235,7 +20271,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="Q93">
         <v>3</v>
@@ -20441,7 +20477,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="Q94">
         <v>2.3</v>
@@ -20519,10 +20555,10 @@
         <v>0.67</v>
       </c>
       <c r="AP94">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ94">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR94">
         <v>1.38</v>
@@ -20647,7 +20683,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="Q95">
         <v>3.5</v>
@@ -20728,7 +20764,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ95">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR95">
         <v>1.47</v>
@@ -20934,7 +20970,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ96">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR96">
         <v>1.52</v>
@@ -21059,7 +21095,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="Q97">
         <v>3.25</v>
@@ -21137,7 +21173,7 @@
         <v>0.25</v>
       </c>
       <c r="AP97">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ97">
         <v>1.63</v>
@@ -21677,7 +21713,7 @@
         <v>157</v>
       </c>
       <c r="P100" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="Q100">
         <v>2.6</v>
@@ -21755,10 +21791,10 @@
         <v>0.75</v>
       </c>
       <c r="AP100">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ100">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR100">
         <v>1.51</v>
@@ -21883,7 +21919,7 @@
         <v>122</v>
       </c>
       <c r="P101" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="Q101">
         <v>3.25</v>
@@ -21961,7 +21997,7 @@
         <v>0.25</v>
       </c>
       <c r="AP101">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ101">
         <v>1</v>
@@ -22089,7 +22125,7 @@
         <v>158</v>
       </c>
       <c r="P102" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="Q102">
         <v>2.25</v>
@@ -22170,7 +22206,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ102">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR102">
         <v>1.46</v>
@@ -22707,7 +22743,7 @@
         <v>160</v>
       </c>
       <c r="P105" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="Q105">
         <v>2.38</v>
@@ -22788,7 +22824,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ105">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR105">
         <v>1.64</v>
@@ -22913,7 +22949,7 @@
         <v>90</v>
       </c>
       <c r="P106" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -22991,7 +23027,7 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ106">
         <v>1</v>
@@ -23119,7 +23155,7 @@
         <v>90</v>
       </c>
       <c r="P107" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="Q107">
         <v>3.25</v>
@@ -23325,7 +23361,7 @@
         <v>161</v>
       </c>
       <c r="P108" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23531,7 +23567,7 @@
         <v>162</v>
       </c>
       <c r="P109" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="Q109">
         <v>2.3</v>
@@ -23609,7 +23645,7 @@
         <v>0.8</v>
       </c>
       <c r="AP109">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ109">
         <v>1</v>
@@ -23815,7 +23851,7 @@
         <v>1</v>
       </c>
       <c r="AP110">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ110">
         <v>0.78</v>
@@ -23943,7 +23979,7 @@
         <v>122</v>
       </c>
       <c r="P111" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="Q111">
         <v>4</v>
@@ -24021,10 +24057,10 @@
         <v>2.5</v>
       </c>
       <c r="AP111">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ111">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR111">
         <v>1.26</v>
@@ -24227,7 +24263,7 @@
         <v>1</v>
       </c>
       <c r="AP112">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ112">
         <v>0.82</v>
@@ -24355,7 +24391,7 @@
         <v>164</v>
       </c>
       <c r="P113" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="Q113">
         <v>3.6</v>
@@ -24433,10 +24469,10 @@
         <v>2</v>
       </c>
       <c r="AP113">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ113">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR113">
         <v>1.23</v>
@@ -24642,7 +24678,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ114">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR114">
         <v>1.57</v>
@@ -24767,7 +24803,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="Q115">
         <v>3.75</v>
@@ -24973,7 +25009,7 @@
         <v>165</v>
       </c>
       <c r="P116" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="Q116">
         <v>3.25</v>
@@ -25051,7 +25087,7 @@
         <v>0.6</v>
       </c>
       <c r="AP116">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ116">
         <v>1.11</v>
@@ -25257,7 +25293,7 @@
         <v>1</v>
       </c>
       <c r="AP117">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ117">
         <v>1.25</v>
@@ -25466,7 +25502,7 @@
         <v>1</v>
       </c>
       <c r="AQ118">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR118">
         <v>1.57</v>
@@ -25672,7 +25708,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ119">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AR119">
         <v>1.4</v>
@@ -25875,7 +25911,7 @@
         <v>0.4</v>
       </c>
       <c r="AP120">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ120">
         <v>0.67</v>
@@ -26003,7 +26039,7 @@
         <v>167</v>
       </c>
       <c r="P121" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="Q121">
         <v>3.4</v>
@@ -26084,7 +26120,7 @@
         <v>0.22</v>
       </c>
       <c r="AQ121">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR121">
         <v>1.17</v>
@@ -26209,7 +26245,7 @@
         <v>168</v>
       </c>
       <c r="P122" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26415,7 +26451,7 @@
         <v>169</v>
       </c>
       <c r="P123" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="Q123">
         <v>3.4</v>
@@ -26496,7 +26532,7 @@
         <v>1</v>
       </c>
       <c r="AQ123">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR123">
         <v>1.58</v>
@@ -26621,7 +26657,7 @@
         <v>90</v>
       </c>
       <c r="P124" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="Q124">
         <v>4</v>
@@ -26699,7 +26735,7 @@
         <v>1.29</v>
       </c>
       <c r="AP124">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ124">
         <v>1.8</v>
@@ -26905,7 +26941,7 @@
         <v>1.6</v>
       </c>
       <c r="AP125">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ125">
         <v>1</v>
@@ -27114,7 +27150,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ126">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AR126">
         <v>1.32</v>
@@ -27239,7 +27275,7 @@
         <v>171</v>
       </c>
       <c r="P127" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27445,7 +27481,7 @@
         <v>90</v>
       </c>
       <c r="P128" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="Q128">
         <v>2.88</v>
@@ -27523,7 +27559,7 @@
         <v>0.86</v>
       </c>
       <c r="AP128">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ128">
         <v>1</v>
@@ -27651,7 +27687,7 @@
         <v>172</v>
       </c>
       <c r="P129" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -27857,7 +27893,7 @@
         <v>90</v>
       </c>
       <c r="P130" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="Q130">
         <v>3.4</v>
@@ -28063,7 +28099,7 @@
         <v>173</v>
       </c>
       <c r="P131" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="Q131">
         <v>2.1</v>
@@ -28141,10 +28177,10 @@
         <v>1.2</v>
       </c>
       <c r="AP131">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ131">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR131">
         <v>2.03</v>
@@ -28269,7 +28305,7 @@
         <v>174</v>
       </c>
       <c r="P132" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="Q132">
         <v>2.5</v>
@@ -28350,7 +28386,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ132">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR132">
         <v>1.48</v>
@@ -28475,7 +28511,7 @@
         <v>175</v>
       </c>
       <c r="P133" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="Q133">
         <v>4</v>
@@ -28553,7 +28589,7 @@
         <v>0.67</v>
       </c>
       <c r="AP133">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ133">
         <v>1.11</v>
@@ -28681,7 +28717,7 @@
         <v>176</v>
       </c>
       <c r="P134" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="Q134">
         <v>3.4</v>
@@ -28759,7 +28795,7 @@
         <v>1.17</v>
       </c>
       <c r="AP134">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ134">
         <v>1.63</v>
@@ -28887,7 +28923,7 @@
         <v>177</v>
       </c>
       <c r="P135" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -28965,7 +29001,7 @@
         <v>0.83</v>
       </c>
       <c r="AP135">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ135">
         <v>1.11</v>
@@ -29171,7 +29207,7 @@
         <v>1.33</v>
       </c>
       <c r="AP136">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ136">
         <v>1</v>
@@ -29299,7 +29335,7 @@
         <v>179</v>
       </c>
       <c r="P137" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="Q137">
         <v>4</v>
@@ -29505,7 +29541,7 @@
         <v>90</v>
       </c>
       <c r="P138" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="Q138">
         <v>3.75</v>
@@ -29586,7 +29622,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ138">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR138">
         <v>1.54</v>
@@ -29711,7 +29747,7 @@
         <v>90</v>
       </c>
       <c r="P139" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="Q139">
         <v>3</v>
@@ -29917,7 +29953,7 @@
         <v>90</v>
       </c>
       <c r="P140" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="Q140">
         <v>3</v>
@@ -29995,7 +30031,7 @@
         <v>0.8</v>
       </c>
       <c r="AP140">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ140">
         <v>1.25</v>
@@ -30123,7 +30159,7 @@
         <v>180</v>
       </c>
       <c r="P141" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30204,7 +30240,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ141">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR141">
         <v>1.59</v>
@@ -30410,7 +30446,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ142">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR142">
         <v>1.79</v>
@@ -30535,7 +30571,7 @@
         <v>182</v>
       </c>
       <c r="P143" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="Q143">
         <v>3.1</v>
@@ -30819,10 +30855,10 @@
         <v>0.86</v>
       </c>
       <c r="AP144">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ144">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR144">
         <v>1.35</v>
@@ -31025,7 +31061,7 @@
         <v>1</v>
       </c>
       <c r="AP145">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ145">
         <v>0.82</v>
@@ -31359,7 +31395,7 @@
         <v>90</v>
       </c>
       <c r="P147" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="Q147">
         <v>3.1</v>
@@ -31440,7 +31476,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ147">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AR147">
         <v>1.55</v>
@@ -31646,7 +31682,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ148">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR148">
         <v>1.54</v>
@@ -31849,7 +31885,7 @@
         <v>0.71</v>
       </c>
       <c r="AP149">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ149">
         <v>0.67</v>
@@ -32055,7 +32091,7 @@
         <v>1.14</v>
       </c>
       <c r="AP150">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ150">
         <v>1</v>
@@ -32183,7 +32219,7 @@
         <v>186</v>
       </c>
       <c r="P151" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="Q151">
         <v>2.38</v>
@@ -32264,7 +32300,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ151">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR151">
         <v>1.46</v>
@@ -32467,10 +32503,10 @@
         <v>2.43</v>
       </c>
       <c r="AP152">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ152">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR152">
         <v>1.16</v>
@@ -32673,7 +32709,7 @@
         <v>0.86</v>
       </c>
       <c r="AP153">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ153">
         <v>0.78</v>
@@ -32801,7 +32837,7 @@
         <v>187</v>
       </c>
       <c r="P154" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="Q154">
         <v>3.4</v>
@@ -33294,7 +33330,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ156">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR156">
         <v>1.69</v>
@@ -33497,7 +33533,7 @@
         <v>1.14</v>
       </c>
       <c r="AP157">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ157">
         <v>1</v>
@@ -33625,7 +33661,7 @@
         <v>90</v>
       </c>
       <c r="P158" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -33706,7 +33742,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ158">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR158">
         <v>1.44</v>
@@ -33909,7 +33945,7 @@
         <v>1</v>
       </c>
       <c r="AP159">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ159">
         <v>0.82</v>
@@ -34037,7 +34073,7 @@
         <v>141</v>
       </c>
       <c r="P160" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="Q160">
         <v>3.75</v>
@@ -34115,7 +34151,7 @@
         <v>1</v>
       </c>
       <c r="AP160">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ160">
         <v>1.11</v>
@@ -34243,7 +34279,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="Q161">
         <v>4.75</v>
@@ -34449,7 +34485,7 @@
         <v>180</v>
       </c>
       <c r="P162" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="Q162">
         <v>3.75</v>
@@ -34530,7 +34566,7 @@
         <v>1</v>
       </c>
       <c r="AQ162">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR162">
         <v>1.61</v>
@@ -34733,10 +34769,10 @@
         <v>2.13</v>
       </c>
       <c r="AP163">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ163">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AR163">
         <v>2.07</v>
@@ -34861,7 +34897,7 @@
         <v>191</v>
       </c>
       <c r="P164" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="Q164">
         <v>3.1</v>
@@ -34939,7 +34975,7 @@
         <v>1.14</v>
       </c>
       <c r="AP164">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ164">
         <v>1.11</v>
@@ -35273,7 +35309,7 @@
         <v>90</v>
       </c>
       <c r="P166" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="Q166">
         <v>2.75</v>
@@ -35351,7 +35387,7 @@
         <v>1.13</v>
       </c>
       <c r="AP166">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ166">
         <v>1.3</v>
@@ -35557,10 +35593,10 @@
         <v>0.75</v>
       </c>
       <c r="AP167">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ167">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR167">
         <v>1.34</v>
@@ -35685,7 +35721,7 @@
         <v>193</v>
       </c>
       <c r="P168" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="Q168">
         <v>2.75</v>
@@ -35766,7 +35802,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ168">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR168">
         <v>1.45</v>
@@ -35891,7 +35927,7 @@
         <v>194</v>
       </c>
       <c r="P169" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -35972,7 +36008,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ169">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR169">
         <v>1.3</v>
@@ -36303,7 +36339,7 @@
         <v>196</v>
       </c>
       <c r="P171" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="Q171">
         <v>2.75</v>
@@ -36715,7 +36751,7 @@
         <v>197</v>
       </c>
       <c r="P173" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="Q173">
         <v>3</v>
@@ -37333,7 +37369,7 @@
         <v>90</v>
       </c>
       <c r="P176" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="Q176">
         <v>3.4</v>
@@ -37617,7 +37653,7 @@
         <v>1.33</v>
       </c>
       <c r="AP177">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ177">
         <v>1.3</v>
@@ -37745,7 +37781,7 @@
         <v>200</v>
       </c>
       <c r="P178" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="Q178">
         <v>3.4</v>
@@ -38157,7 +38193,7 @@
         <v>202</v>
       </c>
       <c r="P180" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="Q180">
         <v>2</v>
@@ -38238,7 +38274,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ180">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR180">
         <v>1.8</v>
@@ -38363,7 +38399,7 @@
         <v>90</v>
       </c>
       <c r="P181" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="Q181">
         <v>4</v>
@@ -38441,7 +38477,7 @@
         <v>1.43</v>
       </c>
       <c r="AP181">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ181">
         <v>1.63</v>
@@ -38726,6 +38762,1860 @@
       </c>
       <c r="BP182">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="183" spans="1:68">
+      <c r="A183" s="1">
+        <v>182</v>
+      </c>
+      <c r="B183">
+        <v>7778673</v>
+      </c>
+      <c r="C183" t="s">
+        <v>68</v>
+      </c>
+      <c r="D183" t="s">
+        <v>69</v>
+      </c>
+      <c r="E183" s="2">
+        <v>45823.08333333334</v>
+      </c>
+      <c r="F183">
+        <v>19</v>
+      </c>
+      <c r="G183" t="s">
+        <v>86</v>
+      </c>
+      <c r="H183" t="s">
+        <v>74</v>
+      </c>
+      <c r="I183">
+        <v>0</v>
+      </c>
+      <c r="J183">
+        <v>0</v>
+      </c>
+      <c r="K183">
+        <v>0</v>
+      </c>
+      <c r="L183">
+        <v>0</v>
+      </c>
+      <c r="M183">
+        <v>1</v>
+      </c>
+      <c r="N183">
+        <v>1</v>
+      </c>
+      <c r="O183" t="s">
+        <v>90</v>
+      </c>
+      <c r="P183" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q183">
+        <v>3</v>
+      </c>
+      <c r="R183">
+        <v>2.05</v>
+      </c>
+      <c r="S183">
+        <v>3.3</v>
+      </c>
+      <c r="T183">
+        <v>1.42</v>
+      </c>
+      <c r="U183">
+        <v>2.65</v>
+      </c>
+      <c r="V183">
+        <v>2.9</v>
+      </c>
+      <c r="W183">
+        <v>1.35</v>
+      </c>
+      <c r="X183">
+        <v>7.75</v>
+      </c>
+      <c r="Y183">
+        <v>1.07</v>
+      </c>
+      <c r="Z183">
+        <v>2.31</v>
+      </c>
+      <c r="AA183">
+        <v>3.13</v>
+      </c>
+      <c r="AB183">
+        <v>2.72</v>
+      </c>
+      <c r="AC183">
+        <v>1.06</v>
+      </c>
+      <c r="AD183">
+        <v>8.25</v>
+      </c>
+      <c r="AE183">
+        <v>1.33</v>
+      </c>
+      <c r="AF183">
+        <v>3</v>
+      </c>
+      <c r="AG183">
+        <v>1.96</v>
+      </c>
+      <c r="AH183">
+        <v>1.74</v>
+      </c>
+      <c r="AI183">
+        <v>1.8</v>
+      </c>
+      <c r="AJ183">
+        <v>1.88</v>
+      </c>
+      <c r="AK183">
+        <v>1.41</v>
+      </c>
+      <c r="AL183">
+        <v>1.31</v>
+      </c>
+      <c r="AM183">
+        <v>1.53</v>
+      </c>
+      <c r="AN183">
+        <v>1</v>
+      </c>
+      <c r="AO183">
+        <v>0.78</v>
+      </c>
+      <c r="AP183">
+        <v>0.9</v>
+      </c>
+      <c r="AQ183">
+        <v>1</v>
+      </c>
+      <c r="AR183">
+        <v>1.23</v>
+      </c>
+      <c r="AS183">
+        <v>1.51</v>
+      </c>
+      <c r="AT183">
+        <v>2.74</v>
+      </c>
+      <c r="AU183">
+        <v>-1</v>
+      </c>
+      <c r="AV183">
+        <v>-1</v>
+      </c>
+      <c r="AW183">
+        <v>-1</v>
+      </c>
+      <c r="AX183">
+        <v>-1</v>
+      </c>
+      <c r="AY183">
+        <v>-1</v>
+      </c>
+      <c r="AZ183">
+        <v>-1</v>
+      </c>
+      <c r="BA183">
+        <v>-1</v>
+      </c>
+      <c r="BB183">
+        <v>-1</v>
+      </c>
+      <c r="BC183">
+        <v>-1</v>
+      </c>
+      <c r="BD183">
+        <v>2.56</v>
+      </c>
+      <c r="BE183">
+        <v>6.4</v>
+      </c>
+      <c r="BF183">
+        <v>1.75</v>
+      </c>
+      <c r="BG183">
+        <v>1.22</v>
+      </c>
+      <c r="BH183">
+        <v>3.5</v>
+      </c>
+      <c r="BI183">
+        <v>1.43</v>
+      </c>
+      <c r="BJ183">
+        <v>2.46</v>
+      </c>
+      <c r="BK183">
+        <v>1.77</v>
+      </c>
+      <c r="BL183">
+        <v>1.9</v>
+      </c>
+      <c r="BM183">
+        <v>2.24</v>
+      </c>
+      <c r="BN183">
+        <v>1.52</v>
+      </c>
+      <c r="BO183">
+        <v>3.04</v>
+      </c>
+      <c r="BP183">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="184" spans="1:68">
+      <c r="A184" s="1">
+        <v>183</v>
+      </c>
+      <c r="B184">
+        <v>7778675</v>
+      </c>
+      <c r="C184" t="s">
+        <v>68</v>
+      </c>
+      <c r="D184" t="s">
+        <v>69</v>
+      </c>
+      <c r="E184" s="2">
+        <v>45823.08333333334</v>
+      </c>
+      <c r="F184">
+        <v>19</v>
+      </c>
+      <c r="G184" t="s">
+        <v>81</v>
+      </c>
+      <c r="H184" t="s">
+        <v>70</v>
+      </c>
+      <c r="I184">
+        <v>1</v>
+      </c>
+      <c r="J184">
+        <v>1</v>
+      </c>
+      <c r="K184">
+        <v>2</v>
+      </c>
+      <c r="L184">
+        <v>2</v>
+      </c>
+      <c r="M184">
+        <v>2</v>
+      </c>
+      <c r="N184">
+        <v>4</v>
+      </c>
+      <c r="O184" t="s">
+        <v>204</v>
+      </c>
+      <c r="P184" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q184">
+        <v>3.1</v>
+      </c>
+      <c r="R184">
+        <v>1.93</v>
+      </c>
+      <c r="S184">
+        <v>3.6</v>
+      </c>
+      <c r="T184">
+        <v>1.49</v>
+      </c>
+      <c r="U184">
+        <v>2.4</v>
+      </c>
+      <c r="V184">
+        <v>3.3</v>
+      </c>
+      <c r="W184">
+        <v>1.29</v>
+      </c>
+      <c r="X184">
+        <v>9.25</v>
+      </c>
+      <c r="Y184">
+        <v>1.05</v>
+      </c>
+      <c r="Z184">
+        <v>2.33</v>
+      </c>
+      <c r="AA184">
+        <v>2.91</v>
+      </c>
+      <c r="AB184">
+        <v>2.89</v>
+      </c>
+      <c r="AC184">
+        <v>1.09</v>
+      </c>
+      <c r="AD184">
+        <v>6.75</v>
+      </c>
+      <c r="AE184">
+        <v>1.44</v>
+      </c>
+      <c r="AF184">
+        <v>2.6</v>
+      </c>
+      <c r="AG184">
+        <v>2.2</v>
+      </c>
+      <c r="AH184">
+        <v>1.59</v>
+      </c>
+      <c r="AI184">
+        <v>2</v>
+      </c>
+      <c r="AJ184">
+        <v>1.7</v>
+      </c>
+      <c r="AK184">
+        <v>1.37</v>
+      </c>
+      <c r="AL184">
+        <v>1.34</v>
+      </c>
+      <c r="AM184">
+        <v>1.53</v>
+      </c>
+      <c r="AN184">
+        <v>1.11</v>
+      </c>
+      <c r="AO184">
+        <v>1</v>
+      </c>
+      <c r="AP184">
+        <v>1.1</v>
+      </c>
+      <c r="AQ184">
+        <v>1</v>
+      </c>
+      <c r="AR184">
+        <v>1.4</v>
+      </c>
+      <c r="AS184">
+        <v>1.16</v>
+      </c>
+      <c r="AT184">
+        <v>2.56</v>
+      </c>
+      <c r="AU184">
+        <v>6</v>
+      </c>
+      <c r="AV184">
+        <v>4</v>
+      </c>
+      <c r="AW184">
+        <v>6</v>
+      </c>
+      <c r="AX184">
+        <v>8</v>
+      </c>
+      <c r="AY184">
+        <v>12</v>
+      </c>
+      <c r="AZ184">
+        <v>12</v>
+      </c>
+      <c r="BA184">
+        <v>4</v>
+      </c>
+      <c r="BB184">
+        <v>5</v>
+      </c>
+      <c r="BC184">
+        <v>9</v>
+      </c>
+      <c r="BD184">
+        <v>1.9</v>
+      </c>
+      <c r="BE184">
+        <v>6.25</v>
+      </c>
+      <c r="BF184">
+        <v>2.32</v>
+      </c>
+      <c r="BG184">
+        <v>1.25</v>
+      </c>
+      <c r="BH184">
+        <v>3.28</v>
+      </c>
+      <c r="BI184">
+        <v>1.47</v>
+      </c>
+      <c r="BJ184">
+        <v>2.35</v>
+      </c>
+      <c r="BK184">
+        <v>1.83</v>
+      </c>
+      <c r="BL184">
+        <v>1.83</v>
+      </c>
+      <c r="BM184">
+        <v>2.35</v>
+      </c>
+      <c r="BN184">
+        <v>1.47</v>
+      </c>
+      <c r="BO184">
+        <v>3.14</v>
+      </c>
+      <c r="BP184">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="185" spans="1:68">
+      <c r="A185" s="1">
+        <v>184</v>
+      </c>
+      <c r="B185">
+        <v>7778669</v>
+      </c>
+      <c r="C185" t="s">
+        <v>68</v>
+      </c>
+      <c r="D185" t="s">
+        <v>69</v>
+      </c>
+      <c r="E185" s="2">
+        <v>45823.08333333334</v>
+      </c>
+      <c r="F185">
+        <v>19</v>
+      </c>
+      <c r="G185" t="s">
+        <v>87</v>
+      </c>
+      <c r="H185" t="s">
+        <v>78</v>
+      </c>
+      <c r="I185">
+        <v>0</v>
+      </c>
+      <c r="J185">
+        <v>1</v>
+      </c>
+      <c r="K185">
+        <v>1</v>
+      </c>
+      <c r="L185">
+        <v>2</v>
+      </c>
+      <c r="M185">
+        <v>2</v>
+      </c>
+      <c r="N185">
+        <v>4</v>
+      </c>
+      <c r="O185" t="s">
+        <v>205</v>
+      </c>
+      <c r="P185" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q185">
+        <v>3.2</v>
+      </c>
+      <c r="R185">
+        <v>2.2</v>
+      </c>
+      <c r="S185">
+        <v>3.4</v>
+      </c>
+      <c r="T185">
+        <v>1.4</v>
+      </c>
+      <c r="U185">
+        <v>2.75</v>
+      </c>
+      <c r="V185">
+        <v>2.75</v>
+      </c>
+      <c r="W185">
+        <v>1.4</v>
+      </c>
+      <c r="X185">
+        <v>8</v>
+      </c>
+      <c r="Y185">
+        <v>1.08</v>
+      </c>
+      <c r="Z185">
+        <v>2.42</v>
+      </c>
+      <c r="AA185">
+        <v>3.18</v>
+      </c>
+      <c r="AB185">
+        <v>2.55</v>
+      </c>
+      <c r="AC185">
+        <v>1.01</v>
+      </c>
+      <c r="AD185">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="AE185">
+        <v>1.29</v>
+      </c>
+      <c r="AF185">
+        <v>3.51</v>
+      </c>
+      <c r="AG185">
+        <v>1.93</v>
+      </c>
+      <c r="AH185">
+        <v>1.77</v>
+      </c>
+      <c r="AI185">
+        <v>1.73</v>
+      </c>
+      <c r="AJ185">
+        <v>2</v>
+      </c>
+      <c r="AK185">
+        <v>1.43</v>
+      </c>
+      <c r="AL185">
+        <v>1.31</v>
+      </c>
+      <c r="AM185">
+        <v>1.51</v>
+      </c>
+      <c r="AN185">
+        <v>1.43</v>
+      </c>
+      <c r="AO185">
+        <v>2.13</v>
+      </c>
+      <c r="AP185">
+        <v>1.38</v>
+      </c>
+      <c r="AQ185">
+        <v>2</v>
+      </c>
+      <c r="AR185">
+        <v>1.65</v>
+      </c>
+      <c r="AS185">
+        <v>1.42</v>
+      </c>
+      <c r="AT185">
+        <v>3.07</v>
+      </c>
+      <c r="AU185">
+        <v>4</v>
+      </c>
+      <c r="AV185">
+        <v>6</v>
+      </c>
+      <c r="AW185">
+        <v>2</v>
+      </c>
+      <c r="AX185">
+        <v>10</v>
+      </c>
+      <c r="AY185">
+        <v>6</v>
+      </c>
+      <c r="AZ185">
+        <v>16</v>
+      </c>
+      <c r="BA185">
+        <v>4</v>
+      </c>
+      <c r="BB185">
+        <v>6</v>
+      </c>
+      <c r="BC185">
+        <v>10</v>
+      </c>
+      <c r="BD185">
+        <v>1.7</v>
+      </c>
+      <c r="BE185">
+        <v>8.1</v>
+      </c>
+      <c r="BF185">
+        <v>2.46</v>
+      </c>
+      <c r="BG185">
+        <v>1.27</v>
+      </c>
+      <c r="BH185">
+        <v>3.14</v>
+      </c>
+      <c r="BI185">
+        <v>1.5</v>
+      </c>
+      <c r="BJ185">
+        <v>2.28</v>
+      </c>
+      <c r="BK185">
+        <v>1.88</v>
+      </c>
+      <c r="BL185">
+        <v>1.78</v>
+      </c>
+      <c r="BM185">
+        <v>2.43</v>
+      </c>
+      <c r="BN185">
+        <v>1.44</v>
+      </c>
+      <c r="BO185">
+        <v>3.34</v>
+      </c>
+      <c r="BP185">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="186" spans="1:68">
+      <c r="A186" s="1">
+        <v>185</v>
+      </c>
+      <c r="B186">
+        <v>7778670</v>
+      </c>
+      <c r="C186" t="s">
+        <v>68</v>
+      </c>
+      <c r="D186" t="s">
+        <v>69</v>
+      </c>
+      <c r="E186" s="2">
+        <v>45823.16666666666</v>
+      </c>
+      <c r="F186">
+        <v>19</v>
+      </c>
+      <c r="G186" t="s">
+        <v>88</v>
+      </c>
+      <c r="H186" t="s">
+        <v>85</v>
+      </c>
+      <c r="I186">
+        <v>1</v>
+      </c>
+      <c r="J186">
+        <v>2</v>
+      </c>
+      <c r="K186">
+        <v>3</v>
+      </c>
+      <c r="L186">
+        <v>2</v>
+      </c>
+      <c r="M186">
+        <v>4</v>
+      </c>
+      <c r="N186">
+        <v>6</v>
+      </c>
+      <c r="O186" t="s">
+        <v>206</v>
+      </c>
+      <c r="P186" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q186">
+        <v>3.75</v>
+      </c>
+      <c r="R186">
+        <v>2.1</v>
+      </c>
+      <c r="S186">
+        <v>3</v>
+      </c>
+      <c r="T186">
+        <v>1.44</v>
+      </c>
+      <c r="U186">
+        <v>2.63</v>
+      </c>
+      <c r="V186">
+        <v>3.25</v>
+      </c>
+      <c r="W186">
+        <v>1.33</v>
+      </c>
+      <c r="X186">
+        <v>9</v>
+      </c>
+      <c r="Y186">
+        <v>1.07</v>
+      </c>
+      <c r="Z186">
+        <v>2.87</v>
+      </c>
+      <c r="AA186">
+        <v>3.13</v>
+      </c>
+      <c r="AB186">
+        <v>2.22</v>
+      </c>
+      <c r="AC186">
+        <v>1</v>
+      </c>
+      <c r="AD186">
+        <v>9.1</v>
+      </c>
+      <c r="AE186">
+        <v>1.36</v>
+      </c>
+      <c r="AF186">
+        <v>3.07</v>
+      </c>
+      <c r="AG186">
+        <v>2.08</v>
+      </c>
+      <c r="AH186">
+        <v>1.66</v>
+      </c>
+      <c r="AI186">
+        <v>1.83</v>
+      </c>
+      <c r="AJ186">
+        <v>1.83</v>
+      </c>
+      <c r="AK186">
+        <v>1.58</v>
+      </c>
+      <c r="AL186">
+        <v>1.33</v>
+      </c>
+      <c r="AM186">
+        <v>1.36</v>
+      </c>
+      <c r="AN186">
+        <v>1.14</v>
+      </c>
+      <c r="AO186">
+        <v>1.89</v>
+      </c>
+      <c r="AP186">
+        <v>1</v>
+      </c>
+      <c r="AQ186">
+        <v>2</v>
+      </c>
+      <c r="AR186">
+        <v>1.35</v>
+      </c>
+      <c r="AS186">
+        <v>1.46</v>
+      </c>
+      <c r="AT186">
+        <v>2.81</v>
+      </c>
+      <c r="AU186">
+        <v>5</v>
+      </c>
+      <c r="AV186">
+        <v>6</v>
+      </c>
+      <c r="AW186">
+        <v>4</v>
+      </c>
+      <c r="AX186">
+        <v>3</v>
+      </c>
+      <c r="AY186">
+        <v>9</v>
+      </c>
+      <c r="AZ186">
+        <v>9</v>
+      </c>
+      <c r="BA186">
+        <v>2</v>
+      </c>
+      <c r="BB186">
+        <v>6</v>
+      </c>
+      <c r="BC186">
+        <v>8</v>
+      </c>
+      <c r="BD186">
+        <v>2.2</v>
+      </c>
+      <c r="BE186">
+        <v>6.2</v>
+      </c>
+      <c r="BF186">
+        <v>1.99</v>
+      </c>
+      <c r="BG186">
+        <v>1.23</v>
+      </c>
+      <c r="BH186">
+        <v>3.42</v>
+      </c>
+      <c r="BI186">
+        <v>1.45</v>
+      </c>
+      <c r="BJ186">
+        <v>2.41</v>
+      </c>
+      <c r="BK186">
+        <v>1.81</v>
+      </c>
+      <c r="BL186">
+        <v>1.85</v>
+      </c>
+      <c r="BM186">
+        <v>2.3</v>
+      </c>
+      <c r="BN186">
+        <v>1.49</v>
+      </c>
+      <c r="BO186">
+        <v>3.08</v>
+      </c>
+      <c r="BP186">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="187" spans="1:68">
+      <c r="A187" s="1">
+        <v>186</v>
+      </c>
+      <c r="B187">
+        <v>7778677</v>
+      </c>
+      <c r="C187" t="s">
+        <v>68</v>
+      </c>
+      <c r="D187" t="s">
+        <v>69</v>
+      </c>
+      <c r="E187" s="2">
+        <v>45823.20833333334</v>
+      </c>
+      <c r="F187">
+        <v>19</v>
+      </c>
+      <c r="G187" t="s">
+        <v>76</v>
+      </c>
+      <c r="H187" t="s">
+        <v>71</v>
+      </c>
+      <c r="I187">
+        <v>1</v>
+      </c>
+      <c r="J187">
+        <v>2</v>
+      </c>
+      <c r="K187">
+        <v>3</v>
+      </c>
+      <c r="L187">
+        <v>2</v>
+      </c>
+      <c r="M187">
+        <v>3</v>
+      </c>
+      <c r="N187">
+        <v>5</v>
+      </c>
+      <c r="O187" t="s">
+        <v>207</v>
+      </c>
+      <c r="P187" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q187">
+        <v>2.8</v>
+      </c>
+      <c r="R187">
+        <v>2.2</v>
+      </c>
+      <c r="S187">
+        <v>3.2</v>
+      </c>
+      <c r="T187">
+        <v>1.32</v>
+      </c>
+      <c r="U187">
+        <v>3.1</v>
+      </c>
+      <c r="V187">
+        <v>2.45</v>
+      </c>
+      <c r="W187">
+        <v>1.47</v>
+      </c>
+      <c r="X187">
+        <v>6</v>
+      </c>
+      <c r="Y187">
+        <v>1.11</v>
+      </c>
+      <c r="Z187">
+        <v>2.22</v>
+      </c>
+      <c r="AA187">
+        <v>3.29</v>
+      </c>
+      <c r="AB187">
+        <v>2.74</v>
+      </c>
+      <c r="AC187">
+        <v>1.03</v>
+      </c>
+      <c r="AD187">
+        <v>11</v>
+      </c>
+      <c r="AE187">
+        <v>1.22</v>
+      </c>
+      <c r="AF187">
+        <v>3.9</v>
+      </c>
+      <c r="AG187">
+        <v>1.62</v>
+      </c>
+      <c r="AH187">
+        <v>2.15</v>
+      </c>
+      <c r="AI187">
+        <v>1.6</v>
+      </c>
+      <c r="AJ187">
+        <v>2.2</v>
+      </c>
+      <c r="AK187">
+        <v>1.41</v>
+      </c>
+      <c r="AL187">
+        <v>1.28</v>
+      </c>
+      <c r="AM187">
+        <v>1.57</v>
+      </c>
+      <c r="AN187">
+        <v>1.89</v>
+      </c>
+      <c r="AO187">
+        <v>1.63</v>
+      </c>
+      <c r="AP187">
+        <v>1.7</v>
+      </c>
+      <c r="AQ187">
+        <v>1.78</v>
+      </c>
+      <c r="AR187">
+        <v>2.02</v>
+      </c>
+      <c r="AS187">
+        <v>1.49</v>
+      </c>
+      <c r="AT187">
+        <v>3.51</v>
+      </c>
+      <c r="AU187">
+        <v>3</v>
+      </c>
+      <c r="AV187">
+        <v>4</v>
+      </c>
+      <c r="AW187">
+        <v>12</v>
+      </c>
+      <c r="AX187">
+        <v>6</v>
+      </c>
+      <c r="AY187">
+        <v>15</v>
+      </c>
+      <c r="AZ187">
+        <v>10</v>
+      </c>
+      <c r="BA187">
+        <v>8</v>
+      </c>
+      <c r="BB187">
+        <v>6</v>
+      </c>
+      <c r="BC187">
+        <v>14</v>
+      </c>
+      <c r="BD187">
+        <v>1.78</v>
+      </c>
+      <c r="BE187">
+        <v>6.45</v>
+      </c>
+      <c r="BF187">
+        <v>2.49</v>
+      </c>
+      <c r="BG187">
+        <v>1.18</v>
+      </c>
+      <c r="BH187">
+        <v>3.86</v>
+      </c>
+      <c r="BI187">
+        <v>1.37</v>
+      </c>
+      <c r="BJ187">
+        <v>2.66</v>
+      </c>
+      <c r="BK187">
+        <v>1.67</v>
+      </c>
+      <c r="BL187">
+        <v>2.02</v>
+      </c>
+      <c r="BM187">
+        <v>2.08</v>
+      </c>
+      <c r="BN187">
+        <v>1.6</v>
+      </c>
+      <c r="BO187">
+        <v>2.74</v>
+      </c>
+      <c r="BP187">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="188" spans="1:68">
+      <c r="A188" s="1">
+        <v>187</v>
+      </c>
+      <c r="B188">
+        <v>7778674</v>
+      </c>
+      <c r="C188" t="s">
+        <v>68</v>
+      </c>
+      <c r="D188" t="s">
+        <v>69</v>
+      </c>
+      <c r="E188" s="2">
+        <v>45823.20833333334</v>
+      </c>
+      <c r="F188">
+        <v>19</v>
+      </c>
+      <c r="G188" t="s">
+        <v>73</v>
+      </c>
+      <c r="H188" t="s">
+        <v>77</v>
+      </c>
+      <c r="I188">
+        <v>0</v>
+      </c>
+      <c r="J188">
+        <v>0</v>
+      </c>
+      <c r="K188">
+        <v>0</v>
+      </c>
+      <c r="L188">
+        <v>4</v>
+      </c>
+      <c r="M188">
+        <v>0</v>
+      </c>
+      <c r="N188">
+        <v>4</v>
+      </c>
+      <c r="O188" t="s">
+        <v>208</v>
+      </c>
+      <c r="P188" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q188">
+        <v>2.2</v>
+      </c>
+      <c r="R188">
+        <v>2.38</v>
+      </c>
+      <c r="S188">
+        <v>4.75</v>
+      </c>
+      <c r="T188">
+        <v>1.3</v>
+      </c>
+      <c r="U188">
+        <v>3.4</v>
+      </c>
+      <c r="V188">
+        <v>2.5</v>
+      </c>
+      <c r="W188">
+        <v>1.5</v>
+      </c>
+      <c r="X188">
+        <v>6</v>
+      </c>
+      <c r="Y188">
+        <v>1.13</v>
+      </c>
+      <c r="Z188">
+        <v>1.58</v>
+      </c>
+      <c r="AA188">
+        <v>3.68</v>
+      </c>
+      <c r="AB188">
+        <v>4.6</v>
+      </c>
+      <c r="AC188">
+        <v>1.01</v>
+      </c>
+      <c r="AD188">
+        <v>11</v>
+      </c>
+      <c r="AE188">
+        <v>1.22</v>
+      </c>
+      <c r="AF188">
+        <v>4.15</v>
+      </c>
+      <c r="AG188">
+        <v>1.71</v>
+      </c>
+      <c r="AH188">
+        <v>2.01</v>
+      </c>
+      <c r="AI188">
+        <v>1.73</v>
+      </c>
+      <c r="AJ188">
+        <v>2</v>
+      </c>
+      <c r="AK188">
+        <v>1.18</v>
+      </c>
+      <c r="AL188">
+        <v>1.24</v>
+      </c>
+      <c r="AM188">
+        <v>2.15</v>
+      </c>
+      <c r="AN188">
+        <v>2.11</v>
+      </c>
+      <c r="AO188">
+        <v>1.33</v>
+      </c>
+      <c r="AP188">
+        <v>2.2</v>
+      </c>
+      <c r="AQ188">
+        <v>1.2</v>
+      </c>
+      <c r="AR188">
+        <v>1.36</v>
+      </c>
+      <c r="AS188">
+        <v>1.28</v>
+      </c>
+      <c r="AT188">
+        <v>2.64</v>
+      </c>
+      <c r="AU188">
+        <v>13</v>
+      </c>
+      <c r="AV188">
+        <v>2</v>
+      </c>
+      <c r="AW188">
+        <v>4</v>
+      </c>
+      <c r="AX188">
+        <v>4</v>
+      </c>
+      <c r="AY188">
+        <v>17</v>
+      </c>
+      <c r="AZ188">
+        <v>6</v>
+      </c>
+      <c r="BA188">
+        <v>13</v>
+      </c>
+      <c r="BB188">
+        <v>2</v>
+      </c>
+      <c r="BC188">
+        <v>15</v>
+      </c>
+      <c r="BD188">
+        <v>1.31</v>
+      </c>
+      <c r="BE188">
+        <v>10.75</v>
+      </c>
+      <c r="BF188">
+        <v>3.84</v>
+      </c>
+      <c r="BG188">
+        <v>1.21</v>
+      </c>
+      <c r="BH188">
+        <v>3.78</v>
+      </c>
+      <c r="BI188">
+        <v>1.34</v>
+      </c>
+      <c r="BJ188">
+        <v>2.78</v>
+      </c>
+      <c r="BK188">
+        <v>1.61</v>
+      </c>
+      <c r="BL188">
+        <v>2.07</v>
+      </c>
+      <c r="BM188">
+        <v>2.04</v>
+      </c>
+      <c r="BN188">
+        <v>1.66</v>
+      </c>
+      <c r="BO188">
+        <v>2.62</v>
+      </c>
+      <c r="BP188">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="189" spans="1:68">
+      <c r="A189" s="1">
+        <v>188</v>
+      </c>
+      <c r="B189">
+        <v>7778678</v>
+      </c>
+      <c r="C189" t="s">
+        <v>68</v>
+      </c>
+      <c r="D189" t="s">
+        <v>69</v>
+      </c>
+      <c r="E189" s="2">
+        <v>45823.25</v>
+      </c>
+      <c r="F189">
+        <v>19</v>
+      </c>
+      <c r="G189" t="s">
+        <v>79</v>
+      </c>
+      <c r="H189" t="s">
+        <v>89</v>
+      </c>
+      <c r="I189">
+        <v>1</v>
+      </c>
+      <c r="J189">
+        <v>0</v>
+      </c>
+      <c r="K189">
+        <v>1</v>
+      </c>
+      <c r="L189">
+        <v>1</v>
+      </c>
+      <c r="M189">
+        <v>2</v>
+      </c>
+      <c r="N189">
+        <v>3</v>
+      </c>
+      <c r="O189" t="s">
+        <v>180</v>
+      </c>
+      <c r="P189" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q189">
+        <v>2.88</v>
+      </c>
+      <c r="R189">
+        <v>1.95</v>
+      </c>
+      <c r="S189">
+        <v>4.33</v>
+      </c>
+      <c r="T189">
+        <v>1.53</v>
+      </c>
+      <c r="U189">
+        <v>2.38</v>
+      </c>
+      <c r="V189">
+        <v>3.75</v>
+      </c>
+      <c r="W189">
+        <v>1.25</v>
+      </c>
+      <c r="X189">
+        <v>11</v>
+      </c>
+      <c r="Y189">
+        <v>1.05</v>
+      </c>
+      <c r="Z189">
+        <v>2.07</v>
+      </c>
+      <c r="AA189">
+        <v>2.91</v>
+      </c>
+      <c r="AB189">
+        <v>3.41</v>
+      </c>
+      <c r="AC189">
+        <v>1.1</v>
+      </c>
+      <c r="AD189">
+        <v>6.71</v>
+      </c>
+      <c r="AE189">
+        <v>1.55</v>
+      </c>
+      <c r="AF189">
+        <v>2.3</v>
+      </c>
+      <c r="AG189">
+        <v>2.33</v>
+      </c>
+      <c r="AH189">
+        <v>1.53</v>
+      </c>
+      <c r="AI189">
+        <v>2.2</v>
+      </c>
+      <c r="AJ189">
+        <v>1.62</v>
+      </c>
+      <c r="AK189">
+        <v>1.28</v>
+      </c>
+      <c r="AL189">
+        <v>1.34</v>
+      </c>
+      <c r="AM189">
+        <v>1.66</v>
+      </c>
+      <c r="AN189">
+        <v>1.56</v>
+      </c>
+      <c r="AO189">
+        <v>1</v>
+      </c>
+      <c r="AP189">
+        <v>1.4</v>
+      </c>
+      <c r="AQ189">
+        <v>1.18</v>
+      </c>
+      <c r="AR189">
+        <v>1.12</v>
+      </c>
+      <c r="AS189">
+        <v>1.4</v>
+      </c>
+      <c r="AT189">
+        <v>2.52</v>
+      </c>
+      <c r="AU189">
+        <v>4</v>
+      </c>
+      <c r="AV189">
+        <v>5</v>
+      </c>
+      <c r="AW189">
+        <v>3</v>
+      </c>
+      <c r="AX189">
+        <v>1</v>
+      </c>
+      <c r="AY189">
+        <v>7</v>
+      </c>
+      <c r="AZ189">
+        <v>6</v>
+      </c>
+      <c r="BA189">
+        <v>7</v>
+      </c>
+      <c r="BB189">
+        <v>1</v>
+      </c>
+      <c r="BC189">
+        <v>8</v>
+      </c>
+      <c r="BD189">
+        <v>1.68</v>
+      </c>
+      <c r="BE189">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF189">
+        <v>2.5</v>
+      </c>
+      <c r="BG189">
+        <v>1.26</v>
+      </c>
+      <c r="BH189">
+        <v>3.22</v>
+      </c>
+      <c r="BI189">
+        <v>1.49</v>
+      </c>
+      <c r="BJ189">
+        <v>2.3</v>
+      </c>
+      <c r="BK189">
+        <v>1.87</v>
+      </c>
+      <c r="BL189">
+        <v>1.79</v>
+      </c>
+      <c r="BM189">
+        <v>2.42</v>
+      </c>
+      <c r="BN189">
+        <v>1.44</v>
+      </c>
+      <c r="BO189">
+        <v>3.28</v>
+      </c>
+      <c r="BP189">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="190" spans="1:68">
+      <c r="A190" s="1">
+        <v>189</v>
+      </c>
+      <c r="B190">
+        <v>7778672</v>
+      </c>
+      <c r="C190" t="s">
+        <v>68</v>
+      </c>
+      <c r="D190" t="s">
+        <v>69</v>
+      </c>
+      <c r="E190" s="2">
+        <v>45823.27083333334</v>
+      </c>
+      <c r="F190">
+        <v>19</v>
+      </c>
+      <c r="G190" t="s">
+        <v>72</v>
+      </c>
+      <c r="H190" t="s">
+        <v>82</v>
+      </c>
+      <c r="I190">
+        <v>1</v>
+      </c>
+      <c r="J190">
+        <v>0</v>
+      </c>
+      <c r="K190">
+        <v>1</v>
+      </c>
+      <c r="L190">
+        <v>1</v>
+      </c>
+      <c r="M190">
+        <v>1</v>
+      </c>
+      <c r="N190">
+        <v>2</v>
+      </c>
+      <c r="O190" t="s">
+        <v>141</v>
+      </c>
+      <c r="P190" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q190">
+        <v>3.1</v>
+      </c>
+      <c r="R190">
+        <v>1.98</v>
+      </c>
+      <c r="S190">
+        <v>3.3</v>
+      </c>
+      <c r="T190">
+        <v>1.46</v>
+      </c>
+      <c r="U190">
+        <v>2.5</v>
+      </c>
+      <c r="V190">
+        <v>3.1</v>
+      </c>
+      <c r="W190">
+        <v>1.31</v>
+      </c>
+      <c r="X190">
+        <v>8.75</v>
+      </c>
+      <c r="Y190">
+        <v>1.06</v>
+      </c>
+      <c r="Z190">
+        <v>2.52</v>
+      </c>
+      <c r="AA190">
+        <v>3.01</v>
+      </c>
+      <c r="AB190">
+        <v>2.56</v>
+      </c>
+      <c r="AC190">
+        <v>1.08</v>
+      </c>
+      <c r="AD190">
+        <v>7.5</v>
+      </c>
+      <c r="AE190">
+        <v>1.39</v>
+      </c>
+      <c r="AF190">
+        <v>2.75</v>
+      </c>
+      <c r="AG190">
+        <v>2.19</v>
+      </c>
+      <c r="AH190">
+        <v>1.6</v>
+      </c>
+      <c r="AI190">
+        <v>1.9</v>
+      </c>
+      <c r="AJ190">
+        <v>1.77</v>
+      </c>
+      <c r="AK190">
+        <v>1.43</v>
+      </c>
+      <c r="AL190">
+        <v>1.33</v>
+      </c>
+      <c r="AM190">
+        <v>1.49</v>
+      </c>
+      <c r="AN190">
+        <v>1.38</v>
+      </c>
+      <c r="AO190">
+        <v>1</v>
+      </c>
+      <c r="AP190">
+        <v>1.33</v>
+      </c>
+      <c r="AQ190">
+        <v>1</v>
+      </c>
+      <c r="AR190">
+        <v>1.17</v>
+      </c>
+      <c r="AS190">
+        <v>1.37</v>
+      </c>
+      <c r="AT190">
+        <v>2.54</v>
+      </c>
+      <c r="AU190">
+        <v>2</v>
+      </c>
+      <c r="AV190">
+        <v>2</v>
+      </c>
+      <c r="AW190">
+        <v>-1</v>
+      </c>
+      <c r="AX190">
+        <v>-1</v>
+      </c>
+      <c r="AY190">
+        <v>1</v>
+      </c>
+      <c r="AZ190">
+        <v>1</v>
+      </c>
+      <c r="BA190">
+        <v>-1</v>
+      </c>
+      <c r="BB190">
+        <v>-1</v>
+      </c>
+      <c r="BC190">
+        <v>-1</v>
+      </c>
+      <c r="BD190">
+        <v>2.15</v>
+      </c>
+      <c r="BE190">
+        <v>6.25</v>
+      </c>
+      <c r="BF190">
+        <v>2.03</v>
+      </c>
+      <c r="BG190">
+        <v>1.23</v>
+      </c>
+      <c r="BH190">
+        <v>3.42</v>
+      </c>
+      <c r="BI190">
+        <v>1.44</v>
+      </c>
+      <c r="BJ190">
+        <v>2.42</v>
+      </c>
+      <c r="BK190">
+        <v>1.8</v>
+      </c>
+      <c r="BL190">
+        <v>1.86</v>
+      </c>
+      <c r="BM190">
+        <v>2.28</v>
+      </c>
+      <c r="BN190">
+        <v>1.5</v>
+      </c>
+      <c r="BO190">
+        <v>3.08</v>
+      </c>
+      <c r="BP190">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="191" spans="1:68">
+      <c r="A191" s="1">
+        <v>190</v>
+      </c>
+      <c r="B191">
+        <v>7778676</v>
+      </c>
+      <c r="C191" t="s">
+        <v>68</v>
+      </c>
+      <c r="D191" t="s">
+        <v>69</v>
+      </c>
+      <c r="E191" s="2">
+        <v>45823.29166666666</v>
+      </c>
+      <c r="F191">
+        <v>19</v>
+      </c>
+      <c r="G191" t="s">
+        <v>83</v>
+      </c>
+      <c r="H191" t="s">
+        <v>80</v>
+      </c>
+      <c r="I191">
+        <v>2</v>
+      </c>
+      <c r="J191">
+        <v>2</v>
+      </c>
+      <c r="K191">
+        <v>4</v>
+      </c>
+      <c r="L191">
+        <v>3</v>
+      </c>
+      <c r="M191">
+        <v>3</v>
+      </c>
+      <c r="N191">
+        <v>6</v>
+      </c>
+      <c r="O191" t="s">
+        <v>209</v>
+      </c>
+      <c r="P191" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q191">
+        <v>3.2</v>
+      </c>
+      <c r="R191">
+        <v>1.87</v>
+      </c>
+      <c r="S191">
+        <v>3.6</v>
+      </c>
+      <c r="T191">
+        <v>1.55</v>
+      </c>
+      <c r="U191">
+        <v>2.3</v>
+      </c>
+      <c r="V191">
+        <v>3.5</v>
+      </c>
+      <c r="W191">
+        <v>1.26</v>
+      </c>
+      <c r="X191">
+        <v>10</v>
+      </c>
+      <c r="Y191">
+        <v>1.04</v>
+      </c>
+      <c r="Z191">
+        <v>2.41</v>
+      </c>
+      <c r="AA191">
+        <v>2.81</v>
+      </c>
+      <c r="AB191">
+        <v>2.86</v>
+      </c>
+      <c r="AC191">
+        <v>1.11</v>
+      </c>
+      <c r="AD191">
+        <v>6</v>
+      </c>
+      <c r="AE191">
+        <v>1.48</v>
+      </c>
+      <c r="AF191">
+        <v>2.37</v>
+      </c>
+      <c r="AG191">
+        <v>2.62</v>
+      </c>
+      <c r="AH191">
+        <v>1.42</v>
+      </c>
+      <c r="AI191">
+        <v>2.1</v>
+      </c>
+      <c r="AJ191">
+        <v>1.63</v>
+      </c>
+      <c r="AK191">
+        <v>1.37</v>
+      </c>
+      <c r="AL191">
+        <v>1.37</v>
+      </c>
+      <c r="AM191">
+        <v>1.49</v>
+      </c>
+      <c r="AN191">
+        <v>1.75</v>
+      </c>
+      <c r="AO191">
+        <v>1.89</v>
+      </c>
+      <c r="AP191">
+        <v>1.67</v>
+      </c>
+      <c r="AQ191">
+        <v>1.8</v>
+      </c>
+      <c r="AR191">
+        <v>1.34</v>
+      </c>
+      <c r="AS191">
+        <v>1.18</v>
+      </c>
+      <c r="AT191">
+        <v>2.52</v>
+      </c>
+      <c r="AU191">
+        <v>4</v>
+      </c>
+      <c r="AV191">
+        <v>4</v>
+      </c>
+      <c r="AW191">
+        <v>-1</v>
+      </c>
+      <c r="AX191">
+        <v>-1</v>
+      </c>
+      <c r="AY191">
+        <v>3</v>
+      </c>
+      <c r="AZ191">
+        <v>3</v>
+      </c>
+      <c r="BA191">
+        <v>-1</v>
+      </c>
+      <c r="BB191">
+        <v>-1</v>
+      </c>
+      <c r="BC191">
+        <v>-1</v>
+      </c>
+      <c r="BD191">
+        <v>1.93</v>
+      </c>
+      <c r="BE191">
+        <v>6.15</v>
+      </c>
+      <c r="BF191">
+        <v>2.29</v>
+      </c>
+      <c r="BG191">
+        <v>1.31</v>
+      </c>
+      <c r="BH191">
+        <v>2.92</v>
+      </c>
+      <c r="BI191">
+        <v>1.58</v>
+      </c>
+      <c r="BJ191">
+        <v>2.12</v>
+      </c>
+      <c r="BK191">
+        <v>2.01</v>
+      </c>
+      <c r="BL191">
+        <v>1.68</v>
+      </c>
+      <c r="BM191">
+        <v>2.62</v>
+      </c>
+      <c r="BN191">
+        <v>1.38</v>
+      </c>
+      <c r="BO191">
+        <v>3.68</v>
+      </c>
+      <c r="BP191">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="304">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -646,6 +646,18 @@
     <t>['34', '36', '76']</t>
   </si>
   <si>
+    <t>['43', '51', '86']</t>
+  </si>
+  <si>
+    <t>['46', '65']</t>
+  </si>
+  <si>
+    <t>['89']</t>
+  </si>
+  <si>
+    <t>['16', '54']</t>
+  </si>
+  <si>
     <t>['31', '60']</t>
   </si>
   <si>
@@ -908,6 +920,12 @@
   </si>
   <si>
     <t>['23', '40', '65']</t>
+  </si>
+  <si>
+    <t>['49', '86']</t>
+  </si>
+  <si>
+    <t>['22', '49', '9004']</t>
   </si>
 </sst>
 </file>
@@ -1269,7 +1287,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP191"/>
+  <dimension ref="A1:BP198"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1525,7 +1543,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q2">
         <v>3.6</v>
@@ -1603,7 +1621,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ2">
         <v>1.8</v>
@@ -1809,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ3">
         <v>0.82</v>
@@ -2018,7 +2036,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ4">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2143,7 +2161,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2224,7 +2242,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ5">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2349,7 +2367,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q6">
         <v>4.1</v>
@@ -2427,7 +2445,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ6">
         <v>1.8</v>
@@ -2761,7 +2779,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q8">
         <v>2.28</v>
@@ -3045,10 +3063,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0.22</v>
+        <v>0.5</v>
       </c>
       <c r="AQ9">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3251,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ10">
         <v>1.18</v>
@@ -3460,7 +3478,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ11">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3666,7 +3684,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ12">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR12">
         <v>1.68</v>
@@ -3869,10 +3887,10 @@
         <v>3</v>
       </c>
       <c r="AP13">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ13">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4075,7 +4093,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ14">
         <v>1.3</v>
@@ -4203,7 +4221,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q15">
         <v>4.1</v>
@@ -4490,7 +4508,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ16">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4693,7 +4711,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ17">
         <v>2</v>
@@ -5105,7 +5123,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ19">
         <v>1</v>
@@ -5439,7 +5457,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q21">
         <v>4.4</v>
@@ -5517,7 +5535,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>0.22</v>
+        <v>0.5</v>
       </c>
       <c r="AQ21">
         <v>1.18</v>
@@ -5726,7 +5744,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5851,7 +5869,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -6138,7 +6156,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ24">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR24">
         <v>3.04</v>
@@ -6263,7 +6281,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -6341,7 +6359,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ25">
         <v>0.82</v>
@@ -6547,7 +6565,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ26">
         <v>1.18</v>
@@ -6675,7 +6693,7 @@
         <v>90</v>
       </c>
       <c r="P27" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q27">
         <v>3.2</v>
@@ -6959,7 +6977,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ28">
         <v>1.8</v>
@@ -7580,7 +7598,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ31">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR31">
         <v>1.27</v>
@@ -7705,7 +7723,7 @@
         <v>113</v>
       </c>
       <c r="P32" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q32">
         <v>3.45</v>
@@ -7911,7 +7929,7 @@
         <v>114</v>
       </c>
       <c r="P33" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -7989,10 +8007,10 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ33">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR33">
         <v>1.88</v>
@@ -8117,7 +8135,7 @@
         <v>115</v>
       </c>
       <c r="P34" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8195,7 +8213,7 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>0.22</v>
+        <v>0.5</v>
       </c>
       <c r="AQ34">
         <v>2</v>
@@ -8323,7 +8341,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q35">
         <v>3.4</v>
@@ -8529,7 +8547,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q36">
         <v>2.8</v>
@@ -8813,10 +8831,10 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ37">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR37">
         <v>1.86</v>
@@ -8941,7 +8959,7 @@
         <v>118</v>
       </c>
       <c r="P38" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q38">
         <v>2.6</v>
@@ -9228,7 +9246,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ39">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR39">
         <v>1.33</v>
@@ -9431,7 +9449,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ40">
         <v>1</v>
@@ -9640,7 +9658,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ41">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR41">
         <v>1.46</v>
@@ -9765,7 +9783,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9846,7 +9864,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ42">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR42">
         <v>0</v>
@@ -10049,7 +10067,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ43">
         <v>1</v>
@@ -10795,7 +10813,7 @@
         <v>105</v>
       </c>
       <c r="P47" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -11001,7 +11019,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q48">
         <v>3.6</v>
@@ -11207,7 +11225,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q49">
         <v>3.6</v>
@@ -11288,7 +11306,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ49">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR49">
         <v>1.15</v>
@@ -11491,10 +11509,10 @@
         <v>1.5</v>
       </c>
       <c r="AP50">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ50">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR50">
         <v>1.08</v>
@@ -11619,7 +11637,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q51">
         <v>1.91</v>
@@ -11697,7 +11715,7 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ51">
         <v>1.2</v>
@@ -11825,7 +11843,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -11906,7 +11924,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ52">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR52">
         <v>1.25</v>
@@ -12031,7 +12049,7 @@
         <v>90</v>
       </c>
       <c r="P53" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12524,7 +12542,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ55">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR55">
         <v>1.39</v>
@@ -12649,7 +12667,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q56">
         <v>4.33</v>
@@ -12727,10 +12745,10 @@
         <v>0.75</v>
       </c>
       <c r="AP56">
-        <v>0.22</v>
+        <v>0.5</v>
       </c>
       <c r="AQ56">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR56">
         <v>1.03</v>
@@ -12933,7 +12951,7 @@
         <v>3</v>
       </c>
       <c r="AP57">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ57">
         <v>2</v>
@@ -13139,10 +13157,10 @@
         <v>0.5</v>
       </c>
       <c r="AP58">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ58">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR58">
         <v>1.9</v>
@@ -13267,7 +13285,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13679,7 +13697,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13885,7 +13903,7 @@
         <v>90</v>
       </c>
       <c r="P62" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q62">
         <v>2.75</v>
@@ -14172,7 +14190,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ63">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR63">
         <v>1.46</v>
@@ -14503,7 +14521,7 @@
         <v>90</v>
       </c>
       <c r="P65" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q65">
         <v>3.6</v>
@@ -14709,7 +14727,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q66">
         <v>4.75</v>
@@ -14787,7 +14805,7 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ66">
         <v>1.11</v>
@@ -14915,7 +14933,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q67">
         <v>2.88</v>
@@ -14993,7 +15011,7 @@
         <v>0.75</v>
       </c>
       <c r="AP67">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ67">
         <v>0.82</v>
@@ -15202,7 +15220,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ68">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR68">
         <v>1.93</v>
@@ -15611,10 +15629,10 @@
         <v>0.5</v>
       </c>
       <c r="AP70">
-        <v>0.22</v>
+        <v>0.5</v>
       </c>
       <c r="AQ70">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR70">
         <v>1.09</v>
@@ -15817,7 +15835,7 @@
         <v>1.5</v>
       </c>
       <c r="AP71">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ71">
         <v>1.78</v>
@@ -16641,10 +16659,10 @@
         <v>0.33</v>
       </c>
       <c r="AP75">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ75">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR75">
         <v>1.77</v>
@@ -17056,7 +17074,7 @@
         <v>1</v>
       </c>
       <c r="AQ77">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR77">
         <v>1.29</v>
@@ -17387,7 +17405,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q79">
         <v>2.63</v>
@@ -17465,10 +17483,10 @@
         <v>1.33</v>
       </c>
       <c r="AP79">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ79">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR79">
         <v>2.01</v>
@@ -17674,7 +17692,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ80">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR80">
         <v>1.56</v>
@@ -17799,7 +17817,7 @@
         <v>145</v>
       </c>
       <c r="P81" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q81">
         <v>3.2</v>
@@ -17877,7 +17895,7 @@
         <v>0.67</v>
       </c>
       <c r="AP81">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ81">
         <v>1.11</v>
@@ -18289,7 +18307,7 @@
         <v>0.8</v>
       </c>
       <c r="AP83">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ83">
         <v>0.82</v>
@@ -18498,7 +18516,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ84">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR84">
         <v>1.56</v>
@@ -18829,7 +18847,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19035,7 +19053,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19116,7 +19134,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ87">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR87">
         <v>1.26</v>
@@ -19241,7 +19259,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19319,7 +19337,7 @@
         <v>2.25</v>
       </c>
       <c r="AP88">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ88">
         <v>1.8</v>
@@ -19447,7 +19465,7 @@
         <v>90</v>
       </c>
       <c r="P89" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19528,7 +19546,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ89">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR89">
         <v>2.31</v>
@@ -19937,7 +19955,7 @@
         <v>0.75</v>
       </c>
       <c r="AP91">
-        <v>0.22</v>
+        <v>0.5</v>
       </c>
       <c r="AQ91">
         <v>1.3</v>
@@ -20065,7 +20083,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q92">
         <v>4</v>
@@ -20271,7 +20289,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q93">
         <v>3</v>
@@ -20352,7 +20370,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ93">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR93">
         <v>1.32</v>
@@ -20477,7 +20495,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q94">
         <v>2.3</v>
@@ -20683,7 +20701,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q95">
         <v>3.5</v>
@@ -20967,7 +20985,7 @@
         <v>1.5</v>
       </c>
       <c r="AP96">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ96">
         <v>1.78</v>
@@ -21095,7 +21113,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q97">
         <v>3.25</v>
@@ -21173,10 +21191,10 @@
         <v>0.25</v>
       </c>
       <c r="AP97">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ97">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR97">
         <v>1.35</v>
@@ -21379,10 +21397,10 @@
         <v>1.25</v>
       </c>
       <c r="AP98">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ98">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR98">
         <v>1.74</v>
@@ -21588,7 +21606,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ99">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR99">
         <v>1.86</v>
@@ -21713,7 +21731,7 @@
         <v>157</v>
       </c>
       <c r="P100" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q100">
         <v>2.6</v>
@@ -21919,7 +21937,7 @@
         <v>122</v>
       </c>
       <c r="P101" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q101">
         <v>3.25</v>
@@ -22125,7 +22143,7 @@
         <v>158</v>
       </c>
       <c r="P102" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q102">
         <v>2.25</v>
@@ -22615,10 +22633,10 @@
         <v>1</v>
       </c>
       <c r="AP104">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ104">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR104">
         <v>1.89</v>
@@ -22743,7 +22761,7 @@
         <v>160</v>
       </c>
       <c r="P105" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q105">
         <v>2.38</v>
@@ -22821,7 +22839,7 @@
         <v>1</v>
       </c>
       <c r="AP105">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ105">
         <v>1.18</v>
@@ -22949,7 +22967,7 @@
         <v>90</v>
       </c>
       <c r="P106" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23030,7 +23048,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ106">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR106">
         <v>1.3</v>
@@ -23155,7 +23173,7 @@
         <v>90</v>
       </c>
       <c r="P107" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q107">
         <v>3.25</v>
@@ -23233,7 +23251,7 @@
         <v>1.25</v>
       </c>
       <c r="AP107">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ107">
         <v>1</v>
@@ -23361,7 +23379,7 @@
         <v>161</v>
       </c>
       <c r="P108" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23567,7 +23585,7 @@
         <v>162</v>
       </c>
       <c r="P109" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q109">
         <v>2.3</v>
@@ -23851,10 +23869,10 @@
         <v>1</v>
       </c>
       <c r="AP110">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ110">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR110">
         <v>1.34</v>
@@ -23979,7 +23997,7 @@
         <v>122</v>
       </c>
       <c r="P111" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q111">
         <v>4</v>
@@ -24391,7 +24409,7 @@
         <v>164</v>
       </c>
       <c r="P113" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q113">
         <v>3.6</v>
@@ -24803,7 +24821,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q115">
         <v>3.75</v>
@@ -25009,7 +25027,7 @@
         <v>165</v>
       </c>
       <c r="P116" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q116">
         <v>3.25</v>
@@ -25296,7 +25314,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ117">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR117">
         <v>1.11</v>
@@ -25499,7 +25517,7 @@
         <v>1.4</v>
       </c>
       <c r="AP118">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ118">
         <v>1.78</v>
@@ -25914,7 +25932,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ120">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR120">
         <v>1.38</v>
@@ -26039,7 +26057,7 @@
         <v>167</v>
       </c>
       <c r="P121" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q121">
         <v>3.4</v>
@@ -26117,7 +26135,7 @@
         <v>0.6</v>
       </c>
       <c r="AP121">
-        <v>0.22</v>
+        <v>0.5</v>
       </c>
       <c r="AQ121">
         <v>1</v>
@@ -26245,7 +26263,7 @@
         <v>168</v>
       </c>
       <c r="P122" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26326,7 +26344,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ122">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR122">
         <v>1.51</v>
@@ -26451,7 +26469,7 @@
         <v>169</v>
       </c>
       <c r="P123" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q123">
         <v>3.4</v>
@@ -26529,7 +26547,7 @@
         <v>0.86</v>
       </c>
       <c r="AP123">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ123">
         <v>1.18</v>
@@ -26657,7 +26675,7 @@
         <v>90</v>
       </c>
       <c r="P124" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q124">
         <v>4</v>
@@ -27275,7 +27293,7 @@
         <v>171</v>
       </c>
       <c r="P127" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27353,10 +27371,10 @@
         <v>0.8</v>
       </c>
       <c r="AP127">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ127">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR127">
         <v>1.52</v>
@@ -27481,7 +27499,7 @@
         <v>90</v>
       </c>
       <c r="P128" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q128">
         <v>2.88</v>
@@ -27562,7 +27580,7 @@
         <v>1</v>
       </c>
       <c r="AQ128">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR128">
         <v>1.41</v>
@@ -27687,7 +27705,7 @@
         <v>172</v>
       </c>
       <c r="P129" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -27765,10 +27783,10 @@
         <v>0.83</v>
       </c>
       <c r="AP129">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ129">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR129">
         <v>1.79</v>
@@ -27893,7 +27911,7 @@
         <v>90</v>
       </c>
       <c r="P130" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q130">
         <v>3.4</v>
@@ -27971,10 +27989,10 @@
         <v>0.8</v>
       </c>
       <c r="AP130">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ130">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR130">
         <v>1.35</v>
@@ -28099,7 +28117,7 @@
         <v>173</v>
       </c>
       <c r="P131" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q131">
         <v>2.1</v>
@@ -28305,7 +28323,7 @@
         <v>174</v>
       </c>
       <c r="P132" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q132">
         <v>2.5</v>
@@ -28511,7 +28529,7 @@
         <v>175</v>
       </c>
       <c r="P133" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q133">
         <v>4</v>
@@ -28717,7 +28735,7 @@
         <v>176</v>
       </c>
       <c r="P134" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q134">
         <v>3.4</v>
@@ -28798,7 +28816,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ134">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR134">
         <v>1.18</v>
@@ -28923,7 +28941,7 @@
         <v>177</v>
       </c>
       <c r="P135" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -29004,7 +29022,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ135">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR135">
         <v>1.52</v>
@@ -29210,7 +29228,7 @@
         <v>1</v>
       </c>
       <c r="AQ136">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR136">
         <v>1.4</v>
@@ -29335,7 +29353,7 @@
         <v>179</v>
       </c>
       <c r="P137" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q137">
         <v>4</v>
@@ -29413,7 +29431,7 @@
         <v>1.17</v>
       </c>
       <c r="AP137">
-        <v>0.22</v>
+        <v>0.5</v>
       </c>
       <c r="AQ137">
         <v>1</v>
@@ -29541,7 +29559,7 @@
         <v>90</v>
       </c>
       <c r="P138" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q138">
         <v>3.75</v>
@@ -29747,7 +29765,7 @@
         <v>90</v>
       </c>
       <c r="P139" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q139">
         <v>3</v>
@@ -29953,7 +29971,7 @@
         <v>90</v>
       </c>
       <c r="P140" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q140">
         <v>3</v>
@@ -30031,10 +30049,10 @@
         <v>0.8</v>
       </c>
       <c r="AP140">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ140">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR140">
         <v>1.32</v>
@@ -30159,7 +30177,7 @@
         <v>180</v>
       </c>
       <c r="P141" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30237,7 +30255,7 @@
         <v>1.17</v>
       </c>
       <c r="AP141">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ141">
         <v>1.78</v>
@@ -30443,7 +30461,7 @@
         <v>2.17</v>
       </c>
       <c r="AP142">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ142">
         <v>2</v>
@@ -30571,7 +30589,7 @@
         <v>182</v>
       </c>
       <c r="P143" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q143">
         <v>3.1</v>
@@ -30649,10 +30667,10 @@
         <v>1.13</v>
       </c>
       <c r="AP143">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ143">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR143">
         <v>1.61</v>
@@ -31395,7 +31413,7 @@
         <v>90</v>
       </c>
       <c r="P147" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q147">
         <v>3.1</v>
@@ -31473,7 +31491,7 @@
         <v>2</v>
       </c>
       <c r="AP147">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ147">
         <v>1.8</v>
@@ -31885,10 +31903,10 @@
         <v>0.71</v>
       </c>
       <c r="AP149">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ149">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR149">
         <v>1.34</v>
@@ -32094,7 +32112,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ150">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR150">
         <v>1.24</v>
@@ -32219,7 +32237,7 @@
         <v>186</v>
       </c>
       <c r="P151" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q151">
         <v>2.38</v>
@@ -32712,7 +32730,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ153">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR153">
         <v>1.56</v>
@@ -32837,7 +32855,7 @@
         <v>187</v>
       </c>
       <c r="P154" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q154">
         <v>3.4</v>
@@ -32918,7 +32936,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ154">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR154">
         <v>1.59</v>
@@ -33327,7 +33345,7 @@
         <v>1.86</v>
       </c>
       <c r="AP156">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ156">
         <v>2</v>
@@ -33661,7 +33679,7 @@
         <v>90</v>
       </c>
       <c r="P158" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -33739,7 +33757,7 @@
         <v>1.43</v>
       </c>
       <c r="AP158">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ158">
         <v>1.78</v>
@@ -34073,7 +34091,7 @@
         <v>141</v>
       </c>
       <c r="P160" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q160">
         <v>3.75</v>
@@ -34279,7 +34297,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q161">
         <v>4.75</v>
@@ -34357,7 +34375,7 @@
         <v>1.5</v>
       </c>
       <c r="AP161">
-        <v>0.22</v>
+        <v>0.5</v>
       </c>
       <c r="AQ161">
         <v>1.8</v>
@@ -34485,7 +34503,7 @@
         <v>180</v>
       </c>
       <c r="P162" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q162">
         <v>3.75</v>
@@ -34563,7 +34581,7 @@
         <v>1.75</v>
       </c>
       <c r="AP162">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ162">
         <v>2</v>
@@ -34897,7 +34915,7 @@
         <v>191</v>
       </c>
       <c r="P164" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q164">
         <v>3.1</v>
@@ -34975,10 +34993,10 @@
         <v>1.14</v>
       </c>
       <c r="AP164">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ164">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR164">
         <v>1.35</v>
@@ -35184,7 +35202,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ165">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR165">
         <v>1.25</v>
@@ -35309,7 +35327,7 @@
         <v>90</v>
       </c>
       <c r="P166" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q166">
         <v>2.75</v>
@@ -35721,7 +35739,7 @@
         <v>193</v>
       </c>
       <c r="P168" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q168">
         <v>2.75</v>
@@ -35927,7 +35945,7 @@
         <v>194</v>
       </c>
       <c r="P169" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36211,7 +36229,7 @@
         <v>0.9</v>
       </c>
       <c r="AP170">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ170">
         <v>0.82</v>
@@ -36339,7 +36357,7 @@
         <v>196</v>
       </c>
       <c r="P171" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q171">
         <v>2.75</v>
@@ -36417,10 +36435,10 @@
         <v>1.13</v>
       </c>
       <c r="AP171">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ171">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR171">
         <v>1.8</v>
@@ -36623,10 +36641,10 @@
         <v>0.63</v>
       </c>
       <c r="AP172">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ172">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR172">
         <v>1.63</v>
@@ -36751,7 +36769,7 @@
         <v>197</v>
       </c>
       <c r="P173" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q173">
         <v>3</v>
@@ -36832,7 +36850,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ173">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR173">
         <v>1.56</v>
@@ -37038,7 +37056,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ174">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR174">
         <v>1.5</v>
@@ -37369,7 +37387,7 @@
         <v>90</v>
       </c>
       <c r="P176" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q176">
         <v>3.4</v>
@@ -37447,7 +37465,7 @@
         <v>1.67</v>
       </c>
       <c r="AP176">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ176">
         <v>1.8</v>
@@ -37781,7 +37799,7 @@
         <v>200</v>
       </c>
       <c r="P178" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q178">
         <v>3.4</v>
@@ -37859,7 +37877,7 @@
         <v>1.14</v>
       </c>
       <c r="AP178">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ178">
         <v>1</v>
@@ -38065,10 +38083,10 @@
         <v>1.13</v>
       </c>
       <c r="AP179">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ179">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR179">
         <v>1.53</v>
@@ -38193,7 +38211,7 @@
         <v>202</v>
       </c>
       <c r="P180" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q180">
         <v>2</v>
@@ -38271,7 +38289,7 @@
         <v>1.38</v>
       </c>
       <c r="AP180">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ180">
         <v>1.2</v>
@@ -38399,7 +38417,7 @@
         <v>90</v>
       </c>
       <c r="P181" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q181">
         <v>4</v>
@@ -38480,7 +38498,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ181">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR181">
         <v>1.23</v>
@@ -38686,7 +38704,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ182">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR182">
         <v>1.66</v>
@@ -39017,7 +39035,7 @@
         <v>204</v>
       </c>
       <c r="P184" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39223,7 +39241,7 @@
         <v>205</v>
       </c>
       <c r="P185" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q185">
         <v>3.2</v>
@@ -39429,7 +39447,7 @@
         <v>206</v>
       </c>
       <c r="P186" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -39635,7 +39653,7 @@
         <v>207</v>
       </c>
       <c r="P187" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q187">
         <v>2.8</v>
@@ -40047,7 +40065,7 @@
         <v>180</v>
       </c>
       <c r="P189" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q189">
         <v>2.88</v>
@@ -40459,7 +40477,7 @@
         <v>209</v>
       </c>
       <c r="P191" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -40537,7 +40555,7 @@
         <v>1.89</v>
       </c>
       <c r="AP191">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ191">
         <v>1.8</v>
@@ -40616,6 +40634,1448 @@
       </c>
       <c r="BP191">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:68">
+      <c r="A192" s="1">
+        <v>191</v>
+      </c>
+      <c r="B192">
+        <v>7778682</v>
+      </c>
+      <c r="C192" t="s">
+        <v>68</v>
+      </c>
+      <c r="D192" t="s">
+        <v>69</v>
+      </c>
+      <c r="E192" s="2">
+        <v>45829.16666666666</v>
+      </c>
+      <c r="F192">
+        <v>20</v>
+      </c>
+      <c r="G192" t="s">
+        <v>70</v>
+      </c>
+      <c r="H192" t="s">
+        <v>86</v>
+      </c>
+      <c r="I192">
+        <v>1</v>
+      </c>
+      <c r="J192">
+        <v>0</v>
+      </c>
+      <c r="K192">
+        <v>1</v>
+      </c>
+      <c r="L192">
+        <v>3</v>
+      </c>
+      <c r="M192">
+        <v>1</v>
+      </c>
+      <c r="N192">
+        <v>4</v>
+      </c>
+      <c r="O192" t="s">
+        <v>210</v>
+      </c>
+      <c r="P192" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q192">
+        <v>2.63</v>
+      </c>
+      <c r="R192">
+        <v>2</v>
+      </c>
+      <c r="S192">
+        <v>4</v>
+      </c>
+      <c r="T192">
+        <v>1.42</v>
+      </c>
+      <c r="U192">
+        <v>2.81</v>
+      </c>
+      <c r="V192">
+        <v>3.14</v>
+      </c>
+      <c r="W192">
+        <v>1.35</v>
+      </c>
+      <c r="X192">
+        <v>7.6</v>
+      </c>
+      <c r="Y192">
+        <v>1.05</v>
+      </c>
+      <c r="Z192">
+        <v>2.1</v>
+      </c>
+      <c r="AA192">
+        <v>3.19</v>
+      </c>
+      <c r="AB192">
+        <v>3.02</v>
+      </c>
+      <c r="AC192">
+        <v>1.03</v>
+      </c>
+      <c r="AD192">
+        <v>9</v>
+      </c>
+      <c r="AE192">
+        <v>1.3</v>
+      </c>
+      <c r="AF192">
+        <v>3.2</v>
+      </c>
+      <c r="AG192">
+        <v>2.02</v>
+      </c>
+      <c r="AH192">
+        <v>1.7</v>
+      </c>
+      <c r="AI192">
+        <v>1.83</v>
+      </c>
+      <c r="AJ192">
+        <v>1.83</v>
+      </c>
+      <c r="AK192">
+        <v>1.24</v>
+      </c>
+      <c r="AL192">
+        <v>1.27</v>
+      </c>
+      <c r="AM192">
+        <v>1.72</v>
+      </c>
+      <c r="AN192">
+        <v>1</v>
+      </c>
+      <c r="AO192">
+        <v>0.78</v>
+      </c>
+      <c r="AP192">
+        <v>1.18</v>
+      </c>
+      <c r="AQ192">
+        <v>0.7</v>
+      </c>
+      <c r="AR192">
+        <v>1.63</v>
+      </c>
+      <c r="AS192">
+        <v>1.15</v>
+      </c>
+      <c r="AT192">
+        <v>2.78</v>
+      </c>
+      <c r="AU192">
+        <v>4</v>
+      </c>
+      <c r="AV192">
+        <v>2</v>
+      </c>
+      <c r="AW192">
+        <v>8</v>
+      </c>
+      <c r="AX192">
+        <v>3</v>
+      </c>
+      <c r="AY192">
+        <v>12</v>
+      </c>
+      <c r="AZ192">
+        <v>5</v>
+      </c>
+      <c r="BA192">
+        <v>9</v>
+      </c>
+      <c r="BB192">
+        <v>4</v>
+      </c>
+      <c r="BC192">
+        <v>13</v>
+      </c>
+      <c r="BD192">
+        <v>1.59</v>
+      </c>
+      <c r="BE192">
+        <v>8</v>
+      </c>
+      <c r="BF192">
+        <v>2.8</v>
+      </c>
+      <c r="BG192">
+        <v>1.29</v>
+      </c>
+      <c r="BH192">
+        <v>3.3</v>
+      </c>
+      <c r="BI192">
+        <v>1.49</v>
+      </c>
+      <c r="BJ192">
+        <v>2.52</v>
+      </c>
+      <c r="BK192">
+        <v>1.85</v>
+      </c>
+      <c r="BL192">
+        <v>1.95</v>
+      </c>
+      <c r="BM192">
+        <v>2.32</v>
+      </c>
+      <c r="BN192">
+        <v>1.57</v>
+      </c>
+      <c r="BO192">
+        <v>3.1</v>
+      </c>
+      <c r="BP192">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="193" spans="1:68">
+      <c r="A193" s="1">
+        <v>192</v>
+      </c>
+      <c r="B193">
+        <v>7778688</v>
+      </c>
+      <c r="C193" t="s">
+        <v>68</v>
+      </c>
+      <c r="D193" t="s">
+        <v>69</v>
+      </c>
+      <c r="E193" s="2">
+        <v>45829.25</v>
+      </c>
+      <c r="F193">
+        <v>20</v>
+      </c>
+      <c r="G193" t="s">
+        <v>78</v>
+      </c>
+      <c r="H193" t="s">
+        <v>84</v>
+      </c>
+      <c r="I193">
+        <v>0</v>
+      </c>
+      <c r="J193">
+        <v>0</v>
+      </c>
+      <c r="K193">
+        <v>0</v>
+      </c>
+      <c r="L193">
+        <v>1</v>
+      </c>
+      <c r="M193">
+        <v>2</v>
+      </c>
+      <c r="N193">
+        <v>3</v>
+      </c>
+      <c r="O193" t="s">
+        <v>101</v>
+      </c>
+      <c r="P193" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q193">
+        <v>3.1</v>
+      </c>
+      <c r="R193">
+        <v>2</v>
+      </c>
+      <c r="S193">
+        <v>3.4</v>
+      </c>
+      <c r="T193">
+        <v>1.45</v>
+      </c>
+      <c r="U193">
+        <v>2.7</v>
+      </c>
+      <c r="V193">
+        <v>3.29</v>
+      </c>
+      <c r="W193">
+        <v>1.32</v>
+      </c>
+      <c r="X193">
+        <v>8</v>
+      </c>
+      <c r="Y193">
+        <v>1.05</v>
+      </c>
+      <c r="Z193">
+        <v>2.27</v>
+      </c>
+      <c r="AA193">
+        <v>3.14</v>
+      </c>
+      <c r="AB193">
+        <v>2.77</v>
+      </c>
+      <c r="AC193">
+        <v>1.05</v>
+      </c>
+      <c r="AD193">
+        <v>8</v>
+      </c>
+      <c r="AE193">
+        <v>1.36</v>
+      </c>
+      <c r="AF193">
+        <v>2.88</v>
+      </c>
+      <c r="AG193">
+        <v>2.15</v>
+      </c>
+      <c r="AH193">
+        <v>1.62</v>
+      </c>
+      <c r="AI193">
+        <v>1.83</v>
+      </c>
+      <c r="AJ193">
+        <v>1.83</v>
+      </c>
+      <c r="AK193">
+        <v>1.38</v>
+      </c>
+      <c r="AL193">
+        <v>1.3</v>
+      </c>
+      <c r="AM193">
+        <v>1.48</v>
+      </c>
+      <c r="AN193">
+        <v>1.1</v>
+      </c>
+      <c r="AO193">
+        <v>1.63</v>
+      </c>
+      <c r="AP193">
+        <v>1</v>
+      </c>
+      <c r="AQ193">
+        <v>1.78</v>
+      </c>
+      <c r="AR193">
+        <v>1.57</v>
+      </c>
+      <c r="AS193">
+        <v>1.43</v>
+      </c>
+      <c r="AT193">
+        <v>3</v>
+      </c>
+      <c r="AU193">
+        <v>2</v>
+      </c>
+      <c r="AV193">
+        <v>3</v>
+      </c>
+      <c r="AW193">
+        <v>2</v>
+      </c>
+      <c r="AX193">
+        <v>9</v>
+      </c>
+      <c r="AY193">
+        <v>4</v>
+      </c>
+      <c r="AZ193">
+        <v>12</v>
+      </c>
+      <c r="BA193">
+        <v>3</v>
+      </c>
+      <c r="BB193">
+        <v>5</v>
+      </c>
+      <c r="BC193">
+        <v>8</v>
+      </c>
+      <c r="BD193">
+        <v>1.95</v>
+      </c>
+      <c r="BE193">
+        <v>8</v>
+      </c>
+      <c r="BF193">
+        <v>2.1</v>
+      </c>
+      <c r="BG193">
+        <v>1.29</v>
+      </c>
+      <c r="BH193">
+        <v>3.3</v>
+      </c>
+      <c r="BI193">
+        <v>1.66</v>
+      </c>
+      <c r="BJ193">
+        <v>2.21</v>
+      </c>
+      <c r="BK193">
+        <v>2.07</v>
+      </c>
+      <c r="BL193">
+        <v>1.74</v>
+      </c>
+      <c r="BM193">
+        <v>2.7</v>
+      </c>
+      <c r="BN193">
+        <v>1.41</v>
+      </c>
+      <c r="BO193">
+        <v>3.4</v>
+      </c>
+      <c r="BP193">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="194" spans="1:68">
+      <c r="A194" s="1">
+        <v>193</v>
+      </c>
+      <c r="B194">
+        <v>7778687</v>
+      </c>
+      <c r="C194" t="s">
+        <v>68</v>
+      </c>
+      <c r="D194" t="s">
+        <v>69</v>
+      </c>
+      <c r="E194" s="2">
+        <v>45829.25</v>
+      </c>
+      <c r="F194">
+        <v>20</v>
+      </c>
+      <c r="G194" t="s">
+        <v>77</v>
+      </c>
+      <c r="H194" t="s">
+        <v>81</v>
+      </c>
+      <c r="I194">
+        <v>0</v>
+      </c>
+      <c r="J194">
+        <v>0</v>
+      </c>
+      <c r="K194">
+        <v>0</v>
+      </c>
+      <c r="L194">
+        <v>2</v>
+      </c>
+      <c r="M194">
+        <v>0</v>
+      </c>
+      <c r="N194">
+        <v>2</v>
+      </c>
+      <c r="O194" t="s">
+        <v>211</v>
+      </c>
+      <c r="P194" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q194">
+        <v>3.8</v>
+      </c>
+      <c r="R194">
+        <v>1.99</v>
+      </c>
+      <c r="S194">
+        <v>2.84</v>
+      </c>
+      <c r="T194">
+        <v>1.43</v>
+      </c>
+      <c r="U194">
+        <v>2.62</v>
+      </c>
+      <c r="V194">
+        <v>3.14</v>
+      </c>
+      <c r="W194">
+        <v>1.31</v>
+      </c>
+      <c r="X194">
+        <v>8</v>
+      </c>
+      <c r="Y194">
+        <v>1.05</v>
+      </c>
+      <c r="Z194">
+        <v>2.81</v>
+      </c>
+      <c r="AA194">
+        <v>3.15</v>
+      </c>
+      <c r="AB194">
+        <v>2.24</v>
+      </c>
+      <c r="AC194">
+        <v>1.01</v>
+      </c>
+      <c r="AD194">
+        <v>8.6</v>
+      </c>
+      <c r="AE194">
+        <v>1.32</v>
+      </c>
+      <c r="AF194">
+        <v>2.88</v>
+      </c>
+      <c r="AG194">
+        <v>2.07</v>
+      </c>
+      <c r="AH194">
+        <v>1.67</v>
+      </c>
+      <c r="AI194">
+        <v>1.84</v>
+      </c>
+      <c r="AJ194">
+        <v>1.82</v>
+      </c>
+      <c r="AK194">
+        <v>1.59</v>
+      </c>
+      <c r="AL194">
+        <v>1.28</v>
+      </c>
+      <c r="AM194">
+        <v>1.31</v>
+      </c>
+      <c r="AN194">
+        <v>0.22</v>
+      </c>
+      <c r="AO194">
+        <v>0.67</v>
+      </c>
+      <c r="AP194">
+        <v>0.5</v>
+      </c>
+      <c r="AQ194">
+        <v>0.6</v>
+      </c>
+      <c r="AR194">
+        <v>1.19</v>
+      </c>
+      <c r="AS194">
+        <v>1.47</v>
+      </c>
+      <c r="AT194">
+        <v>2.66</v>
+      </c>
+      <c r="AU194">
+        <v>3</v>
+      </c>
+      <c r="AV194">
+        <v>2</v>
+      </c>
+      <c r="AW194">
+        <v>10</v>
+      </c>
+      <c r="AX194">
+        <v>7</v>
+      </c>
+      <c r="AY194">
+        <v>13</v>
+      </c>
+      <c r="AZ194">
+        <v>9</v>
+      </c>
+      <c r="BA194">
+        <v>8</v>
+      </c>
+      <c r="BB194">
+        <v>6</v>
+      </c>
+      <c r="BC194">
+        <v>14</v>
+      </c>
+      <c r="BD194">
+        <v>2.77</v>
+      </c>
+      <c r="BE194">
+        <v>8</v>
+      </c>
+      <c r="BF194">
+        <v>1.64</v>
+      </c>
+      <c r="BG194">
+        <v>1.29</v>
+      </c>
+      <c r="BH194">
+        <v>3.3</v>
+      </c>
+      <c r="BI194">
+        <v>1.51</v>
+      </c>
+      <c r="BJ194">
+        <v>2.51</v>
+      </c>
+      <c r="BK194">
+        <v>1.84</v>
+      </c>
+      <c r="BL194">
+        <v>1.95</v>
+      </c>
+      <c r="BM194">
+        <v>2.31</v>
+      </c>
+      <c r="BN194">
+        <v>1.59</v>
+      </c>
+      <c r="BO194">
+        <v>3.1</v>
+      </c>
+      <c r="BP194">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="195" spans="1:68">
+      <c r="A195" s="1">
+        <v>194</v>
+      </c>
+      <c r="B195">
+        <v>7778685</v>
+      </c>
+      <c r="C195" t="s">
+        <v>68</v>
+      </c>
+      <c r="D195" t="s">
+        <v>69</v>
+      </c>
+      <c r="E195" s="2">
+        <v>45829.29166666666</v>
+      </c>
+      <c r="F195">
+        <v>20</v>
+      </c>
+      <c r="G195" t="s">
+        <v>74</v>
+      </c>
+      <c r="H195" t="s">
+        <v>87</v>
+      </c>
+      <c r="I195">
+        <v>0</v>
+      </c>
+      <c r="J195">
+        <v>1</v>
+      </c>
+      <c r="K195">
+        <v>1</v>
+      </c>
+      <c r="L195">
+        <v>1</v>
+      </c>
+      <c r="M195">
+        <v>3</v>
+      </c>
+      <c r="N195">
+        <v>4</v>
+      </c>
+      <c r="O195" t="s">
+        <v>212</v>
+      </c>
+      <c r="P195" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q195">
+        <v>3.25</v>
+      </c>
+      <c r="R195">
+        <v>2.2</v>
+      </c>
+      <c r="S195">
+        <v>2.88</v>
+      </c>
+      <c r="T195">
+        <v>1.33</v>
+      </c>
+      <c r="U195">
+        <v>3.27</v>
+      </c>
+      <c r="V195">
+        <v>2.64</v>
+      </c>
+      <c r="W195">
+        <v>1.47</v>
+      </c>
+      <c r="X195">
+        <v>5.9</v>
+      </c>
+      <c r="Y195">
+        <v>1.1</v>
+      </c>
+      <c r="Z195">
+        <v>2.64</v>
+      </c>
+      <c r="AA195">
+        <v>3.38</v>
+      </c>
+      <c r="AB195">
+        <v>2.25</v>
+      </c>
+      <c r="AC195">
+        <v>1.01</v>
+      </c>
+      <c r="AD195">
+        <v>11</v>
+      </c>
+      <c r="AE195">
+        <v>1.2</v>
+      </c>
+      <c r="AF195">
+        <v>4</v>
+      </c>
+      <c r="AG195">
+        <v>1.68</v>
+      </c>
+      <c r="AH195">
+        <v>2.05</v>
+      </c>
+      <c r="AI195">
+        <v>1.57</v>
+      </c>
+      <c r="AJ195">
+        <v>2.25</v>
+      </c>
+      <c r="AK195">
+        <v>1.52</v>
+      </c>
+      <c r="AL195">
+        <v>1.26</v>
+      </c>
+      <c r="AM195">
+        <v>1.39</v>
+      </c>
+      <c r="AN195">
+        <v>1.33</v>
+      </c>
+      <c r="AO195">
+        <v>1</v>
+      </c>
+      <c r="AP195">
+        <v>1.2</v>
+      </c>
+      <c r="AQ195">
+        <v>1.17</v>
+      </c>
+      <c r="AR195">
+        <v>1.44</v>
+      </c>
+      <c r="AS195">
+        <v>1.37</v>
+      </c>
+      <c r="AT195">
+        <v>2.81</v>
+      </c>
+      <c r="AU195">
+        <v>4</v>
+      </c>
+      <c r="AV195">
+        <v>9</v>
+      </c>
+      <c r="AW195">
+        <v>10</v>
+      </c>
+      <c r="AX195">
+        <v>4</v>
+      </c>
+      <c r="AY195">
+        <v>14</v>
+      </c>
+      <c r="AZ195">
+        <v>13</v>
+      </c>
+      <c r="BA195">
+        <v>7</v>
+      </c>
+      <c r="BB195">
+        <v>5</v>
+      </c>
+      <c r="BC195">
+        <v>12</v>
+      </c>
+      <c r="BD195">
+        <v>2.05</v>
+      </c>
+      <c r="BE195">
+        <v>8</v>
+      </c>
+      <c r="BF195">
+        <v>2</v>
+      </c>
+      <c r="BG195">
+        <v>1.29</v>
+      </c>
+      <c r="BH195">
+        <v>3.4</v>
+      </c>
+      <c r="BI195">
+        <v>1.48</v>
+      </c>
+      <c r="BJ195">
+        <v>2.6</v>
+      </c>
+      <c r="BK195">
+        <v>1.8</v>
+      </c>
+      <c r="BL195">
+        <v>2</v>
+      </c>
+      <c r="BM195">
+        <v>2.25</v>
+      </c>
+      <c r="BN195">
+        <v>1.62</v>
+      </c>
+      <c r="BO195">
+        <v>3</v>
+      </c>
+      <c r="BP195">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="196" spans="1:68">
+      <c r="A196" s="1">
+        <v>195</v>
+      </c>
+      <c r="B196">
+        <v>7778686</v>
+      </c>
+      <c r="C196" t="s">
+        <v>68</v>
+      </c>
+      <c r="D196" t="s">
+        <v>69</v>
+      </c>
+      <c r="E196" s="2">
+        <v>45829.29166666666</v>
+      </c>
+      <c r="F196">
+        <v>20</v>
+      </c>
+      <c r="G196" t="s">
+        <v>83</v>
+      </c>
+      <c r="H196" t="s">
+        <v>79</v>
+      </c>
+      <c r="I196">
+        <v>1</v>
+      </c>
+      <c r="J196">
+        <v>0</v>
+      </c>
+      <c r="K196">
+        <v>1</v>
+      </c>
+      <c r="L196">
+        <v>2</v>
+      </c>
+      <c r="M196">
+        <v>0</v>
+      </c>
+      <c r="N196">
+        <v>2</v>
+      </c>
+      <c r="O196" t="s">
+        <v>213</v>
+      </c>
+      <c r="P196" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q196">
+        <v>2.78</v>
+      </c>
+      <c r="R196">
+        <v>1.79</v>
+      </c>
+      <c r="S196">
+        <v>5.05</v>
+      </c>
+      <c r="T196">
+        <v>1.63</v>
+      </c>
+      <c r="U196">
+        <v>2.19</v>
+      </c>
+      <c r="V196">
+        <v>4.2</v>
+      </c>
+      <c r="W196">
+        <v>1.17</v>
+      </c>
+      <c r="X196">
+        <v>10</v>
+      </c>
+      <c r="Y196">
+        <v>1.02</v>
+      </c>
+      <c r="Z196">
+        <v>2.07</v>
+      </c>
+      <c r="AA196">
+        <v>2.72</v>
+      </c>
+      <c r="AB196">
+        <v>3.72</v>
+      </c>
+      <c r="AC196">
+        <v>1.06</v>
+      </c>
+      <c r="AD196">
+        <v>6.1</v>
+      </c>
+      <c r="AE196">
+        <v>1.6</v>
+      </c>
+      <c r="AF196">
+        <v>2.1</v>
+      </c>
+      <c r="AG196">
+        <v>2.65</v>
+      </c>
+      <c r="AH196">
+        <v>1.41</v>
+      </c>
+      <c r="AI196">
+        <v>2.4</v>
+      </c>
+      <c r="AJ196">
+        <v>1.48</v>
+      </c>
+      <c r="AK196">
+        <v>1.19</v>
+      </c>
+      <c r="AL196">
+        <v>1.33</v>
+      </c>
+      <c r="AM196">
+        <v>1.72</v>
+      </c>
+      <c r="AN196">
+        <v>1.67</v>
+      </c>
+      <c r="AO196">
+        <v>1</v>
+      </c>
+      <c r="AP196">
+        <v>1.8</v>
+      </c>
+      <c r="AQ196">
+        <v>0.9</v>
+      </c>
+      <c r="AR196">
+        <v>1.34</v>
+      </c>
+      <c r="AS196">
+        <v>1.24</v>
+      </c>
+      <c r="AT196">
+        <v>2.58</v>
+      </c>
+      <c r="AU196">
+        <v>3</v>
+      </c>
+      <c r="AV196">
+        <v>6</v>
+      </c>
+      <c r="AW196">
+        <v>3</v>
+      </c>
+      <c r="AX196">
+        <v>5</v>
+      </c>
+      <c r="AY196">
+        <v>6</v>
+      </c>
+      <c r="AZ196">
+        <v>11</v>
+      </c>
+      <c r="BA196">
+        <v>3</v>
+      </c>
+      <c r="BB196">
+        <v>7</v>
+      </c>
+      <c r="BC196">
+        <v>10</v>
+      </c>
+      <c r="BD196">
+        <v>1.75</v>
+      </c>
+      <c r="BE196">
+        <v>7.5</v>
+      </c>
+      <c r="BF196">
+        <v>2.53</v>
+      </c>
+      <c r="BG196">
+        <v>1.52</v>
+      </c>
+      <c r="BH196">
+        <v>2.48</v>
+      </c>
+      <c r="BI196">
+        <v>1.89</v>
+      </c>
+      <c r="BJ196">
+        <v>1.91</v>
+      </c>
+      <c r="BK196">
+        <v>2.43</v>
+      </c>
+      <c r="BL196">
+        <v>1.54</v>
+      </c>
+      <c r="BM196">
+        <v>3</v>
+      </c>
+      <c r="BN196">
+        <v>1.33</v>
+      </c>
+      <c r="BO196">
+        <v>4</v>
+      </c>
+      <c r="BP196">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:68">
+      <c r="A197" s="1">
+        <v>196</v>
+      </c>
+      <c r="B197">
+        <v>7778683</v>
+      </c>
+      <c r="C197" t="s">
+        <v>68</v>
+      </c>
+      <c r="D197" t="s">
+        <v>69</v>
+      </c>
+      <c r="E197" s="2">
+        <v>45829.29166666666</v>
+      </c>
+      <c r="F197">
+        <v>20</v>
+      </c>
+      <c r="G197" t="s">
+        <v>71</v>
+      </c>
+      <c r="H197" t="s">
+        <v>75</v>
+      </c>
+      <c r="I197">
+        <v>0</v>
+      </c>
+      <c r="J197">
+        <v>0</v>
+      </c>
+      <c r="K197">
+        <v>0</v>
+      </c>
+      <c r="L197">
+        <v>0</v>
+      </c>
+      <c r="M197">
+        <v>0</v>
+      </c>
+      <c r="N197">
+        <v>0</v>
+      </c>
+      <c r="O197" t="s">
+        <v>90</v>
+      </c>
+      <c r="P197" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q197">
+        <v>2.45</v>
+      </c>
+      <c r="R197">
+        <v>2.08</v>
+      </c>
+      <c r="S197">
+        <v>4.4</v>
+      </c>
+      <c r="T197">
+        <v>1.4</v>
+      </c>
+      <c r="U197">
+        <v>2.72</v>
+      </c>
+      <c r="V197">
+        <v>2.89</v>
+      </c>
+      <c r="W197">
+        <v>1.36</v>
+      </c>
+      <c r="X197">
+        <v>7.2</v>
+      </c>
+      <c r="Y197">
+        <v>1.06</v>
+      </c>
+      <c r="Z197">
+        <v>1.95</v>
+      </c>
+      <c r="AA197">
+        <v>3.17</v>
+      </c>
+      <c r="AB197">
+        <v>3.45</v>
+      </c>
+      <c r="AC197">
+        <v>1.02</v>
+      </c>
+      <c r="AD197">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE197">
+        <v>1.28</v>
+      </c>
+      <c r="AF197">
+        <v>3.05</v>
+      </c>
+      <c r="AG197">
+        <v>1.96</v>
+      </c>
+      <c r="AH197">
+        <v>1.74</v>
+      </c>
+      <c r="AI197">
+        <v>1.81</v>
+      </c>
+      <c r="AJ197">
+        <v>1.85</v>
+      </c>
+      <c r="AK197">
+        <v>1.22</v>
+      </c>
+      <c r="AL197">
+        <v>1.26</v>
+      </c>
+      <c r="AM197">
+        <v>1.8</v>
+      </c>
+      <c r="AN197">
+        <v>2.2</v>
+      </c>
+      <c r="AO197">
+        <v>1.25</v>
+      </c>
+      <c r="AP197">
+        <v>2.09</v>
+      </c>
+      <c r="AQ197">
+        <v>1.22</v>
+      </c>
+      <c r="AR197">
+        <v>1.8</v>
+      </c>
+      <c r="AS197">
+        <v>1.35</v>
+      </c>
+      <c r="AT197">
+        <v>3.15</v>
+      </c>
+      <c r="AU197">
+        <v>2</v>
+      </c>
+      <c r="AV197">
+        <v>2</v>
+      </c>
+      <c r="AW197">
+        <v>3</v>
+      </c>
+      <c r="AX197">
+        <v>10</v>
+      </c>
+      <c r="AY197">
+        <v>5</v>
+      </c>
+      <c r="AZ197">
+        <v>12</v>
+      </c>
+      <c r="BA197">
+        <v>3</v>
+      </c>
+      <c r="BB197">
+        <v>4</v>
+      </c>
+      <c r="BC197">
+        <v>7</v>
+      </c>
+      <c r="BD197">
+        <v>1.75</v>
+      </c>
+      <c r="BE197">
+        <v>8</v>
+      </c>
+      <c r="BF197">
+        <v>2.42</v>
+      </c>
+      <c r="BG197">
+        <v>1.29</v>
+      </c>
+      <c r="BH197">
+        <v>3.4</v>
+      </c>
+      <c r="BI197">
+        <v>1.47</v>
+      </c>
+      <c r="BJ197">
+        <v>2.59</v>
+      </c>
+      <c r="BK197">
+        <v>1.79</v>
+      </c>
+      <c r="BL197">
+        <v>2.01</v>
+      </c>
+      <c r="BM197">
+        <v>2.25</v>
+      </c>
+      <c r="BN197">
+        <v>1.61</v>
+      </c>
+      <c r="BO197">
+        <v>3</v>
+      </c>
+      <c r="BP197">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="198" spans="1:68">
+      <c r="A198" s="1">
+        <v>197</v>
+      </c>
+      <c r="B198">
+        <v>7778684</v>
+      </c>
+      <c r="C198" t="s">
+        <v>68</v>
+      </c>
+      <c r="D198" t="s">
+        <v>69</v>
+      </c>
+      <c r="E198" s="2">
+        <v>45829.29166666666</v>
+      </c>
+      <c r="F198">
+        <v>20</v>
+      </c>
+      <c r="G198" t="s">
+        <v>80</v>
+      </c>
+      <c r="H198" t="s">
+        <v>73</v>
+      </c>
+      <c r="I198">
+        <v>0</v>
+      </c>
+      <c r="J198">
+        <v>1</v>
+      </c>
+      <c r="K198">
+        <v>1</v>
+      </c>
+      <c r="L198">
+        <v>0</v>
+      </c>
+      <c r="M198">
+        <v>1</v>
+      </c>
+      <c r="N198">
+        <v>1</v>
+      </c>
+      <c r="O198" t="s">
+        <v>90</v>
+      </c>
+      <c r="P198" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q198">
+        <v>2.6</v>
+      </c>
+      <c r="R198">
+        <v>2.16</v>
+      </c>
+      <c r="S198">
+        <v>3.72</v>
+      </c>
+      <c r="T198">
+        <v>1.33</v>
+      </c>
+      <c r="U198">
+        <v>3.04</v>
+      </c>
+      <c r="V198">
+        <v>2.58</v>
+      </c>
+      <c r="W198">
+        <v>1.44</v>
+      </c>
+      <c r="X198">
+        <v>5.75</v>
+      </c>
+      <c r="Y198">
+        <v>1.1</v>
+      </c>
+      <c r="Z198">
+        <v>2.02</v>
+      </c>
+      <c r="AA198">
+        <v>3.38</v>
+      </c>
+      <c r="AB198">
+        <v>3.05</v>
+      </c>
+      <c r="AC198">
+        <v>1.02</v>
+      </c>
+      <c r="AD198">
+        <v>10</v>
+      </c>
+      <c r="AE198">
+        <v>1.21</v>
+      </c>
+      <c r="AF198">
+        <v>3.58</v>
+      </c>
+      <c r="AG198">
+        <v>1.82</v>
+      </c>
+      <c r="AH198">
+        <v>1.88</v>
+      </c>
+      <c r="AI198">
+        <v>1.63</v>
+      </c>
+      <c r="AJ198">
+        <v>2.09</v>
+      </c>
+      <c r="AK198">
+        <v>1.3</v>
+      </c>
+      <c r="AL198">
+        <v>1.25</v>
+      </c>
+      <c r="AM198">
+        <v>1.67</v>
+      </c>
+      <c r="AN198">
+        <v>2.22</v>
+      </c>
+      <c r="AO198">
+        <v>1.11</v>
+      </c>
+      <c r="AP198">
+        <v>2</v>
+      </c>
+      <c r="AQ198">
+        <v>1.3</v>
+      </c>
+      <c r="AR198">
+        <v>1.63</v>
+      </c>
+      <c r="AS198">
+        <v>1.24</v>
+      </c>
+      <c r="AT198">
+        <v>2.87</v>
+      </c>
+      <c r="AU198">
+        <v>0</v>
+      </c>
+      <c r="AV198">
+        <v>6</v>
+      </c>
+      <c r="AW198">
+        <v>4</v>
+      </c>
+      <c r="AX198">
+        <v>7</v>
+      </c>
+      <c r="AY198">
+        <v>4</v>
+      </c>
+      <c r="AZ198">
+        <v>13</v>
+      </c>
+      <c r="BA198">
+        <v>6</v>
+      </c>
+      <c r="BB198">
+        <v>4</v>
+      </c>
+      <c r="BC198">
+        <v>10</v>
+      </c>
+      <c r="BD198">
+        <v>1.95</v>
+      </c>
+      <c r="BE198">
+        <v>8</v>
+      </c>
+      <c r="BF198">
+        <v>2.1</v>
+      </c>
+      <c r="BG198">
+        <v>1.25</v>
+      </c>
+      <c r="BH198">
+        <v>3.6</v>
+      </c>
+      <c r="BI198">
+        <v>1.43</v>
+      </c>
+      <c r="BJ198">
+        <v>2.62</v>
+      </c>
+      <c r="BK198">
+        <v>1.75</v>
+      </c>
+      <c r="BL198">
+        <v>2.05</v>
+      </c>
+      <c r="BM198">
+        <v>2.19</v>
+      </c>
+      <c r="BN198">
+        <v>1.65</v>
+      </c>
+      <c r="BO198">
+        <v>2.9</v>
+      </c>
+      <c r="BP198">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="307">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -658,6 +658,9 @@
     <t>['16', '54']</t>
   </si>
   <si>
+    <t>['5', '66']</t>
+  </si>
+  <si>
     <t>['31', '60']</t>
   </si>
   <si>
@@ -926,6 +929,12 @@
   </si>
   <si>
     <t>['22', '49', '9004']</t>
+  </si>
+  <si>
+    <t>['13', '29', '9003']</t>
+  </si>
+  <si>
+    <t>['9', '81', '86']</t>
   </si>
 </sst>
 </file>
@@ -1287,7 +1296,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP198"/>
+  <dimension ref="A1:BP201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1543,7 +1552,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q2">
         <v>3.6</v>
@@ -1830,7 +1839,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ3">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2161,7 +2170,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2367,7 +2376,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q6">
         <v>4.1</v>
@@ -2779,7 +2788,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q8">
         <v>2.28</v>
@@ -4096,7 +4105,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ14">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR14">
         <v>2.25</v>
@@ -4221,7 +4230,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q15">
         <v>4.1</v>
@@ -4302,7 +4311,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ15">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4505,7 +4514,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ16">
         <v>1.17</v>
@@ -4920,7 +4929,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ18">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5457,7 +5466,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q21">
         <v>4.4</v>
@@ -5741,7 +5750,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ22">
         <v>0.9</v>
@@ -5869,7 +5878,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -6281,7 +6290,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -6362,7 +6371,7 @@
         <v>2</v>
       </c>
       <c r="AQ25">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR25">
         <v>1.45</v>
@@ -6693,7 +6702,7 @@
         <v>90</v>
       </c>
       <c r="P27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q27">
         <v>3.2</v>
@@ -6771,7 +6780,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ27">
         <v>1.78</v>
@@ -7186,7 +7195,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ29">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR29">
         <v>0</v>
@@ -7723,7 +7732,7 @@
         <v>113</v>
       </c>
       <c r="P32" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q32">
         <v>3.45</v>
@@ -7801,10 +7810,10 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ32">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR32">
         <v>1.26</v>
@@ -7929,7 +7938,7 @@
         <v>114</v>
       </c>
       <c r="P33" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8135,7 +8144,7 @@
         <v>115</v>
       </c>
       <c r="P34" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8341,7 +8350,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q35">
         <v>3.4</v>
@@ -8547,7 +8556,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q36">
         <v>2.8</v>
@@ -8959,7 +8968,7 @@
         <v>118</v>
       </c>
       <c r="P38" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q38">
         <v>2.6</v>
@@ -9783,7 +9792,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9861,7 +9870,7 @@
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ42">
         <v>1.17</v>
@@ -10276,7 +10285,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ44">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR44">
         <v>1.37</v>
@@ -10813,7 +10822,7 @@
         <v>105</v>
       </c>
       <c r="P47" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10891,10 +10900,10 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ47">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR47">
         <v>1.58</v>
@@ -11019,7 +11028,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q48">
         <v>3.6</v>
@@ -11225,7 +11234,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q49">
         <v>3.6</v>
@@ -11637,7 +11646,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q51">
         <v>1.91</v>
@@ -11843,7 +11852,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -11921,7 +11930,7 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ52">
         <v>1.3</v>
@@ -12049,7 +12058,7 @@
         <v>90</v>
       </c>
       <c r="P53" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12667,7 +12676,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q56">
         <v>4.33</v>
@@ -13285,7 +13294,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13697,7 +13706,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13903,7 +13912,7 @@
         <v>90</v>
       </c>
       <c r="P62" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q62">
         <v>2.75</v>
@@ -13984,7 +13993,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ62">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR62">
         <v>1.82</v>
@@ -14187,7 +14196,7 @@
         <v>0.5</v>
       </c>
       <c r="AP63">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ63">
         <v>1.22</v>
@@ -14521,7 +14530,7 @@
         <v>90</v>
       </c>
       <c r="P65" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q65">
         <v>3.6</v>
@@ -14727,7 +14736,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q66">
         <v>4.75</v>
@@ -14808,7 +14817,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ66">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR66">
         <v>1.04</v>
@@ -14933,7 +14942,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q67">
         <v>2.88</v>
@@ -15014,7 +15023,7 @@
         <v>1</v>
       </c>
       <c r="AQ67">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR67">
         <v>1.24</v>
@@ -15217,7 +15226,7 @@
         <v>0</v>
       </c>
       <c r="AP68">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ68">
         <v>0.6</v>
@@ -16041,7 +16050,7 @@
         <v>1.2</v>
       </c>
       <c r="AP72">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ72">
         <v>1.18</v>
@@ -17405,7 +17414,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q79">
         <v>2.63</v>
@@ -17689,7 +17698,7 @@
         <v>1</v>
       </c>
       <c r="AP80">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ80">
         <v>0.7</v>
@@ -17817,7 +17826,7 @@
         <v>145</v>
       </c>
       <c r="P81" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q81">
         <v>3.2</v>
@@ -17898,7 +17907,7 @@
         <v>1</v>
       </c>
       <c r="AQ81">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR81">
         <v>1.55</v>
@@ -18101,7 +18110,7 @@
         <v>3</v>
       </c>
       <c r="AP82">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ82">
         <v>2</v>
@@ -18310,7 +18319,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ83">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR83">
         <v>1.52</v>
@@ -18847,7 +18856,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -18925,7 +18934,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ86">
         <v>1.78</v>
@@ -19053,7 +19062,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19259,7 +19268,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19465,7 +19474,7 @@
         <v>90</v>
       </c>
       <c r="P89" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19958,7 +19967,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ91">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR91">
         <v>1.1</v>
@@ -20083,7 +20092,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q92">
         <v>4</v>
@@ -20164,7 +20173,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ92">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR92">
         <v>1.1</v>
@@ -20289,7 +20298,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q93">
         <v>3</v>
@@ -20495,7 +20504,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q94">
         <v>2.3</v>
@@ -20701,7 +20710,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q95">
         <v>3.5</v>
@@ -20779,7 +20788,7 @@
         <v>1.75</v>
       </c>
       <c r="AP95">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ95">
         <v>2</v>
@@ -21113,7 +21122,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q97">
         <v>3.25</v>
@@ -21603,7 +21612,7 @@
         <v>1</v>
       </c>
       <c r="AP99">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ99">
         <v>1.3</v>
@@ -21731,7 +21740,7 @@
         <v>157</v>
       </c>
       <c r="P100" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q100">
         <v>2.6</v>
@@ -21937,7 +21946,7 @@
         <v>122</v>
       </c>
       <c r="P101" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q101">
         <v>3.25</v>
@@ -22143,7 +22152,7 @@
         <v>158</v>
       </c>
       <c r="P102" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q102">
         <v>2.25</v>
@@ -22221,7 +22230,7 @@
         <v>1.25</v>
       </c>
       <c r="AP102">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ102">
         <v>1.2</v>
@@ -22430,7 +22439,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ103">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR103">
         <v>1.59</v>
@@ -22761,7 +22770,7 @@
         <v>160</v>
       </c>
       <c r="P105" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q105">
         <v>2.38</v>
@@ -22967,7 +22976,7 @@
         <v>90</v>
       </c>
       <c r="P106" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23173,7 +23182,7 @@
         <v>90</v>
       </c>
       <c r="P107" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q107">
         <v>3.25</v>
@@ -23379,7 +23388,7 @@
         <v>161</v>
       </c>
       <c r="P108" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23460,7 +23469,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ108">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR108">
         <v>1.33</v>
@@ -23585,7 +23594,7 @@
         <v>162</v>
       </c>
       <c r="P109" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q109">
         <v>2.3</v>
@@ -23997,7 +24006,7 @@
         <v>122</v>
       </c>
       <c r="P111" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q111">
         <v>4</v>
@@ -24284,7 +24293,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ112">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR112">
         <v>1.39</v>
@@ -24409,7 +24418,7 @@
         <v>164</v>
       </c>
       <c r="P113" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q113">
         <v>3.6</v>
@@ -24821,7 +24830,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q115">
         <v>3.75</v>
@@ -24899,7 +24908,7 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ115">
         <v>1.8</v>
@@ -25027,7 +25036,7 @@
         <v>165</v>
       </c>
       <c r="P116" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q116">
         <v>3.25</v>
@@ -25108,7 +25117,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ116">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR116">
         <v>1.54</v>
@@ -25723,7 +25732,7 @@
         <v>2.4</v>
       </c>
       <c r="AP119">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ119">
         <v>1.8</v>
@@ -26057,7 +26066,7 @@
         <v>167</v>
       </c>
       <c r="P121" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q121">
         <v>3.4</v>
@@ -26263,7 +26272,7 @@
         <v>168</v>
       </c>
       <c r="P122" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26341,7 +26350,7 @@
         <v>0.83</v>
       </c>
       <c r="AP122">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ122">
         <v>0.6</v>
@@ -26469,7 +26478,7 @@
         <v>169</v>
       </c>
       <c r="P123" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q123">
         <v>3.4</v>
@@ -26675,7 +26684,7 @@
         <v>90</v>
       </c>
       <c r="P124" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q124">
         <v>4</v>
@@ -27293,7 +27302,7 @@
         <v>171</v>
       </c>
       <c r="P127" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27499,7 +27508,7 @@
         <v>90</v>
       </c>
       <c r="P128" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q128">
         <v>2.88</v>
@@ -27705,7 +27714,7 @@
         <v>172</v>
       </c>
       <c r="P129" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -27911,7 +27920,7 @@
         <v>90</v>
       </c>
       <c r="P130" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q130">
         <v>3.4</v>
@@ -28117,7 +28126,7 @@
         <v>173</v>
       </c>
       <c r="P131" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q131">
         <v>2.1</v>
@@ -28323,7 +28332,7 @@
         <v>174</v>
       </c>
       <c r="P132" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q132">
         <v>2.5</v>
@@ -28401,7 +28410,7 @@
         <v>1</v>
       </c>
       <c r="AP132">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ132">
         <v>1</v>
@@ -28529,7 +28538,7 @@
         <v>175</v>
       </c>
       <c r="P133" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q133">
         <v>4</v>
@@ -28610,7 +28619,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ133">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR133">
         <v>1.27</v>
@@ -28735,7 +28744,7 @@
         <v>176</v>
       </c>
       <c r="P134" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q134">
         <v>3.4</v>
@@ -28941,7 +28950,7 @@
         <v>177</v>
       </c>
       <c r="P135" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -29353,7 +29362,7 @@
         <v>179</v>
       </c>
       <c r="P137" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q137">
         <v>4</v>
@@ -29559,7 +29568,7 @@
         <v>90</v>
       </c>
       <c r="P138" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q138">
         <v>3.75</v>
@@ -29637,7 +29646,7 @@
         <v>2.33</v>
       </c>
       <c r="AP138">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ138">
         <v>2</v>
@@ -29765,7 +29774,7 @@
         <v>90</v>
       </c>
       <c r="P139" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q139">
         <v>3</v>
@@ -29843,10 +29852,10 @@
         <v>0.83</v>
       </c>
       <c r="AP139">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ139">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR139">
         <v>1.74</v>
@@ -29971,7 +29980,7 @@
         <v>90</v>
       </c>
       <c r="P140" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q140">
         <v>3</v>
@@ -30177,7 +30186,7 @@
         <v>180</v>
       </c>
       <c r="P141" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30589,7 +30598,7 @@
         <v>182</v>
       </c>
       <c r="P143" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q143">
         <v>3.1</v>
@@ -31082,7 +31091,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ145">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR145">
         <v>2.16</v>
@@ -31288,7 +31297,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ146">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR146">
         <v>1.32</v>
@@ -31413,7 +31422,7 @@
         <v>90</v>
       </c>
       <c r="P147" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q147">
         <v>3.1</v>
@@ -32237,7 +32246,7 @@
         <v>186</v>
       </c>
       <c r="P151" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q151">
         <v>2.38</v>
@@ -32315,7 +32324,7 @@
         <v>1.17</v>
       </c>
       <c r="AP151">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ151">
         <v>1.2</v>
@@ -32855,7 +32864,7 @@
         <v>187</v>
       </c>
       <c r="P154" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q154">
         <v>3.4</v>
@@ -32933,7 +32942,7 @@
         <v>1.17</v>
       </c>
       <c r="AP154">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ154">
         <v>1.22</v>
@@ -33679,7 +33688,7 @@
         <v>90</v>
       </c>
       <c r="P158" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -33966,7 +33975,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ159">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR159">
         <v>1.33</v>
@@ -34091,7 +34100,7 @@
         <v>141</v>
       </c>
       <c r="P160" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q160">
         <v>3.75</v>
@@ -34172,7 +34181,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ160">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR160">
         <v>1.07</v>
@@ -34297,7 +34306,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q161">
         <v>4.75</v>
@@ -34503,7 +34512,7 @@
         <v>180</v>
       </c>
       <c r="P162" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q162">
         <v>3.75</v>
@@ -34915,7 +34924,7 @@
         <v>191</v>
       </c>
       <c r="P164" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q164">
         <v>3.1</v>
@@ -35327,7 +35336,7 @@
         <v>90</v>
       </c>
       <c r="P166" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q166">
         <v>2.75</v>
@@ -35408,7 +35417,7 @@
         <v>1</v>
       </c>
       <c r="AQ166">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR166">
         <v>1.35</v>
@@ -35739,7 +35748,7 @@
         <v>193</v>
       </c>
       <c r="P168" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q168">
         <v>2.75</v>
@@ -35817,7 +35826,7 @@
         <v>0.78</v>
       </c>
       <c r="AP168">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ168">
         <v>1.18</v>
@@ -35945,7 +35954,7 @@
         <v>194</v>
       </c>
       <c r="P169" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36232,7 +36241,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ170">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR170">
         <v>1.44</v>
@@ -36357,7 +36366,7 @@
         <v>196</v>
       </c>
       <c r="P171" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q171">
         <v>2.75</v>
@@ -36769,7 +36778,7 @@
         <v>197</v>
       </c>
       <c r="P173" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q173">
         <v>3</v>
@@ -36847,7 +36856,7 @@
         <v>0.75</v>
       </c>
       <c r="AP173">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ173">
         <v>0.7</v>
@@ -37053,7 +37062,7 @@
         <v>1</v>
       </c>
       <c r="AP174">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ174">
         <v>1.17</v>
@@ -37262,7 +37271,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ175">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR175">
         <v>1.66</v>
@@ -37387,7 +37396,7 @@
         <v>90</v>
       </c>
       <c r="P176" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q176">
         <v>3.4</v>
@@ -37674,7 +37683,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ177">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR177">
         <v>1.12</v>
@@ -37799,7 +37808,7 @@
         <v>200</v>
       </c>
       <c r="P178" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q178">
         <v>3.4</v>
@@ -38211,7 +38220,7 @@
         <v>202</v>
       </c>
       <c r="P180" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q180">
         <v>2</v>
@@ -38417,7 +38426,7 @@
         <v>90</v>
       </c>
       <c r="P181" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q181">
         <v>4</v>
@@ -39035,7 +39044,7 @@
         <v>204</v>
       </c>
       <c r="P184" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39241,7 +39250,7 @@
         <v>205</v>
       </c>
       <c r="P185" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q185">
         <v>3.2</v>
@@ -39447,7 +39456,7 @@
         <v>206</v>
       </c>
       <c r="P186" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -39653,7 +39662,7 @@
         <v>207</v>
       </c>
       <c r="P187" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q187">
         <v>2.8</v>
@@ -40065,7 +40074,7 @@
         <v>180</v>
       </c>
       <c r="P189" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q189">
         <v>2.88</v>
@@ -40477,7 +40486,7 @@
         <v>209</v>
       </c>
       <c r="P191" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -40889,7 +40898,7 @@
         <v>101</v>
       </c>
       <c r="P193" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q193">
         <v>3.1</v>
@@ -41301,7 +41310,7 @@
         <v>212</v>
       </c>
       <c r="P195" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q195">
         <v>3.25</v>
@@ -41919,7 +41928,7 @@
         <v>90</v>
       </c>
       <c r="P198" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q198">
         <v>2.6</v>
@@ -42076,6 +42085,624 @@
       </c>
       <c r="BP198">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="199" spans="1:68">
+      <c r="A199" s="1">
+        <v>198</v>
+      </c>
+      <c r="B199">
+        <v>7778689</v>
+      </c>
+      <c r="C199" t="s">
+        <v>68</v>
+      </c>
+      <c r="D199" t="s">
+        <v>69</v>
+      </c>
+      <c r="E199" s="2">
+        <v>45830.06597222222</v>
+      </c>
+      <c r="F199">
+        <v>20</v>
+      </c>
+      <c r="G199" t="s">
+        <v>82</v>
+      </c>
+      <c r="H199" t="s">
+        <v>76</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+      <c r="J199">
+        <v>2</v>
+      </c>
+      <c r="K199">
+        <v>2</v>
+      </c>
+      <c r="L199">
+        <v>1</v>
+      </c>
+      <c r="M199">
+        <v>3</v>
+      </c>
+      <c r="N199">
+        <v>4</v>
+      </c>
+      <c r="O199" t="s">
+        <v>202</v>
+      </c>
+      <c r="P199" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q199">
+        <v>3.3</v>
+      </c>
+      <c r="R199">
+        <v>2.25</v>
+      </c>
+      <c r="S199">
+        <v>2.8</v>
+      </c>
+      <c r="T199">
+        <v>1.33</v>
+      </c>
+      <c r="U199">
+        <v>3.2</v>
+      </c>
+      <c r="V199">
+        <v>2.6</v>
+      </c>
+      <c r="W199">
+        <v>1.44</v>
+      </c>
+      <c r="X199">
+        <v>6.5</v>
+      </c>
+      <c r="Y199">
+        <v>1.11</v>
+      </c>
+      <c r="Z199">
+        <v>2.82</v>
+      </c>
+      <c r="AA199">
+        <v>3.26</v>
+      </c>
+      <c r="AB199">
+        <v>2.18</v>
+      </c>
+      <c r="AC199">
+        <v>1.01</v>
+      </c>
+      <c r="AD199">
+        <v>11</v>
+      </c>
+      <c r="AE199">
+        <v>1.2</v>
+      </c>
+      <c r="AF199">
+        <v>3.7</v>
+      </c>
+      <c r="AG199">
+        <v>1.67</v>
+      </c>
+      <c r="AH199">
+        <v>2.07</v>
+      </c>
+      <c r="AI199">
+        <v>1.62</v>
+      </c>
+      <c r="AJ199">
+        <v>2.2</v>
+      </c>
+      <c r="AK199">
+        <v>1.6</v>
+      </c>
+      <c r="AL199">
+        <v>1.3</v>
+      </c>
+      <c r="AM199">
+        <v>1.36</v>
+      </c>
+      <c r="AN199">
+        <v>0.9</v>
+      </c>
+      <c r="AO199">
+        <v>1.11</v>
+      </c>
+      <c r="AP199">
+        <v>0.82</v>
+      </c>
+      <c r="AQ199">
+        <v>1.3</v>
+      </c>
+      <c r="AR199">
+        <v>1.44</v>
+      </c>
+      <c r="AS199">
+        <v>1.56</v>
+      </c>
+      <c r="AT199">
+        <v>3</v>
+      </c>
+      <c r="AU199">
+        <v>3</v>
+      </c>
+      <c r="AV199">
+        <v>10</v>
+      </c>
+      <c r="AW199">
+        <v>9</v>
+      </c>
+      <c r="AX199">
+        <v>11</v>
+      </c>
+      <c r="AY199">
+        <v>12</v>
+      </c>
+      <c r="AZ199">
+        <v>21</v>
+      </c>
+      <c r="BA199">
+        <v>9</v>
+      </c>
+      <c r="BB199">
+        <v>13</v>
+      </c>
+      <c r="BC199">
+        <v>22</v>
+      </c>
+      <c r="BD199">
+        <v>1.75</v>
+      </c>
+      <c r="BE199">
+        <v>8</v>
+      </c>
+      <c r="BF199">
+        <v>2.52</v>
+      </c>
+      <c r="BG199">
+        <v>1.25</v>
+      </c>
+      <c r="BH199">
+        <v>3.6</v>
+      </c>
+      <c r="BI199">
+        <v>1.41</v>
+      </c>
+      <c r="BJ199">
+        <v>2.7</v>
+      </c>
+      <c r="BK199">
+        <v>1.75</v>
+      </c>
+      <c r="BL199">
+        <v>2.06</v>
+      </c>
+      <c r="BM199">
+        <v>2.2</v>
+      </c>
+      <c r="BN199">
+        <v>1.66</v>
+      </c>
+      <c r="BO199">
+        <v>2.9</v>
+      </c>
+      <c r="BP199">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="200" spans="1:68">
+      <c r="A200" s="1">
+        <v>199</v>
+      </c>
+      <c r="B200">
+        <v>7778680</v>
+      </c>
+      <c r="C200" t="s">
+        <v>68</v>
+      </c>
+      <c r="D200" t="s">
+        <v>69</v>
+      </c>
+      <c r="E200" s="2">
+        <v>45830.08333333334</v>
+      </c>
+      <c r="F200">
+        <v>20</v>
+      </c>
+      <c r="G200" t="s">
+        <v>89</v>
+      </c>
+      <c r="H200" t="s">
+        <v>88</v>
+      </c>
+      <c r="I200">
+        <v>1</v>
+      </c>
+      <c r="J200">
+        <v>1</v>
+      </c>
+      <c r="K200">
+        <v>2</v>
+      </c>
+      <c r="L200">
+        <v>2</v>
+      </c>
+      <c r="M200">
+        <v>3</v>
+      </c>
+      <c r="N200">
+        <v>5</v>
+      </c>
+      <c r="O200" t="s">
+        <v>214</v>
+      </c>
+      <c r="P200" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q200">
+        <v>3.4</v>
+      </c>
+      <c r="R200">
+        <v>2.05</v>
+      </c>
+      <c r="S200">
+        <v>3.4</v>
+      </c>
+      <c r="T200">
+        <v>1.44</v>
+      </c>
+      <c r="U200">
+        <v>2.63</v>
+      </c>
+      <c r="V200">
+        <v>3.25</v>
+      </c>
+      <c r="W200">
+        <v>1.33</v>
+      </c>
+      <c r="X200">
+        <v>9</v>
+      </c>
+      <c r="Y200">
+        <v>1.07</v>
+      </c>
+      <c r="Z200">
+        <v>2.75</v>
+      </c>
+      <c r="AA200">
+        <v>2.99</v>
+      </c>
+      <c r="AB200">
+        <v>2.37</v>
+      </c>
+      <c r="AC200">
+        <v>1.01</v>
+      </c>
+      <c r="AD200">
+        <v>8.5</v>
+      </c>
+      <c r="AE200">
+        <v>1.32</v>
+      </c>
+      <c r="AF200">
+        <v>2.88</v>
+      </c>
+      <c r="AG200">
+        <v>1.93</v>
+      </c>
+      <c r="AH200">
+        <v>1.77</v>
+      </c>
+      <c r="AI200">
+        <v>1.83</v>
+      </c>
+      <c r="AJ200">
+        <v>1.83</v>
+      </c>
+      <c r="AK200">
+        <v>1.44</v>
+      </c>
+      <c r="AL200">
+        <v>1.36</v>
+      </c>
+      <c r="AM200">
+        <v>1.44</v>
+      </c>
+      <c r="AN200">
+        <v>0.88</v>
+      </c>
+      <c r="AO200">
+        <v>0.82</v>
+      </c>
+      <c r="AP200">
+        <v>0.78</v>
+      </c>
+      <c r="AQ200">
+        <v>1</v>
+      </c>
+      <c r="AR200">
+        <v>1.56</v>
+      </c>
+      <c r="AS200">
+        <v>1.32</v>
+      </c>
+      <c r="AT200">
+        <v>2.88</v>
+      </c>
+      <c r="AU200">
+        <v>7</v>
+      </c>
+      <c r="AV200">
+        <v>7</v>
+      </c>
+      <c r="AW200">
+        <v>5</v>
+      </c>
+      <c r="AX200">
+        <v>6</v>
+      </c>
+      <c r="AY200">
+        <v>12</v>
+      </c>
+      <c r="AZ200">
+        <v>13</v>
+      </c>
+      <c r="BA200">
+        <v>8</v>
+      </c>
+      <c r="BB200">
+        <v>3</v>
+      </c>
+      <c r="BC200">
+        <v>11</v>
+      </c>
+      <c r="BD200">
+        <v>1.82</v>
+      </c>
+      <c r="BE200">
+        <v>8</v>
+      </c>
+      <c r="BF200">
+        <v>2.33</v>
+      </c>
+      <c r="BG200">
+        <v>1.3</v>
+      </c>
+      <c r="BH200">
+        <v>3.2</v>
+      </c>
+      <c r="BI200">
+        <v>1.52</v>
+      </c>
+      <c r="BJ200">
+        <v>2.45</v>
+      </c>
+      <c r="BK200">
+        <v>1.91</v>
+      </c>
+      <c r="BL200">
+        <v>1.89</v>
+      </c>
+      <c r="BM200">
+        <v>2.36</v>
+      </c>
+      <c r="BN200">
+        <v>1.56</v>
+      </c>
+      <c r="BO200">
+        <v>3.2</v>
+      </c>
+      <c r="BP200">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="201" spans="1:68">
+      <c r="A201" s="1">
+        <v>200</v>
+      </c>
+      <c r="B201">
+        <v>7778679</v>
+      </c>
+      <c r="C201" t="s">
+        <v>68</v>
+      </c>
+      <c r="D201" t="s">
+        <v>69</v>
+      </c>
+      <c r="E201" s="2">
+        <v>45830.25</v>
+      </c>
+      <c r="F201">
+        <v>20</v>
+      </c>
+      <c r="G201" t="s">
+        <v>85</v>
+      </c>
+      <c r="H201" t="s">
+        <v>72</v>
+      </c>
+      <c r="I201">
+        <v>0</v>
+      </c>
+      <c r="J201">
+        <v>0</v>
+      </c>
+      <c r="K201">
+        <v>0</v>
+      </c>
+      <c r="L201">
+        <v>0</v>
+      </c>
+      <c r="M201">
+        <v>0</v>
+      </c>
+      <c r="N201">
+        <v>0</v>
+      </c>
+      <c r="O201" t="s">
+        <v>90</v>
+      </c>
+      <c r="P201" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q201">
+        <v>2.8</v>
+      </c>
+      <c r="R201">
+        <v>1.95</v>
+      </c>
+      <c r="S201">
+        <v>4.4</v>
+      </c>
+      <c r="T201">
+        <v>1.55</v>
+      </c>
+      <c r="U201">
+        <v>2.4</v>
+      </c>
+      <c r="V201">
+        <v>3.6</v>
+      </c>
+      <c r="W201">
+        <v>1.25</v>
+      </c>
+      <c r="X201">
+        <v>12</v>
+      </c>
+      <c r="Y201">
+        <v>1.04</v>
+      </c>
+      <c r="Z201">
+        <v>1.93</v>
+      </c>
+      <c r="AA201">
+        <v>3.06</v>
+      </c>
+      <c r="AB201">
+        <v>3.66</v>
+      </c>
+      <c r="AC201">
+        <v>1.06</v>
+      </c>
+      <c r="AD201">
+        <v>6.25</v>
+      </c>
+      <c r="AE201">
+        <v>1.5</v>
+      </c>
+      <c r="AF201">
+        <v>2.3</v>
+      </c>
+      <c r="AG201">
+        <v>2.33</v>
+      </c>
+      <c r="AH201">
+        <v>1.53</v>
+      </c>
+      <c r="AI201">
+        <v>2.2</v>
+      </c>
+      <c r="AJ201">
+        <v>1.62</v>
+      </c>
+      <c r="AK201">
+        <v>1.25</v>
+      </c>
+      <c r="AL201">
+        <v>1.4</v>
+      </c>
+      <c r="AM201">
+        <v>1.7</v>
+      </c>
+      <c r="AN201">
+        <v>1.78</v>
+      </c>
+      <c r="AO201">
+        <v>1.3</v>
+      </c>
+      <c r="AP201">
+        <v>1.7</v>
+      </c>
+      <c r="AQ201">
+        <v>1.27</v>
+      </c>
+      <c r="AR201">
+        <v>1.5</v>
+      </c>
+      <c r="AS201">
+        <v>1.31</v>
+      </c>
+      <c r="AT201">
+        <v>2.81</v>
+      </c>
+      <c r="AU201">
+        <v>-1</v>
+      </c>
+      <c r="AV201">
+        <v>-1</v>
+      </c>
+      <c r="AW201">
+        <v>-1</v>
+      </c>
+      <c r="AX201">
+        <v>-1</v>
+      </c>
+      <c r="AY201">
+        <v>-1</v>
+      </c>
+      <c r="AZ201">
+        <v>-1</v>
+      </c>
+      <c r="BA201">
+        <v>1</v>
+      </c>
+      <c r="BB201">
+        <v>0</v>
+      </c>
+      <c r="BC201">
+        <v>1</v>
+      </c>
+      <c r="BD201">
+        <v>1.69</v>
+      </c>
+      <c r="BE201">
+        <v>8</v>
+      </c>
+      <c r="BF201">
+        <v>2.65</v>
+      </c>
+      <c r="BG201">
+        <v>1.29</v>
+      </c>
+      <c r="BH201">
+        <v>3.3</v>
+      </c>
+      <c r="BI201">
+        <v>1.64</v>
+      </c>
+      <c r="BJ201">
+        <v>2.22</v>
+      </c>
+      <c r="BK201">
+        <v>2.06</v>
+      </c>
+      <c r="BL201">
+        <v>1.75</v>
+      </c>
+      <c r="BM201">
+        <v>2.65</v>
+      </c>
+      <c r="BN201">
+        <v>1.42</v>
+      </c>
+      <c r="BO201">
+        <v>3.3</v>
+      </c>
+      <c r="BP201">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -628,16 +628,16 @@
     <t>['84']</t>
   </si>
   <si>
-    <t>['23', '9002']</t>
+    <t>['23', '9003']</t>
   </si>
   <si>
-    <t>['59', '69']</t>
+    <t>['58', '69']</t>
   </si>
   <si>
     <t>['12', '76']</t>
   </si>
   <si>
-    <t>['38', '81']</t>
+    <t>['38', '52', '80']</t>
   </si>
   <si>
     <t>['67', '73', '87', '9001']</t>
@@ -2866,7 +2866,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AQ8">
         <v>1</v>
@@ -6162,7 +6162,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AQ24">
         <v>1.3</v>
@@ -6783,7 +6783,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ27">
-        <v>1.78</v>
+        <v>1.56</v>
       </c>
       <c r="AR27">
         <v>1.59</v>
@@ -10491,7 +10491,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ45">
-        <v>1.78</v>
+        <v>1.56</v>
       </c>
       <c r="AR45">
         <v>1.47</v>
@@ -10694,7 +10694,7 @@
         <v>2</v>
       </c>
       <c r="AP46">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AQ46">
         <v>1.8</v>
@@ -12342,7 +12342,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AQ54">
         <v>1.18</v>
@@ -15847,7 +15847,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ71">
-        <v>1.78</v>
+        <v>1.56</v>
       </c>
       <c r="AR71">
         <v>1.39</v>
@@ -18937,7 +18937,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ86">
-        <v>1.78</v>
+        <v>1.56</v>
       </c>
       <c r="AR86">
         <v>1.94</v>
@@ -19552,7 +19552,7 @@
         <v>0.33</v>
       </c>
       <c r="AP89">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AQ89">
         <v>1.22</v>
@@ -20997,7 +20997,7 @@
         <v>1</v>
       </c>
       <c r="AQ96">
-        <v>1.78</v>
+        <v>1.56</v>
       </c>
       <c r="AR96">
         <v>1.52</v>
@@ -23672,7 +23672,7 @@
         <v>0.8</v>
       </c>
       <c r="AP109">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AQ109">
         <v>1</v>
@@ -25529,7 +25529,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ118">
-        <v>1.78</v>
+        <v>1.56</v>
       </c>
       <c r="AR118">
         <v>1.57</v>
@@ -28204,7 +28204,7 @@
         <v>1.2</v>
       </c>
       <c r="AP131">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AQ131">
         <v>1.2</v>
@@ -30267,7 +30267,7 @@
         <v>2</v>
       </c>
       <c r="AQ141">
-        <v>1.78</v>
+        <v>1.56</v>
       </c>
       <c r="AR141">
         <v>1.59</v>
@@ -31088,7 +31088,7 @@
         <v>1</v>
       </c>
       <c r="AP145">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AQ145">
         <v>1</v>
@@ -33769,7 +33769,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ158">
-        <v>1.78</v>
+        <v>1.56</v>
       </c>
       <c r="AR158">
         <v>1.44</v>
@@ -34796,7 +34796,7 @@
         <v>2.13</v>
       </c>
       <c r="AP163">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AQ163">
         <v>1.8</v>
@@ -38319,16 +38319,16 @@
         <v>4</v>
       </c>
       <c r="AW180">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="AX180">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY180">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AZ180">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BA180">
         <v>13</v>
@@ -38519,22 +38519,22 @@
         <v>2.66</v>
       </c>
       <c r="AU181">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV181">
         <v>4</v>
       </c>
       <c r="AW181">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX181">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY181">
+        <v>9</v>
+      </c>
+      <c r="AZ181">
         <v>10</v>
-      </c>
-      <c r="AZ181">
-        <v>11</v>
       </c>
       <c r="BA181">
         <v>4</v>
@@ -38725,31 +38725,31 @@
         <v>3.01</v>
       </c>
       <c r="AU182">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV182">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AW182">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AX182">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AY182">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AZ182">
-        <v>-2</v>
+        <v>11</v>
       </c>
       <c r="BA182">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BB182">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BC182">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BD182">
         <v>1.69</v>
@@ -38931,31 +38931,31 @@
         <v>2.74</v>
       </c>
       <c r="AU183">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AV183">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AW183">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AX183">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AY183">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AZ183">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BA183">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BB183">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BC183">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="BD183">
         <v>2.56</v>
@@ -39137,22 +39137,22 @@
         <v>2.56</v>
       </c>
       <c r="AU184">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AV184">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW184">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX184">
+        <v>5</v>
+      </c>
+      <c r="AY184">
+        <v>13</v>
+      </c>
+      <c r="AZ184">
         <v>8</v>
-      </c>
-      <c r="AY184">
-        <v>12</v>
-      </c>
-      <c r="AZ184">
-        <v>12</v>
       </c>
       <c r="BA184">
         <v>4</v>
@@ -39650,13 +39650,13 @@
         <v>3</v>
       </c>
       <c r="L187">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M187">
         <v>3</v>
       </c>
       <c r="N187">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O187" t="s">
         <v>207</v>
@@ -39740,10 +39740,10 @@
         <v>1.63</v>
       </c>
       <c r="AP187">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AQ187">
-        <v>1.78</v>
+        <v>1.56</v>
       </c>
       <c r="AR187">
         <v>2.02</v>
@@ -39755,22 +39755,22 @@
         <v>3.51</v>
       </c>
       <c r="AU187">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV187">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AW187">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AX187">
         <v>6</v>
       </c>
       <c r="AY187">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ187">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BA187">
         <v>8</v>
@@ -40373,31 +40373,31 @@
         <v>2.54</v>
       </c>
       <c r="AU190">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV190">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW190">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AX190">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AY190">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AZ190">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BA190">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BB190">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BC190">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BD190">
         <v>2.15</v>
@@ -40579,31 +40579,31 @@
         <v>2.52</v>
       </c>
       <c r="AU191">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AV191">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AW191">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AX191">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AY191">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="AZ191">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="BA191">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BB191">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BC191">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BD191">
         <v>1.93</v>
@@ -40785,31 +40785,31 @@
         <v>2.78</v>
       </c>
       <c r="AU192">
+        <v>12</v>
+      </c>
+      <c r="AV192">
+        <v>2</v>
+      </c>
+      <c r="AW192">
+        <v>5</v>
+      </c>
+      <c r="AX192">
+        <v>2</v>
+      </c>
+      <c r="AY192">
+        <v>17</v>
+      </c>
+      <c r="AZ192">
         <v>4</v>
-      </c>
-      <c r="AV192">
-        <v>2</v>
-      </c>
-      <c r="AW192">
-        <v>8</v>
-      </c>
-      <c r="AX192">
-        <v>3</v>
-      </c>
-      <c r="AY192">
-        <v>12</v>
-      </c>
-      <c r="AZ192">
-        <v>5</v>
       </c>
       <c r="BA192">
         <v>9</v>
       </c>
       <c r="BB192">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC192">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD192">
         <v>1.59</v>
@@ -40991,22 +40991,22 @@
         <v>3</v>
       </c>
       <c r="AU193">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV193">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW193">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AX193">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AY193">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AZ193">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA193">
         <v>3</v>
@@ -41197,22 +41197,22 @@
         <v>2.66</v>
       </c>
       <c r="AU194">
+        <v>5</v>
+      </c>
+      <c r="AV194">
+        <v>4</v>
+      </c>
+      <c r="AW194">
+        <v>4</v>
+      </c>
+      <c r="AX194">
         <v>3</v>
       </c>
-      <c r="AV194">
-        <v>2</v>
-      </c>
-      <c r="AW194">
-        <v>10</v>
-      </c>
-      <c r="AX194">
+      <c r="AY194">
+        <v>9</v>
+      </c>
+      <c r="AZ194">
         <v>7</v>
-      </c>
-      <c r="AY194">
-        <v>13</v>
-      </c>
-      <c r="AZ194">
-        <v>9</v>
       </c>
       <c r="BA194">
         <v>8</v>
@@ -41609,22 +41609,22 @@
         <v>2.58</v>
       </c>
       <c r="AU196">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV196">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW196">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX196">
         <v>5</v>
       </c>
       <c r="AY196">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AZ196">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA196">
         <v>3</v>
@@ -41815,22 +41815,22 @@
         <v>3.15</v>
       </c>
       <c r="AU197">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AV197">
         <v>2</v>
       </c>
       <c r="AW197">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AX197">
+        <v>8</v>
+      </c>
+      <c r="AY197">
+        <v>8</v>
+      </c>
+      <c r="AZ197">
         <v>10</v>
-      </c>
-      <c r="AY197">
-        <v>5</v>
-      </c>
-      <c r="AZ197">
-        <v>12</v>
       </c>
       <c r="BA197">
         <v>3</v>
@@ -42639,22 +42639,22 @@
         <v>2.81</v>
       </c>
       <c r="AU201">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AV201">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AW201">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AX201">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AY201">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AZ201">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BA201">
         <v>1</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="309">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -661,6 +661,9 @@
     <t>['5', '66']</t>
   </si>
   <si>
+    <t>['56', '87', '9004']</t>
+  </si>
+  <si>
     <t>['31', '60']</t>
   </si>
   <si>
@@ -935,6 +938,9 @@
   </si>
   <si>
     <t>['9', '81', '86']</t>
+  </si>
+  <si>
+    <t>['4', '61']</t>
   </si>
 </sst>
 </file>
@@ -1296,7 +1302,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP201"/>
+  <dimension ref="A1:BP202"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1552,7 +1558,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q2">
         <v>3.6</v>
@@ -2170,7 +2176,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2376,7 +2382,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q6">
         <v>4.1</v>
@@ -2788,7 +2794,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q8">
         <v>2.28</v>
@@ -2869,7 +2875,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ8">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -4230,7 +4236,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q15">
         <v>4.1</v>
@@ -5466,7 +5472,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q21">
         <v>4.4</v>
@@ -5878,7 +5884,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -6290,7 +6296,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -6702,7 +6708,7 @@
         <v>90</v>
       </c>
       <c r="P27" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q27">
         <v>3.2</v>
@@ -7732,7 +7738,7 @@
         <v>113</v>
       </c>
       <c r="P32" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q32">
         <v>3.45</v>
@@ -7938,7 +7944,7 @@
         <v>114</v>
       </c>
       <c r="P33" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8144,7 +8150,7 @@
         <v>115</v>
       </c>
       <c r="P34" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8350,7 +8356,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q35">
         <v>3.4</v>
@@ -8428,7 +8434,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ35">
         <v>1.8</v>
@@ -8556,7 +8562,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q36">
         <v>2.8</v>
@@ -8968,7 +8974,7 @@
         <v>118</v>
       </c>
       <c r="P38" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q38">
         <v>2.6</v>
@@ -9461,7 +9467,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ40">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR40">
         <v>1.47</v>
@@ -9792,7 +9798,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10822,7 +10828,7 @@
         <v>105</v>
       </c>
       <c r="P47" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -11028,7 +11034,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q48">
         <v>3.6</v>
@@ -11234,7 +11240,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q49">
         <v>3.6</v>
@@ -11646,7 +11652,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q51">
         <v>1.91</v>
@@ -11852,7 +11858,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -12058,7 +12064,7 @@
         <v>90</v>
       </c>
       <c r="P53" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12139,7 +12145,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ53">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR53">
         <v>1.15</v>
@@ -12676,7 +12682,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q56">
         <v>4.33</v>
@@ -13294,7 +13300,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13706,7 +13712,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13912,7 +13918,7 @@
         <v>90</v>
       </c>
       <c r="P62" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q62">
         <v>2.75</v>
@@ -13990,7 +13996,7 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ62">
         <v>1.27</v>
@@ -14530,7 +14536,7 @@
         <v>90</v>
       </c>
       <c r="P65" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q65">
         <v>3.6</v>
@@ -14736,7 +14742,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q66">
         <v>4.75</v>
@@ -14942,7 +14948,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q67">
         <v>2.88</v>
@@ -17286,7 +17292,7 @@
         <v>1.25</v>
       </c>
       <c r="AP78">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ78">
         <v>1.8</v>
@@ -17414,7 +17420,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q79">
         <v>2.63</v>
@@ -17826,7 +17832,7 @@
         <v>145</v>
       </c>
       <c r="P81" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q81">
         <v>3.2</v>
@@ -18856,7 +18862,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19062,7 +19068,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19268,7 +19274,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19474,7 +19480,7 @@
         <v>90</v>
       </c>
       <c r="P89" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19761,7 +19767,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ90">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR90">
         <v>1.26</v>
@@ -20092,7 +20098,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q92">
         <v>4</v>
@@ -20298,7 +20304,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q93">
         <v>3</v>
@@ -20504,7 +20510,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q94">
         <v>2.3</v>
@@ -20710,7 +20716,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q95">
         <v>3.5</v>
@@ -21122,7 +21128,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q97">
         <v>3.25</v>
@@ -21740,7 +21746,7 @@
         <v>157</v>
       </c>
       <c r="P100" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q100">
         <v>2.6</v>
@@ -21818,7 +21824,7 @@
         <v>0.75</v>
       </c>
       <c r="AP100">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ100">
         <v>1</v>
@@ -21946,7 +21952,7 @@
         <v>122</v>
       </c>
       <c r="P101" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q101">
         <v>3.25</v>
@@ -22152,7 +22158,7 @@
         <v>158</v>
       </c>
       <c r="P102" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q102">
         <v>2.25</v>
@@ -22770,7 +22776,7 @@
         <v>160</v>
       </c>
       <c r="P105" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q105">
         <v>2.38</v>
@@ -22976,7 +22982,7 @@
         <v>90</v>
       </c>
       <c r="P106" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23182,7 +23188,7 @@
         <v>90</v>
       </c>
       <c r="P107" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q107">
         <v>3.25</v>
@@ -23263,7 +23269,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ107">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR107">
         <v>1.3</v>
@@ -23388,7 +23394,7 @@
         <v>161</v>
       </c>
       <c r="P108" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23594,7 +23600,7 @@
         <v>162</v>
       </c>
       <c r="P109" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q109">
         <v>2.3</v>
@@ -24006,7 +24012,7 @@
         <v>122</v>
       </c>
       <c r="P111" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q111">
         <v>4</v>
@@ -24418,7 +24424,7 @@
         <v>164</v>
       </c>
       <c r="P113" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q113">
         <v>3.6</v>
@@ -24830,7 +24836,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q115">
         <v>3.75</v>
@@ -25036,7 +25042,7 @@
         <v>165</v>
       </c>
       <c r="P116" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q116">
         <v>3.25</v>
@@ -25114,7 +25120,7 @@
         <v>0.6</v>
       </c>
       <c r="AP116">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ116">
         <v>1.3</v>
@@ -26066,7 +26072,7 @@
         <v>167</v>
       </c>
       <c r="P121" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q121">
         <v>3.4</v>
@@ -26272,7 +26278,7 @@
         <v>168</v>
       </c>
       <c r="P122" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26478,7 +26484,7 @@
         <v>169</v>
       </c>
       <c r="P123" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q123">
         <v>3.4</v>
@@ -26684,7 +26690,7 @@
         <v>90</v>
       </c>
       <c r="P124" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q124">
         <v>4</v>
@@ -26971,7 +26977,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ125">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR125">
         <v>1.1</v>
@@ -27302,7 +27308,7 @@
         <v>171</v>
       </c>
       <c r="P127" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27508,7 +27514,7 @@
         <v>90</v>
       </c>
       <c r="P128" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q128">
         <v>2.88</v>
@@ -27714,7 +27720,7 @@
         <v>172</v>
       </c>
       <c r="P129" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -27920,7 +27926,7 @@
         <v>90</v>
       </c>
       <c r="P130" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q130">
         <v>3.4</v>
@@ -28126,7 +28132,7 @@
         <v>173</v>
       </c>
       <c r="P131" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q131">
         <v>2.1</v>
@@ -28332,7 +28338,7 @@
         <v>174</v>
       </c>
       <c r="P132" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q132">
         <v>2.5</v>
@@ -28538,7 +28544,7 @@
         <v>175</v>
       </c>
       <c r="P133" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q133">
         <v>4</v>
@@ -28744,7 +28750,7 @@
         <v>176</v>
       </c>
       <c r="P134" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q134">
         <v>3.4</v>
@@ -28950,7 +28956,7 @@
         <v>177</v>
       </c>
       <c r="P135" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -29028,7 +29034,7 @@
         <v>0.83</v>
       </c>
       <c r="AP135">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ135">
         <v>1.3</v>
@@ -29362,7 +29368,7 @@
         <v>179</v>
       </c>
       <c r="P137" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q137">
         <v>4</v>
@@ -29568,7 +29574,7 @@
         <v>90</v>
       </c>
       <c r="P138" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q138">
         <v>3.75</v>
@@ -29774,7 +29780,7 @@
         <v>90</v>
       </c>
       <c r="P139" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q139">
         <v>3</v>
@@ -29980,7 +29986,7 @@
         <v>90</v>
       </c>
       <c r="P140" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q140">
         <v>3</v>
@@ -30186,7 +30192,7 @@
         <v>180</v>
       </c>
       <c r="P141" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30598,7 +30604,7 @@
         <v>182</v>
       </c>
       <c r="P143" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q143">
         <v>3.1</v>
@@ -31422,7 +31428,7 @@
         <v>90</v>
       </c>
       <c r="P147" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q147">
         <v>3.1</v>
@@ -32246,7 +32252,7 @@
         <v>186</v>
       </c>
       <c r="P151" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q151">
         <v>2.38</v>
@@ -32736,7 +32742,7 @@
         <v>0.86</v>
       </c>
       <c r="AP153">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ153">
         <v>0.7</v>
@@ -32864,7 +32870,7 @@
         <v>187</v>
       </c>
       <c r="P154" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q154">
         <v>3.4</v>
@@ -33151,7 +33157,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ155">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR155">
         <v>1.71</v>
@@ -33688,7 +33694,7 @@
         <v>90</v>
       </c>
       <c r="P158" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -34100,7 +34106,7 @@
         <v>141</v>
       </c>
       <c r="P160" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q160">
         <v>3.75</v>
@@ -34306,7 +34312,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q161">
         <v>4.75</v>
@@ -34512,7 +34518,7 @@
         <v>180</v>
       </c>
       <c r="P162" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q162">
         <v>3.75</v>
@@ -34924,7 +34930,7 @@
         <v>191</v>
       </c>
       <c r="P164" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q164">
         <v>3.1</v>
@@ -35336,7 +35342,7 @@
         <v>90</v>
       </c>
       <c r="P166" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q166">
         <v>2.75</v>
@@ -35748,7 +35754,7 @@
         <v>193</v>
       </c>
       <c r="P168" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q168">
         <v>2.75</v>
@@ -35954,7 +35960,7 @@
         <v>194</v>
       </c>
       <c r="P169" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36366,7 +36372,7 @@
         <v>196</v>
       </c>
       <c r="P171" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q171">
         <v>2.75</v>
@@ -36778,7 +36784,7 @@
         <v>197</v>
       </c>
       <c r="P173" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q173">
         <v>3</v>
@@ -37396,7 +37402,7 @@
         <v>90</v>
       </c>
       <c r="P176" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q176">
         <v>3.4</v>
@@ -37808,7 +37814,7 @@
         <v>200</v>
       </c>
       <c r="P178" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q178">
         <v>3.4</v>
@@ -37889,7 +37895,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ178">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR178">
         <v>1.63</v>
@@ -38220,7 +38226,7 @@
         <v>202</v>
       </c>
       <c r="P180" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q180">
         <v>2</v>
@@ -38426,7 +38432,7 @@
         <v>90</v>
       </c>
       <c r="P181" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q181">
         <v>4</v>
@@ -39044,7 +39050,7 @@
         <v>204</v>
       </c>
       <c r="P184" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39250,7 +39256,7 @@
         <v>205</v>
       </c>
       <c r="P185" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q185">
         <v>3.2</v>
@@ -39328,7 +39334,7 @@
         <v>2.13</v>
       </c>
       <c r="AP185">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ185">
         <v>2</v>
@@ -39456,7 +39462,7 @@
         <v>206</v>
       </c>
       <c r="P186" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -39662,7 +39668,7 @@
         <v>207</v>
       </c>
       <c r="P187" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q187">
         <v>2.8</v>
@@ -40074,7 +40080,7 @@
         <v>180</v>
       </c>
       <c r="P189" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q189">
         <v>2.88</v>
@@ -40361,7 +40367,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ190">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR190">
         <v>1.17</v>
@@ -40486,7 +40492,7 @@
         <v>209</v>
       </c>
       <c r="P191" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -40898,7 +40904,7 @@
         <v>101</v>
       </c>
       <c r="P193" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q193">
         <v>3.1</v>
@@ -41310,7 +41316,7 @@
         <v>212</v>
       </c>
       <c r="P195" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q195">
         <v>3.25</v>
@@ -41928,7 +41934,7 @@
         <v>90</v>
       </c>
       <c r="P198" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q198">
         <v>2.6</v>
@@ -42134,7 +42140,7 @@
         <v>202</v>
       </c>
       <c r="P199" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q199">
         <v>3.3</v>
@@ -42340,7 +42346,7 @@
         <v>214</v>
       </c>
       <c r="P200" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q200">
         <v>3.4</v>
@@ -42703,6 +42709,212 @@
       </c>
       <c r="BP201">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="202" spans="1:68">
+      <c r="A202" s="1">
+        <v>201</v>
+      </c>
+      <c r="B202">
+        <v>7778690</v>
+      </c>
+      <c r="C202" t="s">
+        <v>68</v>
+      </c>
+      <c r="D202" t="s">
+        <v>69</v>
+      </c>
+      <c r="E202" s="2">
+        <v>45836.08333333334</v>
+      </c>
+      <c r="F202">
+        <v>21</v>
+      </c>
+      <c r="G202" t="s">
+        <v>87</v>
+      </c>
+      <c r="H202" t="s">
+        <v>82</v>
+      </c>
+      <c r="I202">
+        <v>0</v>
+      </c>
+      <c r="J202">
+        <v>1</v>
+      </c>
+      <c r="K202">
+        <v>1</v>
+      </c>
+      <c r="L202">
+        <v>3</v>
+      </c>
+      <c r="M202">
+        <v>2</v>
+      </c>
+      <c r="N202">
+        <v>5</v>
+      </c>
+      <c r="O202" t="s">
+        <v>215</v>
+      </c>
+      <c r="P202" t="s">
+        <v>308</v>
+      </c>
+      <c r="Q202">
+        <v>2.59</v>
+      </c>
+      <c r="R202">
+        <v>2.19</v>
+      </c>
+      <c r="S202">
+        <v>3.64</v>
+      </c>
+      <c r="T202">
+        <v>1.31</v>
+      </c>
+      <c r="U202">
+        <v>3.14</v>
+      </c>
+      <c r="V202">
+        <v>2.52</v>
+      </c>
+      <c r="W202">
+        <v>1.46</v>
+      </c>
+      <c r="X202">
+        <v>5.7</v>
+      </c>
+      <c r="Y202">
+        <v>1.1</v>
+      </c>
+      <c r="Z202">
+        <v>1.99</v>
+      </c>
+      <c r="AA202">
+        <v>3.37</v>
+      </c>
+      <c r="AB202">
+        <v>3.13</v>
+      </c>
+      <c r="AC202">
+        <v>1</v>
+      </c>
+      <c r="AD202">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE202">
+        <v>1.18</v>
+      </c>
+      <c r="AF202">
+        <v>3.92</v>
+      </c>
+      <c r="AG202">
+        <v>1.8</v>
+      </c>
+      <c r="AH202">
+        <v>1.9</v>
+      </c>
+      <c r="AI202">
+        <v>1.58</v>
+      </c>
+      <c r="AJ202">
+        <v>2.17</v>
+      </c>
+      <c r="AK202">
+        <v>1.31</v>
+      </c>
+      <c r="AL202">
+        <v>1.25</v>
+      </c>
+      <c r="AM202">
+        <v>1.66</v>
+      </c>
+      <c r="AN202">
+        <v>1.38</v>
+      </c>
+      <c r="AO202">
+        <v>1</v>
+      </c>
+      <c r="AP202">
+        <v>1.56</v>
+      </c>
+      <c r="AQ202">
+        <v>0.9</v>
+      </c>
+      <c r="AR202">
+        <v>1.57</v>
+      </c>
+      <c r="AS202">
+        <v>1.37</v>
+      </c>
+      <c r="AT202">
+        <v>2.94</v>
+      </c>
+      <c r="AU202">
+        <v>7</v>
+      </c>
+      <c r="AV202">
+        <v>5</v>
+      </c>
+      <c r="AW202">
+        <v>5</v>
+      </c>
+      <c r="AX202">
+        <v>8</v>
+      </c>
+      <c r="AY202">
+        <v>12</v>
+      </c>
+      <c r="AZ202">
+        <v>13</v>
+      </c>
+      <c r="BA202">
+        <v>5</v>
+      </c>
+      <c r="BB202">
+        <v>9</v>
+      </c>
+      <c r="BC202">
+        <v>14</v>
+      </c>
+      <c r="BD202">
+        <v>1.87</v>
+      </c>
+      <c r="BE202">
+        <v>7.9</v>
+      </c>
+      <c r="BF202">
+        <v>2.29</v>
+      </c>
+      <c r="BG202">
+        <v>1.28</v>
+      </c>
+      <c r="BH202">
+        <v>3.2</v>
+      </c>
+      <c r="BI202">
+        <v>1.52</v>
+      </c>
+      <c r="BJ202">
+        <v>2.36</v>
+      </c>
+      <c r="BK202">
+        <v>1.9</v>
+      </c>
+      <c r="BL202">
+        <v>1.9</v>
+      </c>
+      <c r="BM202">
+        <v>2.37</v>
+      </c>
+      <c r="BN202">
+        <v>1.55</v>
+      </c>
+      <c r="BO202">
+        <v>3.07</v>
+      </c>
+      <c r="BP202">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="314">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -664,6 +664,18 @@
     <t>['56', '87', '9004']</t>
   </si>
   <si>
+    <t>['75']</t>
+  </si>
+  <si>
+    <t>['9005']</t>
+  </si>
+  <si>
+    <t>['31']</t>
+  </si>
+  <si>
+    <t>['4503']</t>
+  </si>
+  <si>
     <t>['31', '60']</t>
   </si>
   <si>
@@ -820,9 +832,6 @@
     <t>['5', '12', '14', '19']</t>
   </si>
   <si>
-    <t>['31']</t>
-  </si>
-  <si>
     <t>['79']</t>
   </si>
   <si>
@@ -875,9 +884,6 @@
   </si>
   <si>
     <t>['35', '90']</t>
-  </si>
-  <si>
-    <t>['75']</t>
   </si>
   <si>
     <t>['21', '59']</t>
@@ -941,6 +947,15 @@
   </si>
   <si>
     <t>['4', '61']</t>
+  </si>
+  <si>
+    <t>['5']</t>
+  </si>
+  <si>
+    <t>['39', '62']</t>
+  </si>
+  <si>
+    <t>['9003']</t>
   </si>
 </sst>
 </file>
@@ -1302,7 +1317,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP202"/>
+  <dimension ref="A1:BP211"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1558,7 +1573,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q2">
         <v>3.6</v>
@@ -1639,7 +1654,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ2">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2048,7 +2063,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ4">
         <v>0.6</v>
@@ -2176,7 +2191,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2254,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ5">
         <v>1.78</v>
@@ -2382,7 +2397,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q6">
         <v>4.1</v>
@@ -2460,10 +2475,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ6">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2666,10 +2681,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ7">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2794,7 +2809,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q8">
         <v>2.28</v>
@@ -3287,7 +3302,7 @@
         <v>1</v>
       </c>
       <c r="AQ10">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3490,7 +3505,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ11">
         <v>1.17</v>
@@ -3696,7 +3711,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ12">
         <v>1.22</v>
@@ -4236,7 +4251,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q15">
         <v>4.1</v>
@@ -4314,10 +4329,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ15">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4729,7 +4744,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ17">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4932,7 +4947,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ18">
         <v>1</v>
@@ -5344,10 +5359,10 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ20">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR20">
         <v>1.61</v>
@@ -5472,7 +5487,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q21">
         <v>4.4</v>
@@ -5553,7 +5568,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ21">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR21">
         <v>1.32</v>
@@ -5884,7 +5899,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5962,10 +5977,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ23">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR23">
         <v>1.4</v>
@@ -6296,7 +6311,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -6580,10 +6595,10 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ26">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR26">
         <v>0.85</v>
@@ -6708,7 +6723,7 @@
         <v>90</v>
       </c>
       <c r="P27" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q27">
         <v>3.2</v>
@@ -6789,7 +6804,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ27">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR27">
         <v>1.59</v>
@@ -6995,7 +7010,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ28">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR28">
         <v>2.36</v>
@@ -7198,7 +7213,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ29">
         <v>1.27</v>
@@ -7404,10 +7419,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ30">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR30">
         <v>1.54</v>
@@ -7610,7 +7625,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ31">
         <v>1.17</v>
@@ -7738,7 +7753,7 @@
         <v>113</v>
       </c>
       <c r="P32" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q32">
         <v>3.45</v>
@@ -7819,7 +7834,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ32">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR32">
         <v>1.26</v>
@@ -7944,7 +7959,7 @@
         <v>114</v>
       </c>
       <c r="P33" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8150,7 +8165,7 @@
         <v>115</v>
       </c>
       <c r="P34" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8231,7 +8246,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ34">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR34">
         <v>1.24</v>
@@ -8356,7 +8371,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q35">
         <v>3.4</v>
@@ -8437,7 +8452,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ35">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR35">
         <v>0</v>
@@ -8562,7 +8577,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q36">
         <v>2.8</v>
@@ -8640,10 +8655,10 @@
         <v>2</v>
       </c>
       <c r="AP36">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ36">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR36">
         <v>0</v>
@@ -8974,7 +8989,7 @@
         <v>118</v>
       </c>
       <c r="P38" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q38">
         <v>2.6</v>
@@ -9052,7 +9067,7 @@
         <v>1</v>
       </c>
       <c r="AP38">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ38">
         <v>1</v>
@@ -9258,7 +9273,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ39">
         <v>1.3</v>
@@ -9670,7 +9685,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ41">
         <v>1.78</v>
@@ -9798,7 +9813,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10082,10 +10097,10 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ43">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR43">
         <v>1.09</v>
@@ -10288,7 +10303,7 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ44">
         <v>1.27</v>
@@ -10494,10 +10509,10 @@
         <v>3</v>
       </c>
       <c r="AP45">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ45">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR45">
         <v>1.47</v>
@@ -10703,7 +10718,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ46">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR46">
         <v>2.49</v>
@@ -10828,7 +10843,7 @@
         <v>105</v>
       </c>
       <c r="P47" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -11034,7 +11049,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q48">
         <v>3.6</v>
@@ -11112,10 +11127,10 @@
         <v>1.5</v>
       </c>
       <c r="AP48">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ48">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR48">
         <v>1.52</v>
@@ -11240,7 +11255,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q49">
         <v>3.6</v>
@@ -11318,7 +11333,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ49">
         <v>0.9</v>
@@ -11652,7 +11667,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q51">
         <v>1.91</v>
@@ -11733,7 +11748,7 @@
         <v>2</v>
       </c>
       <c r="AQ51">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR51">
         <v>1.69</v>
@@ -11858,7 +11873,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -12064,7 +12079,7 @@
         <v>90</v>
       </c>
       <c r="P53" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12142,7 +12157,7 @@
         <v>0.5</v>
       </c>
       <c r="AP53">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ53">
         <v>0.9</v>
@@ -12351,7 +12366,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ54">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR54">
         <v>2.36</v>
@@ -12554,7 +12569,7 @@
         <v>1.33</v>
       </c>
       <c r="AP55">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ55">
         <v>0.7</v>
@@ -12682,7 +12697,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q56">
         <v>4.33</v>
@@ -12969,7 +12984,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ57">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR57">
         <v>1.77</v>
@@ -13300,7 +13315,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13378,7 +13393,7 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ59">
         <v>1</v>
@@ -13584,10 +13599,10 @@
         <v>1.33</v>
       </c>
       <c r="AP60">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ60">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR60">
         <v>1.48</v>
@@ -13712,7 +13727,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13790,10 +13805,10 @@
         <v>3</v>
       </c>
       <c r="AP61">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ61">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR61">
         <v>1.1</v>
@@ -13918,7 +13933,7 @@
         <v>90</v>
       </c>
       <c r="P62" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q62">
         <v>2.75</v>
@@ -14408,10 +14423,10 @@
         <v>0.5</v>
       </c>
       <c r="AP64">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ64">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR64">
         <v>1.49</v>
@@ -14536,7 +14551,7 @@
         <v>90</v>
       </c>
       <c r="P65" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q65">
         <v>3.6</v>
@@ -14614,10 +14629,10 @@
         <v>1.33</v>
       </c>
       <c r="AP65">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ65">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR65">
         <v>1.13</v>
@@ -14742,7 +14757,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q66">
         <v>4.75</v>
@@ -14820,10 +14835,10 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ66">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR66">
         <v>1.04</v>
@@ -14948,7 +14963,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q67">
         <v>2.88</v>
@@ -15438,10 +15453,10 @@
         <v>3</v>
       </c>
       <c r="AP69">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ69">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR69">
         <v>1.3</v>
@@ -15853,7 +15868,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ71">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR71">
         <v>1.39</v>
@@ -16059,7 +16074,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ72">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR72">
         <v>1.51</v>
@@ -16262,10 +16277,10 @@
         <v>0.33</v>
       </c>
       <c r="AP73">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ73">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR73">
         <v>1.25</v>
@@ -16468,10 +16483,10 @@
         <v>0.5</v>
       </c>
       <c r="AP74">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ74">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR74">
         <v>1.3</v>
@@ -16880,7 +16895,7 @@
         <v>1</v>
       </c>
       <c r="AP76">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ76">
         <v>1</v>
@@ -17086,7 +17101,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ77">
         <v>1.3</v>
@@ -17295,7 +17310,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ78">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR78">
         <v>1.6</v>
@@ -17420,7 +17435,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q79">
         <v>2.63</v>
@@ -17832,7 +17847,7 @@
         <v>145</v>
       </c>
       <c r="P81" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q81">
         <v>3.2</v>
@@ -17913,7 +17928,7 @@
         <v>1</v>
       </c>
       <c r="AQ81">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR81">
         <v>1.55</v>
@@ -18119,7 +18134,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ82">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR82">
         <v>1.31</v>
@@ -18528,7 +18543,7 @@
         <v>1.2</v>
       </c>
       <c r="AP84">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ84">
         <v>1.17</v>
@@ -18734,10 +18749,10 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ85">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR85">
         <v>1.08</v>
@@ -18862,7 +18877,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -18943,7 +18958,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ86">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR86">
         <v>1.94</v>
@@ -19068,7 +19083,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19146,7 +19161,7 @@
         <v>0</v>
       </c>
       <c r="AP87">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ87">
         <v>0.6</v>
@@ -19274,7 +19289,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19352,10 +19367,10 @@
         <v>2.25</v>
       </c>
       <c r="AP88">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ88">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR88">
         <v>1.22</v>
@@ -19480,7 +19495,7 @@
         <v>90</v>
       </c>
       <c r="P89" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19764,7 +19779,7 @@
         <v>1.33</v>
       </c>
       <c r="AP90">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ90">
         <v>0.9</v>
@@ -20098,7 +20113,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q92">
         <v>4</v>
@@ -20176,10 +20191,10 @@
         <v>0.5</v>
       </c>
       <c r="AP92">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ92">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR92">
         <v>1.1</v>
@@ -20304,7 +20319,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q93">
         <v>3</v>
@@ -20382,7 +20397,7 @@
         <v>0.25</v>
       </c>
       <c r="AP93">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ93">
         <v>0.6</v>
@@ -20510,7 +20525,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q94">
         <v>2.3</v>
@@ -20588,10 +20603,10 @@
         <v>0.67</v>
       </c>
       <c r="AP94">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ94">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR94">
         <v>1.38</v>
@@ -20716,7 +20731,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q95">
         <v>3.5</v>
@@ -20797,7 +20812,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ95">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR95">
         <v>1.47</v>
@@ -21003,7 +21018,7 @@
         <v>1</v>
       </c>
       <c r="AQ96">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR96">
         <v>1.52</v>
@@ -21128,7 +21143,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q97">
         <v>3.25</v>
@@ -21746,7 +21761,7 @@
         <v>157</v>
       </c>
       <c r="P100" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q100">
         <v>2.6</v>
@@ -21952,7 +21967,7 @@
         <v>122</v>
       </c>
       <c r="P101" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q101">
         <v>3.25</v>
@@ -22030,10 +22045,10 @@
         <v>0.25</v>
       </c>
       <c r="AP101">
+        <v>1.09</v>
+      </c>
+      <c r="AQ101">
         <v>0.9</v>
-      </c>
-      <c r="AQ101">
-        <v>1</v>
       </c>
       <c r="AR101">
         <v>1.44</v>
@@ -22158,7 +22173,7 @@
         <v>158</v>
       </c>
       <c r="P102" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q102">
         <v>2.25</v>
@@ -22239,7 +22254,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ102">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR102">
         <v>1.46</v>
@@ -22442,7 +22457,7 @@
         <v>0.8</v>
       </c>
       <c r="AP103">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ103">
         <v>1.27</v>
@@ -22776,7 +22791,7 @@
         <v>160</v>
       </c>
       <c r="P105" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q105">
         <v>2.38</v>
@@ -22857,7 +22872,7 @@
         <v>2</v>
       </c>
       <c r="AQ105">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR105">
         <v>1.64</v>
@@ -22982,7 +22997,7 @@
         <v>90</v>
       </c>
       <c r="P106" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23060,7 +23075,7 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ106">
         <v>0.9</v>
@@ -23188,7 +23203,7 @@
         <v>90</v>
       </c>
       <c r="P107" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q107">
         <v>3.25</v>
@@ -23266,7 +23281,7 @@
         <v>1.25</v>
       </c>
       <c r="AP107">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ107">
         <v>0.9</v>
@@ -23394,7 +23409,7 @@
         <v>161</v>
       </c>
       <c r="P108" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23472,7 +23487,7 @@
         <v>1.17</v>
       </c>
       <c r="AP108">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ108">
         <v>1</v>
@@ -23600,7 +23615,7 @@
         <v>162</v>
       </c>
       <c r="P109" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q109">
         <v>2.3</v>
@@ -23681,7 +23696,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ109">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR109">
         <v>2.1</v>
@@ -24012,7 +24027,7 @@
         <v>122</v>
       </c>
       <c r="P111" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q111">
         <v>4</v>
@@ -24090,10 +24105,10 @@
         <v>2.5</v>
       </c>
       <c r="AP111">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ111">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR111">
         <v>1.26</v>
@@ -24296,7 +24311,7 @@
         <v>1</v>
       </c>
       <c r="AP112">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ112">
         <v>1</v>
@@ -24424,7 +24439,7 @@
         <v>164</v>
       </c>
       <c r="P113" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q113">
         <v>3.6</v>
@@ -24502,10 +24517,10 @@
         <v>2</v>
       </c>
       <c r="AP113">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ113">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR113">
         <v>1.23</v>
@@ -24708,10 +24723,10 @@
         <v>2.6</v>
       </c>
       <c r="AP114">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ114">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR114">
         <v>1.57</v>
@@ -24836,7 +24851,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q115">
         <v>3.75</v>
@@ -24917,7 +24932,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ115">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR115">
         <v>1.85</v>
@@ -25042,7 +25057,7 @@
         <v>165</v>
       </c>
       <c r="P116" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q116">
         <v>3.25</v>
@@ -25123,7 +25138,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ116">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR116">
         <v>1.54</v>
@@ -25326,7 +25341,7 @@
         <v>1</v>
       </c>
       <c r="AP117">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ117">
         <v>1.22</v>
@@ -25535,7 +25550,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ118">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR118">
         <v>1.57</v>
@@ -25741,7 +25756,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ119">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR119">
         <v>1.4</v>
@@ -25944,7 +25959,7 @@
         <v>0.4</v>
       </c>
       <c r="AP120">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ120">
         <v>0.6</v>
@@ -26072,7 +26087,7 @@
         <v>167</v>
       </c>
       <c r="P121" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q121">
         <v>3.4</v>
@@ -26278,7 +26293,7 @@
         <v>168</v>
       </c>
       <c r="P122" t="s">
-        <v>268</v>
+        <v>218</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26484,7 +26499,7 @@
         <v>169</v>
       </c>
       <c r="P123" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q123">
         <v>3.4</v>
@@ -26565,7 +26580,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ123">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR123">
         <v>1.58</v>
@@ -26690,7 +26705,7 @@
         <v>90</v>
       </c>
       <c r="P124" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q124">
         <v>4</v>
@@ -26768,10 +26783,10 @@
         <v>1.29</v>
       </c>
       <c r="AP124">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ124">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR124">
         <v>1.17</v>
@@ -26974,7 +26989,7 @@
         <v>1.6</v>
       </c>
       <c r="AP125">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ125">
         <v>0.9</v>
@@ -27180,10 +27195,10 @@
         <v>2.17</v>
       </c>
       <c r="AP126">
+        <v>1.75</v>
+      </c>
+      <c r="AQ126">
         <v>1.64</v>
-      </c>
-      <c r="AQ126">
-        <v>1.8</v>
       </c>
       <c r="AR126">
         <v>1.32</v>
@@ -27308,7 +27323,7 @@
         <v>171</v>
       </c>
       <c r="P127" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27514,7 +27529,7 @@
         <v>90</v>
       </c>
       <c r="P128" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q128">
         <v>2.88</v>
@@ -27592,7 +27607,7 @@
         <v>0.86</v>
       </c>
       <c r="AP128">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ128">
         <v>1.17</v>
@@ -27720,7 +27735,7 @@
         <v>172</v>
       </c>
       <c r="P129" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -27926,7 +27941,7 @@
         <v>90</v>
       </c>
       <c r="P130" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q130">
         <v>3.4</v>
@@ -28004,7 +28019,7 @@
         <v>0.8</v>
       </c>
       <c r="AP130">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ130">
         <v>1.78</v>
@@ -28132,7 +28147,7 @@
         <v>173</v>
       </c>
       <c r="P131" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q131">
         <v>2.1</v>
@@ -28213,7 +28228,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ131">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR131">
         <v>2.03</v>
@@ -28338,7 +28353,7 @@
         <v>174</v>
       </c>
       <c r="P132" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q132">
         <v>2.5</v>
@@ -28544,7 +28559,7 @@
         <v>175</v>
       </c>
       <c r="P133" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q133">
         <v>4</v>
@@ -28622,10 +28637,10 @@
         <v>0.67</v>
       </c>
       <c r="AP133">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ133">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR133">
         <v>1.27</v>
@@ -28750,7 +28765,7 @@
         <v>176</v>
       </c>
       <c r="P134" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q134">
         <v>3.4</v>
@@ -28828,7 +28843,7 @@
         <v>1.17</v>
       </c>
       <c r="AP134">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ134">
         <v>1.78</v>
@@ -28956,7 +28971,7 @@
         <v>177</v>
       </c>
       <c r="P135" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -29240,7 +29255,7 @@
         <v>1.33</v>
       </c>
       <c r="AP136">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ136">
         <v>0.9</v>
@@ -29368,7 +29383,7 @@
         <v>179</v>
       </c>
       <c r="P137" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q137">
         <v>4</v>
@@ -29449,7 +29464,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ137">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR137">
         <v>1.16</v>
@@ -29574,7 +29589,7 @@
         <v>90</v>
       </c>
       <c r="P138" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q138">
         <v>3.75</v>
@@ -29655,7 +29670,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ138">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR138">
         <v>1.54</v>
@@ -29780,7 +29795,7 @@
         <v>90</v>
       </c>
       <c r="P139" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q139">
         <v>3</v>
@@ -29986,7 +30001,7 @@
         <v>90</v>
       </c>
       <c r="P140" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q140">
         <v>3</v>
@@ -30192,7 +30207,7 @@
         <v>180</v>
       </c>
       <c r="P141" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30273,7 +30288,7 @@
         <v>2</v>
       </c>
       <c r="AQ141">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR141">
         <v>1.59</v>
@@ -30479,7 +30494,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ142">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR142">
         <v>1.79</v>
@@ -30604,7 +30619,7 @@
         <v>182</v>
       </c>
       <c r="P143" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q143">
         <v>3.1</v>
@@ -30888,7 +30903,7 @@
         <v>0.86</v>
       </c>
       <c r="AP144">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ144">
         <v>1</v>
@@ -31300,7 +31315,7 @@
         <v>1.14</v>
       </c>
       <c r="AP146">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ146">
         <v>1.27</v>
@@ -31428,7 +31443,7 @@
         <v>90</v>
       </c>
       <c r="P147" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q147">
         <v>3.1</v>
@@ -31509,7 +31524,7 @@
         <v>1</v>
       </c>
       <c r="AQ147">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR147">
         <v>1.55</v>
@@ -31712,10 +31727,10 @@
         <v>0.88</v>
       </c>
       <c r="AP148">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ148">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR148">
         <v>1.54</v>
@@ -32124,7 +32139,7 @@
         <v>1.14</v>
       </c>
       <c r="AP150">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ150">
         <v>0.9</v>
@@ -32252,7 +32267,7 @@
         <v>186</v>
       </c>
       <c r="P151" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q151">
         <v>2.38</v>
@@ -32333,7 +32348,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ151">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR151">
         <v>1.46</v>
@@ -32536,10 +32551,10 @@
         <v>2.43</v>
       </c>
       <c r="AP152">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ152">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR152">
         <v>1.16</v>
@@ -32870,7 +32885,7 @@
         <v>187</v>
       </c>
       <c r="P154" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q154">
         <v>3.4</v>
@@ -33154,7 +33169,7 @@
         <v>1.33</v>
       </c>
       <c r="AP155">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ155">
         <v>0.9</v>
@@ -33363,7 +33378,7 @@
         <v>2</v>
       </c>
       <c r="AQ156">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR156">
         <v>1.69</v>
@@ -33566,10 +33581,10 @@
         <v>1.14</v>
       </c>
       <c r="AP157">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ157">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR157">
         <v>1.38</v>
@@ -33694,7 +33709,7 @@
         <v>90</v>
       </c>
       <c r="P158" t="s">
-        <v>287</v>
+        <v>216</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -33772,10 +33787,10 @@
         <v>1.43</v>
       </c>
       <c r="AP158">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ158">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR158">
         <v>1.44</v>
@@ -33978,7 +33993,7 @@
         <v>1</v>
       </c>
       <c r="AP159">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ159">
         <v>1</v>
@@ -34106,7 +34121,7 @@
         <v>141</v>
       </c>
       <c r="P160" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q160">
         <v>3.75</v>
@@ -34184,10 +34199,10 @@
         <v>1</v>
       </c>
       <c r="AP160">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ160">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR160">
         <v>1.07</v>
@@ -34312,7 +34327,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q161">
         <v>4.75</v>
@@ -34393,7 +34408,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ161">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR161">
         <v>1.16</v>
@@ -34518,7 +34533,7 @@
         <v>180</v>
       </c>
       <c r="P162" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q162">
         <v>3.75</v>
@@ -34599,7 +34614,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ162">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR162">
         <v>1.61</v>
@@ -34805,7 +34820,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ163">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR163">
         <v>2.07</v>
@@ -34930,7 +34945,7 @@
         <v>191</v>
       </c>
       <c r="P164" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q164">
         <v>3.1</v>
@@ -35214,7 +35229,7 @@
         <v>1.11</v>
       </c>
       <c r="AP165">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ165">
         <v>1.17</v>
@@ -35342,7 +35357,7 @@
         <v>90</v>
       </c>
       <c r="P166" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q166">
         <v>2.75</v>
@@ -35420,7 +35435,7 @@
         <v>1.13</v>
       </c>
       <c r="AP166">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ166">
         <v>1.27</v>
@@ -35626,7 +35641,7 @@
         <v>0.75</v>
       </c>
       <c r="AP167">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ167">
         <v>1</v>
@@ -35754,7 +35769,7 @@
         <v>193</v>
       </c>
       <c r="P168" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q168">
         <v>2.75</v>
@@ -35835,7 +35850,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ168">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR168">
         <v>1.45</v>
@@ -35960,7 +35975,7 @@
         <v>194</v>
       </c>
       <c r="P169" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36038,10 +36053,10 @@
         <v>1.14</v>
       </c>
       <c r="AP169">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ169">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR169">
         <v>1.3</v>
@@ -36244,7 +36259,7 @@
         <v>0.9</v>
       </c>
       <c r="AP170">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ170">
         <v>1</v>
@@ -36372,7 +36387,7 @@
         <v>196</v>
       </c>
       <c r="P171" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q171">
         <v>2.75</v>
@@ -36784,7 +36799,7 @@
         <v>197</v>
       </c>
       <c r="P173" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q173">
         <v>3</v>
@@ -37274,10 +37289,10 @@
         <v>1.25</v>
       </c>
       <c r="AP175">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ175">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR175">
         <v>1.66</v>
@@ -37402,7 +37417,7 @@
         <v>90</v>
       </c>
       <c r="P176" t="s">
-        <v>268</v>
+        <v>218</v>
       </c>
       <c r="Q176">
         <v>3.4</v>
@@ -37483,7 +37498,7 @@
         <v>1</v>
       </c>
       <c r="AQ176">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR176">
         <v>1.53</v>
@@ -37686,7 +37701,7 @@
         <v>1.33</v>
       </c>
       <c r="AP177">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ177">
         <v>1.27</v>
@@ -37814,7 +37829,7 @@
         <v>200</v>
       </c>
       <c r="P178" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q178">
         <v>3.4</v>
@@ -38226,7 +38241,7 @@
         <v>202</v>
       </c>
       <c r="P180" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q180">
         <v>2</v>
@@ -38307,7 +38322,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ180">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR180">
         <v>1.8</v>
@@ -38432,7 +38447,7 @@
         <v>90</v>
       </c>
       <c r="P181" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q181">
         <v>4</v>
@@ -38510,7 +38525,7 @@
         <v>1.43</v>
       </c>
       <c r="AP181">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ181">
         <v>1.78</v>
@@ -38716,7 +38731,7 @@
         <v>1.43</v>
       </c>
       <c r="AP182">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ182">
         <v>1.22</v>
@@ -38922,7 +38937,7 @@
         <v>0.78</v>
       </c>
       <c r="AP183">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ183">
         <v>1</v>
@@ -39050,7 +39065,7 @@
         <v>204</v>
       </c>
       <c r="P184" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39128,10 +39143,10 @@
         <v>1</v>
       </c>
       <c r="AP184">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ184">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR184">
         <v>1.4</v>
@@ -39256,7 +39271,7 @@
         <v>205</v>
       </c>
       <c r="P185" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q185">
         <v>3.2</v>
@@ -39337,7 +39352,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ185">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR185">
         <v>1.65</v>
@@ -39462,7 +39477,7 @@
         <v>206</v>
       </c>
       <c r="P186" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -39540,10 +39555,10 @@
         <v>1.89</v>
       </c>
       <c r="AP186">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ186">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR186">
         <v>1.35</v>
@@ -39668,7 +39683,7 @@
         <v>207</v>
       </c>
       <c r="P187" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q187">
         <v>2.8</v>
@@ -39749,7 +39764,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ187">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR187">
         <v>2.02</v>
@@ -39952,10 +39967,10 @@
         <v>1.33</v>
       </c>
       <c r="AP188">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ188">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR188">
         <v>1.36</v>
@@ -40080,7 +40095,7 @@
         <v>180</v>
       </c>
       <c r="P189" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q189">
         <v>2.88</v>
@@ -40158,10 +40173,10 @@
         <v>1</v>
       </c>
       <c r="AP189">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ189">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR189">
         <v>1.12</v>
@@ -40364,7 +40379,7 @@
         <v>1</v>
       </c>
       <c r="AP190">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ190">
         <v>0.9</v>
@@ -40492,7 +40507,7 @@
         <v>209</v>
       </c>
       <c r="P191" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -40573,7 +40588,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ191">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR191">
         <v>1.34</v>
@@ -40904,7 +40919,7 @@
         <v>101</v>
       </c>
       <c r="P193" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q193">
         <v>3.1</v>
@@ -41316,7 +41331,7 @@
         <v>212</v>
       </c>
       <c r="P195" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q195">
         <v>3.25</v>
@@ -41394,7 +41409,7 @@
         <v>1</v>
       </c>
       <c r="AP195">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ195">
         <v>1.17</v>
@@ -41934,7 +41949,7 @@
         <v>90</v>
       </c>
       <c r="P198" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q198">
         <v>2.6</v>
@@ -42140,7 +42155,7 @@
         <v>202</v>
       </c>
       <c r="P199" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q199">
         <v>3.3</v>
@@ -42221,7 +42236,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ199">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR199">
         <v>1.44</v>
@@ -42346,7 +42361,7 @@
         <v>214</v>
       </c>
       <c r="P200" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q200">
         <v>3.4</v>
@@ -42758,7 +42773,7 @@
         <v>215</v>
       </c>
       <c r="P202" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q202">
         <v>2.59</v>
@@ -42915,6 +42930,1860 @@
       </c>
       <c r="BP202">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="203" spans="1:68">
+      <c r="A203" s="1">
+        <v>202</v>
+      </c>
+      <c r="B203">
+        <v>7778694</v>
+      </c>
+      <c r="C203" t="s">
+        <v>68</v>
+      </c>
+      <c r="D203" t="s">
+        <v>69</v>
+      </c>
+      <c r="E203" s="2">
+        <v>45836.25</v>
+      </c>
+      <c r="F203">
+        <v>21</v>
+      </c>
+      <c r="G203" t="s">
+        <v>86</v>
+      </c>
+      <c r="H203" t="s">
+        <v>80</v>
+      </c>
+      <c r="I203">
+        <v>0</v>
+      </c>
+      <c r="J203">
+        <v>0</v>
+      </c>
+      <c r="K203">
+        <v>0</v>
+      </c>
+      <c r="L203">
+        <v>1</v>
+      </c>
+      <c r="M203">
+        <v>0</v>
+      </c>
+      <c r="N203">
+        <v>1</v>
+      </c>
+      <c r="O203" t="s">
+        <v>216</v>
+      </c>
+      <c r="P203" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q203">
+        <v>4.4</v>
+      </c>
+      <c r="R203">
+        <v>2.09</v>
+      </c>
+      <c r="S203">
+        <v>2.43</v>
+      </c>
+      <c r="T203">
+        <v>1.38</v>
+      </c>
+      <c r="U203">
+        <v>2.8</v>
+      </c>
+      <c r="V203">
+        <v>2.89</v>
+      </c>
+      <c r="W203">
+        <v>1.36</v>
+      </c>
+      <c r="X203">
+        <v>7.1</v>
+      </c>
+      <c r="Y203">
+        <v>1.06</v>
+      </c>
+      <c r="Z203">
+        <v>3.7</v>
+      </c>
+      <c r="AA203">
+        <v>3.29</v>
+      </c>
+      <c r="AB203">
+        <v>1.83</v>
+      </c>
+      <c r="AC203">
+        <v>1.01</v>
+      </c>
+      <c r="AD203">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE203">
+        <v>1.26</v>
+      </c>
+      <c r="AF203">
+        <v>3.22</v>
+      </c>
+      <c r="AG203">
+        <v>1.91</v>
+      </c>
+      <c r="AH203">
+        <v>1.79</v>
+      </c>
+      <c r="AI203">
+        <v>1.79</v>
+      </c>
+      <c r="AJ203">
+        <v>1.87</v>
+      </c>
+      <c r="AK203">
+        <v>1.83</v>
+      </c>
+      <c r="AL203">
+        <v>1.25</v>
+      </c>
+      <c r="AM203">
+        <v>1.21</v>
+      </c>
+      <c r="AN203">
+        <v>0.9</v>
+      </c>
+      <c r="AO203">
+        <v>1.8</v>
+      </c>
+      <c r="AP203">
+        <v>1.09</v>
+      </c>
+      <c r="AQ203">
+        <v>1.64</v>
+      </c>
+      <c r="AR203">
+        <v>1.23</v>
+      </c>
+      <c r="AS203">
+        <v>1.18</v>
+      </c>
+      <c r="AT203">
+        <v>2.41</v>
+      </c>
+      <c r="AU203">
+        <v>2</v>
+      </c>
+      <c r="AV203">
+        <v>6</v>
+      </c>
+      <c r="AW203">
+        <v>16</v>
+      </c>
+      <c r="AX203">
+        <v>3</v>
+      </c>
+      <c r="AY203">
+        <v>18</v>
+      </c>
+      <c r="AZ203">
+        <v>9</v>
+      </c>
+      <c r="BA203">
+        <v>7</v>
+      </c>
+      <c r="BB203">
+        <v>3</v>
+      </c>
+      <c r="BC203">
+        <v>10</v>
+      </c>
+      <c r="BD203">
+        <v>2.41</v>
+      </c>
+      <c r="BE203">
+        <v>8</v>
+      </c>
+      <c r="BF203">
+        <v>1.79</v>
+      </c>
+      <c r="BG203">
+        <v>1.28</v>
+      </c>
+      <c r="BH203">
+        <v>3.2</v>
+      </c>
+      <c r="BI203">
+        <v>1.52</v>
+      </c>
+      <c r="BJ203">
+        <v>2.36</v>
+      </c>
+      <c r="BK203">
+        <v>1.88</v>
+      </c>
+      <c r="BL203">
+        <v>1.92</v>
+      </c>
+      <c r="BM203">
+        <v>2.37</v>
+      </c>
+      <c r="BN203">
+        <v>1.55</v>
+      </c>
+      <c r="BO203">
+        <v>3.07</v>
+      </c>
+      <c r="BP203">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="204" spans="1:68">
+      <c r="A204" s="1">
+        <v>203</v>
+      </c>
+      <c r="B204">
+        <v>7778692</v>
+      </c>
+      <c r="C204" t="s">
+        <v>68</v>
+      </c>
+      <c r="D204" t="s">
+        <v>69</v>
+      </c>
+      <c r="E204" s="2">
+        <v>45836.25</v>
+      </c>
+      <c r="F204">
+        <v>21</v>
+      </c>
+      <c r="G204" t="s">
+        <v>84</v>
+      </c>
+      <c r="H204" t="s">
+        <v>83</v>
+      </c>
+      <c r="I204">
+        <v>0</v>
+      </c>
+      <c r="J204">
+        <v>0</v>
+      </c>
+      <c r="K204">
+        <v>0</v>
+      </c>
+      <c r="L204">
+        <v>1</v>
+      </c>
+      <c r="M204">
+        <v>1</v>
+      </c>
+      <c r="N204">
+        <v>2</v>
+      </c>
+      <c r="O204" t="s">
+        <v>217</v>
+      </c>
+      <c r="P204" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q204">
+        <v>3.24</v>
+      </c>
+      <c r="R204">
+        <v>1.83</v>
+      </c>
+      <c r="S204">
+        <v>3.82</v>
+      </c>
+      <c r="T204">
+        <v>1.59</v>
+      </c>
+      <c r="U204">
+        <v>2.27</v>
+      </c>
+      <c r="V204">
+        <v>3.48</v>
+      </c>
+      <c r="W204">
+        <v>1.24</v>
+      </c>
+      <c r="X204">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Y204">
+        <v>1.02</v>
+      </c>
+      <c r="Z204">
+        <v>2.53</v>
+      </c>
+      <c r="AA204">
+        <v>2.79</v>
+      </c>
+      <c r="AB204">
+        <v>2.74</v>
+      </c>
+      <c r="AC204">
+        <v>1.07</v>
+      </c>
+      <c r="AD204">
+        <v>5.8</v>
+      </c>
+      <c r="AE204">
+        <v>1.5</v>
+      </c>
+      <c r="AF204">
+        <v>2.3</v>
+      </c>
+      <c r="AG204">
+        <v>2.4</v>
+      </c>
+      <c r="AH204">
+        <v>1.5</v>
+      </c>
+      <c r="AI204">
+        <v>2.05</v>
+      </c>
+      <c r="AJ204">
+        <v>1.65</v>
+      </c>
+      <c r="AK204">
+        <v>1.34</v>
+      </c>
+      <c r="AL204">
+        <v>1.35</v>
+      </c>
+      <c r="AM204">
+        <v>1.46</v>
+      </c>
+      <c r="AN204">
+        <v>2.27</v>
+      </c>
+      <c r="AO204">
+        <v>1.8</v>
+      </c>
+      <c r="AP204">
+        <v>2.17</v>
+      </c>
+      <c r="AQ204">
+        <v>1.73</v>
+      </c>
+      <c r="AR204">
+        <v>1.66</v>
+      </c>
+      <c r="AS204">
+        <v>1.4</v>
+      </c>
+      <c r="AT204">
+        <v>3.06</v>
+      </c>
+      <c r="AU204">
+        <v>2</v>
+      </c>
+      <c r="AV204">
+        <v>2</v>
+      </c>
+      <c r="AW204">
+        <v>9</v>
+      </c>
+      <c r="AX204">
+        <v>8</v>
+      </c>
+      <c r="AY204">
+        <v>11</v>
+      </c>
+      <c r="AZ204">
+        <v>10</v>
+      </c>
+      <c r="BA204">
+        <v>2</v>
+      </c>
+      <c r="BB204">
+        <v>4</v>
+      </c>
+      <c r="BC204">
+        <v>6</v>
+      </c>
+      <c r="BD204">
+        <v>1.85</v>
+      </c>
+      <c r="BE204">
+        <v>8</v>
+      </c>
+      <c r="BF204">
+        <v>2.28</v>
+      </c>
+      <c r="BG204">
+        <v>1.27</v>
+      </c>
+      <c r="BH204">
+        <v>3.14</v>
+      </c>
+      <c r="BI204">
+        <v>1.51</v>
+      </c>
+      <c r="BJ204">
+        <v>2.26</v>
+      </c>
+      <c r="BK204">
+        <v>1.98</v>
+      </c>
+      <c r="BL204">
+        <v>1.82</v>
+      </c>
+      <c r="BM204">
+        <v>2.46</v>
+      </c>
+      <c r="BN204">
+        <v>1.43</v>
+      </c>
+      <c r="BO204">
+        <v>3.34</v>
+      </c>
+      <c r="BP204">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="205" spans="1:68">
+      <c r="A205" s="1">
+        <v>204</v>
+      </c>
+      <c r="B205">
+        <v>7778693</v>
+      </c>
+      <c r="C205" t="s">
+        <v>68</v>
+      </c>
+      <c r="D205" t="s">
+        <v>69</v>
+      </c>
+      <c r="E205" s="2">
+        <v>45836.27083333334</v>
+      </c>
+      <c r="F205">
+        <v>21</v>
+      </c>
+      <c r="G205" t="s">
+        <v>72</v>
+      </c>
+      <c r="H205" t="s">
+        <v>77</v>
+      </c>
+      <c r="I205">
+        <v>0</v>
+      </c>
+      <c r="J205">
+        <v>0</v>
+      </c>
+      <c r="K205">
+        <v>0</v>
+      </c>
+      <c r="L205">
+        <v>0</v>
+      </c>
+      <c r="M205">
+        <v>0</v>
+      </c>
+      <c r="N205">
+        <v>0</v>
+      </c>
+      <c r="O205" t="s">
+        <v>90</v>
+      </c>
+      <c r="P205" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q205">
+        <v>2.43</v>
+      </c>
+      <c r="R205">
+        <v>2.01</v>
+      </c>
+      <c r="S205">
+        <v>4.8</v>
+      </c>
+      <c r="T205">
+        <v>1.44</v>
+      </c>
+      <c r="U205">
+        <v>2.58</v>
+      </c>
+      <c r="V205">
+        <v>3.1</v>
+      </c>
+      <c r="W205">
+        <v>1.32</v>
+      </c>
+      <c r="X205">
+        <v>8</v>
+      </c>
+      <c r="Y205">
+        <v>1.05</v>
+      </c>
+      <c r="Z205">
+        <v>1.92</v>
+      </c>
+      <c r="AA205">
+        <v>2.96</v>
+      </c>
+      <c r="AB205">
+        <v>3.81</v>
+      </c>
+      <c r="AC205">
+        <v>1.02</v>
+      </c>
+      <c r="AD205">
+        <v>7.9</v>
+      </c>
+      <c r="AE205">
+        <v>1.32</v>
+      </c>
+      <c r="AF205">
+        <v>2.88</v>
+      </c>
+      <c r="AG205">
+        <v>2.01</v>
+      </c>
+      <c r="AH205">
+        <v>1.71</v>
+      </c>
+      <c r="AI205">
+        <v>1.92</v>
+      </c>
+      <c r="AJ205">
+        <v>1.75</v>
+      </c>
+      <c r="AK205">
+        <v>1.18</v>
+      </c>
+      <c r="AL205">
+        <v>1.27</v>
+      </c>
+      <c r="AM205">
+        <v>1.86</v>
+      </c>
+      <c r="AN205">
+        <v>1.33</v>
+      </c>
+      <c r="AO205">
+        <v>1.2</v>
+      </c>
+      <c r="AP205">
+        <v>1.3</v>
+      </c>
+      <c r="AQ205">
+        <v>1.18</v>
+      </c>
+      <c r="AR205">
+        <v>1.17</v>
+      </c>
+      <c r="AS205">
+        <v>1.22</v>
+      </c>
+      <c r="AT205">
+        <v>2.39</v>
+      </c>
+      <c r="AU205">
+        <v>4</v>
+      </c>
+      <c r="AV205">
+        <v>6</v>
+      </c>
+      <c r="AW205">
+        <v>5</v>
+      </c>
+      <c r="AX205">
+        <v>6</v>
+      </c>
+      <c r="AY205">
+        <v>9</v>
+      </c>
+      <c r="AZ205">
+        <v>12</v>
+      </c>
+      <c r="BA205">
+        <v>3</v>
+      </c>
+      <c r="BB205">
+        <v>7</v>
+      </c>
+      <c r="BC205">
+        <v>10</v>
+      </c>
+      <c r="BD205">
+        <v>1.34</v>
+      </c>
+      <c r="BE205">
+        <v>9.4</v>
+      </c>
+      <c r="BF205">
+        <v>4.04</v>
+      </c>
+      <c r="BG205">
+        <v>1.24</v>
+      </c>
+      <c r="BH205">
+        <v>3.48</v>
+      </c>
+      <c r="BI205">
+        <v>1.46</v>
+      </c>
+      <c r="BJ205">
+        <v>2.53</v>
+      </c>
+      <c r="BK205">
+        <v>1.76</v>
+      </c>
+      <c r="BL205">
+        <v>2</v>
+      </c>
+      <c r="BM205">
+        <v>2.2</v>
+      </c>
+      <c r="BN205">
+        <v>1.63</v>
+      </c>
+      <c r="BO205">
+        <v>2.77</v>
+      </c>
+      <c r="BP205">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="206" spans="1:68">
+      <c r="A206" s="1">
+        <v>205</v>
+      </c>
+      <c r="B206">
+        <v>7778698</v>
+      </c>
+      <c r="C206" t="s">
+        <v>68</v>
+      </c>
+      <c r="D206" t="s">
+        <v>69</v>
+      </c>
+      <c r="E206" s="2">
+        <v>45836.29166666666</v>
+      </c>
+      <c r="F206">
+        <v>21</v>
+      </c>
+      <c r="G206" t="s">
+        <v>75</v>
+      </c>
+      <c r="H206" t="s">
+        <v>70</v>
+      </c>
+      <c r="I206">
+        <v>1</v>
+      </c>
+      <c r="J206">
+        <v>0</v>
+      </c>
+      <c r="K206">
+        <v>1</v>
+      </c>
+      <c r="L206">
+        <v>1</v>
+      </c>
+      <c r="M206">
+        <v>0</v>
+      </c>
+      <c r="N206">
+        <v>1</v>
+      </c>
+      <c r="O206" t="s">
+        <v>218</v>
+      </c>
+      <c r="P206" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q206">
+        <v>2.9</v>
+      </c>
+      <c r="R206">
+        <v>1.99</v>
+      </c>
+      <c r="S206">
+        <v>3.7</v>
+      </c>
+      <c r="T206">
+        <v>1.44</v>
+      </c>
+      <c r="U206">
+        <v>2.57</v>
+      </c>
+      <c r="V206">
+        <v>3.1</v>
+      </c>
+      <c r="W206">
+        <v>1.32</v>
+      </c>
+      <c r="X206">
+        <v>7.5</v>
+      </c>
+      <c r="Y206">
+        <v>1.05</v>
+      </c>
+      <c r="Z206">
+        <v>2.25</v>
+      </c>
+      <c r="AA206">
+        <v>3.01</v>
+      </c>
+      <c r="AB206">
+        <v>2.92</v>
+      </c>
+      <c r="AC206">
+        <v>1.03</v>
+      </c>
+      <c r="AD206">
+        <v>7.4</v>
+      </c>
+      <c r="AE206">
+        <v>1.35</v>
+      </c>
+      <c r="AF206">
+        <v>2.74</v>
+      </c>
+      <c r="AG206">
+        <v>1.98</v>
+      </c>
+      <c r="AH206">
+        <v>1.73</v>
+      </c>
+      <c r="AI206">
+        <v>1.85</v>
+      </c>
+      <c r="AJ206">
+        <v>1.81</v>
+      </c>
+      <c r="AK206">
+        <v>1.33</v>
+      </c>
+      <c r="AL206">
+        <v>1.3</v>
+      </c>
+      <c r="AM206">
+        <v>1.54</v>
+      </c>
+      <c r="AN206">
+        <v>1.64</v>
+      </c>
+      <c r="AO206">
+        <v>1</v>
+      </c>
+      <c r="AP206">
+        <v>1.75</v>
+      </c>
+      <c r="AQ206">
+        <v>0.9</v>
+      </c>
+      <c r="AR206">
+        <v>1.3</v>
+      </c>
+      <c r="AS206">
+        <v>1.16</v>
+      </c>
+      <c r="AT206">
+        <v>2.46</v>
+      </c>
+      <c r="AU206">
+        <v>2</v>
+      </c>
+      <c r="AV206">
+        <v>3</v>
+      </c>
+      <c r="AW206">
+        <v>4</v>
+      </c>
+      <c r="AX206">
+        <v>10</v>
+      </c>
+      <c r="AY206">
+        <v>6</v>
+      </c>
+      <c r="AZ206">
+        <v>13</v>
+      </c>
+      <c r="BA206">
+        <v>3</v>
+      </c>
+      <c r="BB206">
+        <v>9</v>
+      </c>
+      <c r="BC206">
+        <v>12</v>
+      </c>
+      <c r="BD206">
+        <v>1.79</v>
+      </c>
+      <c r="BE206">
+        <v>8.1</v>
+      </c>
+      <c r="BF206">
+        <v>2.39</v>
+      </c>
+      <c r="BG206">
+        <v>1.24</v>
+      </c>
+      <c r="BH206">
+        <v>3.52</v>
+      </c>
+      <c r="BI206">
+        <v>1.45</v>
+      </c>
+      <c r="BJ206">
+        <v>2.57</v>
+      </c>
+      <c r="BK206">
+        <v>1.74</v>
+      </c>
+      <c r="BL206">
+        <v>2.01</v>
+      </c>
+      <c r="BM206">
+        <v>2.18</v>
+      </c>
+      <c r="BN206">
+        <v>1.64</v>
+      </c>
+      <c r="BO206">
+        <v>2.73</v>
+      </c>
+      <c r="BP206">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:68">
+      <c r="A207" s="1">
+        <v>206</v>
+      </c>
+      <c r="B207">
+        <v>7778697</v>
+      </c>
+      <c r="C207" t="s">
+        <v>68</v>
+      </c>
+      <c r="D207" t="s">
+        <v>69</v>
+      </c>
+      <c r="E207" s="2">
+        <v>45836.29166666666</v>
+      </c>
+      <c r="F207">
+        <v>21</v>
+      </c>
+      <c r="G207" t="s">
+        <v>81</v>
+      </c>
+      <c r="H207" t="s">
+        <v>89</v>
+      </c>
+      <c r="I207">
+        <v>0</v>
+      </c>
+      <c r="J207">
+        <v>1</v>
+      </c>
+      <c r="K207">
+        <v>1</v>
+      </c>
+      <c r="L207">
+        <v>1</v>
+      </c>
+      <c r="M207">
+        <v>1</v>
+      </c>
+      <c r="N207">
+        <v>2</v>
+      </c>
+      <c r="O207" t="s">
+        <v>96</v>
+      </c>
+      <c r="P207" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q207">
+        <v>2.88</v>
+      </c>
+      <c r="R207">
+        <v>1.94</v>
+      </c>
+      <c r="S207">
+        <v>3.94</v>
+      </c>
+      <c r="T207">
+        <v>1.49</v>
+      </c>
+      <c r="U207">
+        <v>2.44</v>
+      </c>
+      <c r="V207">
+        <v>3.34</v>
+      </c>
+      <c r="W207">
+        <v>1.28</v>
+      </c>
+      <c r="X207">
+        <v>8.5</v>
+      </c>
+      <c r="Y207">
+        <v>1.04</v>
+      </c>
+      <c r="Z207">
+        <v>2.14</v>
+      </c>
+      <c r="AA207">
+        <v>3.09</v>
+      </c>
+      <c r="AB207">
+        <v>3.05</v>
+      </c>
+      <c r="AC207">
+        <v>1.04</v>
+      </c>
+      <c r="AD207">
+        <v>6.8</v>
+      </c>
+      <c r="AE207">
+        <v>1.4</v>
+      </c>
+      <c r="AF207">
+        <v>2.56</v>
+      </c>
+      <c r="AG207">
+        <v>2.15</v>
+      </c>
+      <c r="AH207">
+        <v>1.62</v>
+      </c>
+      <c r="AI207">
+        <v>1.95</v>
+      </c>
+      <c r="AJ207">
+        <v>1.72</v>
+      </c>
+      <c r="AK207">
+        <v>1.31</v>
+      </c>
+      <c r="AL207">
+        <v>1.31</v>
+      </c>
+      <c r="AM207">
+        <v>1.57</v>
+      </c>
+      <c r="AN207">
+        <v>1.1</v>
+      </c>
+      <c r="AO207">
+        <v>1.18</v>
+      </c>
+      <c r="AP207">
+        <v>1.09</v>
+      </c>
+      <c r="AQ207">
+        <v>1.17</v>
+      </c>
+      <c r="AR207">
+        <v>1.4</v>
+      </c>
+      <c r="AS207">
+        <v>1.38</v>
+      </c>
+      <c r="AT207">
+        <v>2.78</v>
+      </c>
+      <c r="AU207">
+        <v>2</v>
+      </c>
+      <c r="AV207">
+        <v>2</v>
+      </c>
+      <c r="AW207">
+        <v>1</v>
+      </c>
+      <c r="AX207">
+        <v>3</v>
+      </c>
+      <c r="AY207">
+        <v>3</v>
+      </c>
+      <c r="AZ207">
+        <v>5</v>
+      </c>
+      <c r="BA207">
+        <v>6</v>
+      </c>
+      <c r="BB207">
+        <v>0</v>
+      </c>
+      <c r="BC207">
+        <v>6</v>
+      </c>
+      <c r="BD207">
+        <v>1.89</v>
+      </c>
+      <c r="BE207">
+        <v>6.25</v>
+      </c>
+      <c r="BF207">
+        <v>2.33</v>
+      </c>
+      <c r="BG207">
+        <v>1.25</v>
+      </c>
+      <c r="BH207">
+        <v>3.28</v>
+      </c>
+      <c r="BI207">
+        <v>1.47</v>
+      </c>
+      <c r="BJ207">
+        <v>2.35</v>
+      </c>
+      <c r="BK207">
+        <v>1.83</v>
+      </c>
+      <c r="BL207">
+        <v>1.83</v>
+      </c>
+      <c r="BM207">
+        <v>2.35</v>
+      </c>
+      <c r="BN207">
+        <v>1.47</v>
+      </c>
+      <c r="BO207">
+        <v>3.2</v>
+      </c>
+      <c r="BP207">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="208" spans="1:68">
+      <c r="A208" s="1">
+        <v>207</v>
+      </c>
+      <c r="B208">
+        <v>7778699</v>
+      </c>
+      <c r="C208" t="s">
+        <v>68</v>
+      </c>
+      <c r="D208" t="s">
+        <v>69</v>
+      </c>
+      <c r="E208" s="2">
+        <v>45836.29166666666</v>
+      </c>
+      <c r="F208">
+        <v>21</v>
+      </c>
+      <c r="G208" t="s">
+        <v>79</v>
+      </c>
+      <c r="H208" t="s">
+        <v>71</v>
+      </c>
+      <c r="I208">
+        <v>0</v>
+      </c>
+      <c r="J208">
+        <v>0</v>
+      </c>
+      <c r="K208">
+        <v>0</v>
+      </c>
+      <c r="L208">
+        <v>0</v>
+      </c>
+      <c r="M208">
+        <v>0</v>
+      </c>
+      <c r="N208">
+        <v>0</v>
+      </c>
+      <c r="O208" t="s">
+        <v>90</v>
+      </c>
+      <c r="P208" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q208">
+        <v>3.48</v>
+      </c>
+      <c r="R208">
+        <v>1.95</v>
+      </c>
+      <c r="S208">
+        <v>3.16</v>
+      </c>
+      <c r="T208">
+        <v>1.44</v>
+      </c>
+      <c r="U208">
+        <v>2.58</v>
+      </c>
+      <c r="V208">
+        <v>3.26</v>
+      </c>
+      <c r="W208">
+        <v>1.29</v>
+      </c>
+      <c r="X208">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y208">
+        <v>1.04</v>
+      </c>
+      <c r="Z208">
+        <v>2.86</v>
+      </c>
+      <c r="AA208">
+        <v>2.97</v>
+      </c>
+      <c r="AB208">
+        <v>2.31</v>
+      </c>
+      <c r="AC208">
+        <v>1.01</v>
+      </c>
+      <c r="AD208">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE208">
+        <v>1.33</v>
+      </c>
+      <c r="AF208">
+        <v>2.81</v>
+      </c>
+      <c r="AG208">
+        <v>2.1</v>
+      </c>
+      <c r="AH208">
+        <v>1.65</v>
+      </c>
+      <c r="AI208">
+        <v>1.86</v>
+      </c>
+      <c r="AJ208">
+        <v>1.8</v>
+      </c>
+      <c r="AK208">
+        <v>1.47</v>
+      </c>
+      <c r="AL208">
+        <v>1.3</v>
+      </c>
+      <c r="AM208">
+        <v>1.39</v>
+      </c>
+      <c r="AN208">
+        <v>1.4</v>
+      </c>
+      <c r="AO208">
+        <v>1.56</v>
+      </c>
+      <c r="AP208">
+        <v>1.36</v>
+      </c>
+      <c r="AQ208">
+        <v>1.5</v>
+      </c>
+      <c r="AR208">
+        <v>1.13</v>
+      </c>
+      <c r="AS208">
+        <v>1.49</v>
+      </c>
+      <c r="AT208">
+        <v>2.62</v>
+      </c>
+      <c r="AU208">
+        <v>3</v>
+      </c>
+      <c r="AV208">
+        <v>2</v>
+      </c>
+      <c r="AW208">
+        <v>3</v>
+      </c>
+      <c r="AX208">
+        <v>12</v>
+      </c>
+      <c r="AY208">
+        <v>6</v>
+      </c>
+      <c r="AZ208">
+        <v>14</v>
+      </c>
+      <c r="BA208">
+        <v>3</v>
+      </c>
+      <c r="BB208">
+        <v>5</v>
+      </c>
+      <c r="BC208">
+        <v>8</v>
+      </c>
+      <c r="BD208">
+        <v>1.75</v>
+      </c>
+      <c r="BE208">
+        <v>8</v>
+      </c>
+      <c r="BF208">
+        <v>2.42</v>
+      </c>
+      <c r="BG208">
+        <v>1.28</v>
+      </c>
+      <c r="BH208">
+        <v>3.2</v>
+      </c>
+      <c r="BI208">
+        <v>1.52</v>
+      </c>
+      <c r="BJ208">
+        <v>2.36</v>
+      </c>
+      <c r="BK208">
+        <v>1.92</v>
+      </c>
+      <c r="BL208">
+        <v>1.88</v>
+      </c>
+      <c r="BM208">
+        <v>2.37</v>
+      </c>
+      <c r="BN208">
+        <v>1.55</v>
+      </c>
+      <c r="BO208">
+        <v>3.07</v>
+      </c>
+      <c r="BP208">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="209" spans="1:68">
+      <c r="A209" s="1">
+        <v>208</v>
+      </c>
+      <c r="B209">
+        <v>7778691</v>
+      </c>
+      <c r="C209" t="s">
+        <v>68</v>
+      </c>
+      <c r="D209" t="s">
+        <v>69</v>
+      </c>
+      <c r="E209" s="2">
+        <v>45836.29166666666</v>
+      </c>
+      <c r="F209">
+        <v>21</v>
+      </c>
+      <c r="G209" t="s">
+        <v>88</v>
+      </c>
+      <c r="H209" t="s">
+        <v>76</v>
+      </c>
+      <c r="I209">
+        <v>1</v>
+      </c>
+      <c r="J209">
+        <v>1</v>
+      </c>
+      <c r="K209">
+        <v>2</v>
+      </c>
+      <c r="L209">
+        <v>1</v>
+      </c>
+      <c r="M209">
+        <v>2</v>
+      </c>
+      <c r="N209">
+        <v>3</v>
+      </c>
+      <c r="O209" t="s">
+        <v>219</v>
+      </c>
+      <c r="P209" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q209">
+        <v>3.78</v>
+      </c>
+      <c r="R209">
+        <v>2.2</v>
+      </c>
+      <c r="S209">
+        <v>2.51</v>
+      </c>
+      <c r="T209">
+        <v>1.29</v>
+      </c>
+      <c r="U209">
+        <v>3.26</v>
+      </c>
+      <c r="V209">
+        <v>2.49</v>
+      </c>
+      <c r="W209">
+        <v>1.47</v>
+      </c>
+      <c r="X209">
+        <v>5.5</v>
+      </c>
+      <c r="Y209">
+        <v>1.11</v>
+      </c>
+      <c r="Z209">
+        <v>3.02</v>
+      </c>
+      <c r="AA209">
+        <v>3.41</v>
+      </c>
+      <c r="AB209">
+        <v>2.02</v>
+      </c>
+      <c r="AC209">
+        <v>1.02</v>
+      </c>
+      <c r="AD209">
+        <v>10</v>
+      </c>
+      <c r="AE209">
+        <v>1.16</v>
+      </c>
+      <c r="AF209">
+        <v>4.15</v>
+      </c>
+      <c r="AG209">
+        <v>1.7</v>
+      </c>
+      <c r="AH209">
+        <v>1.95</v>
+      </c>
+      <c r="AI209">
+        <v>1.57</v>
+      </c>
+      <c r="AJ209">
+        <v>2.19</v>
+      </c>
+      <c r="AK209">
+        <v>1.73</v>
+      </c>
+      <c r="AL209">
+        <v>1.24</v>
+      </c>
+      <c r="AM209">
+        <v>1.28</v>
+      </c>
+      <c r="AN209">
+        <v>1</v>
+      </c>
+      <c r="AO209">
+        <v>1.3</v>
+      </c>
+      <c r="AP209">
+        <v>0.89</v>
+      </c>
+      <c r="AQ209">
+        <v>1.45</v>
+      </c>
+      <c r="AR209">
+        <v>1.34</v>
+      </c>
+      <c r="AS209">
+        <v>1.66</v>
+      </c>
+      <c r="AT209">
+        <v>3</v>
+      </c>
+      <c r="AU209">
+        <v>2</v>
+      </c>
+      <c r="AV209">
+        <v>3</v>
+      </c>
+      <c r="AW209">
+        <v>7</v>
+      </c>
+      <c r="AX209">
+        <v>13</v>
+      </c>
+      <c r="AY209">
+        <v>9</v>
+      </c>
+      <c r="AZ209">
+        <v>16</v>
+      </c>
+      <c r="BA209">
+        <v>2</v>
+      </c>
+      <c r="BB209">
+        <v>5</v>
+      </c>
+      <c r="BC209">
+        <v>7</v>
+      </c>
+      <c r="BD209">
+        <v>2.44</v>
+      </c>
+      <c r="BE209">
+        <v>8</v>
+      </c>
+      <c r="BF209">
+        <v>1.75</v>
+      </c>
+      <c r="BG209">
+        <v>1.26</v>
+      </c>
+      <c r="BH209">
+        <v>3.32</v>
+      </c>
+      <c r="BI209">
+        <v>1.49</v>
+      </c>
+      <c r="BJ209">
+        <v>2.44</v>
+      </c>
+      <c r="BK209">
+        <v>1.82</v>
+      </c>
+      <c r="BL209">
+        <v>1.98</v>
+      </c>
+      <c r="BM209">
+        <v>2.29</v>
+      </c>
+      <c r="BN209">
+        <v>1.58</v>
+      </c>
+      <c r="BO209">
+        <v>2.9</v>
+      </c>
+      <c r="BP209">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="210" spans="1:68">
+      <c r="A210" s="1">
+        <v>209</v>
+      </c>
+      <c r="B210">
+        <v>7778696</v>
+      </c>
+      <c r="C210" t="s">
+        <v>68</v>
+      </c>
+      <c r="D210" t="s">
+        <v>69</v>
+      </c>
+      <c r="E210" s="2">
+        <v>45836.29166666666</v>
+      </c>
+      <c r="F210">
+        <v>21</v>
+      </c>
+      <c r="G210" t="s">
+        <v>74</v>
+      </c>
+      <c r="H210" t="s">
+        <v>78</v>
+      </c>
+      <c r="I210">
+        <v>0</v>
+      </c>
+      <c r="J210">
+        <v>0</v>
+      </c>
+      <c r="K210">
+        <v>0</v>
+      </c>
+      <c r="L210">
+        <v>0</v>
+      </c>
+      <c r="M210">
+        <v>0</v>
+      </c>
+      <c r="N210">
+        <v>0</v>
+      </c>
+      <c r="O210" t="s">
+        <v>90</v>
+      </c>
+      <c r="P210" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q210">
+        <v>3.8</v>
+      </c>
+      <c r="R210">
+        <v>2.02</v>
+      </c>
+      <c r="S210">
+        <v>2.79</v>
+      </c>
+      <c r="T210">
+        <v>1.39</v>
+      </c>
+      <c r="U210">
+        <v>2.76</v>
+      </c>
+      <c r="V210">
+        <v>2.98</v>
+      </c>
+      <c r="W210">
+        <v>1.34</v>
+      </c>
+      <c r="X210">
+        <v>7.2</v>
+      </c>
+      <c r="Y210">
+        <v>1.06</v>
+      </c>
+      <c r="Z210">
+        <v>3.04</v>
+      </c>
+      <c r="AA210">
+        <v>3.14</v>
+      </c>
+      <c r="AB210">
+        <v>2.12</v>
+      </c>
+      <c r="AC210">
+        <v>1.02</v>
+      </c>
+      <c r="AD210">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE210">
+        <v>1.27</v>
+      </c>
+      <c r="AF210">
+        <v>3.14</v>
+      </c>
+      <c r="AG210">
+        <v>1.96</v>
+      </c>
+      <c r="AH210">
+        <v>1.74</v>
+      </c>
+      <c r="AI210">
+        <v>1.76</v>
+      </c>
+      <c r="AJ210">
+        <v>1.91</v>
+      </c>
+      <c r="AK210">
+        <v>1.61</v>
+      </c>
+      <c r="AL210">
+        <v>1.28</v>
+      </c>
+      <c r="AM210">
+        <v>1.3</v>
+      </c>
+      <c r="AN210">
+        <v>1.2</v>
+      </c>
+      <c r="AO210">
+        <v>2</v>
+      </c>
+      <c r="AP210">
+        <v>1.18</v>
+      </c>
+      <c r="AQ210">
+        <v>1.9</v>
+      </c>
+      <c r="AR210">
+        <v>1.47</v>
+      </c>
+      <c r="AS210">
+        <v>1.47</v>
+      </c>
+      <c r="AT210">
+        <v>2.94</v>
+      </c>
+      <c r="AU210">
+        <v>9</v>
+      </c>
+      <c r="AV210">
+        <v>6</v>
+      </c>
+      <c r="AW210">
+        <v>12</v>
+      </c>
+      <c r="AX210">
+        <v>11</v>
+      </c>
+      <c r="AY210">
+        <v>21</v>
+      </c>
+      <c r="AZ210">
+        <v>17</v>
+      </c>
+      <c r="BA210">
+        <v>7</v>
+      </c>
+      <c r="BB210">
+        <v>2</v>
+      </c>
+      <c r="BC210">
+        <v>9</v>
+      </c>
+      <c r="BD210">
+        <v>2.05</v>
+      </c>
+      <c r="BE210">
+        <v>8</v>
+      </c>
+      <c r="BF210">
+        <v>2</v>
+      </c>
+      <c r="BG210">
+        <v>1.28</v>
+      </c>
+      <c r="BH210">
+        <v>3.2</v>
+      </c>
+      <c r="BI210">
+        <v>1.52</v>
+      </c>
+      <c r="BJ210">
+        <v>2.36</v>
+      </c>
+      <c r="BK210">
+        <v>1.9</v>
+      </c>
+      <c r="BL210">
+        <v>1.9</v>
+      </c>
+      <c r="BM210">
+        <v>2.37</v>
+      </c>
+      <c r="BN210">
+        <v>1.55</v>
+      </c>
+      <c r="BO210">
+        <v>3.07</v>
+      </c>
+      <c r="BP210">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="211" spans="1:68">
+      <c r="A211" s="1">
+        <v>210</v>
+      </c>
+      <c r="B211">
+        <v>7778695</v>
+      </c>
+      <c r="C211" t="s">
+        <v>68</v>
+      </c>
+      <c r="D211" t="s">
+        <v>69</v>
+      </c>
+      <c r="E211" s="2">
+        <v>45836.3125</v>
+      </c>
+      <c r="F211">
+        <v>21</v>
+      </c>
+      <c r="G211" t="s">
+        <v>73</v>
+      </c>
+      <c r="H211" t="s">
+        <v>85</v>
+      </c>
+      <c r="I211">
+        <v>0</v>
+      </c>
+      <c r="J211">
+        <v>0</v>
+      </c>
+      <c r="K211">
+        <v>0</v>
+      </c>
+      <c r="L211">
+        <v>0</v>
+      </c>
+      <c r="M211">
+        <v>1</v>
+      </c>
+      <c r="N211">
+        <v>1</v>
+      </c>
+      <c r="O211" t="s">
+        <v>90</v>
+      </c>
+      <c r="P211" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q211">
+        <v>2.89</v>
+      </c>
+      <c r="R211">
+        <v>2.05</v>
+      </c>
+      <c r="S211">
+        <v>3.52</v>
+      </c>
+      <c r="T211">
+        <v>1.4</v>
+      </c>
+      <c r="U211">
+        <v>2.72</v>
+      </c>
+      <c r="V211">
+        <v>2.89</v>
+      </c>
+      <c r="W211">
+        <v>1.36</v>
+      </c>
+      <c r="X211">
+        <v>7.2</v>
+      </c>
+      <c r="Y211">
+        <v>1.06</v>
+      </c>
+      <c r="Z211">
+        <v>2.27</v>
+      </c>
+      <c r="AA211">
+        <v>3.14</v>
+      </c>
+      <c r="AB211">
+        <v>2.77</v>
+      </c>
+      <c r="AC211">
+        <v>1.02</v>
+      </c>
+      <c r="AD211">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AE211">
+        <v>1.29</v>
+      </c>
+      <c r="AF211">
+        <v>3.04</v>
+      </c>
+      <c r="AG211">
+        <v>1.96</v>
+      </c>
+      <c r="AH211">
+        <v>1.74</v>
+      </c>
+      <c r="AI211">
+        <v>1.76</v>
+      </c>
+      <c r="AJ211">
+        <v>1.91</v>
+      </c>
+      <c r="AK211">
+        <v>1.36</v>
+      </c>
+      <c r="AL211">
+        <v>1.28</v>
+      </c>
+      <c r="AM211">
+        <v>1.53</v>
+      </c>
+      <c r="AN211">
+        <v>2.2</v>
+      </c>
+      <c r="AO211">
+        <v>2</v>
+      </c>
+      <c r="AP211">
+        <v>2</v>
+      </c>
+      <c r="AQ211">
+        <v>2.09</v>
+      </c>
+      <c r="AR211">
+        <v>1.47</v>
+      </c>
+      <c r="AS211">
+        <v>1.45</v>
+      </c>
+      <c r="AT211">
+        <v>2.92</v>
+      </c>
+      <c r="AU211">
+        <v>3</v>
+      </c>
+      <c r="AV211">
+        <v>2</v>
+      </c>
+      <c r="AW211">
+        <v>9</v>
+      </c>
+      <c r="AX211">
+        <v>3</v>
+      </c>
+      <c r="AY211">
+        <v>12</v>
+      </c>
+      <c r="AZ211">
+        <v>5</v>
+      </c>
+      <c r="BA211">
+        <v>5</v>
+      </c>
+      <c r="BB211">
+        <v>1</v>
+      </c>
+      <c r="BC211">
+        <v>6</v>
+      </c>
+      <c r="BD211">
+        <v>1.87</v>
+      </c>
+      <c r="BE211">
+        <v>7.95</v>
+      </c>
+      <c r="BF211">
+        <v>2.28</v>
+      </c>
+      <c r="BG211">
+        <v>1.26</v>
+      </c>
+      <c r="BH211">
+        <v>3.32</v>
+      </c>
+      <c r="BI211">
+        <v>1.49</v>
+      </c>
+      <c r="BJ211">
+        <v>2.44</v>
+      </c>
+      <c r="BK211">
+        <v>1.8</v>
+      </c>
+      <c r="BL211">
+        <v>2</v>
+      </c>
+      <c r="BM211">
+        <v>2.29</v>
+      </c>
+      <c r="BN211">
+        <v>1.58</v>
+      </c>
+      <c r="BO211">
+        <v>2.9</v>
+      </c>
+      <c r="BP211">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -43693,19 +43693,19 @@
         <v>2</v>
       </c>
       <c r="AV206">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW206">
         <v>4</v>
       </c>
       <c r="AX206">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AY206">
         <v>6</v>
       </c>
       <c r="AZ206">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BA206">
         <v>3</v>
@@ -44514,22 +44514,22 @@
         <v>2.94</v>
       </c>
       <c r="AU210">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AV210">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AW210">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX210">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AY210">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ210">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA210">
         <v>7</v>
@@ -44720,22 +44720,22 @@
         <v>2.92</v>
       </c>
       <c r="AU211">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AV211">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AW211">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX211">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY211">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AZ211">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BA211">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="318">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -622,25 +622,25 @@
     <t>['73']</t>
   </si>
   <si>
-    <t>['9001']</t>
+    <t>['90+1']</t>
   </si>
   <si>
     <t>['84']</t>
   </si>
   <si>
-    <t>['23', '9003']</t>
+    <t>['23', '90+3']</t>
   </si>
   <si>
     <t>['58', '69']</t>
   </si>
   <si>
-    <t>['12', '76']</t>
+    <t>['12', '22', '76']</t>
   </si>
   <si>
     <t>['38', '52', '80']</t>
   </si>
   <si>
-    <t>['67', '73', '87', '9001']</t>
+    <t>['67', '73', '87', '90+1']</t>
   </si>
   <si>
     <t>['34', '36', '76']</t>
@@ -661,19 +661,19 @@
     <t>['5', '66']</t>
   </si>
   <si>
-    <t>['56', '87', '9004']</t>
+    <t>['56', '87', '90+4']</t>
   </si>
   <si>
     <t>['75']</t>
   </si>
   <si>
-    <t>['9005']</t>
-  </si>
-  <si>
     <t>['31']</t>
   </si>
   <si>
-    <t>['4503']</t>
+    <t>['45+3']</t>
+  </si>
+  <si>
+    <t>['8', '43']</t>
   </si>
   <si>
     <t>['31', '60']</t>
@@ -919,13 +919,13 @@
     <t>['15', '68']</t>
   </si>
   <si>
-    <t>['36', '9001']</t>
+    <t>['36', '90+1']</t>
   </si>
   <si>
-    <t>['9', '18', '81', '9002']</t>
+    <t>['9', '18', '81', '90+2']</t>
   </si>
   <si>
-    <t>['14', '4502', '55']</t>
+    <t>['14', '45+2', '55']</t>
   </si>
   <si>
     <t>['73', '83']</t>
@@ -937,10 +937,10 @@
     <t>['49', '86']</t>
   </si>
   <si>
-    <t>['22', '49', '9004']</t>
+    <t>['22', '49', '90+4']</t>
   </si>
   <si>
-    <t>['13', '29', '9003']</t>
+    <t>['13', '29', '90+3']</t>
   </si>
   <si>
     <t>['9', '81', '86']</t>
@@ -955,7 +955,19 @@
     <t>['39', '62']</t>
   </si>
   <si>
-    <t>['9003']</t>
+    <t>['8', '61']</t>
+  </si>
+  <si>
+    <t>['49', '83']</t>
+  </si>
+  <si>
+    <t>['31', '69']</t>
+  </si>
+  <si>
+    <t>['16', '80']</t>
+  </si>
+  <si>
+    <t>['59', '64', '67', '70']</t>
   </si>
 </sst>
 </file>
@@ -1317,7 +1329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP211"/>
+  <dimension ref="A1:BP219"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1857,7 +1869,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ3">
         <v>1</v>
@@ -2066,7 +2078,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ4">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2272,7 +2284,7 @@
         <v>2</v>
       </c>
       <c r="AQ5">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2887,7 +2899,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ8">
         <v>0.9</v>
@@ -3096,7 +3108,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ9">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3299,7 +3311,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ10">
         <v>1.17</v>
@@ -3714,7 +3726,7 @@
         <v>2</v>
       </c>
       <c r="AQ12">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR12">
         <v>1.68</v>
@@ -3917,10 +3929,10 @@
         <v>3</v>
       </c>
       <c r="AP13">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ13">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4123,10 +4135,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ14">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR14">
         <v>2.25</v>
@@ -4741,7 +4753,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ17">
         <v>2.09</v>
@@ -5153,10 +5165,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ19">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR19">
         <v>1.74</v>
@@ -5362,7 +5374,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ20">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR20">
         <v>1.61</v>
@@ -5771,10 +5783,10 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ22">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6183,7 +6195,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ24">
         <v>1.3</v>
@@ -6389,7 +6401,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ25">
         <v>1</v>
@@ -7216,7 +7228,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ29">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR29">
         <v>0</v>
@@ -7831,7 +7843,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ32">
         <v>1.45</v>
@@ -8037,10 +8049,10 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ33">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR33">
         <v>1.88</v>
@@ -8449,7 +8461,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ35">
         <v>1.64</v>
@@ -8864,7 +8876,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ37">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR37">
         <v>1.86</v>
@@ -9070,7 +9082,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ38">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR38">
         <v>1.1</v>
@@ -9479,7 +9491,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ40">
         <v>0.9</v>
@@ -9688,7 +9700,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ41">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR41">
         <v>1.46</v>
@@ -9891,7 +9903,7 @@
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ42">
         <v>1.17</v>
@@ -10100,7 +10112,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ43">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR43">
         <v>1.09</v>
@@ -10306,7 +10318,7 @@
         <v>2</v>
       </c>
       <c r="AQ44">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR44">
         <v>1.37</v>
@@ -10715,7 +10727,7 @@
         <v>2</v>
       </c>
       <c r="AP46">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ46">
         <v>1.73</v>
@@ -11336,7 +11348,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ49">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR49">
         <v>1.15</v>
@@ -11539,10 +11551,10 @@
         <v>1.5</v>
       </c>
       <c r="AP50">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ50">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR50">
         <v>1.08</v>
@@ -11745,7 +11757,7 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ51">
         <v>1.18</v>
@@ -11951,7 +11963,7 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ52">
         <v>1.3</v>
@@ -12363,7 +12375,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ54">
         <v>1.17</v>
@@ -12572,7 +12584,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ55">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR55">
         <v>1.39</v>
@@ -13187,10 +13199,10 @@
         <v>0.5</v>
       </c>
       <c r="AP58">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ58">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR58">
         <v>1.9</v>
@@ -13396,7 +13408,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ59">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR59">
         <v>1.09</v>
@@ -14011,10 +14023,10 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ62">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR62">
         <v>1.82</v>
@@ -14220,7 +14232,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ63">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR63">
         <v>1.46</v>
@@ -14426,7 +14438,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ64">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR64">
         <v>1.49</v>
@@ -15041,7 +15053,7 @@
         <v>0.75</v>
       </c>
       <c r="AP67">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ67">
         <v>1</v>
@@ -15247,10 +15259,10 @@
         <v>0</v>
       </c>
       <c r="AP68">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ68">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR68">
         <v>1.93</v>
@@ -15662,7 +15674,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ70">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR70">
         <v>1.09</v>
@@ -15865,7 +15877,7 @@
         <v>1.5</v>
       </c>
       <c r="AP71">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ71">
         <v>1.5</v>
@@ -16071,7 +16083,7 @@
         <v>1.2</v>
       </c>
       <c r="AP72">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ72">
         <v>1.17</v>
@@ -16280,7 +16292,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ73">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR73">
         <v>1.25</v>
@@ -16689,10 +16701,10 @@
         <v>0.33</v>
       </c>
       <c r="AP75">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ75">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR75">
         <v>1.77</v>
@@ -16898,7 +16910,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ76">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR76">
         <v>1.39</v>
@@ -17307,7 +17319,7 @@
         <v>1.25</v>
       </c>
       <c r="AP78">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ78">
         <v>1.73</v>
@@ -17513,10 +17525,10 @@
         <v>1.33</v>
       </c>
       <c r="AP79">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ79">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR79">
         <v>2.01</v>
@@ -17722,7 +17734,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ80">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR80">
         <v>1.56</v>
@@ -17925,7 +17937,7 @@
         <v>0.67</v>
       </c>
       <c r="AP81">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ81">
         <v>1.45</v>
@@ -18131,7 +18143,7 @@
         <v>3</v>
       </c>
       <c r="AP82">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ82">
         <v>1.9</v>
@@ -18955,7 +18967,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ86">
         <v>1.5</v>
@@ -19164,7 +19176,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ87">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR87">
         <v>1.26</v>
@@ -19573,10 +19585,10 @@
         <v>0.33</v>
       </c>
       <c r="AP89">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ89">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR89">
         <v>2.31</v>
@@ -19988,7 +20000,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ91">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR91">
         <v>1.1</v>
@@ -20400,7 +20412,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ93">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR93">
         <v>1.32</v>
@@ -21015,7 +21027,7 @@
         <v>1.5</v>
       </c>
       <c r="AP96">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ96">
         <v>1.5</v>
@@ -21221,10 +21233,10 @@
         <v>0.25</v>
       </c>
       <c r="AP97">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ97">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR97">
         <v>1.35</v>
@@ -21427,10 +21439,10 @@
         <v>1.25</v>
       </c>
       <c r="AP98">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ98">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR98">
         <v>1.74</v>
@@ -21633,7 +21645,7 @@
         <v>1</v>
       </c>
       <c r="AP99">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ99">
         <v>1.3</v>
@@ -21839,10 +21851,10 @@
         <v>0.75</v>
       </c>
       <c r="AP100">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ100">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR100">
         <v>1.51</v>
@@ -22048,7 +22060,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ101">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR101">
         <v>1.44</v>
@@ -22251,7 +22263,7 @@
         <v>1.25</v>
       </c>
       <c r="AP102">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ102">
         <v>1.18</v>
@@ -22460,7 +22472,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ103">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR103">
         <v>1.59</v>
@@ -22663,7 +22675,7 @@
         <v>1</v>
       </c>
       <c r="AP104">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ104">
         <v>1.17</v>
@@ -22869,7 +22881,7 @@
         <v>1</v>
       </c>
       <c r="AP105">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ105">
         <v>1.17</v>
@@ -23078,7 +23090,7 @@
         <v>2</v>
       </c>
       <c r="AQ106">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR106">
         <v>1.3</v>
@@ -23693,10 +23705,10 @@
         <v>0.8</v>
       </c>
       <c r="AP109">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ109">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR109">
         <v>2.1</v>
@@ -23899,10 +23911,10 @@
         <v>1</v>
       </c>
       <c r="AP110">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ110">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR110">
         <v>1.34</v>
@@ -24929,7 +24941,7 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ115">
         <v>1.73</v>
@@ -25135,7 +25147,7 @@
         <v>0.6</v>
       </c>
       <c r="AP116">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ116">
         <v>1.45</v>
@@ -25344,7 +25356,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ117">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR117">
         <v>1.11</v>
@@ -25962,7 +25974,7 @@
         <v>2</v>
       </c>
       <c r="AQ120">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR120">
         <v>1.38</v>
@@ -26168,7 +26180,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ121">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR121">
         <v>1.17</v>
@@ -26293,7 +26305,7 @@
         <v>168</v>
       </c>
       <c r="P122" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26371,10 +26383,10 @@
         <v>0.83</v>
       </c>
       <c r="AP122">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ122">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR122">
         <v>1.51</v>
@@ -27401,7 +27413,7 @@
         <v>0.8</v>
       </c>
       <c r="AP127">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ127">
         <v>1.3</v>
@@ -27813,10 +27825,10 @@
         <v>0.83</v>
       </c>
       <c r="AP129">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ129">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR129">
         <v>1.79</v>
@@ -28022,7 +28034,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ130">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR130">
         <v>1.35</v>
@@ -28225,7 +28237,7 @@
         <v>1.2</v>
       </c>
       <c r="AP131">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ131">
         <v>1.18</v>
@@ -28431,10 +28443,10 @@
         <v>1</v>
       </c>
       <c r="AP132">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ132">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR132">
         <v>1.48</v>
@@ -28846,7 +28858,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ134">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR134">
         <v>1.18</v>
@@ -29049,7 +29061,7 @@
         <v>0.83</v>
       </c>
       <c r="AP135">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ135">
         <v>1.3</v>
@@ -29258,7 +29270,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ136">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR136">
         <v>1.4</v>
@@ -29464,7 +29476,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ137">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR137">
         <v>1.16</v>
@@ -29873,10 +29885,10 @@
         <v>0.83</v>
       </c>
       <c r="AP139">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ139">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR139">
         <v>1.74</v>
@@ -30079,10 +30091,10 @@
         <v>0.8</v>
       </c>
       <c r="AP140">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ140">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR140">
         <v>1.32</v>
@@ -30285,7 +30297,7 @@
         <v>1.17</v>
       </c>
       <c r="AP141">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ141">
         <v>1.5</v>
@@ -30491,7 +30503,7 @@
         <v>2.17</v>
       </c>
       <c r="AP142">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ142">
         <v>2.09</v>
@@ -30906,7 +30918,7 @@
         <v>2</v>
       </c>
       <c r="AQ144">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR144">
         <v>1.35</v>
@@ -31109,7 +31121,7 @@
         <v>1</v>
       </c>
       <c r="AP145">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ145">
         <v>1</v>
@@ -31318,7 +31330,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ146">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR146">
         <v>1.32</v>
@@ -31521,7 +31533,7 @@
         <v>2</v>
       </c>
       <c r="AP147">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ147">
         <v>1.64</v>
@@ -31933,10 +31945,10 @@
         <v>0.71</v>
       </c>
       <c r="AP149">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ149">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR149">
         <v>1.34</v>
@@ -32142,7 +32154,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ150">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR150">
         <v>1.24</v>
@@ -32757,10 +32769,10 @@
         <v>0.86</v>
       </c>
       <c r="AP153">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ153">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR153">
         <v>1.56</v>
@@ -32963,10 +32975,10 @@
         <v>1.17</v>
       </c>
       <c r="AP154">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ154">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR154">
         <v>1.59</v>
@@ -33375,7 +33387,7 @@
         <v>1.86</v>
       </c>
       <c r="AP156">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ156">
         <v>2.09</v>
@@ -33584,7 +33596,7 @@
         <v>2</v>
       </c>
       <c r="AQ157">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR157">
         <v>1.38</v>
@@ -34817,7 +34829,7 @@
         <v>2.13</v>
       </c>
       <c r="AP163">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ163">
         <v>1.64</v>
@@ -35023,7 +35035,7 @@
         <v>1.14</v>
       </c>
       <c r="AP164">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ164">
         <v>1.3</v>
@@ -35438,7 +35450,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ166">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR166">
         <v>1.35</v>
@@ -35644,7 +35656,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ167">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR167">
         <v>1.34</v>
@@ -36465,7 +36477,7 @@
         <v>1.13</v>
       </c>
       <c r="AP171">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ171">
         <v>1.3</v>
@@ -36671,10 +36683,10 @@
         <v>0.63</v>
       </c>
       <c r="AP172">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ172">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR172">
         <v>1.63</v>
@@ -36877,10 +36889,10 @@
         <v>0.75</v>
       </c>
       <c r="AP173">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ173">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR173">
         <v>1.56</v>
@@ -37083,7 +37095,7 @@
         <v>1</v>
       </c>
       <c r="AP174">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ174">
         <v>1.17</v>
@@ -37417,7 +37429,7 @@
         <v>90</v>
       </c>
       <c r="P176" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q176">
         <v>3.4</v>
@@ -37495,7 +37507,7 @@
         <v>1.67</v>
       </c>
       <c r="AP176">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ176">
         <v>1.73</v>
@@ -37704,7 +37716,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ177">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR177">
         <v>1.12</v>
@@ -38017,25 +38029,25 @@
         <v>0</v>
       </c>
       <c r="J179">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K179">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L179">
         <v>1</v>
       </c>
       <c r="M179">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N179">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O179" t="s">
         <v>201</v>
       </c>
       <c r="P179" t="s">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="Q179">
         <v>2.78</v>
@@ -38113,10 +38125,10 @@
         <v>1.13</v>
       </c>
       <c r="AP179">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ179">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR179">
         <v>1.53</v>
@@ -38319,7 +38331,7 @@
         <v>1.38</v>
       </c>
       <c r="AP180">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ180">
         <v>1.18</v>
@@ -38528,7 +38540,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ181">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR181">
         <v>1.23</v>
@@ -38734,7 +38746,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ182">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR182">
         <v>1.66</v>
@@ -38940,7 +38952,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ183">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR183">
         <v>1.23</v>
@@ -39146,7 +39158,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ184">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR184">
         <v>1.4</v>
@@ -39349,7 +39361,7 @@
         <v>2.13</v>
       </c>
       <c r="AP185">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ185">
         <v>1.9</v>
@@ -39456,22 +39468,22 @@
         <v>85</v>
       </c>
       <c r="I186">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J186">
         <v>2</v>
       </c>
       <c r="K186">
+        <v>4</v>
+      </c>
+      <c r="L186">
         <v>3</v>
-      </c>
-      <c r="L186">
-        <v>2</v>
       </c>
       <c r="M186">
         <v>4</v>
       </c>
       <c r="N186">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O186" t="s">
         <v>206</v>
@@ -39761,7 +39773,7 @@
         <v>1.63</v>
       </c>
       <c r="AP187">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ187">
         <v>1.5</v>
@@ -40585,7 +40597,7 @@
         <v>1.89</v>
       </c>
       <c r="AP191">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ191">
         <v>1.64</v>
@@ -40794,7 +40806,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ192">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR192">
         <v>1.63</v>
@@ -40991,16 +41003,16 @@
         <v>1.48</v>
       </c>
       <c r="AN193">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AO193">
         <v>1.63</v>
       </c>
       <c r="AP193">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ193">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR193">
         <v>1.57</v>
@@ -41206,7 +41218,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ194">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR194">
         <v>1.19</v>
@@ -41612,13 +41624,13 @@
         <v>1.67</v>
       </c>
       <c r="AO196">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AP196">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ196">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR196">
         <v>1.34</v>
@@ -41821,10 +41833,10 @@
         <v>1.25</v>
       </c>
       <c r="AP197">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ197">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR197">
         <v>1.8</v>
@@ -42027,7 +42039,7 @@
         <v>1.11</v>
       </c>
       <c r="AP198">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ198">
         <v>1.3</v>
@@ -42439,7 +42451,7 @@
         <v>0.82</v>
       </c>
       <c r="AP200">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ200">
         <v>1</v>
@@ -42645,10 +42657,10 @@
         <v>1.3</v>
       </c>
       <c r="AP201">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ201">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR201">
         <v>1.5</v>
@@ -42851,7 +42863,7 @@
         <v>1</v>
       </c>
       <c r="AP202">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ202">
         <v>0.9</v>
@@ -43072,22 +43084,22 @@
         <v>2.41</v>
       </c>
       <c r="AU203">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AV203">
         <v>6</v>
       </c>
       <c r="AW203">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AX203">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY203">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ203">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA203">
         <v>7</v>
@@ -43182,7 +43194,7 @@
         <v>2</v>
       </c>
       <c r="O204" t="s">
-        <v>217</v>
+        <v>143</v>
       </c>
       <c r="P204" t="s">
         <v>164</v>
@@ -43278,22 +43290,22 @@
         <v>3.06</v>
       </c>
       <c r="AU204">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV204">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AW204">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AX204">
+        <v>3</v>
+      </c>
+      <c r="AY204">
+        <v>12</v>
+      </c>
+      <c r="AZ204">
         <v>8</v>
-      </c>
-      <c r="AY204">
-        <v>11</v>
-      </c>
-      <c r="AZ204">
-        <v>10</v>
       </c>
       <c r="BA204">
         <v>2</v>
@@ -43484,19 +43496,19 @@
         <v>2.39</v>
       </c>
       <c r="AU205">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV205">
         <v>6</v>
       </c>
       <c r="AW205">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX205">
         <v>6</v>
       </c>
       <c r="AY205">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ205">
         <v>12</v>
@@ -43505,10 +43517,10 @@
         <v>3</v>
       </c>
       <c r="BB205">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC205">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD205">
         <v>1.34</v>
@@ -43594,7 +43606,7 @@
         <v>1</v>
       </c>
       <c r="O206" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P206" t="s">
         <v>90</v>
@@ -43678,7 +43690,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ206">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR206">
         <v>1.3</v>
@@ -43896,22 +43908,22 @@
         <v>2.78</v>
       </c>
       <c r="AU207">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV207">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW207">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AX207">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY207">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AZ207">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BA207">
         <v>6</v>
@@ -44111,13 +44123,13 @@
         <v>3</v>
       </c>
       <c r="AX208">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AY208">
         <v>6</v>
       </c>
       <c r="AZ208">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="BA208">
         <v>3</v>
@@ -44212,7 +44224,7 @@
         <v>3</v>
       </c>
       <c r="O209" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P209" t="s">
         <v>312</v>
@@ -44308,22 +44320,22 @@
         <v>3</v>
       </c>
       <c r="AU209">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV209">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AW209">
+        <v>2</v>
+      </c>
+      <c r="AX209">
         <v>7</v>
       </c>
-      <c r="AX209">
+      <c r="AY209">
+        <v>6</v>
+      </c>
+      <c r="AZ209">
         <v>13</v>
-      </c>
-      <c r="AY209">
-        <v>9</v>
-      </c>
-      <c r="AZ209">
-        <v>16</v>
       </c>
       <c r="BA209">
         <v>2</v>
@@ -44627,7 +44639,7 @@
         <v>90</v>
       </c>
       <c r="P211" t="s">
-        <v>313</v>
+        <v>176</v>
       </c>
       <c r="Q211">
         <v>2.89</v>
@@ -44784,6 +44796,1654 @@
       </c>
       <c r="BP211">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="212" spans="1:68">
+      <c r="A212" s="1">
+        <v>211</v>
+      </c>
+      <c r="B212">
+        <v>7778700</v>
+      </c>
+      <c r="C212" t="s">
+        <v>68</v>
+      </c>
+      <c r="D212" t="s">
+        <v>69</v>
+      </c>
+      <c r="E212" s="2">
+        <v>45843.08333333334</v>
+      </c>
+      <c r="F212">
+        <v>22</v>
+      </c>
+      <c r="G212" t="s">
+        <v>87</v>
+      </c>
+      <c r="H212" t="s">
+        <v>81</v>
+      </c>
+      <c r="I212">
+        <v>1</v>
+      </c>
+      <c r="J212">
+        <v>0</v>
+      </c>
+      <c r="K212">
+        <v>1</v>
+      </c>
+      <c r="L212">
+        <v>1</v>
+      </c>
+      <c r="M212">
+        <v>0</v>
+      </c>
+      <c r="N212">
+        <v>1</v>
+      </c>
+      <c r="O212" t="s">
+        <v>198</v>
+      </c>
+      <c r="P212" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q212">
+        <v>2.8</v>
+      </c>
+      <c r="R212">
+        <v>2.15</v>
+      </c>
+      <c r="S212">
+        <v>3.6</v>
+      </c>
+      <c r="T212">
+        <v>1.36</v>
+      </c>
+      <c r="U212">
+        <v>2.9</v>
+      </c>
+      <c r="V212">
+        <v>2.8</v>
+      </c>
+      <c r="W212">
+        <v>1.4</v>
+      </c>
+      <c r="X212">
+        <v>7.5</v>
+      </c>
+      <c r="Y212">
+        <v>1.08</v>
+      </c>
+      <c r="Z212">
+        <v>2.09</v>
+      </c>
+      <c r="AA212">
+        <v>3.19</v>
+      </c>
+      <c r="AB212">
+        <v>3.05</v>
+      </c>
+      <c r="AC212">
+        <v>1.01</v>
+      </c>
+      <c r="AD212">
+        <v>8.4</v>
+      </c>
+      <c r="AE212">
+        <v>1.28</v>
+      </c>
+      <c r="AF212">
+        <v>3.08</v>
+      </c>
+      <c r="AG212">
+        <v>1.92</v>
+      </c>
+      <c r="AH212">
+        <v>1.78</v>
+      </c>
+      <c r="AI212">
+        <v>1.75</v>
+      </c>
+      <c r="AJ212">
+        <v>2</v>
+      </c>
+      <c r="AK212">
+        <v>1.35</v>
+      </c>
+      <c r="AL212">
+        <v>1.33</v>
+      </c>
+      <c r="AM212">
+        <v>1.62</v>
+      </c>
+      <c r="AN212">
+        <v>1.56</v>
+      </c>
+      <c r="AO212">
+        <v>0.6</v>
+      </c>
+      <c r="AP212">
+        <v>1.7</v>
+      </c>
+      <c r="AQ212">
+        <v>0.55</v>
+      </c>
+      <c r="AR212">
+        <v>1.57</v>
+      </c>
+      <c r="AS212">
+        <v>1.47</v>
+      </c>
+      <c r="AT212">
+        <v>3.04</v>
+      </c>
+      <c r="AU212">
+        <v>2</v>
+      </c>
+      <c r="AV212">
+        <v>4</v>
+      </c>
+      <c r="AW212">
+        <v>10</v>
+      </c>
+      <c r="AX212">
+        <v>12</v>
+      </c>
+      <c r="AY212">
+        <v>12</v>
+      </c>
+      <c r="AZ212">
+        <v>16</v>
+      </c>
+      <c r="BA212">
+        <v>7</v>
+      </c>
+      <c r="BB212">
+        <v>9</v>
+      </c>
+      <c r="BC212">
+        <v>16</v>
+      </c>
+      <c r="BD212">
+        <v>1.82</v>
+      </c>
+      <c r="BE212">
+        <v>7.13</v>
+      </c>
+      <c r="BF212">
+        <v>2.6</v>
+      </c>
+      <c r="BG212">
+        <v>1.31</v>
+      </c>
+      <c r="BH212">
+        <v>2.98</v>
+      </c>
+      <c r="BI212">
+        <v>1.6</v>
+      </c>
+      <c r="BJ212">
+        <v>2.18</v>
+      </c>
+      <c r="BK212">
+        <v>1.99</v>
+      </c>
+      <c r="BL212">
+        <v>1.73</v>
+      </c>
+      <c r="BM212">
+        <v>2.57</v>
+      </c>
+      <c r="BN212">
+        <v>1.42</v>
+      </c>
+      <c r="BO212">
+        <v>3.56</v>
+      </c>
+      <c r="BP212">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="213" spans="1:68">
+      <c r="A213" s="1">
+        <v>212</v>
+      </c>
+      <c r="B213">
+        <v>7778702</v>
+      </c>
+      <c r="C213" t="s">
+        <v>68</v>
+      </c>
+      <c r="D213" t="s">
+        <v>69</v>
+      </c>
+      <c r="E213" s="2">
+        <v>45843.25</v>
+      </c>
+      <c r="F213">
+        <v>22</v>
+      </c>
+      <c r="G213" t="s">
+        <v>89</v>
+      </c>
+      <c r="H213" t="s">
+        <v>84</v>
+      </c>
+      <c r="I213">
+        <v>0</v>
+      </c>
+      <c r="J213">
+        <v>1</v>
+      </c>
+      <c r="K213">
+        <v>1</v>
+      </c>
+      <c r="L213">
+        <v>0</v>
+      </c>
+      <c r="M213">
+        <v>2</v>
+      </c>
+      <c r="N213">
+        <v>2</v>
+      </c>
+      <c r="O213" t="s">
+        <v>90</v>
+      </c>
+      <c r="P213" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q213">
+        <v>3.7</v>
+      </c>
+      <c r="R213">
+        <v>2.05</v>
+      </c>
+      <c r="S213">
+        <v>2.9</v>
+      </c>
+      <c r="T213">
+        <v>1.44</v>
+      </c>
+      <c r="U213">
+        <v>2.7</v>
+      </c>
+      <c r="V213">
+        <v>3.1</v>
+      </c>
+      <c r="W213">
+        <v>1.33</v>
+      </c>
+      <c r="X213">
+        <v>9</v>
+      </c>
+      <c r="Y213">
+        <v>1.07</v>
+      </c>
+      <c r="Z213">
+        <v>3.07</v>
+      </c>
+      <c r="AA213">
+        <v>3.03</v>
+      </c>
+      <c r="AB213">
+        <v>2.15</v>
+      </c>
+      <c r="AC213">
+        <v>1.04</v>
+      </c>
+      <c r="AD213">
+        <v>6.85</v>
+      </c>
+      <c r="AE213">
+        <v>1.37</v>
+      </c>
+      <c r="AF213">
+        <v>2.66</v>
+      </c>
+      <c r="AG213">
+        <v>2.08</v>
+      </c>
+      <c r="AH213">
+        <v>1.66</v>
+      </c>
+      <c r="AI213">
+        <v>1.91</v>
+      </c>
+      <c r="AJ213">
+        <v>1.85</v>
+      </c>
+      <c r="AK213">
+        <v>1.62</v>
+      </c>
+      <c r="AL213">
+        <v>1.35</v>
+      </c>
+      <c r="AM213">
+        <v>1.33</v>
+      </c>
+      <c r="AN213">
+        <v>0.78</v>
+      </c>
+      <c r="AO213">
+        <v>1.78</v>
+      </c>
+      <c r="AP213">
+        <v>0.7</v>
+      </c>
+      <c r="AQ213">
+        <v>1.9</v>
+      </c>
+      <c r="AR213">
+        <v>1.57</v>
+      </c>
+      <c r="AS213">
+        <v>1.43</v>
+      </c>
+      <c r="AT213">
+        <v>3</v>
+      </c>
+      <c r="AU213">
+        <v>2</v>
+      </c>
+      <c r="AV213">
+        <v>3</v>
+      </c>
+      <c r="AW213">
+        <v>7</v>
+      </c>
+      <c r="AX213">
+        <v>3</v>
+      </c>
+      <c r="AY213">
+        <v>9</v>
+      </c>
+      <c r="AZ213">
+        <v>6</v>
+      </c>
+      <c r="BA213">
+        <v>4</v>
+      </c>
+      <c r="BB213">
+        <v>2</v>
+      </c>
+      <c r="BC213">
+        <v>6</v>
+      </c>
+      <c r="BD213">
+        <v>2.32</v>
+      </c>
+      <c r="BE213">
+        <v>7.06</v>
+      </c>
+      <c r="BF213">
+        <v>1.97</v>
+      </c>
+      <c r="BG213">
+        <v>1.28</v>
+      </c>
+      <c r="BH213">
+        <v>3.1</v>
+      </c>
+      <c r="BI213">
+        <v>1.56</v>
+      </c>
+      <c r="BJ213">
+        <v>2.24</v>
+      </c>
+      <c r="BK213">
+        <v>1.94</v>
+      </c>
+      <c r="BL213">
+        <v>1.77</v>
+      </c>
+      <c r="BM213">
+        <v>2.49</v>
+      </c>
+      <c r="BN213">
+        <v>1.45</v>
+      </c>
+      <c r="BO213">
+        <v>3.41</v>
+      </c>
+      <c r="BP213">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="214" spans="1:68">
+      <c r="A214" s="1">
+        <v>213</v>
+      </c>
+      <c r="B214">
+        <v>7778708</v>
+      </c>
+      <c r="C214" t="s">
+        <v>68</v>
+      </c>
+      <c r="D214" t="s">
+        <v>69</v>
+      </c>
+      <c r="E214" s="2">
+        <v>45843.25</v>
+      </c>
+      <c r="F214">
+        <v>22</v>
+      </c>
+      <c r="G214" t="s">
+        <v>76</v>
+      </c>
+      <c r="H214" t="s">
+        <v>79</v>
+      </c>
+      <c r="I214">
+        <v>0</v>
+      </c>
+      <c r="J214">
+        <v>0</v>
+      </c>
+      <c r="K214">
+        <v>0</v>
+      </c>
+      <c r="L214">
+        <v>1</v>
+      </c>
+      <c r="M214">
+        <v>0</v>
+      </c>
+      <c r="N214">
+        <v>1</v>
+      </c>
+      <c r="O214" t="s">
+        <v>182</v>
+      </c>
+      <c r="P214" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q214">
+        <v>2.3</v>
+      </c>
+      <c r="R214">
+        <v>2.2</v>
+      </c>
+      <c r="S214">
+        <v>4.6</v>
+      </c>
+      <c r="T214">
+        <v>1.36</v>
+      </c>
+      <c r="U214">
+        <v>3</v>
+      </c>
+      <c r="V214">
+        <v>2.7</v>
+      </c>
+      <c r="W214">
+        <v>1.4</v>
+      </c>
+      <c r="X214">
+        <v>7</v>
+      </c>
+      <c r="Y214">
+        <v>1.08</v>
+      </c>
+      <c r="Z214">
+        <v>1.71</v>
+      </c>
+      <c r="AA214">
+        <v>3.41</v>
+      </c>
+      <c r="AB214">
+        <v>4.1</v>
+      </c>
+      <c r="AC214">
+        <v>1</v>
+      </c>
+      <c r="AD214">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE214">
+        <v>1.25</v>
+      </c>
+      <c r="AF214">
+        <v>3.28</v>
+      </c>
+      <c r="AG214">
+        <v>1.9</v>
+      </c>
+      <c r="AH214">
+        <v>1.8</v>
+      </c>
+      <c r="AI214">
+        <v>1.83</v>
+      </c>
+      <c r="AJ214">
+        <v>1.91</v>
+      </c>
+      <c r="AK214">
+        <v>1.22</v>
+      </c>
+      <c r="AL214">
+        <v>1.3</v>
+      </c>
+      <c r="AM214">
+        <v>1.95</v>
+      </c>
+      <c r="AN214">
+        <v>1.8</v>
+      </c>
+      <c r="AO214">
+        <v>1</v>
+      </c>
+      <c r="AP214">
+        <v>1.91</v>
+      </c>
+      <c r="AQ214">
+        <v>0.91</v>
+      </c>
+      <c r="AR214">
+        <v>2.02</v>
+      </c>
+      <c r="AS214">
+        <v>1.24</v>
+      </c>
+      <c r="AT214">
+        <v>3.26</v>
+      </c>
+      <c r="AU214">
+        <v>2</v>
+      </c>
+      <c r="AV214">
+        <v>2</v>
+      </c>
+      <c r="AW214">
+        <v>9</v>
+      </c>
+      <c r="AX214">
+        <v>6</v>
+      </c>
+      <c r="AY214">
+        <v>11</v>
+      </c>
+      <c r="AZ214">
+        <v>8</v>
+      </c>
+      <c r="BA214">
+        <v>2</v>
+      </c>
+      <c r="BB214">
+        <v>6</v>
+      </c>
+      <c r="BC214">
+        <v>8</v>
+      </c>
+      <c r="BD214">
+        <v>1.64</v>
+      </c>
+      <c r="BE214">
+        <v>7.49</v>
+      </c>
+      <c r="BF214">
+        <v>3.02</v>
+      </c>
+      <c r="BG214">
+        <v>1.26</v>
+      </c>
+      <c r="BH214">
+        <v>3.24</v>
+      </c>
+      <c r="BI214">
+        <v>1.52</v>
+      </c>
+      <c r="BJ214">
+        <v>2.33</v>
+      </c>
+      <c r="BK214">
+        <v>1.88</v>
+      </c>
+      <c r="BL214">
+        <v>1.82</v>
+      </c>
+      <c r="BM214">
+        <v>2.39</v>
+      </c>
+      <c r="BN214">
+        <v>1.49</v>
+      </c>
+      <c r="BO214">
+        <v>3.24</v>
+      </c>
+      <c r="BP214">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="215" spans="1:68">
+      <c r="A215" s="1">
+        <v>214</v>
+      </c>
+      <c r="B215">
+        <v>7778701</v>
+      </c>
+      <c r="C215" t="s">
+        <v>68</v>
+      </c>
+      <c r="D215" t="s">
+        <v>69</v>
+      </c>
+      <c r="E215" s="2">
+        <v>45843.29166666666</v>
+      </c>
+      <c r="F215">
+        <v>22</v>
+      </c>
+      <c r="G215" t="s">
+        <v>85</v>
+      </c>
+      <c r="H215" t="s">
+        <v>86</v>
+      </c>
+      <c r="I215">
+        <v>0</v>
+      </c>
+      <c r="J215">
+        <v>1</v>
+      </c>
+      <c r="K215">
+        <v>1</v>
+      </c>
+      <c r="L215">
+        <v>0</v>
+      </c>
+      <c r="M215">
+        <v>1</v>
+      </c>
+      <c r="N215">
+        <v>1</v>
+      </c>
+      <c r="O215" t="s">
+        <v>90</v>
+      </c>
+      <c r="P215" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q215">
+        <v>2.25</v>
+      </c>
+      <c r="R215">
+        <v>2.2</v>
+      </c>
+      <c r="S215">
+        <v>5</v>
+      </c>
+      <c r="T215">
+        <v>1.4</v>
+      </c>
+      <c r="U215">
+        <v>2.75</v>
+      </c>
+      <c r="V215">
+        <v>3</v>
+      </c>
+      <c r="W215">
+        <v>1.36</v>
+      </c>
+      <c r="X215">
+        <v>8.5</v>
+      </c>
+      <c r="Y215">
+        <v>1.07</v>
+      </c>
+      <c r="Z215">
+        <v>1.61</v>
+      </c>
+      <c r="AA215">
+        <v>3.45</v>
+      </c>
+      <c r="AB215">
+        <v>4.8</v>
+      </c>
+      <c r="AC215">
+        <v>1.01</v>
+      </c>
+      <c r="AD215">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE215">
+        <v>1.31</v>
+      </c>
+      <c r="AF215">
+        <v>2.92</v>
+      </c>
+      <c r="AG215">
+        <v>2.1</v>
+      </c>
+      <c r="AH215">
+        <v>1.65</v>
+      </c>
+      <c r="AI215">
+        <v>2</v>
+      </c>
+      <c r="AJ215">
+        <v>1.75</v>
+      </c>
+      <c r="AK215">
+        <v>1.18</v>
+      </c>
+      <c r="AL215">
+        <v>1.3</v>
+      </c>
+      <c r="AM215">
+        <v>2.05</v>
+      </c>
+      <c r="AN215">
+        <v>1.7</v>
+      </c>
+      <c r="AO215">
+        <v>0.7</v>
+      </c>
+      <c r="AP215">
+        <v>1.55</v>
+      </c>
+      <c r="AQ215">
+        <v>0.91</v>
+      </c>
+      <c r="AR215">
+        <v>1.43</v>
+      </c>
+      <c r="AS215">
+        <v>1.15</v>
+      </c>
+      <c r="AT215">
+        <v>2.58</v>
+      </c>
+      <c r="AU215">
+        <v>6</v>
+      </c>
+      <c r="AV215">
+        <v>2</v>
+      </c>
+      <c r="AW215">
+        <v>21</v>
+      </c>
+      <c r="AX215">
+        <v>1</v>
+      </c>
+      <c r="AY215">
+        <v>27</v>
+      </c>
+      <c r="AZ215">
+        <v>3</v>
+      </c>
+      <c r="BA215">
+        <v>12</v>
+      </c>
+      <c r="BB215">
+        <v>4</v>
+      </c>
+      <c r="BC215">
+        <v>16</v>
+      </c>
+      <c r="BD215">
+        <v>1.29</v>
+      </c>
+      <c r="BE215">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="BF215">
+        <v>5.32</v>
+      </c>
+      <c r="BG215">
+        <v>1.42</v>
+      </c>
+      <c r="BH215">
+        <v>2.58</v>
+      </c>
+      <c r="BI215">
+        <v>1.76</v>
+      </c>
+      <c r="BJ215">
+        <v>1.95</v>
+      </c>
+      <c r="BK215">
+        <v>2.23</v>
+      </c>
+      <c r="BL215">
+        <v>1.57</v>
+      </c>
+      <c r="BM215">
+        <v>3</v>
+      </c>
+      <c r="BN215">
+        <v>1.3</v>
+      </c>
+      <c r="BO215">
+        <v>4.34</v>
+      </c>
+      <c r="BP215">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="216" spans="1:68">
+      <c r="A216" s="1">
+        <v>215</v>
+      </c>
+      <c r="B216">
+        <v>7778703</v>
+      </c>
+      <c r="C216" t="s">
+        <v>68</v>
+      </c>
+      <c r="D216" t="s">
+        <v>69</v>
+      </c>
+      <c r="E216" s="2">
+        <v>45843.29166666666</v>
+      </c>
+      <c r="F216">
+        <v>22</v>
+      </c>
+      <c r="G216" t="s">
+        <v>71</v>
+      </c>
+      <c r="H216" t="s">
+        <v>70</v>
+      </c>
+      <c r="I216">
+        <v>1</v>
+      </c>
+      <c r="J216">
+        <v>0</v>
+      </c>
+      <c r="K216">
+        <v>1</v>
+      </c>
+      <c r="L216">
+        <v>1</v>
+      </c>
+      <c r="M216">
+        <v>2</v>
+      </c>
+      <c r="N216">
+        <v>3</v>
+      </c>
+      <c r="O216" t="s">
+        <v>193</v>
+      </c>
+      <c r="P216" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q216">
+        <v>2.5</v>
+      </c>
+      <c r="R216">
+        <v>2.25</v>
+      </c>
+      <c r="S216">
+        <v>4</v>
+      </c>
+      <c r="T216">
+        <v>1.35</v>
+      </c>
+      <c r="U216">
+        <v>3.1</v>
+      </c>
+      <c r="V216">
+        <v>2.62</v>
+      </c>
+      <c r="W216">
+        <v>1.44</v>
+      </c>
+      <c r="X216">
+        <v>6.5</v>
+      </c>
+      <c r="Y216">
+        <v>1.1</v>
+      </c>
+      <c r="Z216">
+        <v>1.85</v>
+      </c>
+      <c r="AA216">
+        <v>3.39</v>
+      </c>
+      <c r="AB216">
+        <v>3.53</v>
+      </c>
+      <c r="AC216">
+        <v>1.02</v>
+      </c>
+      <c r="AD216">
+        <v>10</v>
+      </c>
+      <c r="AE216">
+        <v>1.21</v>
+      </c>
+      <c r="AF216">
+        <v>3.58</v>
+      </c>
+      <c r="AG216">
+        <v>1.8</v>
+      </c>
+      <c r="AH216">
+        <v>1.9</v>
+      </c>
+      <c r="AI216">
+        <v>1.73</v>
+      </c>
+      <c r="AJ216">
+        <v>2.05</v>
+      </c>
+      <c r="AK216">
+        <v>1.25</v>
+      </c>
+      <c r="AL216">
+        <v>1.3</v>
+      </c>
+      <c r="AM216">
+        <v>1.83</v>
+      </c>
+      <c r="AN216">
+        <v>2.09</v>
+      </c>
+      <c r="AO216">
+        <v>0.9</v>
+      </c>
+      <c r="AP216">
+        <v>1.92</v>
+      </c>
+      <c r="AQ216">
+        <v>1.09</v>
+      </c>
+      <c r="AR216">
+        <v>1.8</v>
+      </c>
+      <c r="AS216">
+        <v>1.14</v>
+      </c>
+      <c r="AT216">
+        <v>2.94</v>
+      </c>
+      <c r="AU216">
+        <v>2</v>
+      </c>
+      <c r="AV216">
+        <v>4</v>
+      </c>
+      <c r="AW216">
+        <v>6</v>
+      </c>
+      <c r="AX216">
+        <v>16</v>
+      </c>
+      <c r="AY216">
+        <v>8</v>
+      </c>
+      <c r="AZ216">
+        <v>20</v>
+      </c>
+      <c r="BA216">
+        <v>4</v>
+      </c>
+      <c r="BB216">
+        <v>12</v>
+      </c>
+      <c r="BC216">
+        <v>16</v>
+      </c>
+      <c r="BD216">
+        <v>1.75</v>
+      </c>
+      <c r="BE216">
+        <v>7.49</v>
+      </c>
+      <c r="BF216">
+        <v>2.7</v>
+      </c>
+      <c r="BG216">
+        <v>1.17</v>
+      </c>
+      <c r="BH216">
+        <v>3.92</v>
+      </c>
+      <c r="BI216">
+        <v>1.38</v>
+      </c>
+      <c r="BJ216">
+        <v>2.7</v>
+      </c>
+      <c r="BK216">
+        <v>1.68</v>
+      </c>
+      <c r="BL216">
+        <v>2.05</v>
+      </c>
+      <c r="BM216">
+        <v>2.09</v>
+      </c>
+      <c r="BN216">
+        <v>1.66</v>
+      </c>
+      <c r="BO216">
+        <v>2.71</v>
+      </c>
+      <c r="BP216">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="217" spans="1:68">
+      <c r="A217" s="1">
+        <v>216</v>
+      </c>
+      <c r="B217">
+        <v>7778704</v>
+      </c>
+      <c r="C217" t="s">
+        <v>68</v>
+      </c>
+      <c r="D217" t="s">
+        <v>69</v>
+      </c>
+      <c r="E217" s="2">
+        <v>45843.29166666666</v>
+      </c>
+      <c r="F217">
+        <v>22</v>
+      </c>
+      <c r="G217" t="s">
+        <v>80</v>
+      </c>
+      <c r="H217" t="s">
+        <v>75</v>
+      </c>
+      <c r="I217">
+        <v>0</v>
+      </c>
+      <c r="J217">
+        <v>1</v>
+      </c>
+      <c r="K217">
+        <v>1</v>
+      </c>
+      <c r="L217">
+        <v>0</v>
+      </c>
+      <c r="M217">
+        <v>2</v>
+      </c>
+      <c r="N217">
+        <v>2</v>
+      </c>
+      <c r="O217" t="s">
+        <v>90</v>
+      </c>
+      <c r="P217" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q217">
+        <v>2.75</v>
+      </c>
+      <c r="R217">
+        <v>2.1</v>
+      </c>
+      <c r="S217">
+        <v>4.33</v>
+      </c>
+      <c r="T217">
+        <v>1.44</v>
+      </c>
+      <c r="U217">
+        <v>2.63</v>
+      </c>
+      <c r="V217">
+        <v>3</v>
+      </c>
+      <c r="W217">
+        <v>1.36</v>
+      </c>
+      <c r="X217">
+        <v>9</v>
+      </c>
+      <c r="Y217">
+        <v>1.07</v>
+      </c>
+      <c r="Z217">
+        <v>1.94</v>
+      </c>
+      <c r="AA217">
+        <v>3.26</v>
+      </c>
+      <c r="AB217">
+        <v>3.35</v>
+      </c>
+      <c r="AC217">
+        <v>1</v>
+      </c>
+      <c r="AD217">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE217">
+        <v>1.34</v>
+      </c>
+      <c r="AF217">
+        <v>3.21</v>
+      </c>
+      <c r="AG217">
+        <v>2.15</v>
+      </c>
+      <c r="AH217">
+        <v>1.62</v>
+      </c>
+      <c r="AI217">
+        <v>1.83</v>
+      </c>
+      <c r="AJ217">
+        <v>1.83</v>
+      </c>
+      <c r="AK217">
+        <v>1.29</v>
+      </c>
+      <c r="AL217">
+        <v>1.33</v>
+      </c>
+      <c r="AM217">
+        <v>1.73</v>
+      </c>
+      <c r="AN217">
+        <v>2</v>
+      </c>
+      <c r="AO217">
+        <v>1.22</v>
+      </c>
+      <c r="AP217">
+        <v>1.82</v>
+      </c>
+      <c r="AQ217">
+        <v>1.4</v>
+      </c>
+      <c r="AR217">
+        <v>1.52</v>
+      </c>
+      <c r="AS217">
+        <v>1.35</v>
+      </c>
+      <c r="AT217">
+        <v>2.87</v>
+      </c>
+      <c r="AU217">
+        <v>4</v>
+      </c>
+      <c r="AV217">
+        <v>7</v>
+      </c>
+      <c r="AW217">
+        <v>1</v>
+      </c>
+      <c r="AX217">
+        <v>5</v>
+      </c>
+      <c r="AY217">
+        <v>5</v>
+      </c>
+      <c r="AZ217">
+        <v>12</v>
+      </c>
+      <c r="BA217">
+        <v>4</v>
+      </c>
+      <c r="BB217">
+        <v>5</v>
+      </c>
+      <c r="BC217">
+        <v>9</v>
+      </c>
+      <c r="BD217">
+        <v>1.87</v>
+      </c>
+      <c r="BE217">
+        <v>7.12</v>
+      </c>
+      <c r="BF217">
+        <v>2.5</v>
+      </c>
+      <c r="BG217">
+        <v>1.28</v>
+      </c>
+      <c r="BH217">
+        <v>3.1</v>
+      </c>
+      <c r="BI217">
+        <v>1.56</v>
+      </c>
+      <c r="BJ217">
+        <v>2.25</v>
+      </c>
+      <c r="BK217">
+        <v>1.94</v>
+      </c>
+      <c r="BL217">
+        <v>1.77</v>
+      </c>
+      <c r="BM217">
+        <v>2.49</v>
+      </c>
+      <c r="BN217">
+        <v>1.45</v>
+      </c>
+      <c r="BO217">
+        <v>3.41</v>
+      </c>
+      <c r="BP217">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="218" spans="1:68">
+      <c r="A218" s="1">
+        <v>217</v>
+      </c>
+      <c r="B218">
+        <v>7778705</v>
+      </c>
+      <c r="C218" t="s">
+        <v>68</v>
+      </c>
+      <c r="D218" t="s">
+        <v>69</v>
+      </c>
+      <c r="E218" s="2">
+        <v>45843.29166666666</v>
+      </c>
+      <c r="F218">
+        <v>22</v>
+      </c>
+      <c r="G218" t="s">
+        <v>83</v>
+      </c>
+      <c r="H218" t="s">
+        <v>74</v>
+      </c>
+      <c r="I218">
+        <v>0</v>
+      </c>
+      <c r="J218">
+        <v>1</v>
+      </c>
+      <c r="K218">
+        <v>1</v>
+      </c>
+      <c r="L218">
+        <v>0</v>
+      </c>
+      <c r="M218">
+        <v>2</v>
+      </c>
+      <c r="N218">
+        <v>2</v>
+      </c>
+      <c r="O218" t="s">
+        <v>90</v>
+      </c>
+      <c r="P218" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q218">
+        <v>2.4</v>
+      </c>
+      <c r="R218">
+        <v>2.15</v>
+      </c>
+      <c r="S218">
+        <v>4.5</v>
+      </c>
+      <c r="T218">
+        <v>1.36</v>
+      </c>
+      <c r="U218">
+        <v>2.9</v>
+      </c>
+      <c r="V218">
+        <v>2.8</v>
+      </c>
+      <c r="W218">
+        <v>1.4</v>
+      </c>
+      <c r="X218">
+        <v>7.5</v>
+      </c>
+      <c r="Y218">
+        <v>1.08</v>
+      </c>
+      <c r="Z218">
+        <v>1.74</v>
+      </c>
+      <c r="AA218">
+        <v>3.37</v>
+      </c>
+      <c r="AB218">
+        <v>4</v>
+      </c>
+      <c r="AC218">
+        <v>1.02</v>
+      </c>
+      <c r="AD218">
+        <v>7.7</v>
+      </c>
+      <c r="AE218">
+        <v>1.32</v>
+      </c>
+      <c r="AF218">
+        <v>2.88</v>
+      </c>
+      <c r="AG218">
+        <v>1.95</v>
+      </c>
+      <c r="AH218">
+        <v>1.75</v>
+      </c>
+      <c r="AI218">
+        <v>1.85</v>
+      </c>
+      <c r="AJ218">
+        <v>1.85</v>
+      </c>
+      <c r="AK218">
+        <v>1.22</v>
+      </c>
+      <c r="AL218">
+        <v>1.3</v>
+      </c>
+      <c r="AM218">
+        <v>1.91</v>
+      </c>
+      <c r="AN218">
+        <v>1.8</v>
+      </c>
+      <c r="AO218">
+        <v>1</v>
+      </c>
+      <c r="AP218">
+        <v>1.64</v>
+      </c>
+      <c r="AQ218">
+        <v>1.18</v>
+      </c>
+      <c r="AR218">
+        <v>1.34</v>
+      </c>
+      <c r="AS218">
+        <v>1.51</v>
+      </c>
+      <c r="AT218">
+        <v>2.85</v>
+      </c>
+      <c r="AU218">
+        <v>10</v>
+      </c>
+      <c r="AV218">
+        <v>3</v>
+      </c>
+      <c r="AW218">
+        <v>17</v>
+      </c>
+      <c r="AX218">
+        <v>6</v>
+      </c>
+      <c r="AY218">
+        <v>27</v>
+      </c>
+      <c r="AZ218">
+        <v>9</v>
+      </c>
+      <c r="BA218">
+        <v>5</v>
+      </c>
+      <c r="BB218">
+        <v>3</v>
+      </c>
+      <c r="BC218">
+        <v>8</v>
+      </c>
+      <c r="BD218">
+        <v>1.77</v>
+      </c>
+      <c r="BE218">
+        <v>7.22</v>
+      </c>
+      <c r="BF218">
+        <v>2.69</v>
+      </c>
+      <c r="BG218">
+        <v>1.28</v>
+      </c>
+      <c r="BH218">
+        <v>3.1</v>
+      </c>
+      <c r="BI218">
+        <v>1.56</v>
+      </c>
+      <c r="BJ218">
+        <v>2.25</v>
+      </c>
+      <c r="BK218">
+        <v>1.94</v>
+      </c>
+      <c r="BL218">
+        <v>1.77</v>
+      </c>
+      <c r="BM218">
+        <v>2.49</v>
+      </c>
+      <c r="BN218">
+        <v>1.45</v>
+      </c>
+      <c r="BO218">
+        <v>3.4</v>
+      </c>
+      <c r="BP218">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="219" spans="1:68">
+      <c r="A219" s="1">
+        <v>218</v>
+      </c>
+      <c r="B219">
+        <v>7778707</v>
+      </c>
+      <c r="C219" t="s">
+        <v>68</v>
+      </c>
+      <c r="D219" t="s">
+        <v>69</v>
+      </c>
+      <c r="E219" s="2">
+        <v>45843.29166666666</v>
+      </c>
+      <c r="F219">
+        <v>22</v>
+      </c>
+      <c r="G219" t="s">
+        <v>78</v>
+      </c>
+      <c r="H219" t="s">
+        <v>72</v>
+      </c>
+      <c r="I219">
+        <v>2</v>
+      </c>
+      <c r="J219">
+        <v>0</v>
+      </c>
+      <c r="K219">
+        <v>2</v>
+      </c>
+      <c r="L219">
+        <v>2</v>
+      </c>
+      <c r="M219">
+        <v>4</v>
+      </c>
+      <c r="N219">
+        <v>6</v>
+      </c>
+      <c r="O219" t="s">
+        <v>219</v>
+      </c>
+      <c r="P219" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q219">
+        <v>2.8</v>
+      </c>
+      <c r="R219">
+        <v>1.95</v>
+      </c>
+      <c r="S219">
+        <v>4.4</v>
+      </c>
+      <c r="T219">
+        <v>1.57</v>
+      </c>
+      <c r="U219">
+        <v>2.3</v>
+      </c>
+      <c r="V219">
+        <v>3.9</v>
+      </c>
+      <c r="W219">
+        <v>1.22</v>
+      </c>
+      <c r="X219">
+        <v>12</v>
+      </c>
+      <c r="Y219">
+        <v>1.04</v>
+      </c>
+      <c r="Z219">
+        <v>1.97</v>
+      </c>
+      <c r="AA219">
+        <v>2.96</v>
+      </c>
+      <c r="AB219">
+        <v>3.65</v>
+      </c>
+      <c r="AC219">
+        <v>1.07</v>
+      </c>
+      <c r="AD219">
+        <v>5.95</v>
+      </c>
+      <c r="AE219">
+        <v>1.5</v>
+      </c>
+      <c r="AF219">
+        <v>2.25</v>
+      </c>
+      <c r="AG219">
+        <v>2.45</v>
+      </c>
+      <c r="AH219">
+        <v>1.48</v>
+      </c>
+      <c r="AI219">
+        <v>2.2</v>
+      </c>
+      <c r="AJ219">
+        <v>1.62</v>
+      </c>
+      <c r="AK219">
+        <v>1.29</v>
+      </c>
+      <c r="AL219">
+        <v>1.36</v>
+      </c>
+      <c r="AM219">
+        <v>1.67</v>
+      </c>
+      <c r="AN219">
+        <v>0.82</v>
+      </c>
+      <c r="AO219">
+        <v>1.27</v>
+      </c>
+      <c r="AP219">
+        <v>0.75</v>
+      </c>
+      <c r="AQ219">
+        <v>1.42</v>
+      </c>
+      <c r="AR219">
+        <v>1.57</v>
+      </c>
+      <c r="AS219">
+        <v>1.27</v>
+      </c>
+      <c r="AT219">
+        <v>2.84</v>
+      </c>
+      <c r="AU219">
+        <v>3</v>
+      </c>
+      <c r="AV219">
+        <v>5</v>
+      </c>
+      <c r="AW219">
+        <v>17</v>
+      </c>
+      <c r="AX219">
+        <v>7</v>
+      </c>
+      <c r="AY219">
+        <v>20</v>
+      </c>
+      <c r="AZ219">
+        <v>12</v>
+      </c>
+      <c r="BA219">
+        <v>2</v>
+      </c>
+      <c r="BB219">
+        <v>8</v>
+      </c>
+      <c r="BC219">
+        <v>10</v>
+      </c>
+      <c r="BD219">
+        <v>1.93</v>
+      </c>
+      <c r="BE219">
+        <v>7.04</v>
+      </c>
+      <c r="BF219">
+        <v>2.42</v>
+      </c>
+      <c r="BG219">
+        <v>1.31</v>
+      </c>
+      <c r="BH219">
+        <v>2.98</v>
+      </c>
+      <c r="BI219">
+        <v>1.6</v>
+      </c>
+      <c r="BJ219">
+        <v>2.18</v>
+      </c>
+      <c r="BK219">
+        <v>1.99</v>
+      </c>
+      <c r="BL219">
+        <v>1.73</v>
+      </c>
+      <c r="BM219">
+        <v>2.58</v>
+      </c>
+      <c r="BN219">
+        <v>1.42</v>
+      </c>
+      <c r="BO219">
+        <v>3.57</v>
+      </c>
+      <c r="BP219">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -38140,22 +38140,22 @@
         <v>2.78</v>
       </c>
       <c r="AU179">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV179">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW179">
         <v>7</v>
       </c>
       <c r="AX179">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY179">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ179">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BA179">
         <v>3</v>
@@ -39379,19 +39379,19 @@
         <v>4</v>
       </c>
       <c r="AV185">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW185">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX185">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AY185">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ185">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA185">
         <v>4</v>
@@ -39582,7 +39582,7 @@
         <v>2.81</v>
       </c>
       <c r="AU186">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV186">
         <v>6</v>
@@ -39594,7 +39594,7 @@
         <v>3</v>
       </c>
       <c r="AY186">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ186">
         <v>9</v>
@@ -39994,22 +39994,22 @@
         <v>2.64</v>
       </c>
       <c r="AU188">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AV188">
         <v>2</v>
       </c>
       <c r="AW188">
+        <v>5</v>
+      </c>
+      <c r="AX188">
+        <v>2</v>
+      </c>
+      <c r="AY188">
+        <v>23</v>
+      </c>
+      <c r="AZ188">
         <v>4</v>
-      </c>
-      <c r="AX188">
-        <v>4</v>
-      </c>
-      <c r="AY188">
-        <v>17</v>
-      </c>
-      <c r="AZ188">
-        <v>6</v>
       </c>
       <c r="BA188">
         <v>13</v>
@@ -40203,19 +40203,19 @@
         <v>4</v>
       </c>
       <c r="AV189">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW189">
         <v>3</v>
       </c>
       <c r="AX189">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY189">
         <v>7</v>
       </c>
       <c r="AZ189">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA189">
         <v>7</v>
@@ -41015,13 +41015,13 @@
         <v>1.9</v>
       </c>
       <c r="AR193">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AS193">
         <v>1.43</v>
       </c>
       <c r="AT193">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="AU193">
         <v>6</v>
@@ -41436,22 +41436,22 @@
         <v>2.81</v>
       </c>
       <c r="AU195">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV195">
         <v>9</v>
       </c>
       <c r="AW195">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AX195">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY195">
+        <v>12</v>
+      </c>
+      <c r="AZ195">
         <v>14</v>
-      </c>
-      <c r="AZ195">
-        <v>13</v>
       </c>
       <c r="BA195">
         <v>7</v>
@@ -41636,10 +41636,10 @@
         <v>1.34</v>
       </c>
       <c r="AS196">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AT196">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="AU196">
         <v>5</v>
@@ -42054,22 +42054,22 @@
         <v>2.87</v>
       </c>
       <c r="AU198">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV198">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW198">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="AX198">
         <v>7</v>
       </c>
       <c r="AY198">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AZ198">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA198">
         <v>6</v>
@@ -42263,19 +42263,19 @@
         <v>3</v>
       </c>
       <c r="AV199">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW199">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AX199">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AY199">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AZ199">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BA199">
         <v>9</v>
@@ -42466,22 +42466,22 @@
         <v>2.88</v>
       </c>
       <c r="AU200">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV200">
         <v>7</v>
       </c>
       <c r="AW200">
+        <v>4</v>
+      </c>
+      <c r="AX200">
         <v>5</v>
       </c>
-      <c r="AX200">
-        <v>6</v>
-      </c>
       <c r="AY200">
+        <v>10</v>
+      </c>
+      <c r="AZ200">
         <v>12</v>
-      </c>
-      <c r="AZ200">
-        <v>13</v>
       </c>
       <c r="BA200">
         <v>8</v>
@@ -42690,13 +42690,13 @@
         <v>8</v>
       </c>
       <c r="BA201">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BB201">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BC201">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="BD201">
         <v>1.69</v>
@@ -42869,31 +42869,31 @@
         <v>0.9</v>
       </c>
       <c r="AR202">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AS202">
         <v>1.37</v>
       </c>
       <c r="AT202">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
       <c r="AU202">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV202">
+        <v>6</v>
+      </c>
+      <c r="AW202">
+        <v>6</v>
+      </c>
+      <c r="AX202">
         <v>5</v>
       </c>
-      <c r="AW202">
-        <v>5</v>
-      </c>
-      <c r="AX202">
-        <v>8</v>
-      </c>
       <c r="AY202">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ202">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA202">
         <v>5</v>
@@ -43490,10 +43490,10 @@
         <v>1.17</v>
       </c>
       <c r="AS205">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AT205">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="AU205">
         <v>3</v>
@@ -43702,31 +43702,31 @@
         <v>2.46</v>
       </c>
       <c r="AU206">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV206">
         <v>2</v>
       </c>
       <c r="AW206">
+        <v>3</v>
+      </c>
+      <c r="AX206">
         <v>4</v>
-      </c>
-      <c r="AX206">
-        <v>5</v>
       </c>
       <c r="AY206">
         <v>6</v>
       </c>
       <c r="AZ206">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA206">
         <v>3</v>
       </c>
       <c r="BB206">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC206">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD206">
         <v>1.79</v>
@@ -43902,10 +43902,10 @@
         <v>1.4</v>
       </c>
       <c r="AS207">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AT207">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AU207">
         <v>3</v>
@@ -44105,13 +44105,13 @@
         <v>1.5</v>
       </c>
       <c r="AR208">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AS208">
         <v>1.49</v>
       </c>
       <c r="AT208">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="AU208">
         <v>3</v>
@@ -44311,13 +44311,13 @@
         <v>1.45</v>
       </c>
       <c r="AR209">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AS209">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AT209">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="AU209">
         <v>4</v>
@@ -44517,28 +44517,28 @@
         <v>1.9</v>
       </c>
       <c r="AR210">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AS210">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AT210">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="AU210">
+        <v>8</v>
+      </c>
+      <c r="AV210">
+        <v>5</v>
+      </c>
+      <c r="AW210">
         <v>6</v>
       </c>
-      <c r="AV210">
-        <v>8</v>
-      </c>
-      <c r="AW210">
-        <v>11</v>
-      </c>
       <c r="AX210">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AY210">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ210">
         <v>15</v>
@@ -44723,31 +44723,31 @@
         <v>2.09</v>
       </c>
       <c r="AR211">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AS211">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AT211">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="AU211">
+        <v>6</v>
+      </c>
+      <c r="AV211">
+        <v>5</v>
+      </c>
+      <c r="AW211">
+        <v>6</v>
+      </c>
+      <c r="AX211">
+        <v>2</v>
+      </c>
+      <c r="AY211">
+        <v>12</v>
+      </c>
+      <c r="AZ211">
         <v>7</v>
-      </c>
-      <c r="AV211">
-        <v>6</v>
-      </c>
-      <c r="AW211">
-        <v>10</v>
-      </c>
-      <c r="AX211">
-        <v>2</v>
-      </c>
-      <c r="AY211">
-        <v>17</v>
-      </c>
-      <c r="AZ211">
-        <v>8</v>
       </c>
       <c r="BA211">
         <v>5</v>
@@ -44929,13 +44929,13 @@
         <v>0.55</v>
       </c>
       <c r="AR212">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AS212">
         <v>1.47</v>
       </c>
       <c r="AT212">
-        <v>3.04</v>
+        <v>3.12</v>
       </c>
       <c r="AU212">
         <v>2</v>
@@ -45135,13 +45135,13 @@
         <v>1.9</v>
       </c>
       <c r="AR213">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AS213">
         <v>1.43</v>
       </c>
       <c r="AT213">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="AU213">
         <v>2</v>
@@ -45344,10 +45344,10 @@
         <v>2.02</v>
       </c>
       <c r="AS214">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AT214">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="AU214">
         <v>2</v>
@@ -45547,13 +45547,13 @@
         <v>0.91</v>
       </c>
       <c r="AR215">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AS215">
         <v>1.15</v>
       </c>
       <c r="AT215">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="AU215">
         <v>6</v>
@@ -45756,10 +45756,10 @@
         <v>1.8</v>
       </c>
       <c r="AS216">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AT216">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="AU216">
         <v>2</v>
@@ -45959,13 +45959,13 @@
         <v>1.4</v>
       </c>
       <c r="AR217">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="AS217">
         <v>1.35</v>
       </c>
       <c r="AT217">
-        <v>2.87</v>
+        <v>2.98</v>
       </c>
       <c r="AU217">
         <v>4</v>
@@ -46371,10 +46371,10 @@
         <v>1.42</v>
       </c>
       <c r="AR219">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AS219">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AT219">
         <v>2.84</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -38140,22 +38140,22 @@
         <v>2.78</v>
       </c>
       <c r="AU179">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV179">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW179">
         <v>7</v>
       </c>
       <c r="AX179">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY179">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ179">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BA179">
         <v>3</v>
@@ -39379,19 +39379,19 @@
         <v>4</v>
       </c>
       <c r="AV185">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW185">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX185">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AY185">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ185">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA185">
         <v>4</v>
@@ -39582,7 +39582,7 @@
         <v>2.81</v>
       </c>
       <c r="AU186">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV186">
         <v>6</v>
@@ -39594,7 +39594,7 @@
         <v>3</v>
       </c>
       <c r="AY186">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AZ186">
         <v>9</v>
@@ -39994,22 +39994,22 @@
         <v>2.64</v>
       </c>
       <c r="AU188">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AV188">
         <v>2</v>
       </c>
       <c r="AW188">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX188">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY188">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AZ188">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BA188">
         <v>13</v>
@@ -40203,19 +40203,19 @@
         <v>4</v>
       </c>
       <c r="AV189">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW189">
         <v>3</v>
       </c>
       <c r="AX189">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY189">
         <v>7</v>
       </c>
       <c r="AZ189">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA189">
         <v>7</v>
@@ -41015,13 +41015,13 @@
         <v>1.9</v>
       </c>
       <c r="AR193">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AS193">
         <v>1.43</v>
       </c>
       <c r="AT193">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="AU193">
         <v>6</v>
@@ -41436,22 +41436,22 @@
         <v>2.81</v>
       </c>
       <c r="AU195">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV195">
         <v>9</v>
       </c>
       <c r="AW195">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AX195">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY195">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ195">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA195">
         <v>7</v>
@@ -41636,10 +41636,10 @@
         <v>1.34</v>
       </c>
       <c r="AS196">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AT196">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="AU196">
         <v>5</v>
@@ -42054,22 +42054,22 @@
         <v>2.87</v>
       </c>
       <c r="AU198">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV198">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW198">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AX198">
         <v>7</v>
       </c>
       <c r="AY198">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AZ198">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA198">
         <v>6</v>
@@ -42263,19 +42263,19 @@
         <v>3</v>
       </c>
       <c r="AV199">
+        <v>10</v>
+      </c>
+      <c r="AW199">
         <v>9</v>
       </c>
-      <c r="AW199">
-        <v>4</v>
-      </c>
       <c r="AX199">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AY199">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AZ199">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="BA199">
         <v>9</v>
@@ -42466,22 +42466,22 @@
         <v>2.88</v>
       </c>
       <c r="AU200">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV200">
         <v>7</v>
       </c>
       <c r="AW200">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX200">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY200">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ200">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA200">
         <v>8</v>
@@ -42690,13 +42690,13 @@
         <v>8</v>
       </c>
       <c r="BA201">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BB201">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BC201">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="BD201">
         <v>1.69</v>
@@ -42869,31 +42869,31 @@
         <v>0.9</v>
       </c>
       <c r="AR202">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AS202">
         <v>1.37</v>
       </c>
       <c r="AT202">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="AU202">
+        <v>7</v>
+      </c>
+      <c r="AV202">
+        <v>5</v>
+      </c>
+      <c r="AW202">
+        <v>5</v>
+      </c>
+      <c r="AX202">
         <v>8</v>
       </c>
-      <c r="AV202">
-        <v>6</v>
-      </c>
-      <c r="AW202">
-        <v>6</v>
-      </c>
-      <c r="AX202">
-        <v>5</v>
-      </c>
       <c r="AY202">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ202">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA202">
         <v>5</v>
@@ -43490,10 +43490,10 @@
         <v>1.17</v>
       </c>
       <c r="AS205">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AT205">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AU205">
         <v>3</v>
@@ -43702,31 +43702,31 @@
         <v>2.46</v>
       </c>
       <c r="AU206">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV206">
         <v>2</v>
       </c>
       <c r="AW206">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX206">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY206">
         <v>6</v>
       </c>
       <c r="AZ206">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA206">
         <v>3</v>
       </c>
       <c r="BB206">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC206">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD206">
         <v>1.79</v>
@@ -43902,10 +43902,10 @@
         <v>1.4</v>
       </c>
       <c r="AS207">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AT207">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="AU207">
         <v>3</v>
@@ -44105,13 +44105,13 @@
         <v>1.5</v>
       </c>
       <c r="AR208">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AS208">
         <v>1.49</v>
       </c>
       <c r="AT208">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="AU208">
         <v>3</v>
@@ -44311,13 +44311,13 @@
         <v>1.45</v>
       </c>
       <c r="AR209">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AS209">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AT209">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="AU209">
         <v>4</v>
@@ -44517,28 +44517,28 @@
         <v>1.9</v>
       </c>
       <c r="AR210">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AS210">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AT210">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="AU210">
+        <v>6</v>
+      </c>
+      <c r="AV210">
         <v>8</v>
       </c>
-      <c r="AV210">
-        <v>5</v>
-      </c>
       <c r="AW210">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AX210">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AY210">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AZ210">
         <v>15</v>
@@ -44723,31 +44723,31 @@
         <v>2.09</v>
       </c>
       <c r="AR211">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AS211">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AT211">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="AU211">
+        <v>7</v>
+      </c>
+      <c r="AV211">
         <v>6</v>
       </c>
-      <c r="AV211">
-        <v>5</v>
-      </c>
       <c r="AW211">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AX211">
         <v>2</v>
       </c>
       <c r="AY211">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AZ211">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA211">
         <v>5</v>
@@ -44929,13 +44929,13 @@
         <v>0.55</v>
       </c>
       <c r="AR212">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AS212">
         <v>1.47</v>
       </c>
       <c r="AT212">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="AU212">
         <v>2</v>
@@ -45135,13 +45135,13 @@
         <v>1.9</v>
       </c>
       <c r="AR213">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AS213">
         <v>1.43</v>
       </c>
       <c r="AT213">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="AU213">
         <v>2</v>
@@ -45344,10 +45344,10 @@
         <v>2.02</v>
       </c>
       <c r="AS214">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AT214">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="AU214">
         <v>2</v>
@@ -45547,13 +45547,13 @@
         <v>0.91</v>
       </c>
       <c r="AR215">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AS215">
         <v>1.15</v>
       </c>
       <c r="AT215">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="AU215">
         <v>6</v>
@@ -45756,10 +45756,10 @@
         <v>1.8</v>
       </c>
       <c r="AS216">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AT216">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="AU216">
         <v>2</v>
@@ -45959,13 +45959,13 @@
         <v>1.4</v>
       </c>
       <c r="AR217">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="AS217">
         <v>1.35</v>
       </c>
       <c r="AT217">
-        <v>2.98</v>
+        <v>2.87</v>
       </c>
       <c r="AU217">
         <v>4</v>
@@ -46371,10 +46371,10 @@
         <v>1.42</v>
       </c>
       <c r="AR219">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AS219">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AT219">
         <v>2.84</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="321">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -676,6 +676,12 @@
     <t>['8', '43']</t>
   </si>
   <si>
+    <t>['61', '75']</t>
+  </si>
+  <si>
+    <t>['90+7']</t>
+  </si>
+  <si>
     <t>['31', '60']</t>
   </si>
   <si>
@@ -968,6 +974,9 @@
   </si>
   <si>
     <t>['59', '64', '67', '70']</t>
+  </si>
+  <si>
+    <t>['16', '72', '82']</t>
   </si>
 </sst>
 </file>
@@ -1329,7 +1338,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP219"/>
+  <dimension ref="A1:BP221"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1585,7 +1594,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q2">
         <v>3.6</v>
@@ -1872,7 +1881,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ3">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2203,7 +2212,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2409,7 +2418,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q6">
         <v>4.1</v>
@@ -2821,7 +2830,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q8">
         <v>2.28</v>
@@ -3105,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ9">
         <v>0.91</v>
@@ -4263,7 +4272,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q15">
         <v>4.1</v>
@@ -4547,7 +4556,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ16">
         <v>1.17</v>
@@ -4962,7 +4971,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ18">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5499,7 +5508,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q21">
         <v>4.4</v>
@@ -5577,7 +5586,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ21">
         <v>1.17</v>
@@ -5911,7 +5920,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -6198,7 +6207,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ24">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR24">
         <v>3.04</v>
@@ -6323,7 +6332,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -6404,7 +6413,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR25">
         <v>1.45</v>
@@ -6735,7 +6744,7 @@
         <v>90</v>
       </c>
       <c r="P27" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q27">
         <v>3.2</v>
@@ -6813,7 +6822,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ27">
         <v>1.5</v>
@@ -7765,7 +7774,7 @@
         <v>113</v>
       </c>
       <c r="P32" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q32">
         <v>3.45</v>
@@ -7971,7 +7980,7 @@
         <v>114</v>
       </c>
       <c r="P33" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8177,7 +8186,7 @@
         <v>115</v>
       </c>
       <c r="P34" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8255,7 +8264,7 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ34">
         <v>1.9</v>
@@ -8383,7 +8392,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q35">
         <v>3.4</v>
@@ -8589,7 +8598,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q36">
         <v>2.8</v>
@@ -9001,7 +9010,7 @@
         <v>118</v>
       </c>
       <c r="P38" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q38">
         <v>2.6</v>
@@ -9288,7 +9297,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ39">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR39">
         <v>1.33</v>
@@ -9825,7 +9834,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10855,7 +10864,7 @@
         <v>105</v>
       </c>
       <c r="P47" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10933,10 +10942,10 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ47">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR47">
         <v>1.58</v>
@@ -11061,7 +11070,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q48">
         <v>3.6</v>
@@ -11267,7 +11276,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q49">
         <v>3.6</v>
@@ -11679,7 +11688,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q51">
         <v>1.91</v>
@@ -11885,7 +11894,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -11966,7 +11975,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ52">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR52">
         <v>1.25</v>
@@ -12091,7 +12100,7 @@
         <v>90</v>
       </c>
       <c r="P53" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12709,7 +12718,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q56">
         <v>4.33</v>
@@ -12787,7 +12796,7 @@
         <v>0.75</v>
       </c>
       <c r="AP56">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ56">
         <v>1.17</v>
@@ -13327,7 +13336,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13739,7 +13748,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13945,7 +13954,7 @@
         <v>90</v>
       </c>
       <c r="P62" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q62">
         <v>2.75</v>
@@ -14229,7 +14238,7 @@
         <v>0.5</v>
       </c>
       <c r="AP63">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ63">
         <v>1.4</v>
@@ -14563,7 +14572,7 @@
         <v>90</v>
       </c>
       <c r="P65" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q65">
         <v>3.6</v>
@@ -14769,7 +14778,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q66">
         <v>4.75</v>
@@ -14975,7 +14984,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q67">
         <v>2.88</v>
@@ -15056,7 +15065,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ67">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR67">
         <v>1.24</v>
@@ -15671,7 +15680,7 @@
         <v>0.5</v>
       </c>
       <c r="AP70">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ70">
         <v>0.91</v>
@@ -17116,7 +17125,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ77">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR77">
         <v>1.29</v>
@@ -17447,7 +17456,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q79">
         <v>2.63</v>
@@ -17731,7 +17740,7 @@
         <v>1</v>
       </c>
       <c r="AP80">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ80">
         <v>0.91</v>
@@ -17859,7 +17868,7 @@
         <v>145</v>
       </c>
       <c r="P81" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q81">
         <v>3.2</v>
@@ -18352,7 +18361,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ83">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR83">
         <v>1.52</v>
@@ -18889,7 +18898,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19095,7 +19104,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19301,7 +19310,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19507,7 +19516,7 @@
         <v>90</v>
       </c>
       <c r="P89" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19997,7 +20006,7 @@
         <v>0.75</v>
       </c>
       <c r="AP91">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ91">
         <v>1.42</v>
@@ -20125,7 +20134,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q92">
         <v>4</v>
@@ -20331,7 +20340,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q93">
         <v>3</v>
@@ -20537,7 +20546,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q94">
         <v>2.3</v>
@@ -20743,7 +20752,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q95">
         <v>3.5</v>
@@ -20821,7 +20830,7 @@
         <v>1.75</v>
       </c>
       <c r="AP95">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ95">
         <v>2.09</v>
@@ -21155,7 +21164,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q97">
         <v>3.25</v>
@@ -21648,7 +21657,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ99">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR99">
         <v>1.86</v>
@@ -21773,7 +21782,7 @@
         <v>157</v>
       </c>
       <c r="P100" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q100">
         <v>2.6</v>
@@ -21979,7 +21988,7 @@
         <v>122</v>
       </c>
       <c r="P101" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q101">
         <v>3.25</v>
@@ -22185,7 +22194,7 @@
         <v>158</v>
       </c>
       <c r="P102" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q102">
         <v>2.25</v>
@@ -22803,7 +22812,7 @@
         <v>160</v>
       </c>
       <c r="P105" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q105">
         <v>2.38</v>
@@ -23009,7 +23018,7 @@
         <v>90</v>
       </c>
       <c r="P106" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23215,7 +23224,7 @@
         <v>90</v>
       </c>
       <c r="P107" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q107">
         <v>3.25</v>
@@ -23421,7 +23430,7 @@
         <v>161</v>
       </c>
       <c r="P108" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23502,7 +23511,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ108">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR108">
         <v>1.33</v>
@@ -23627,7 +23636,7 @@
         <v>162</v>
       </c>
       <c r="P109" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q109">
         <v>2.3</v>
@@ -24039,7 +24048,7 @@
         <v>122</v>
       </c>
       <c r="P111" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q111">
         <v>4</v>
@@ -24326,7 +24335,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ112">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR112">
         <v>1.39</v>
@@ -24451,7 +24460,7 @@
         <v>164</v>
       </c>
       <c r="P113" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q113">
         <v>3.6</v>
@@ -24863,7 +24872,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q115">
         <v>3.75</v>
@@ -25069,7 +25078,7 @@
         <v>165</v>
       </c>
       <c r="P116" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q116">
         <v>3.25</v>
@@ -25765,7 +25774,7 @@
         <v>2.4</v>
       </c>
       <c r="AP119">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ119">
         <v>1.64</v>
@@ -26099,7 +26108,7 @@
         <v>167</v>
       </c>
       <c r="P121" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q121">
         <v>3.4</v>
@@ -26177,7 +26186,7 @@
         <v>0.6</v>
       </c>
       <c r="AP121">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ121">
         <v>1.18</v>
@@ -26511,7 +26520,7 @@
         <v>169</v>
       </c>
       <c r="P123" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q123">
         <v>3.4</v>
@@ -26717,7 +26726,7 @@
         <v>90</v>
       </c>
       <c r="P124" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q124">
         <v>4</v>
@@ -27335,7 +27344,7 @@
         <v>171</v>
       </c>
       <c r="P127" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27416,7 +27425,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ127">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR127">
         <v>1.52</v>
@@ -27541,7 +27550,7 @@
         <v>90</v>
       </c>
       <c r="P128" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q128">
         <v>2.88</v>
@@ -27747,7 +27756,7 @@
         <v>172</v>
       </c>
       <c r="P129" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -27953,7 +27962,7 @@
         <v>90</v>
       </c>
       <c r="P130" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q130">
         <v>3.4</v>
@@ -28159,7 +28168,7 @@
         <v>173</v>
       </c>
       <c r="P131" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q131">
         <v>2.1</v>
@@ -28365,7 +28374,7 @@
         <v>174</v>
       </c>
       <c r="P132" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q132">
         <v>2.5</v>
@@ -28571,7 +28580,7 @@
         <v>175</v>
       </c>
       <c r="P133" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q133">
         <v>4</v>
@@ -28777,7 +28786,7 @@
         <v>176</v>
       </c>
       <c r="P134" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q134">
         <v>3.4</v>
@@ -28983,7 +28992,7 @@
         <v>177</v>
       </c>
       <c r="P135" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -29064,7 +29073,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ135">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR135">
         <v>1.52</v>
@@ -29395,7 +29404,7 @@
         <v>179</v>
       </c>
       <c r="P137" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q137">
         <v>4</v>
@@ -29473,7 +29482,7 @@
         <v>1.17</v>
       </c>
       <c r="AP137">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ137">
         <v>1.09</v>
@@ -29601,7 +29610,7 @@
         <v>90</v>
       </c>
       <c r="P138" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q138">
         <v>3.75</v>
@@ -29679,7 +29688,7 @@
         <v>2.33</v>
       </c>
       <c r="AP138">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ138">
         <v>1.9</v>
@@ -29807,7 +29816,7 @@
         <v>90</v>
       </c>
       <c r="P139" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q139">
         <v>3</v>
@@ -30013,7 +30022,7 @@
         <v>90</v>
       </c>
       <c r="P140" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q140">
         <v>3</v>
@@ -30219,7 +30228,7 @@
         <v>180</v>
       </c>
       <c r="P141" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30631,7 +30640,7 @@
         <v>182</v>
       </c>
       <c r="P143" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q143">
         <v>3.1</v>
@@ -31124,7 +31133,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ145">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR145">
         <v>2.16</v>
@@ -31455,7 +31464,7 @@
         <v>90</v>
       </c>
       <c r="P147" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q147">
         <v>3.1</v>
@@ -32279,7 +32288,7 @@
         <v>186</v>
       </c>
       <c r="P151" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q151">
         <v>2.38</v>
@@ -32357,7 +32366,7 @@
         <v>1.17</v>
       </c>
       <c r="AP151">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ151">
         <v>1.18</v>
@@ -32897,7 +32906,7 @@
         <v>187</v>
       </c>
       <c r="P154" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q154">
         <v>3.4</v>
@@ -34008,7 +34017,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ159">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR159">
         <v>1.33</v>
@@ -34133,7 +34142,7 @@
         <v>141</v>
       </c>
       <c r="P160" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q160">
         <v>3.75</v>
@@ -34339,7 +34348,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q161">
         <v>4.75</v>
@@ -34417,7 +34426,7 @@
         <v>1.5</v>
       </c>
       <c r="AP161">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ161">
         <v>1.73</v>
@@ -34545,7 +34554,7 @@
         <v>180</v>
       </c>
       <c r="P162" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q162">
         <v>3.75</v>
@@ -34957,7 +34966,7 @@
         <v>191</v>
       </c>
       <c r="P164" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q164">
         <v>3.1</v>
@@ -35038,7 +35047,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ164">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR164">
         <v>1.35</v>
@@ -35369,7 +35378,7 @@
         <v>90</v>
       </c>
       <c r="P166" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q166">
         <v>2.75</v>
@@ -35781,7 +35790,7 @@
         <v>193</v>
       </c>
       <c r="P168" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q168">
         <v>2.75</v>
@@ -35859,7 +35868,7 @@
         <v>0.78</v>
       </c>
       <c r="AP168">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ168">
         <v>1.17</v>
@@ -35987,7 +35996,7 @@
         <v>194</v>
       </c>
       <c r="P169" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36274,7 +36283,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ170">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR170">
         <v>1.44</v>
@@ -36399,7 +36408,7 @@
         <v>196</v>
       </c>
       <c r="P171" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q171">
         <v>2.75</v>
@@ -36480,7 +36489,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ171">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR171">
         <v>1.8</v>
@@ -36811,7 +36820,7 @@
         <v>197</v>
       </c>
       <c r="P173" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q173">
         <v>3</v>
@@ -37841,7 +37850,7 @@
         <v>200</v>
       </c>
       <c r="P178" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q178">
         <v>3.4</v>
@@ -38253,7 +38262,7 @@
         <v>202</v>
       </c>
       <c r="P180" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q180">
         <v>2</v>
@@ -38459,7 +38468,7 @@
         <v>90</v>
       </c>
       <c r="P181" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q181">
         <v>4</v>
@@ -39077,7 +39086,7 @@
         <v>204</v>
       </c>
       <c r="P184" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39283,7 +39292,7 @@
         <v>205</v>
       </c>
       <c r="P185" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q185">
         <v>3.2</v>
@@ -39489,7 +39498,7 @@
         <v>206</v>
       </c>
       <c r="P186" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -39695,7 +39704,7 @@
         <v>207</v>
       </c>
       <c r="P187" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q187">
         <v>2.8</v>
@@ -40107,7 +40116,7 @@
         <v>180</v>
       </c>
       <c r="P189" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q189">
         <v>2.88</v>
@@ -40519,7 +40528,7 @@
         <v>209</v>
       </c>
       <c r="P191" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -40931,7 +40940,7 @@
         <v>101</v>
       </c>
       <c r="P193" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q193">
         <v>3.1</v>
@@ -41215,7 +41224,7 @@
         <v>0.67</v>
       </c>
       <c r="AP194">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ194">
         <v>0.55</v>
@@ -41343,7 +41352,7 @@
         <v>212</v>
       </c>
       <c r="P195" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q195">
         <v>3.25</v>
@@ -41961,7 +41970,7 @@
         <v>90</v>
       </c>
       <c r="P198" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q198">
         <v>2.6</v>
@@ -42042,7 +42051,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ198">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR198">
         <v>1.63</v>
@@ -42167,7 +42176,7 @@
         <v>202</v>
       </c>
       <c r="P199" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q199">
         <v>3.3</v>
@@ -42245,7 +42254,7 @@
         <v>1.11</v>
       </c>
       <c r="AP199">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ199">
         <v>1.45</v>
@@ -42373,7 +42382,7 @@
         <v>214</v>
       </c>
       <c r="P200" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q200">
         <v>3.4</v>
@@ -42454,7 +42463,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ200">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR200">
         <v>1.56</v>
@@ -42785,7 +42794,7 @@
         <v>215</v>
       </c>
       <c r="P202" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q202">
         <v>2.59</v>
@@ -43815,7 +43824,7 @@
         <v>96</v>
       </c>
       <c r="P207" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q207">
         <v>2.88</v>
@@ -44227,7 +44236,7 @@
         <v>218</v>
       </c>
       <c r="P209" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q209">
         <v>3.78</v>
@@ -45051,7 +45060,7 @@
         <v>90</v>
       </c>
       <c r="P213" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q213">
         <v>3.7</v>
@@ -45463,7 +45472,7 @@
         <v>90</v>
       </c>
       <c r="P215" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q215">
         <v>2.25</v>
@@ -45669,7 +45678,7 @@
         <v>193</v>
       </c>
       <c r="P216" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q216">
         <v>2.5</v>
@@ -45875,7 +45884,7 @@
         <v>90</v>
       </c>
       <c r="P217" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q217">
         <v>2.75</v>
@@ -46081,7 +46090,7 @@
         <v>90</v>
       </c>
       <c r="P218" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q218">
         <v>2.4</v>
@@ -46287,7 +46296,7 @@
         <v>219</v>
       </c>
       <c r="P219" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q219">
         <v>2.8</v>
@@ -46444,6 +46453,418 @@
       </c>
       <c r="BP219">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="220" spans="1:68">
+      <c r="A220" s="1">
+        <v>219</v>
+      </c>
+      <c r="B220">
+        <v>7778709</v>
+      </c>
+      <c r="C220" t="s">
+        <v>68</v>
+      </c>
+      <c r="D220" t="s">
+        <v>69</v>
+      </c>
+      <c r="E220" s="2">
+        <v>45844.25</v>
+      </c>
+      <c r="F220">
+        <v>22</v>
+      </c>
+      <c r="G220" t="s">
+        <v>82</v>
+      </c>
+      <c r="H220" t="s">
+        <v>73</v>
+      </c>
+      <c r="I220">
+        <v>0</v>
+      </c>
+      <c r="J220">
+        <v>0</v>
+      </c>
+      <c r="K220">
+        <v>0</v>
+      </c>
+      <c r="L220">
+        <v>2</v>
+      </c>
+      <c r="M220">
+        <v>0</v>
+      </c>
+      <c r="N220">
+        <v>2</v>
+      </c>
+      <c r="O220" t="s">
+        <v>220</v>
+      </c>
+      <c r="P220" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q220">
+        <v>3.75</v>
+      </c>
+      <c r="R220">
+        <v>2.25</v>
+      </c>
+      <c r="S220">
+        <v>2.75</v>
+      </c>
+      <c r="T220">
+        <v>1.33</v>
+      </c>
+      <c r="U220">
+        <v>3.25</v>
+      </c>
+      <c r="V220">
+        <v>2.63</v>
+      </c>
+      <c r="W220">
+        <v>1.44</v>
+      </c>
+      <c r="X220">
+        <v>7</v>
+      </c>
+      <c r="Y220">
+        <v>1.1</v>
+      </c>
+      <c r="Z220">
+        <v>2.82</v>
+      </c>
+      <c r="AA220">
+        <v>3.28</v>
+      </c>
+      <c r="AB220">
+        <v>2.17</v>
+      </c>
+      <c r="AC220">
+        <v>1</v>
+      </c>
+      <c r="AD220">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE220">
+        <v>1.19</v>
+      </c>
+      <c r="AF220">
+        <v>3.74</v>
+      </c>
+      <c r="AG220">
+        <v>1.76</v>
+      </c>
+      <c r="AH220">
+        <v>1.94</v>
+      </c>
+      <c r="AI220">
+        <v>1.67</v>
+      </c>
+      <c r="AJ220">
+        <v>2.1</v>
+      </c>
+      <c r="AK220">
+        <v>1.66</v>
+      </c>
+      <c r="AL220">
+        <v>1.25</v>
+      </c>
+      <c r="AM220">
+        <v>1.3</v>
+      </c>
+      <c r="AN220">
+        <v>0.82</v>
+      </c>
+      <c r="AO220">
+        <v>1.3</v>
+      </c>
+      <c r="AP220">
+        <v>1</v>
+      </c>
+      <c r="AQ220">
+        <v>1.18</v>
+      </c>
+      <c r="AR220">
+        <v>1.43</v>
+      </c>
+      <c r="AS220">
+        <v>1.28</v>
+      </c>
+      <c r="AT220">
+        <v>2.71</v>
+      </c>
+      <c r="AU220">
+        <v>7</v>
+      </c>
+      <c r="AV220">
+        <v>3</v>
+      </c>
+      <c r="AW220">
+        <v>8</v>
+      </c>
+      <c r="AX220">
+        <v>3</v>
+      </c>
+      <c r="AY220">
+        <v>15</v>
+      </c>
+      <c r="AZ220">
+        <v>6</v>
+      </c>
+      <c r="BA220">
+        <v>6</v>
+      </c>
+      <c r="BB220">
+        <v>5</v>
+      </c>
+      <c r="BC220">
+        <v>11</v>
+      </c>
+      <c r="BD220">
+        <v>1.99</v>
+      </c>
+      <c r="BE220">
+        <v>7.15</v>
+      </c>
+      <c r="BF220">
+        <v>2.28</v>
+      </c>
+      <c r="BG220">
+        <v>1.23</v>
+      </c>
+      <c r="BH220">
+        <v>3.4</v>
+      </c>
+      <c r="BI220">
+        <v>1.48</v>
+      </c>
+      <c r="BJ220">
+        <v>2.42</v>
+      </c>
+      <c r="BK220">
+        <v>1.82</v>
+      </c>
+      <c r="BL220">
+        <v>1.88</v>
+      </c>
+      <c r="BM220">
+        <v>2.3</v>
+      </c>
+      <c r="BN220">
+        <v>1.53</v>
+      </c>
+      <c r="BO220">
+        <v>3.08</v>
+      </c>
+      <c r="BP220">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="221" spans="1:68">
+      <c r="A221" s="1">
+        <v>220</v>
+      </c>
+      <c r="B221">
+        <v>7778706</v>
+      </c>
+      <c r="C221" t="s">
+        <v>68</v>
+      </c>
+      <c r="D221" t="s">
+        <v>69</v>
+      </c>
+      <c r="E221" s="2">
+        <v>45844.29166666666</v>
+      </c>
+      <c r="F221">
+        <v>22</v>
+      </c>
+      <c r="G221" t="s">
+        <v>77</v>
+      </c>
+      <c r="H221" t="s">
+        <v>88</v>
+      </c>
+      <c r="I221">
+        <v>0</v>
+      </c>
+      <c r="J221">
+        <v>1</v>
+      </c>
+      <c r="K221">
+        <v>1</v>
+      </c>
+      <c r="L221">
+        <v>1</v>
+      </c>
+      <c r="M221">
+        <v>3</v>
+      </c>
+      <c r="N221">
+        <v>4</v>
+      </c>
+      <c r="O221" t="s">
+        <v>221</v>
+      </c>
+      <c r="P221" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q221">
+        <v>3.6</v>
+      </c>
+      <c r="R221">
+        <v>2.2</v>
+      </c>
+      <c r="S221">
+        <v>2.75</v>
+      </c>
+      <c r="T221">
+        <v>1.36</v>
+      </c>
+      <c r="U221">
+        <v>3</v>
+      </c>
+      <c r="V221">
+        <v>2.63</v>
+      </c>
+      <c r="W221">
+        <v>1.44</v>
+      </c>
+      <c r="X221">
+        <v>7</v>
+      </c>
+      <c r="Y221">
+        <v>1.1</v>
+      </c>
+      <c r="Z221">
+        <v>2.93</v>
+      </c>
+      <c r="AA221">
+        <v>3.26</v>
+      </c>
+      <c r="AB221">
+        <v>2.12</v>
+      </c>
+      <c r="AC221">
+        <v>1.01</v>
+      </c>
+      <c r="AD221">
+        <v>11</v>
+      </c>
+      <c r="AE221">
+        <v>1.22</v>
+      </c>
+      <c r="AF221">
+        <v>3.5</v>
+      </c>
+      <c r="AG221">
+        <v>1.82</v>
+      </c>
+      <c r="AH221">
+        <v>1.88</v>
+      </c>
+      <c r="AI221">
+        <v>1.67</v>
+      </c>
+      <c r="AJ221">
+        <v>2.1</v>
+      </c>
+      <c r="AK221">
+        <v>1.61</v>
+      </c>
+      <c r="AL221">
+        <v>1.26</v>
+      </c>
+      <c r="AM221">
+        <v>1.32</v>
+      </c>
+      <c r="AN221">
+        <v>0.5</v>
+      </c>
+      <c r="AO221">
+        <v>1</v>
+      </c>
+      <c r="AP221">
+        <v>0.45</v>
+      </c>
+      <c r="AQ221">
+        <v>1.15</v>
+      </c>
+      <c r="AR221">
+        <v>1.19</v>
+      </c>
+      <c r="AS221">
+        <v>1.36</v>
+      </c>
+      <c r="AT221">
+        <v>2.55</v>
+      </c>
+      <c r="AU221">
+        <v>3</v>
+      </c>
+      <c r="AV221">
+        <v>4</v>
+      </c>
+      <c r="AW221">
+        <v>5</v>
+      </c>
+      <c r="AX221">
+        <v>13</v>
+      </c>
+      <c r="AY221">
+        <v>8</v>
+      </c>
+      <c r="AZ221">
+        <v>17</v>
+      </c>
+      <c r="BA221">
+        <v>2</v>
+      </c>
+      <c r="BB221">
+        <v>9</v>
+      </c>
+      <c r="BC221">
+        <v>11</v>
+      </c>
+      <c r="BD221">
+        <v>2.43</v>
+      </c>
+      <c r="BE221">
+        <v>7.38</v>
+      </c>
+      <c r="BF221">
+        <v>1.89</v>
+      </c>
+      <c r="BG221">
+        <v>1.16</v>
+      </c>
+      <c r="BH221">
+        <v>4.04</v>
+      </c>
+      <c r="BI221">
+        <v>1.36</v>
+      </c>
+      <c r="BJ221">
+        <v>2.76</v>
+      </c>
+      <c r="BK221">
+        <v>1.66</v>
+      </c>
+      <c r="BL221">
+        <v>2.09</v>
+      </c>
+      <c r="BM221">
+        <v>2.05</v>
+      </c>
+      <c r="BN221">
+        <v>1.68</v>
+      </c>
+      <c r="BO221">
+        <v>2.64</v>
+      </c>
+      <c r="BP221">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Japan J2 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="330">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -682,6 +682,24 @@
     <t>['90+7']</t>
   </si>
   <si>
+    <t>['25', '45+1', '45+4']</t>
+  </si>
+  <si>
+    <t>['69']</t>
+  </si>
+  <si>
+    <t>['56', '64', '79']</t>
+  </si>
+  <si>
+    <t>['85']</t>
+  </si>
+  <si>
+    <t>['18', '59']</t>
+  </si>
+  <si>
+    <t>['6', '29', '31', '68', '90+3']</t>
+  </si>
+  <si>
     <t>['31', '60']</t>
   </si>
   <si>
@@ -859,9 +877,6 @@
     <t>['61']</t>
   </si>
   <si>
-    <t>['69']</t>
-  </si>
-  <si>
     <t>['46', '55']</t>
   </si>
   <si>
@@ -977,6 +992,18 @@
   </si>
   <si>
     <t>['16', '72', '82']</t>
+  </si>
+  <si>
+    <t>['43', '51']</t>
+  </si>
+  <si>
+    <t>['81']</t>
+  </si>
+  <si>
+    <t>['46']</t>
+  </si>
+  <si>
+    <t>['45+2']</t>
   </si>
 </sst>
 </file>
@@ -1338,7 +1365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP221"/>
+  <dimension ref="A1:BP231"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1594,7 +1621,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="Q2">
         <v>3.6</v>
@@ -1672,10 +1699,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ2">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2084,7 +2111,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ4">
         <v>0.55</v>
@@ -2212,7 +2239,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2290,7 +2317,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ5">
         <v>1.9</v>
@@ -2418,7 +2445,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="Q6">
         <v>4.1</v>
@@ -2496,10 +2523,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ6">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2702,10 +2729,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ7">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2830,7 +2857,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Q8">
         <v>2.28</v>
@@ -2911,7 +2938,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ8">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3117,7 +3144,7 @@
         <v>0.45</v>
       </c>
       <c r="AQ9">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3320,7 +3347,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ10">
         <v>1.17</v>
@@ -3529,7 +3556,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ11">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3732,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ12">
         <v>1.4</v>
@@ -3941,7 +3968,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ13">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4272,7 +4299,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="Q15">
         <v>4.1</v>
@@ -4350,10 +4377,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ15">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4559,7 +4586,7 @@
         <v>1</v>
       </c>
       <c r="AQ16">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4765,7 +4792,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ17">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4968,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ18">
         <v>1.15</v>
@@ -5174,7 +5201,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ19">
         <v>1.18</v>
@@ -5508,7 +5535,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="Q21">
         <v>4.4</v>
@@ -5795,7 +5822,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ22">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5920,7 +5947,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5998,7 +6025,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ23">
         <v>1.9</v>
@@ -6332,7 +6359,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -6616,7 +6643,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ26">
         <v>1.17</v>
@@ -6744,7 +6771,7 @@
         <v>90</v>
       </c>
       <c r="P27" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="Q27">
         <v>3.2</v>
@@ -6825,7 +6852,7 @@
         <v>1</v>
       </c>
       <c r="AQ27">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR27">
         <v>1.59</v>
@@ -7028,10 +7055,10 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ28">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR28">
         <v>2.36</v>
@@ -7440,10 +7467,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ30">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR30">
         <v>1.54</v>
@@ -7646,10 +7673,10 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ31">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR31">
         <v>1.27</v>
@@ -7774,7 +7801,7 @@
         <v>113</v>
       </c>
       <c r="P32" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="Q32">
         <v>3.45</v>
@@ -7855,7 +7882,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ32">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR32">
         <v>1.26</v>
@@ -7980,7 +8007,7 @@
         <v>114</v>
       </c>
       <c r="P33" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8186,7 +8213,7 @@
         <v>115</v>
       </c>
       <c r="P34" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8392,7 +8419,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="Q35">
         <v>3.4</v>
@@ -8473,7 +8500,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ35">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR35">
         <v>0</v>
@@ -8598,7 +8625,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="Q36">
         <v>2.8</v>
@@ -8676,7 +8703,7 @@
         <v>2</v>
       </c>
       <c r="AP36">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ36">
         <v>1.17</v>
@@ -8882,7 +8909,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ37">
         <v>1.4</v>
@@ -9010,7 +9037,7 @@
         <v>118</v>
       </c>
       <c r="P38" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="Q38">
         <v>2.6</v>
@@ -9088,7 +9115,7 @@
         <v>1</v>
       </c>
       <c r="AP38">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ38">
         <v>1.18</v>
@@ -9503,7 +9530,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ40">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR40">
         <v>1.47</v>
@@ -9834,7 +9861,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9912,10 +9939,10 @@
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ42">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR42">
         <v>0</v>
@@ -10118,7 +10145,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ43">
         <v>1.09</v>
@@ -10324,7 +10351,7 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ44">
         <v>1.42</v>
@@ -10530,10 +10557,10 @@
         <v>3</v>
       </c>
       <c r="AP45">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ45">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR45">
         <v>1.47</v>
@@ -10739,7 +10766,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ46">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR46">
         <v>2.49</v>
@@ -10864,7 +10891,7 @@
         <v>105</v>
       </c>
       <c r="P47" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -11070,7 +11097,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="Q48">
         <v>3.6</v>
@@ -11148,10 +11175,10 @@
         <v>1.5</v>
       </c>
       <c r="AP48">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ48">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR48">
         <v>1.52</v>
@@ -11276,7 +11303,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="Q49">
         <v>3.6</v>
@@ -11354,10 +11381,10 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ49">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR49">
         <v>1.15</v>
@@ -11560,10 +11587,10 @@
         <v>1.5</v>
       </c>
       <c r="AP50">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ50">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR50">
         <v>1.08</v>
@@ -11688,7 +11715,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="Q51">
         <v>1.91</v>
@@ -11769,7 +11796,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ51">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR51">
         <v>1.69</v>
@@ -11894,7 +11921,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -12100,7 +12127,7 @@
         <v>90</v>
       </c>
       <c r="P53" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12178,10 +12205,10 @@
         <v>0.5</v>
       </c>
       <c r="AP53">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ53">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR53">
         <v>1.15</v>
@@ -12590,10 +12617,10 @@
         <v>1.33</v>
       </c>
       <c r="AP55">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ55">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR55">
         <v>1.39</v>
@@ -12718,7 +12745,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="Q56">
         <v>4.33</v>
@@ -12799,7 +12826,7 @@
         <v>0.45</v>
       </c>
       <c r="AQ56">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR56">
         <v>1.03</v>
@@ -13002,7 +13029,7 @@
         <v>3</v>
       </c>
       <c r="AP57">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ57">
         <v>1.9</v>
@@ -13336,7 +13363,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13620,10 +13647,10 @@
         <v>1.33</v>
       </c>
       <c r="AP60">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ60">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR60">
         <v>1.48</v>
@@ -13748,7 +13775,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13826,10 +13853,10 @@
         <v>3</v>
       </c>
       <c r="AP61">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ61">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR61">
         <v>1.1</v>
@@ -13954,7 +13981,7 @@
         <v>90</v>
       </c>
       <c r="P62" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="Q62">
         <v>2.75</v>
@@ -14444,7 +14471,7 @@
         <v>0.5</v>
       </c>
       <c r="AP64">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ64">
         <v>1.09</v>
@@ -14572,7 +14599,7 @@
         <v>90</v>
       </c>
       <c r="P65" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="Q65">
         <v>3.6</v>
@@ -14653,7 +14680,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ65">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR65">
         <v>1.13</v>
@@ -14778,7 +14805,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="Q66">
         <v>4.75</v>
@@ -14856,10 +14883,10 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ66">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR66">
         <v>1.04</v>
@@ -14984,7 +15011,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="Q67">
         <v>2.88</v>
@@ -15062,7 +15089,7 @@
         <v>0.75</v>
       </c>
       <c r="AP67">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ67">
         <v>1.15</v>
@@ -15268,7 +15295,7 @@
         <v>0</v>
       </c>
       <c r="AP68">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ68">
         <v>0.55</v>
@@ -15474,10 +15501,10 @@
         <v>3</v>
       </c>
       <c r="AP69">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ69">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR69">
         <v>1.3</v>
@@ -15683,7 +15710,7 @@
         <v>0.45</v>
       </c>
       <c r="AQ70">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR70">
         <v>1.09</v>
@@ -15889,7 +15916,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ71">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR71">
         <v>1.39</v>
@@ -16298,7 +16325,7 @@
         <v>0.33</v>
       </c>
       <c r="AP73">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ73">
         <v>1.09</v>
@@ -16504,10 +16531,10 @@
         <v>0.5</v>
       </c>
       <c r="AP74">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ74">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR74">
         <v>1.3</v>
@@ -16916,7 +16943,7 @@
         <v>1</v>
       </c>
       <c r="AP76">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ76">
         <v>1.18</v>
@@ -17122,7 +17149,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ77">
         <v>1.18</v>
@@ -17331,7 +17358,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ78">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR78">
         <v>1.6</v>
@@ -17456,7 +17483,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="Q79">
         <v>2.63</v>
@@ -17537,7 +17564,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ79">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR79">
         <v>2.01</v>
@@ -17743,7 +17770,7 @@
         <v>1</v>
       </c>
       <c r="AQ80">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR80">
         <v>1.56</v>
@@ -17868,7 +17895,7 @@
         <v>145</v>
       </c>
       <c r="P81" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="Q81">
         <v>3.2</v>
@@ -17946,10 +17973,10 @@
         <v>0.67</v>
       </c>
       <c r="AP81">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ81">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR81">
         <v>1.55</v>
@@ -18358,7 +18385,7 @@
         <v>0.8</v>
       </c>
       <c r="AP83">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ83">
         <v>1.15</v>
@@ -18564,10 +18591,10 @@
         <v>1.2</v>
       </c>
       <c r="AP84">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ84">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR84">
         <v>1.56</v>
@@ -18773,7 +18800,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ85">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR85">
         <v>1.08</v>
@@ -18898,7 +18925,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -18976,10 +19003,10 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ86">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR86">
         <v>1.94</v>
@@ -19104,7 +19131,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19310,7 +19337,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19388,10 +19415,10 @@
         <v>2.25</v>
       </c>
       <c r="AP88">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ88">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR88">
         <v>1.22</v>
@@ -19516,7 +19543,7 @@
         <v>90</v>
       </c>
       <c r="P89" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19800,10 +19827,10 @@
         <v>1.33</v>
       </c>
       <c r="AP90">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ90">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR90">
         <v>1.26</v>
@@ -20134,7 +20161,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="Q92">
         <v>4</v>
@@ -20212,10 +20239,10 @@
         <v>0.5</v>
       </c>
       <c r="AP92">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ92">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR92">
         <v>1.1</v>
@@ -20340,7 +20367,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="Q93">
         <v>3</v>
@@ -20418,7 +20445,7 @@
         <v>0.25</v>
       </c>
       <c r="AP93">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ93">
         <v>0.55</v>
@@ -20546,7 +20573,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="Q94">
         <v>2.3</v>
@@ -20624,10 +20651,10 @@
         <v>0.67</v>
       </c>
       <c r="AP94">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ94">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR94">
         <v>1.38</v>
@@ -20752,7 +20779,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="Q95">
         <v>3.5</v>
@@ -20833,7 +20860,7 @@
         <v>1</v>
       </c>
       <c r="AQ95">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR95">
         <v>1.47</v>
@@ -21036,10 +21063,10 @@
         <v>1.5</v>
       </c>
       <c r="AP96">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ96">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR96">
         <v>1.52</v>
@@ -21164,7 +21191,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="Q97">
         <v>3.25</v>
@@ -21451,7 +21478,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ98">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR98">
         <v>1.74</v>
@@ -21654,7 +21681,7 @@
         <v>1</v>
       </c>
       <c r="AP99">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ99">
         <v>1.18</v>
@@ -21782,7 +21809,7 @@
         <v>157</v>
       </c>
       <c r="P100" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="Q100">
         <v>2.6</v>
@@ -21988,7 +22015,7 @@
         <v>122</v>
       </c>
       <c r="P101" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="Q101">
         <v>3.25</v>
@@ -22194,7 +22221,7 @@
         <v>158</v>
       </c>
       <c r="P102" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="Q102">
         <v>2.25</v>
@@ -22275,7 +22302,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ102">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR102">
         <v>1.46</v>
@@ -22478,7 +22505,7 @@
         <v>0.8</v>
       </c>
       <c r="AP103">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ103">
         <v>1.42</v>
@@ -22687,7 +22714,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ104">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR104">
         <v>1.89</v>
@@ -22812,7 +22839,7 @@
         <v>160</v>
       </c>
       <c r="P105" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="Q105">
         <v>2.38</v>
@@ -23018,7 +23045,7 @@
         <v>90</v>
       </c>
       <c r="P106" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23096,10 +23123,10 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ106">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR106">
         <v>1.3</v>
@@ -23224,7 +23251,7 @@
         <v>90</v>
       </c>
       <c r="P107" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="Q107">
         <v>3.25</v>
@@ -23302,10 +23329,10 @@
         <v>1.25</v>
       </c>
       <c r="AP107">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ107">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR107">
         <v>1.3</v>
@@ -23430,7 +23457,7 @@
         <v>161</v>
       </c>
       <c r="P108" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="Q108">
         <v>3.4</v>
@@ -23508,7 +23535,7 @@
         <v>1.17</v>
       </c>
       <c r="AP108">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ108">
         <v>1.15</v>
@@ -23636,7 +23663,7 @@
         <v>162</v>
       </c>
       <c r="P109" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="Q109">
         <v>2.3</v>
@@ -23923,7 +23950,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ110">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR110">
         <v>1.34</v>
@@ -24048,7 +24075,7 @@
         <v>122</v>
       </c>
       <c r="P111" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="Q111">
         <v>4</v>
@@ -24126,7 +24153,7 @@
         <v>2.5</v>
       </c>
       <c r="AP111">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ111">
         <v>1.9</v>
@@ -24460,7 +24487,7 @@
         <v>164</v>
       </c>
       <c r="P113" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="Q113">
         <v>3.6</v>
@@ -24538,10 +24565,10 @@
         <v>2</v>
       </c>
       <c r="AP113">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ113">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR113">
         <v>1.23</v>
@@ -24744,7 +24771,7 @@
         <v>2.6</v>
       </c>
       <c r="AP114">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ114">
         <v>1.9</v>
@@ -24872,7 +24899,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="Q115">
         <v>3.75</v>
@@ -24950,10 +24977,10 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ115">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR115">
         <v>1.85</v>
@@ -25078,7 +25105,7 @@
         <v>165</v>
       </c>
       <c r="P116" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="Q116">
         <v>3.25</v>
@@ -25159,7 +25186,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ116">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR116">
         <v>1.54</v>
@@ -25568,10 +25595,10 @@
         <v>1.4</v>
       </c>
       <c r="AP118">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ118">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR118">
         <v>1.57</v>
@@ -25777,7 +25804,7 @@
         <v>1</v>
       </c>
       <c r="AQ119">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR119">
         <v>1.4</v>
@@ -25980,7 +26007,7 @@
         <v>0.4</v>
       </c>
       <c r="AP120">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ120">
         <v>0.55</v>
@@ -26108,7 +26135,7 @@
         <v>167</v>
       </c>
       <c r="P121" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="Q121">
         <v>3.4</v>
@@ -26520,7 +26547,7 @@
         <v>169</v>
       </c>
       <c r="P123" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="Q123">
         <v>3.4</v>
@@ -26598,7 +26625,7 @@
         <v>0.86</v>
       </c>
       <c r="AP123">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ123">
         <v>1.17</v>
@@ -26726,7 +26753,7 @@
         <v>90</v>
       </c>
       <c r="P124" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="Q124">
         <v>4</v>
@@ -26804,10 +26831,10 @@
         <v>1.29</v>
       </c>
       <c r="AP124">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ124">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR124">
         <v>1.17</v>
@@ -27013,7 +27040,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ125">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR125">
         <v>1.1</v>
@@ -27216,10 +27243,10 @@
         <v>2.17</v>
       </c>
       <c r="AP126">
+        <v>1.85</v>
+      </c>
+      <c r="AQ126">
         <v>1.75</v>
-      </c>
-      <c r="AQ126">
-        <v>1.64</v>
       </c>
       <c r="AR126">
         <v>1.32</v>
@@ -27344,7 +27371,7 @@
         <v>171</v>
       </c>
       <c r="P127" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27422,7 +27449,7 @@
         <v>0.8</v>
       </c>
       <c r="AP127">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ127">
         <v>1.18</v>
@@ -27550,7 +27577,7 @@
         <v>90</v>
       </c>
       <c r="P128" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="Q128">
         <v>2.88</v>
@@ -27628,10 +27655,10 @@
         <v>0.86</v>
       </c>
       <c r="AP128">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ128">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR128">
         <v>1.41</v>
@@ -27756,7 +27783,7 @@
         <v>172</v>
       </c>
       <c r="P129" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -27837,7 +27864,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ129">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR129">
         <v>1.79</v>
@@ -27962,7 +27989,7 @@
         <v>90</v>
       </c>
       <c r="P130" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="Q130">
         <v>3.4</v>
@@ -28040,7 +28067,7 @@
         <v>0.8</v>
       </c>
       <c r="AP130">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ130">
         <v>1.9</v>
@@ -28168,7 +28195,7 @@
         <v>173</v>
       </c>
       <c r="P131" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="Q131">
         <v>2.1</v>
@@ -28249,7 +28276,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ131">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR131">
         <v>2.03</v>
@@ -28374,7 +28401,7 @@
         <v>174</v>
       </c>
       <c r="P132" t="s">
-        <v>281</v>
+        <v>223</v>
       </c>
       <c r="Q132">
         <v>2.5</v>
@@ -28580,7 +28607,7 @@
         <v>175</v>
       </c>
       <c r="P133" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="Q133">
         <v>4</v>
@@ -28661,7 +28688,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ133">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR133">
         <v>1.27</v>
@@ -28786,7 +28813,7 @@
         <v>176</v>
       </c>
       <c r="P134" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="Q134">
         <v>3.4</v>
@@ -28864,7 +28891,7 @@
         <v>1.17</v>
       </c>
       <c r="AP134">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ134">
         <v>1.9</v>
@@ -28992,7 +29019,7 @@
         <v>177</v>
       </c>
       <c r="P135" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -29276,10 +29303,10 @@
         <v>1.33</v>
       </c>
       <c r="AP136">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ136">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR136">
         <v>1.4</v>
@@ -29404,7 +29431,7 @@
         <v>179</v>
       </c>
       <c r="P137" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="Q137">
         <v>4</v>
@@ -29610,7 +29637,7 @@
         <v>90</v>
       </c>
       <c r="P138" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="Q138">
         <v>3.75</v>
@@ -29816,7 +29843,7 @@
         <v>90</v>
       </c>
       <c r="P139" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="Q139">
         <v>3</v>
@@ -29894,7 +29921,7 @@
         <v>0.83</v>
       </c>
       <c r="AP139">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ139">
         <v>1.42</v>
@@ -30022,7 +30049,7 @@
         <v>90</v>
       </c>
       <c r="P140" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="Q140">
         <v>3</v>
@@ -30228,7 +30255,7 @@
         <v>180</v>
       </c>
       <c r="P141" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30309,7 +30336,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ141">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR141">
         <v>1.59</v>
@@ -30515,7 +30542,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ142">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR142">
         <v>1.79</v>
@@ -30640,7 +30667,7 @@
         <v>182</v>
       </c>
       <c r="P143" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="Q143">
         <v>3.1</v>
@@ -30718,10 +30745,10 @@
         <v>1.13</v>
       </c>
       <c r="AP143">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ143">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR143">
         <v>1.61</v>
@@ -30924,7 +30951,7 @@
         <v>0.86</v>
       </c>
       <c r="AP144">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ144">
         <v>1.18</v>
@@ -31336,7 +31363,7 @@
         <v>1.14</v>
       </c>
       <c r="AP146">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ146">
         <v>1.42</v>
@@ -31464,7 +31491,7 @@
         <v>90</v>
       </c>
       <c r="P147" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="Q147">
         <v>3.1</v>
@@ -31542,10 +31569,10 @@
         <v>2</v>
       </c>
       <c r="AP147">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ147">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR147">
         <v>1.55</v>
@@ -31748,7 +31775,7 @@
         <v>0.88</v>
       </c>
       <c r="AP148">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ148">
         <v>1.17</v>
@@ -32163,7 +32190,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ150">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR150">
         <v>1.24</v>
@@ -32288,7 +32315,7 @@
         <v>186</v>
       </c>
       <c r="P151" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Q151">
         <v>2.38</v>
@@ -32369,7 +32396,7 @@
         <v>1</v>
       </c>
       <c r="AQ151">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR151">
         <v>1.46</v>
@@ -32572,7 +32599,7 @@
         <v>2.43</v>
       </c>
       <c r="AP152">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ152">
         <v>1.9</v>
@@ -32781,7 +32808,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ153">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR153">
         <v>1.56</v>
@@ -32906,7 +32933,7 @@
         <v>187</v>
       </c>
       <c r="P154" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="Q154">
         <v>3.4</v>
@@ -32984,7 +33011,7 @@
         <v>1.17</v>
       </c>
       <c r="AP154">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ154">
         <v>1.4</v>
@@ -33190,10 +33217,10 @@
         <v>1.33</v>
       </c>
       <c r="AP155">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ155">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR155">
         <v>1.71</v>
@@ -33399,7 +33426,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ156">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR156">
         <v>1.69</v>
@@ -33602,7 +33629,7 @@
         <v>1.14</v>
       </c>
       <c r="AP157">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ157">
         <v>1.09</v>
@@ -33808,10 +33835,10 @@
         <v>1.43</v>
       </c>
       <c r="AP158">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ158">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR158">
         <v>1.44</v>
@@ -34014,7 +34041,7 @@
         <v>1</v>
       </c>
       <c r="AP159">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ159">
         <v>1.15</v>
@@ -34142,7 +34169,7 @@
         <v>141</v>
       </c>
       <c r="P160" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="Q160">
         <v>3.75</v>
@@ -34223,7 +34250,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ160">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR160">
         <v>1.07</v>
@@ -34348,7 +34375,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="Q161">
         <v>4.75</v>
@@ -34429,7 +34456,7 @@
         <v>0.45</v>
       </c>
       <c r="AQ161">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR161">
         <v>1.16</v>
@@ -34554,7 +34581,7 @@
         <v>180</v>
       </c>
       <c r="P162" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="Q162">
         <v>3.75</v>
@@ -34632,10 +34659,10 @@
         <v>1.75</v>
       </c>
       <c r="AP162">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ162">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR162">
         <v>1.61</v>
@@ -34841,7 +34868,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ163">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR163">
         <v>2.07</v>
@@ -34966,7 +34993,7 @@
         <v>191</v>
       </c>
       <c r="P164" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="Q164">
         <v>3.1</v>
@@ -35250,10 +35277,10 @@
         <v>1.11</v>
       </c>
       <c r="AP165">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ165">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR165">
         <v>1.25</v>
@@ -35378,7 +35405,7 @@
         <v>90</v>
       </c>
       <c r="P166" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="Q166">
         <v>2.75</v>
@@ -35456,7 +35483,7 @@
         <v>1.13</v>
       </c>
       <c r="AP166">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ166">
         <v>1.42</v>
@@ -35662,7 +35689,7 @@
         <v>0.75</v>
       </c>
       <c r="AP167">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ167">
         <v>1.18</v>
@@ -35790,7 +35817,7 @@
         <v>193</v>
       </c>
       <c r="P168" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="Q168">
         <v>2.75</v>
@@ -35996,7 +36023,7 @@
         <v>194</v>
       </c>
       <c r="P169" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36074,10 +36101,10 @@
         <v>1.14</v>
       </c>
       <c r="AP169">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ169">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR169">
         <v>1.3</v>
@@ -36280,7 +36307,7 @@
         <v>0.9</v>
       </c>
       <c r="AP170">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ170">
         <v>1.15</v>
@@ -36408,7 +36435,7 @@
         <v>196</v>
       </c>
       <c r="P171" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="Q171">
         <v>2.75</v>
@@ -36820,7 +36847,7 @@
         <v>197</v>
       </c>
       <c r="P173" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="Q173">
         <v>3</v>
@@ -36898,10 +36925,10 @@
         <v>0.75</v>
       </c>
       <c r="AP173">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ173">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR173">
         <v>1.56</v>
@@ -37107,7 +37134,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ174">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR174">
         <v>1.5</v>
@@ -37310,10 +37337,10 @@
         <v>1.25</v>
       </c>
       <c r="AP175">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ175">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR175">
         <v>1.66</v>
@@ -37516,10 +37543,10 @@
         <v>1.67</v>
       </c>
       <c r="AP176">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ176">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR176">
         <v>1.53</v>
@@ -37850,7 +37877,7 @@
         <v>200</v>
       </c>
       <c r="P178" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="Q178">
         <v>3.4</v>
@@ -37928,10 +37955,10 @@
         <v>1.14</v>
       </c>
       <c r="AP178">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ178">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR178">
         <v>1.63</v>
@@ -38134,10 +38161,10 @@
         <v>1.13</v>
       </c>
       <c r="AP179">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ179">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR179">
         <v>1.53</v>
@@ -38262,7 +38289,7 @@
         <v>202</v>
       </c>
       <c r="P180" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="Q180">
         <v>2</v>
@@ -38343,7 +38370,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ180">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR180">
         <v>1.8</v>
@@ -38468,7 +38495,7 @@
         <v>90</v>
       </c>
       <c r="P181" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="Q181">
         <v>4</v>
@@ -38752,7 +38779,7 @@
         <v>1.43</v>
       </c>
       <c r="AP182">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ182">
         <v>1.4</v>
@@ -39086,7 +39113,7 @@
         <v>204</v>
       </c>
       <c r="P184" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39164,7 +39191,7 @@
         <v>1</v>
       </c>
       <c r="AP184">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ184">
         <v>1.09</v>
@@ -39292,7 +39319,7 @@
         <v>205</v>
       </c>
       <c r="P185" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="Q185">
         <v>3.2</v>
@@ -39498,7 +39525,7 @@
         <v>206</v>
       </c>
       <c r="P186" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="Q186">
         <v>3.75</v>
@@ -39576,10 +39603,10 @@
         <v>1.89</v>
       </c>
       <c r="AP186">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ186">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR186">
         <v>1.35</v>
@@ -39704,7 +39731,7 @@
         <v>207</v>
       </c>
       <c r="P187" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="Q187">
         <v>2.8</v>
@@ -39785,7 +39812,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ187">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR187">
         <v>2.02</v>
@@ -39988,10 +40015,10 @@
         <v>1.33</v>
       </c>
       <c r="AP188">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ188">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR188">
         <v>1.36</v>
@@ -40116,7 +40143,7 @@
         <v>180</v>
       </c>
       <c r="P189" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="Q189">
         <v>2.88</v>
@@ -40400,10 +40427,10 @@
         <v>1</v>
       </c>
       <c r="AP190">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ190">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR190">
         <v>1.17</v>
@@ -40528,7 +40555,7 @@
         <v>209</v>
       </c>
       <c r="P191" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -40609,7 +40636,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ191">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR191">
         <v>1.34</v>
@@ -40812,10 +40839,10 @@
         <v>0.78</v>
       </c>
       <c r="AP192">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ192">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR192">
         <v>1.63</v>
@@ -40940,7 +40967,7 @@
         <v>101</v>
       </c>
       <c r="P193" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="Q193">
         <v>3.1</v>
@@ -41018,7 +41045,7 @@
         <v>1.63</v>
       </c>
       <c r="AP193">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ193">
         <v>1.9</v>
@@ -41352,7 +41379,7 @@
         <v>212</v>
       </c>
       <c r="P195" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="Q195">
         <v>3.25</v>
@@ -41430,10 +41457,10 @@
         <v>1</v>
       </c>
       <c r="AP195">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ195">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR195">
         <v>1.44</v>
@@ -41639,7 +41666,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ196">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR196">
         <v>1.34</v>
@@ -41970,7 +41997,7 @@
         <v>90</v>
       </c>
       <c r="P198" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="Q198">
         <v>2.6</v>
@@ -42176,7 +42203,7 @@
         <v>202</v>
       </c>
       <c r="P199" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="Q199">
         <v>3.3</v>
@@ -42257,7 +42284,7 @@
         <v>1</v>
       </c>
       <c r="AQ199">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR199">
         <v>1.44</v>
@@ -42382,7 +42409,7 @@
         <v>214</v>
       </c>
       <c r="P200" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="Q200">
         <v>3.4</v>
@@ -42460,7 +42487,7 @@
         <v>0.82</v>
       </c>
       <c r="AP200">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ200">
         <v>1.15</v>
@@ -42794,7 +42821,7 @@
         <v>215</v>
       </c>
       <c r="P202" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="Q202">
         <v>2.59</v>
@@ -42875,7 +42902,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ202">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR202">
         <v>1.57</v>
@@ -43081,7 +43108,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ203">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR203">
         <v>1.23</v>
@@ -43284,10 +43311,10 @@
         <v>1.8</v>
       </c>
       <c r="AP204">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ204">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR204">
         <v>1.66</v>
@@ -43490,10 +43517,10 @@
         <v>1.2</v>
       </c>
       <c r="AP205">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ205">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR205">
         <v>1.17</v>
@@ -43696,7 +43723,7 @@
         <v>1</v>
       </c>
       <c r="AP206">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ206">
         <v>1.09</v>
@@ -43824,7 +43851,7 @@
         <v>96</v>
       </c>
       <c r="P207" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="Q207">
         <v>2.88</v>
@@ -43902,7 +43929,7 @@
         <v>1.18</v>
       </c>
       <c r="AP207">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ207">
         <v>1.17</v>
@@ -44111,7 +44138,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ208">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR208">
         <v>1.13</v>
@@ -44236,7 +44263,7 @@
         <v>218</v>
       </c>
       <c r="P209" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="Q209">
         <v>3.78</v>
@@ -44314,10 +44341,10 @@
         <v>1.3</v>
       </c>
       <c r="AP209">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ209">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR209">
         <v>1.34</v>
@@ -44520,7 +44547,7 @@
         <v>2</v>
       </c>
       <c r="AP210">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ210">
         <v>1.9</v>
@@ -44726,10 +44753,10 @@
         <v>2</v>
       </c>
       <c r="AP211">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ211">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR211">
         <v>1.47</v>
@@ -45060,7 +45087,7 @@
         <v>90</v>
       </c>
       <c r="P213" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="Q213">
         <v>3.7</v>
@@ -45138,7 +45165,7 @@
         <v>1.78</v>
       </c>
       <c r="AP213">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ213">
         <v>1.9</v>
@@ -45347,7 +45374,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ214">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR214">
         <v>2.02</v>
@@ -45472,7 +45499,7 @@
         <v>90</v>
       </c>
       <c r="P215" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="Q215">
         <v>2.25</v>
@@ -45553,7 +45580,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ215">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR215">
         <v>1.43</v>
@@ -45678,7 +45705,7 @@
         <v>193</v>
       </c>
       <c r="P216" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="Q216">
         <v>2.5</v>
@@ -45884,7 +45911,7 @@
         <v>90</v>
       </c>
       <c r="P217" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="Q217">
         <v>2.75</v>
@@ -46090,7 +46117,7 @@
         <v>90</v>
       </c>
       <c r="P218" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Q218">
         <v>2.4</v>
@@ -46296,7 +46323,7 @@
         <v>219</v>
       </c>
       <c r="P219" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="Q219">
         <v>2.8</v>
@@ -46374,7 +46401,7 @@
         <v>1.27</v>
       </c>
       <c r="AP219">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ219">
         <v>1.42</v>
@@ -46708,7 +46735,7 @@
         <v>221</v>
       </c>
       <c r="P221" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="Q221">
         <v>3.6</v>
@@ -46865,6 +46892,2066 @@
       </c>
       <c r="BP221">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:68">
+      <c r="A222" s="1">
+        <v>221</v>
+      </c>
+      <c r="B222">
+        <v>7778710</v>
+      </c>
+      <c r="C222" t="s">
+        <v>68</v>
+      </c>
+      <c r="D222" t="s">
+        <v>69</v>
+      </c>
+      <c r="E222" s="2">
+        <v>45850.25</v>
+      </c>
+      <c r="F222">
+        <v>23</v>
+      </c>
+      <c r="G222" t="s">
+        <v>89</v>
+      </c>
+      <c r="H222" t="s">
+        <v>82</v>
+      </c>
+      <c r="I222">
+        <v>3</v>
+      </c>
+      <c r="J222">
+        <v>1</v>
+      </c>
+      <c r="K222">
+        <v>4</v>
+      </c>
+      <c r="L222">
+        <v>3</v>
+      </c>
+      <c r="M222">
+        <v>2</v>
+      </c>
+      <c r="N222">
+        <v>5</v>
+      </c>
+      <c r="O222" t="s">
+        <v>222</v>
+      </c>
+      <c r="P222" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q222">
+        <v>3.5</v>
+      </c>
+      <c r="R222">
+        <v>2</v>
+      </c>
+      <c r="S222">
+        <v>3</v>
+      </c>
+      <c r="T222">
+        <v>1.44</v>
+      </c>
+      <c r="U222">
+        <v>2.57</v>
+      </c>
+      <c r="V222">
+        <v>3.04</v>
+      </c>
+      <c r="W222">
+        <v>1.33</v>
+      </c>
+      <c r="X222">
+        <v>7.9</v>
+      </c>
+      <c r="Y222">
+        <v>1.05</v>
+      </c>
+      <c r="Z222">
+        <v>2.61</v>
+      </c>
+      <c r="AA222">
+        <v>2.9</v>
+      </c>
+      <c r="AB222">
+        <v>2.55</v>
+      </c>
+      <c r="AC222">
+        <v>1.05</v>
+      </c>
+      <c r="AD222">
+        <v>8</v>
+      </c>
+      <c r="AE222">
+        <v>1.33</v>
+      </c>
+      <c r="AF222">
+        <v>3</v>
+      </c>
+      <c r="AG222">
+        <v>1.94</v>
+      </c>
+      <c r="AH222">
+        <v>1.76</v>
+      </c>
+      <c r="AI222">
+        <v>1.83</v>
+      </c>
+      <c r="AJ222">
+        <v>1.83</v>
+      </c>
+      <c r="AK222">
+        <v>1.48</v>
+      </c>
+      <c r="AL222">
+        <v>1.3</v>
+      </c>
+      <c r="AM222">
+        <v>1.38</v>
+      </c>
+      <c r="AN222">
+        <v>0.7</v>
+      </c>
+      <c r="AO222">
+        <v>0.9</v>
+      </c>
+      <c r="AP222">
+        <v>0.91</v>
+      </c>
+      <c r="AQ222">
+        <v>0.82</v>
+      </c>
+      <c r="AR222">
+        <v>1.57</v>
+      </c>
+      <c r="AS222">
+        <v>1.39</v>
+      </c>
+      <c r="AT222">
+        <v>2.96</v>
+      </c>
+      <c r="AU222">
+        <v>4</v>
+      </c>
+      <c r="AV222">
+        <v>4</v>
+      </c>
+      <c r="AW222">
+        <v>2</v>
+      </c>
+      <c r="AX222">
+        <v>9</v>
+      </c>
+      <c r="AY222">
+        <v>6</v>
+      </c>
+      <c r="AZ222">
+        <v>13</v>
+      </c>
+      <c r="BA222">
+        <v>2</v>
+      </c>
+      <c r="BB222">
+        <v>3</v>
+      </c>
+      <c r="BC222">
+        <v>5</v>
+      </c>
+      <c r="BD222">
+        <v>2.79</v>
+      </c>
+      <c r="BE222">
+        <v>7.42</v>
+      </c>
+      <c r="BF222">
+        <v>1.72</v>
+      </c>
+      <c r="BG222">
+        <v>1.22</v>
+      </c>
+      <c r="BH222">
+        <v>3.49</v>
+      </c>
+      <c r="BI222">
+        <v>1.46</v>
+      </c>
+      <c r="BJ222">
+        <v>2.46</v>
+      </c>
+      <c r="BK222">
+        <v>1.8</v>
+      </c>
+      <c r="BL222">
+        <v>1.91</v>
+      </c>
+      <c r="BM222">
+        <v>2.26</v>
+      </c>
+      <c r="BN222">
+        <v>1.55</v>
+      </c>
+      <c r="BO222">
+        <v>3</v>
+      </c>
+      <c r="BP222">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="223" spans="1:68">
+      <c r="A223" s="1">
+        <v>222</v>
+      </c>
+      <c r="B223">
+        <v>7778712</v>
+      </c>
+      <c r="C223" t="s">
+        <v>68</v>
+      </c>
+      <c r="D223" t="s">
+        <v>69</v>
+      </c>
+      <c r="E223" s="2">
+        <v>45850.25</v>
+      </c>
+      <c r="F223">
+        <v>23</v>
+      </c>
+      <c r="G223" t="s">
+        <v>70</v>
+      </c>
+      <c r="H223" t="s">
+        <v>76</v>
+      </c>
+      <c r="I223">
+        <v>0</v>
+      </c>
+      <c r="J223">
+        <v>0</v>
+      </c>
+      <c r="K223">
+        <v>0</v>
+      </c>
+      <c r="L223">
+        <v>1</v>
+      </c>
+      <c r="M223">
+        <v>1</v>
+      </c>
+      <c r="N223">
+        <v>2</v>
+      </c>
+      <c r="O223" t="s">
+        <v>223</v>
+      </c>
+      <c r="P223" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q223">
+        <v>3.75</v>
+      </c>
+      <c r="R223">
+        <v>2.2</v>
+      </c>
+      <c r="S223">
+        <v>2.5</v>
+      </c>
+      <c r="T223">
+        <v>1.32</v>
+      </c>
+      <c r="U223">
+        <v>3.29</v>
+      </c>
+      <c r="V223">
+        <v>2.6</v>
+      </c>
+      <c r="W223">
+        <v>1.49</v>
+      </c>
+      <c r="X223">
+        <v>5.9</v>
+      </c>
+      <c r="Y223">
+        <v>1.1</v>
+      </c>
+      <c r="Z223">
+        <v>3.34</v>
+      </c>
+      <c r="AA223">
+        <v>3.45</v>
+      </c>
+      <c r="AB223">
+        <v>1.89</v>
+      </c>
+      <c r="AC223">
+        <v>1.01</v>
+      </c>
+      <c r="AD223">
+        <v>11</v>
+      </c>
+      <c r="AE223">
+        <v>1.2</v>
+      </c>
+      <c r="AF223">
+        <v>4</v>
+      </c>
+      <c r="AG223">
+        <v>1.54</v>
+      </c>
+      <c r="AH223">
+        <v>2.3</v>
+      </c>
+      <c r="AI223">
+        <v>1.62</v>
+      </c>
+      <c r="AJ223">
+        <v>2.2</v>
+      </c>
+      <c r="AK223">
+        <v>1.66</v>
+      </c>
+      <c r="AL223">
+        <v>1.25</v>
+      </c>
+      <c r="AM223">
+        <v>1.31</v>
+      </c>
+      <c r="AN223">
+        <v>1.18</v>
+      </c>
+      <c r="AO223">
+        <v>1.45</v>
+      </c>
+      <c r="AP223">
+        <v>1.17</v>
+      </c>
+      <c r="AQ223">
+        <v>1.42</v>
+      </c>
+      <c r="AR223">
+        <v>1.63</v>
+      </c>
+      <c r="AS223">
+        <v>1.66</v>
+      </c>
+      <c r="AT223">
+        <v>3.29</v>
+      </c>
+      <c r="AU223">
+        <v>2</v>
+      </c>
+      <c r="AV223">
+        <v>2</v>
+      </c>
+      <c r="AW223">
+        <v>9</v>
+      </c>
+      <c r="AX223">
+        <v>6</v>
+      </c>
+      <c r="AY223">
+        <v>11</v>
+      </c>
+      <c r="AZ223">
+        <v>8</v>
+      </c>
+      <c r="BA223">
+        <v>8</v>
+      </c>
+      <c r="BB223">
+        <v>6</v>
+      </c>
+      <c r="BC223">
+        <v>14</v>
+      </c>
+      <c r="BD223">
+        <v>2.28</v>
+      </c>
+      <c r="BE223">
+        <v>7.15</v>
+      </c>
+      <c r="BF223">
+        <v>1.99</v>
+      </c>
+      <c r="BG223">
+        <v>1.23</v>
+      </c>
+      <c r="BH223">
+        <v>3.4</v>
+      </c>
+      <c r="BI223">
+        <v>1.48</v>
+      </c>
+      <c r="BJ223">
+        <v>2.42</v>
+      </c>
+      <c r="BK223">
+        <v>1.82</v>
+      </c>
+      <c r="BL223">
+        <v>1.88</v>
+      </c>
+      <c r="BM223">
+        <v>2.3</v>
+      </c>
+      <c r="BN223">
+        <v>1.53</v>
+      </c>
+      <c r="BO223">
+        <v>3.08</v>
+      </c>
+      <c r="BP223">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="224" spans="1:68">
+      <c r="A224" s="1">
+        <v>223</v>
+      </c>
+      <c r="B224">
+        <v>7778713</v>
+      </c>
+      <c r="C224" t="s">
+        <v>68</v>
+      </c>
+      <c r="D224" t="s">
+        <v>69</v>
+      </c>
+      <c r="E224" s="2">
+        <v>45850.25</v>
+      </c>
+      <c r="F224">
+        <v>23</v>
+      </c>
+      <c r="G224" t="s">
+        <v>84</v>
+      </c>
+      <c r="H224" t="s">
+        <v>86</v>
+      </c>
+      <c r="I224">
+        <v>0</v>
+      </c>
+      <c r="J224">
+        <v>0</v>
+      </c>
+      <c r="K224">
+        <v>0</v>
+      </c>
+      <c r="L224">
+        <v>3</v>
+      </c>
+      <c r="M224">
+        <v>0</v>
+      </c>
+      <c r="N224">
+        <v>3</v>
+      </c>
+      <c r="O224" t="s">
+        <v>224</v>
+      </c>
+      <c r="P224" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q224">
+        <v>2.25</v>
+      </c>
+      <c r="R224">
+        <v>2.1</v>
+      </c>
+      <c r="S224">
+        <v>5</v>
+      </c>
+      <c r="T224">
+        <v>1.42</v>
+      </c>
+      <c r="U224">
+        <v>2.83</v>
+      </c>
+      <c r="V224">
+        <v>3.12</v>
+      </c>
+      <c r="W224">
+        <v>1.35</v>
+      </c>
+      <c r="X224">
+        <v>7.4</v>
+      </c>
+      <c r="Y224">
+        <v>1.06</v>
+      </c>
+      <c r="Z224">
+        <v>1.61</v>
+      </c>
+      <c r="AA224">
+        <v>3.45</v>
+      </c>
+      <c r="AB224">
+        <v>4.8</v>
+      </c>
+      <c r="AC224">
+        <v>1.03</v>
+      </c>
+      <c r="AD224">
+        <v>9</v>
+      </c>
+      <c r="AE224">
+        <v>1.29</v>
+      </c>
+      <c r="AF224">
+        <v>3.3</v>
+      </c>
+      <c r="AG224">
+        <v>1.97</v>
+      </c>
+      <c r="AH224">
+        <v>1.73</v>
+      </c>
+      <c r="AI224">
+        <v>2</v>
+      </c>
+      <c r="AJ224">
+        <v>1.73</v>
+      </c>
+      <c r="AK224">
+        <v>1.11</v>
+      </c>
+      <c r="AL224">
+        <v>1.24</v>
+      </c>
+      <c r="AM224">
+        <v>2.14</v>
+      </c>
+      <c r="AN224">
+        <v>2.17</v>
+      </c>
+      <c r="AO224">
+        <v>0.91</v>
+      </c>
+      <c r="AP224">
+        <v>2.23</v>
+      </c>
+      <c r="AQ224">
+        <v>0.83</v>
+      </c>
+      <c r="AR224">
+        <v>1.66</v>
+      </c>
+      <c r="AS224">
+        <v>1.15</v>
+      </c>
+      <c r="AT224">
+        <v>2.81</v>
+      </c>
+      <c r="AU224">
+        <v>4</v>
+      </c>
+      <c r="AV224">
+        <v>2</v>
+      </c>
+      <c r="AW224">
+        <v>8</v>
+      </c>
+      <c r="AX224">
+        <v>5</v>
+      </c>
+      <c r="AY224">
+        <v>12</v>
+      </c>
+      <c r="AZ224">
+        <v>7</v>
+      </c>
+      <c r="BA224">
+        <v>7</v>
+      </c>
+      <c r="BB224">
+        <v>4</v>
+      </c>
+      <c r="BC224">
+        <v>11</v>
+      </c>
+      <c r="BD224">
+        <v>1.34</v>
+      </c>
+      <c r="BE224">
+        <v>8.75</v>
+      </c>
+      <c r="BF224">
+        <v>4.7</v>
+      </c>
+      <c r="BG224">
+        <v>1.29</v>
+      </c>
+      <c r="BH224">
+        <v>3.06</v>
+      </c>
+      <c r="BI224">
+        <v>1.57</v>
+      </c>
+      <c r="BJ224">
+        <v>2.22</v>
+      </c>
+      <c r="BK224">
+        <v>1.95</v>
+      </c>
+      <c r="BL224">
+        <v>1.76</v>
+      </c>
+      <c r="BM224">
+        <v>2.52</v>
+      </c>
+      <c r="BN224">
+        <v>1.44</v>
+      </c>
+      <c r="BO224">
+        <v>3.46</v>
+      </c>
+      <c r="BP224">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="225" spans="1:68">
+      <c r="A225" s="1">
+        <v>224</v>
+      </c>
+      <c r="B225">
+        <v>7778718</v>
+      </c>
+      <c r="C225" t="s">
+        <v>68</v>
+      </c>
+      <c r="D225" t="s">
+        <v>69</v>
+      </c>
+      <c r="E225" s="2">
+        <v>45850.25347222222</v>
+      </c>
+      <c r="F225">
+        <v>23</v>
+      </c>
+      <c r="G225" t="s">
+        <v>78</v>
+      </c>
+      <c r="H225" t="s">
+        <v>77</v>
+      </c>
+      <c r="I225">
+        <v>0</v>
+      </c>
+      <c r="J225">
+        <v>0</v>
+      </c>
+      <c r="K225">
+        <v>0</v>
+      </c>
+      <c r="L225">
+        <v>1</v>
+      </c>
+      <c r="M225">
+        <v>0</v>
+      </c>
+      <c r="N225">
+        <v>1</v>
+      </c>
+      <c r="O225" t="s">
+        <v>225</v>
+      </c>
+      <c r="P225" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q225">
+        <v>2.1</v>
+      </c>
+      <c r="R225">
+        <v>2.2</v>
+      </c>
+      <c r="S225">
+        <v>5</v>
+      </c>
+      <c r="T225">
+        <v>1.36</v>
+      </c>
+      <c r="U225">
+        <v>3.07</v>
+      </c>
+      <c r="V225">
+        <v>2.83</v>
+      </c>
+      <c r="W225">
+        <v>1.42</v>
+      </c>
+      <c r="X225">
+        <v>6.2</v>
+      </c>
+      <c r="Y225">
+        <v>1.09</v>
+      </c>
+      <c r="Z225">
+        <v>1.54</v>
+      </c>
+      <c r="AA225">
+        <v>3.63</v>
+      </c>
+      <c r="AB225">
+        <v>5.1</v>
+      </c>
+      <c r="AC225">
+        <v>1.01</v>
+      </c>
+      <c r="AD225">
+        <v>11</v>
+      </c>
+      <c r="AE225">
+        <v>1.25</v>
+      </c>
+      <c r="AF225">
+        <v>3.6</v>
+      </c>
+      <c r="AG225">
+        <v>1.92</v>
+      </c>
+      <c r="AH225">
+        <v>1.78</v>
+      </c>
+      <c r="AI225">
+        <v>1.8</v>
+      </c>
+      <c r="AJ225">
+        <v>1.91</v>
+      </c>
+      <c r="AK225">
+        <v>1.12</v>
+      </c>
+      <c r="AL225">
+        <v>1.2</v>
+      </c>
+      <c r="AM225">
+        <v>2.24</v>
+      </c>
+      <c r="AN225">
+        <v>0.75</v>
+      </c>
+      <c r="AO225">
+        <v>1.18</v>
+      </c>
+      <c r="AP225">
+        <v>0.92</v>
+      </c>
+      <c r="AQ225">
+        <v>1.08</v>
+      </c>
+      <c r="AR225">
+        <v>1.57</v>
+      </c>
+      <c r="AS225">
+        <v>1.22</v>
+      </c>
+      <c r="AT225">
+        <v>2.79</v>
+      </c>
+      <c r="AU225">
+        <v>4</v>
+      </c>
+      <c r="AV225">
+        <v>4</v>
+      </c>
+      <c r="AW225">
+        <v>10</v>
+      </c>
+      <c r="AX225">
+        <v>2</v>
+      </c>
+      <c r="AY225">
+        <v>14</v>
+      </c>
+      <c r="AZ225">
+        <v>6</v>
+      </c>
+      <c r="BA225">
+        <v>5</v>
+      </c>
+      <c r="BB225">
+        <v>3</v>
+      </c>
+      <c r="BC225">
+        <v>8</v>
+      </c>
+      <c r="BD225">
+        <v>1.22</v>
+      </c>
+      <c r="BE225">
+        <v>10.7</v>
+      </c>
+      <c r="BF225">
+        <v>6.28</v>
+      </c>
+      <c r="BG225">
+        <v>1.14</v>
+      </c>
+      <c r="BH225">
+        <v>4.22</v>
+      </c>
+      <c r="BI225">
+        <v>1.34</v>
+      </c>
+      <c r="BJ225">
+        <v>2.86</v>
+      </c>
+      <c r="BK225">
+        <v>1.62</v>
+      </c>
+      <c r="BL225">
+        <v>2.14</v>
+      </c>
+      <c r="BM225">
+        <v>2</v>
+      </c>
+      <c r="BN225">
+        <v>1.72</v>
+      </c>
+      <c r="BO225">
+        <v>2.55</v>
+      </c>
+      <c r="BP225">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="226" spans="1:68">
+      <c r="A226" s="1">
+        <v>225</v>
+      </c>
+      <c r="B226">
+        <v>7778714</v>
+      </c>
+      <c r="C226" t="s">
+        <v>68</v>
+      </c>
+      <c r="D226" t="s">
+        <v>69</v>
+      </c>
+      <c r="E226" s="2">
+        <v>45850.27083333334</v>
+      </c>
+      <c r="F226">
+        <v>23</v>
+      </c>
+      <c r="G226" t="s">
+        <v>72</v>
+      </c>
+      <c r="H226" t="s">
+        <v>71</v>
+      </c>
+      <c r="I226">
+        <v>0</v>
+      </c>
+      <c r="J226">
+        <v>0</v>
+      </c>
+      <c r="K226">
+        <v>0</v>
+      </c>
+      <c r="L226">
+        <v>1</v>
+      </c>
+      <c r="M226">
+        <v>0</v>
+      </c>
+      <c r="N226">
+        <v>1</v>
+      </c>
+      <c r="O226" t="s">
+        <v>148</v>
+      </c>
+      <c r="P226" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q226">
+        <v>3.75</v>
+      </c>
+      <c r="R226">
+        <v>2.1</v>
+      </c>
+      <c r="S226">
+        <v>2.75</v>
+      </c>
+      <c r="T226">
+        <v>1.41</v>
+      </c>
+      <c r="U226">
+        <v>2.87</v>
+      </c>
+      <c r="V226">
+        <v>3.05</v>
+      </c>
+      <c r="W226">
+        <v>1.37</v>
+      </c>
+      <c r="X226">
+        <v>7.5</v>
+      </c>
+      <c r="Y226">
+        <v>1.05</v>
+      </c>
+      <c r="Z226">
+        <v>2.95</v>
+      </c>
+      <c r="AA226">
+        <v>3.04</v>
+      </c>
+      <c r="AB226">
+        <v>2.21</v>
+      </c>
+      <c r="AC226">
+        <v>1.03</v>
+      </c>
+      <c r="AD226">
+        <v>9</v>
+      </c>
+      <c r="AE226">
+        <v>1.3</v>
+      </c>
+      <c r="AF226">
+        <v>3.2</v>
+      </c>
+      <c r="AG226">
+        <v>1.98</v>
+      </c>
+      <c r="AH226">
+        <v>1.73</v>
+      </c>
+      <c r="AI226">
+        <v>1.8</v>
+      </c>
+      <c r="AJ226">
+        <v>1.91</v>
+      </c>
+      <c r="AK226">
+        <v>1.59</v>
+      </c>
+      <c r="AL226">
+        <v>1.28</v>
+      </c>
+      <c r="AM226">
+        <v>1.32</v>
+      </c>
+      <c r="AN226">
+        <v>1.3</v>
+      </c>
+      <c r="AO226">
+        <v>1.5</v>
+      </c>
+      <c r="AP226">
+        <v>1.45</v>
+      </c>
+      <c r="AQ226">
+        <v>1.36</v>
+      </c>
+      <c r="AR226">
+        <v>1.17</v>
+      </c>
+      <c r="AS226">
+        <v>1.49</v>
+      </c>
+      <c r="AT226">
+        <v>2.66</v>
+      </c>
+      <c r="AU226">
+        <v>2</v>
+      </c>
+      <c r="AV226">
+        <v>6</v>
+      </c>
+      <c r="AW226">
+        <v>6</v>
+      </c>
+      <c r="AX226">
+        <v>1</v>
+      </c>
+      <c r="AY226">
+        <v>8</v>
+      </c>
+      <c r="AZ226">
+        <v>7</v>
+      </c>
+      <c r="BA226">
+        <v>6</v>
+      </c>
+      <c r="BB226">
+        <v>3</v>
+      </c>
+      <c r="BC226">
+        <v>9</v>
+      </c>
+      <c r="BD226">
+        <v>2.02</v>
+      </c>
+      <c r="BE226">
+        <v>6.92</v>
+      </c>
+      <c r="BF226">
+        <v>2.27</v>
+      </c>
+      <c r="BG226">
+        <v>1.35</v>
+      </c>
+      <c r="BH226">
+        <v>2.79</v>
+      </c>
+      <c r="BI226">
+        <v>1.67</v>
+      </c>
+      <c r="BJ226">
+        <v>2.07</v>
+      </c>
+      <c r="BK226">
+        <v>2.09</v>
+      </c>
+      <c r="BL226">
+        <v>1.66</v>
+      </c>
+      <c r="BM226">
+        <v>2.75</v>
+      </c>
+      <c r="BN226">
+        <v>1.36</v>
+      </c>
+      <c r="BO226">
+        <v>3.88</v>
+      </c>
+      <c r="BP226">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="227" spans="1:68">
+      <c r="A227" s="1">
+        <v>226</v>
+      </c>
+      <c r="B227">
+        <v>7778711</v>
+      </c>
+      <c r="C227" t="s">
+        <v>68</v>
+      </c>
+      <c r="D227" t="s">
+        <v>69</v>
+      </c>
+      <c r="E227" s="2">
+        <v>45850.29166666666</v>
+      </c>
+      <c r="F227">
+        <v>23</v>
+      </c>
+      <c r="G227" t="s">
+        <v>88</v>
+      </c>
+      <c r="H227" t="s">
+        <v>80</v>
+      </c>
+      <c r="I227">
+        <v>0</v>
+      </c>
+      <c r="J227">
+        <v>0</v>
+      </c>
+      <c r="K227">
+        <v>0</v>
+      </c>
+      <c r="L227">
+        <v>0</v>
+      </c>
+      <c r="M227">
+        <v>1</v>
+      </c>
+      <c r="N227">
+        <v>1</v>
+      </c>
+      <c r="O227" t="s">
+        <v>90</v>
+      </c>
+      <c r="P227" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q227">
+        <v>3.25</v>
+      </c>
+      <c r="R227">
+        <v>2.1</v>
+      </c>
+      <c r="S227">
+        <v>2.88</v>
+      </c>
+      <c r="T227">
+        <v>1.36</v>
+      </c>
+      <c r="U227">
+        <v>3.11</v>
+      </c>
+      <c r="V227">
+        <v>2.78</v>
+      </c>
+      <c r="W227">
+        <v>1.43</v>
+      </c>
+      <c r="X227">
+        <v>6.5</v>
+      </c>
+      <c r="Y227">
+        <v>1.08</v>
+      </c>
+      <c r="Z227">
+        <v>2.86</v>
+      </c>
+      <c r="AA227">
+        <v>3.23</v>
+      </c>
+      <c r="AB227">
+        <v>2.17</v>
+      </c>
+      <c r="AC227">
+        <v>1.02</v>
+      </c>
+      <c r="AD227">
+        <v>10</v>
+      </c>
+      <c r="AE227">
+        <v>1.25</v>
+      </c>
+      <c r="AF227">
+        <v>3.6</v>
+      </c>
+      <c r="AG227">
+        <v>1.81</v>
+      </c>
+      <c r="AH227">
+        <v>1.89</v>
+      </c>
+      <c r="AI227">
+        <v>1.67</v>
+      </c>
+      <c r="AJ227">
+        <v>2.1</v>
+      </c>
+      <c r="AK227">
+        <v>1.46</v>
+      </c>
+      <c r="AL227">
+        <v>1.28</v>
+      </c>
+      <c r="AM227">
+        <v>1.41</v>
+      </c>
+      <c r="AN227">
+        <v>0.89</v>
+      </c>
+      <c r="AO227">
+        <v>1.64</v>
+      </c>
+      <c r="AP227">
+        <v>0.8</v>
+      </c>
+      <c r="AQ227">
+        <v>1.75</v>
+      </c>
+      <c r="AR227">
+        <v>1.34</v>
+      </c>
+      <c r="AS227">
+        <v>1.18</v>
+      </c>
+      <c r="AT227">
+        <v>2.52</v>
+      </c>
+      <c r="AU227">
+        <v>3</v>
+      </c>
+      <c r="AV227">
+        <v>6</v>
+      </c>
+      <c r="AW227">
+        <v>11</v>
+      </c>
+      <c r="AX227">
+        <v>11</v>
+      </c>
+      <c r="AY227">
+        <v>14</v>
+      </c>
+      <c r="AZ227">
+        <v>17</v>
+      </c>
+      <c r="BA227">
+        <v>8</v>
+      </c>
+      <c r="BB227">
+        <v>3</v>
+      </c>
+      <c r="BC227">
+        <v>11</v>
+      </c>
+      <c r="BD227">
+        <v>2.2</v>
+      </c>
+      <c r="BE227">
+        <v>7.09</v>
+      </c>
+      <c r="BF227">
+        <v>2.06</v>
+      </c>
+      <c r="BG227">
+        <v>1.25</v>
+      </c>
+      <c r="BH227">
+        <v>3.26</v>
+      </c>
+      <c r="BI227">
+        <v>1.51</v>
+      </c>
+      <c r="BJ227">
+        <v>2.34</v>
+      </c>
+      <c r="BK227">
+        <v>1.87</v>
+      </c>
+      <c r="BL227">
+        <v>1.83</v>
+      </c>
+      <c r="BM227">
+        <v>2.38</v>
+      </c>
+      <c r="BN227">
+        <v>1.49</v>
+      </c>
+      <c r="BO227">
+        <v>3.21</v>
+      </c>
+      <c r="BP227">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="228" spans="1:68">
+      <c r="A228" s="1">
+        <v>227</v>
+      </c>
+      <c r="B228">
+        <v>7778716</v>
+      </c>
+      <c r="C228" t="s">
+        <v>68</v>
+      </c>
+      <c r="D228" t="s">
+        <v>69</v>
+      </c>
+      <c r="E228" s="2">
+        <v>45850.29166666666</v>
+      </c>
+      <c r="F228">
+        <v>23</v>
+      </c>
+      <c r="G228" t="s">
+        <v>74</v>
+      </c>
+      <c r="H228" t="s">
+        <v>85</v>
+      </c>
+      <c r="I228">
+        <v>1</v>
+      </c>
+      <c r="J228">
+        <v>0</v>
+      </c>
+      <c r="K228">
+        <v>1</v>
+      </c>
+      <c r="L228">
+        <v>1</v>
+      </c>
+      <c r="M228">
+        <v>1</v>
+      </c>
+      <c r="N228">
+        <v>2</v>
+      </c>
+      <c r="O228" t="s">
+        <v>217</v>
+      </c>
+      <c r="P228" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q228">
+        <v>3.75</v>
+      </c>
+      <c r="R228">
+        <v>2.1</v>
+      </c>
+      <c r="S228">
+        <v>2.63</v>
+      </c>
+      <c r="T228">
+        <v>1.39</v>
+      </c>
+      <c r="U228">
+        <v>2.95</v>
+      </c>
+      <c r="V228">
+        <v>2.96</v>
+      </c>
+      <c r="W228">
+        <v>1.39</v>
+      </c>
+      <c r="X228">
+        <v>7.1</v>
+      </c>
+      <c r="Y228">
+        <v>1.06</v>
+      </c>
+      <c r="Z228">
+        <v>3.15</v>
+      </c>
+      <c r="AA228">
+        <v>3.14</v>
+      </c>
+      <c r="AB228">
+        <v>2.06</v>
+      </c>
+      <c r="AC228">
+        <v>1.03</v>
+      </c>
+      <c r="AD228">
+        <v>9</v>
+      </c>
+      <c r="AE228">
+        <v>1.29</v>
+      </c>
+      <c r="AF228">
+        <v>3.3</v>
+      </c>
+      <c r="AG228">
+        <v>1.92</v>
+      </c>
+      <c r="AH228">
+        <v>1.78</v>
+      </c>
+      <c r="AI228">
+        <v>1.73</v>
+      </c>
+      <c r="AJ228">
+        <v>2</v>
+      </c>
+      <c r="AK228">
+        <v>1.56</v>
+      </c>
+      <c r="AL228">
+        <v>1.3</v>
+      </c>
+      <c r="AM228">
+        <v>1.32</v>
+      </c>
+      <c r="AN228">
+        <v>1.18</v>
+      </c>
+      <c r="AO228">
+        <v>2.09</v>
+      </c>
+      <c r="AP228">
+        <v>1.17</v>
+      </c>
+      <c r="AQ228">
+        <v>2</v>
+      </c>
+      <c r="AR228">
+        <v>1.5</v>
+      </c>
+      <c r="AS228">
+        <v>1.43</v>
+      </c>
+      <c r="AT228">
+        <v>2.93</v>
+      </c>
+      <c r="AU228">
+        <v>3</v>
+      </c>
+      <c r="AV228">
+        <v>5</v>
+      </c>
+      <c r="AW228">
+        <v>7</v>
+      </c>
+      <c r="AX228">
+        <v>11</v>
+      </c>
+      <c r="AY228">
+        <v>10</v>
+      </c>
+      <c r="AZ228">
+        <v>16</v>
+      </c>
+      <c r="BA228">
+        <v>2</v>
+      </c>
+      <c r="BB228">
+        <v>5</v>
+      </c>
+      <c r="BC228">
+        <v>7</v>
+      </c>
+      <c r="BD228">
+        <v>2.26</v>
+      </c>
+      <c r="BE228">
+        <v>7.07</v>
+      </c>
+      <c r="BF228">
+        <v>2.01</v>
+      </c>
+      <c r="BG228">
+        <v>1.27</v>
+      </c>
+      <c r="BH228">
+        <v>3.18</v>
+      </c>
+      <c r="BI228">
+        <v>1.54</v>
+      </c>
+      <c r="BJ228">
+        <v>2.29</v>
+      </c>
+      <c r="BK228">
+        <v>1.9</v>
+      </c>
+      <c r="BL228">
+        <v>1.8</v>
+      </c>
+      <c r="BM228">
+        <v>2.43</v>
+      </c>
+      <c r="BN228">
+        <v>1.47</v>
+      </c>
+      <c r="BO228">
+        <v>3.3</v>
+      </c>
+      <c r="BP228">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="229" spans="1:68">
+      <c r="A229" s="1">
+        <v>228</v>
+      </c>
+      <c r="B229">
+        <v>7778717</v>
+      </c>
+      <c r="C229" t="s">
+        <v>68</v>
+      </c>
+      <c r="D229" t="s">
+        <v>69</v>
+      </c>
+      <c r="E229" s="2">
+        <v>45850.29166666666</v>
+      </c>
+      <c r="F229">
+        <v>23</v>
+      </c>
+      <c r="G229" t="s">
+        <v>81</v>
+      </c>
+      <c r="H229" t="s">
+        <v>83</v>
+      </c>
+      <c r="I229">
+        <v>0</v>
+      </c>
+      <c r="J229">
+        <v>0</v>
+      </c>
+      <c r="K229">
+        <v>0</v>
+      </c>
+      <c r="L229">
+        <v>0</v>
+      </c>
+      <c r="M229">
+        <v>0</v>
+      </c>
+      <c r="N229">
+        <v>0</v>
+      </c>
+      <c r="O229" t="s">
+        <v>90</v>
+      </c>
+      <c r="P229" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q229">
+        <v>4.2</v>
+      </c>
+      <c r="R229">
+        <v>1.83</v>
+      </c>
+      <c r="S229">
+        <v>3</v>
+      </c>
+      <c r="T229">
+        <v>1.64</v>
+      </c>
+      <c r="U229">
+        <v>2.23</v>
+      </c>
+      <c r="V229">
+        <v>3.74</v>
+      </c>
+      <c r="W229">
+        <v>1.21</v>
+      </c>
+      <c r="X229">
+        <v>10.5</v>
+      </c>
+      <c r="Y229">
+        <v>1.01</v>
+      </c>
+      <c r="Z229">
+        <v>3.16</v>
+      </c>
+      <c r="AA229">
+        <v>2.82</v>
+      </c>
+      <c r="AB229">
+        <v>2.23</v>
+      </c>
+      <c r="AC229">
+        <v>1.08</v>
+      </c>
+      <c r="AD229">
+        <v>6.5</v>
+      </c>
+      <c r="AE229">
+        <v>1.55</v>
+      </c>
+      <c r="AF229">
+        <v>2.2</v>
+      </c>
+      <c r="AG229">
+        <v>2.62</v>
+      </c>
+      <c r="AH229">
+        <v>1.42</v>
+      </c>
+      <c r="AI229">
+        <v>2.25</v>
+      </c>
+      <c r="AJ229">
+        <v>1.57</v>
+      </c>
+      <c r="AK229">
+        <v>1.51</v>
+      </c>
+      <c r="AL229">
+        <v>1.36</v>
+      </c>
+      <c r="AM229">
+        <v>1.29</v>
+      </c>
+      <c r="AN229">
+        <v>1.09</v>
+      </c>
+      <c r="AO229">
+        <v>1.73</v>
+      </c>
+      <c r="AP229">
+        <v>1.08</v>
+      </c>
+      <c r="AQ229">
+        <v>1.67</v>
+      </c>
+      <c r="AR229">
+        <v>1.4</v>
+      </c>
+      <c r="AS229">
+        <v>1.4</v>
+      </c>
+      <c r="AT229">
+        <v>2.8</v>
+      </c>
+      <c r="AU229">
+        <v>2</v>
+      </c>
+      <c r="AV229">
+        <v>6</v>
+      </c>
+      <c r="AW229">
+        <v>1</v>
+      </c>
+      <c r="AX229">
+        <v>10</v>
+      </c>
+      <c r="AY229">
+        <v>3</v>
+      </c>
+      <c r="AZ229">
+        <v>16</v>
+      </c>
+      <c r="BA229">
+        <v>2</v>
+      </c>
+      <c r="BB229">
+        <v>5</v>
+      </c>
+      <c r="BC229">
+        <v>7</v>
+      </c>
+      <c r="BD229">
+        <v>2.27</v>
+      </c>
+      <c r="BE229">
+        <v>6.92</v>
+      </c>
+      <c r="BF229">
+        <v>2.02</v>
+      </c>
+      <c r="BG229">
+        <v>1.35</v>
+      </c>
+      <c r="BH229">
+        <v>2.79</v>
+      </c>
+      <c r="BI229">
+        <v>1.67</v>
+      </c>
+      <c r="BJ229">
+        <v>2.07</v>
+      </c>
+      <c r="BK229">
+        <v>2.09</v>
+      </c>
+      <c r="BL229">
+        <v>1.66</v>
+      </c>
+      <c r="BM229">
+        <v>2.75</v>
+      </c>
+      <c r="BN229">
+        <v>1.36</v>
+      </c>
+      <c r="BO229">
+        <v>3.88</v>
+      </c>
+      <c r="BP229">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="230" spans="1:68">
+      <c r="A230" s="1">
+        <v>229</v>
+      </c>
+      <c r="B230">
+        <v>7778719</v>
+      </c>
+      <c r="C230" t="s">
+        <v>68</v>
+      </c>
+      <c r="D230" t="s">
+        <v>69</v>
+      </c>
+      <c r="E230" s="2">
+        <v>45850.29166666666</v>
+      </c>
+      <c r="F230">
+        <v>23</v>
+      </c>
+      <c r="G230" t="s">
+        <v>75</v>
+      </c>
+      <c r="H230" t="s">
+        <v>79</v>
+      </c>
+      <c r="I230">
+        <v>1</v>
+      </c>
+      <c r="J230">
+        <v>1</v>
+      </c>
+      <c r="K230">
+        <v>2</v>
+      </c>
+      <c r="L230">
+        <v>2</v>
+      </c>
+      <c r="M230">
+        <v>1</v>
+      </c>
+      <c r="N230">
+        <v>3</v>
+      </c>
+      <c r="O230" t="s">
+        <v>226</v>
+      </c>
+      <c r="P230" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q230">
+        <v>3.1</v>
+      </c>
+      <c r="R230">
+        <v>1.83</v>
+      </c>
+      <c r="S230">
+        <v>4</v>
+      </c>
+      <c r="T230">
+        <v>1.59</v>
+      </c>
+      <c r="U230">
+        <v>2.33</v>
+      </c>
+      <c r="V230">
+        <v>3.74</v>
+      </c>
+      <c r="W230">
+        <v>1.21</v>
+      </c>
+      <c r="X230">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Y230">
+        <v>1.02</v>
+      </c>
+      <c r="Z230">
+        <v>2.13</v>
+      </c>
+      <c r="AA230">
+        <v>2.89</v>
+      </c>
+      <c r="AB230">
+        <v>3.29</v>
+      </c>
+      <c r="AC230">
+        <v>1.07</v>
+      </c>
+      <c r="AD230">
+        <v>7</v>
+      </c>
+      <c r="AE230">
+        <v>1.53</v>
+      </c>
+      <c r="AF230">
+        <v>2.25</v>
+      </c>
+      <c r="AG230">
+        <v>2.48</v>
+      </c>
+      <c r="AH230">
+        <v>1.47</v>
+      </c>
+      <c r="AI230">
+        <v>2.2</v>
+      </c>
+      <c r="AJ230">
+        <v>1.62</v>
+      </c>
+      <c r="AK230">
+        <v>1.28</v>
+      </c>
+      <c r="AL230">
+        <v>1.33</v>
+      </c>
+      <c r="AM230">
+        <v>1.56</v>
+      </c>
+      <c r="AN230">
+        <v>1.75</v>
+      </c>
+      <c r="AO230">
+        <v>0.91</v>
+      </c>
+      <c r="AP230">
+        <v>1.85</v>
+      </c>
+      <c r="AQ230">
+        <v>0.83</v>
+      </c>
+      <c r="AR230">
+        <v>1.26</v>
+      </c>
+      <c r="AS230">
+        <v>1.24</v>
+      </c>
+      <c r="AT230">
+        <v>2.5</v>
+      </c>
+      <c r="AU230">
+        <v>5</v>
+      </c>
+      <c r="AV230">
+        <v>3</v>
+      </c>
+      <c r="AW230">
+        <v>7</v>
+      </c>
+      <c r="AX230">
+        <v>3</v>
+      </c>
+      <c r="AY230">
+        <v>12</v>
+      </c>
+      <c r="AZ230">
+        <v>6</v>
+      </c>
+      <c r="BA230">
+        <v>2</v>
+      </c>
+      <c r="BB230">
+        <v>3</v>
+      </c>
+      <c r="BC230">
+        <v>5</v>
+      </c>
+      <c r="BD230">
+        <v>1.97</v>
+      </c>
+      <c r="BE230">
+        <v>7.06</v>
+      </c>
+      <c r="BF230">
+        <v>2.32</v>
+      </c>
+      <c r="BG230">
+        <v>1.28</v>
+      </c>
+      <c r="BH230">
+        <v>3.1</v>
+      </c>
+      <c r="BI230">
+        <v>1.56</v>
+      </c>
+      <c r="BJ230">
+        <v>2.24</v>
+      </c>
+      <c r="BK230">
+        <v>1.94</v>
+      </c>
+      <c r="BL230">
+        <v>1.77</v>
+      </c>
+      <c r="BM230">
+        <v>2.49</v>
+      </c>
+      <c r="BN230">
+        <v>1.45</v>
+      </c>
+      <c r="BO230">
+        <v>3.41</v>
+      </c>
+      <c r="BP230">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="231" spans="1:68">
+      <c r="A231" s="1">
+        <v>230</v>
+      </c>
+      <c r="B231">
+        <v>7778715</v>
+      </c>
+      <c r="C231" t="s">
+        <v>68</v>
+      </c>
+      <c r="D231" t="s">
+        <v>69</v>
+      </c>
+      <c r="E231" s="2">
+        <v>45850.3125</v>
+      </c>
+      <c r="F231">
+        <v>23</v>
+      </c>
+      <c r="G231" t="s">
+        <v>73</v>
+      </c>
+      <c r="H231" t="s">
+        <v>87</v>
+      </c>
+      <c r="I231">
+        <v>3</v>
+      </c>
+      <c r="J231">
+        <v>1</v>
+      </c>
+      <c r="K231">
+        <v>4</v>
+      </c>
+      <c r="L231">
+        <v>5</v>
+      </c>
+      <c r="M231">
+        <v>1</v>
+      </c>
+      <c r="N231">
+        <v>6</v>
+      </c>
+      <c r="O231" t="s">
+        <v>227</v>
+      </c>
+      <c r="P231" t="s">
+        <v>329</v>
+      </c>
+      <c r="Q231">
+        <v>2.41</v>
+      </c>
+      <c r="R231">
+        <v>2.26</v>
+      </c>
+      <c r="S231">
+        <v>4.04</v>
+      </c>
+      <c r="T231">
+        <v>1.28</v>
+      </c>
+      <c r="U231">
+        <v>3.34</v>
+      </c>
+      <c r="V231">
+        <v>2.39</v>
+      </c>
+      <c r="W231">
+        <v>1.51</v>
+      </c>
+      <c r="X231">
+        <v>5.3</v>
+      </c>
+      <c r="Y231">
+        <v>1.12</v>
+      </c>
+      <c r="Z231">
+        <v>1.82</v>
+      </c>
+      <c r="AA231">
+        <v>3.58</v>
+      </c>
+      <c r="AB231">
+        <v>3.45</v>
+      </c>
+      <c r="AC231">
+        <v>1.01</v>
+      </c>
+      <c r="AD231">
+        <v>13</v>
+      </c>
+      <c r="AE231">
+        <v>1.14</v>
+      </c>
+      <c r="AF231">
+        <v>4.3</v>
+      </c>
+      <c r="AG231">
+        <v>1.64</v>
+      </c>
+      <c r="AH231">
+        <v>2.12</v>
+      </c>
+      <c r="AI231">
+        <v>1.54</v>
+      </c>
+      <c r="AJ231">
+        <v>2.41</v>
+      </c>
+      <c r="AK231">
+        <v>1.25</v>
+      </c>
+      <c r="AL231">
+        <v>1.22</v>
+      </c>
+      <c r="AM231">
+        <v>1.8</v>
+      </c>
+      <c r="AN231">
+        <v>2</v>
+      </c>
+      <c r="AO231">
+        <v>1.17</v>
+      </c>
+      <c r="AP231">
+        <v>2.08</v>
+      </c>
+      <c r="AQ231">
+        <v>1.08</v>
+      </c>
+      <c r="AR231">
+        <v>1.53</v>
+      </c>
+      <c r="AS231">
+        <v>1.4</v>
+      </c>
+      <c r="AT231">
+        <v>2.93</v>
+      </c>
+      <c r="AU231">
+        <v>7</v>
+      </c>
+      <c r="AV231">
+        <v>5</v>
+      </c>
+      <c r="AW231">
+        <v>11</v>
+      </c>
+      <c r="AX231">
+        <v>12</v>
+      </c>
+      <c r="AY231">
+        <v>18</v>
+      </c>
+      <c r="AZ231">
+        <v>17</v>
+      </c>
+      <c r="BA231">
+        <v>2</v>
+      </c>
+      <c r="BB231">
+        <v>9</v>
+      </c>
+      <c r="BC231">
+        <v>11</v>
+      </c>
+      <c r="BD231">
+        <v>1.64</v>
+      </c>
+      <c r="BE231">
+        <v>7.49</v>
+      </c>
+      <c r="BF231">
+        <v>3.02</v>
+      </c>
+      <c r="BG231">
+        <v>1.26</v>
+      </c>
+      <c r="BH231">
+        <v>3.24</v>
+      </c>
+      <c r="BI231">
+        <v>1.52</v>
+      </c>
+      <c r="BJ231">
+        <v>2.33</v>
+      </c>
+      <c r="BK231">
+        <v>1.88</v>
+      </c>
+      <c r="BL231">
+        <v>1.82</v>
+      </c>
+      <c r="BM231">
+        <v>2.39</v>
+      </c>
+      <c r="BN231">
+        <v>1.49</v>
+      </c>
+      <c r="BO231">
+        <v>3.24</v>
+      </c>
+      <c r="BP231">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>
